--- a/housing_notices.xlsx
+++ b/housing_notices.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I150"/>
+  <dimension ref="A1:I152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,37 +466,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>평택시</t>
+          <t>구로구</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>평택시 지역 영구임대주택 예비입주자 모집(2026.08.19)</t>
+          <t>기숙사형 청년주택(개봉동) 2026학년도 2학기 상시 입사생 모집 공고</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260820</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260906</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020564&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://happydorm.or.kr/gaebong/ko/index</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -511,22 +511,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>밀양시</t>
+          <t>서귀포시</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>경남 밀양시 일반 매입임대주택 예비입주자 모집공고</t>
+          <t>제주지역 행복주택 예비입주자 모집(2026.08.18.)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -536,37 +536,37 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020547&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020582&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>오늘 마감</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>김천시</t>
+          <t>안산시 단원구</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>[경상북도 구미시, 김천시] 매입임대주택 예비입주자 모집공고</t>
+          <t>[경기 군포·안산·안성·화성시] 26년 2차 기숙사형 청년주택 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -576,242 +576,242 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020568&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020689&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>오늘 마감</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>대전</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>동구</t>
+          <t>안성시</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>낭월 다가온 청년주택 추가모집 공고</t>
+          <t>[경기 안성시] 26년 2차 기숙사형 청년주택 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.dcco.kr/web/board/list.do?mId=43</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020618&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>오늘 마감</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>전주시 덕진구</t>
+          <t>이천시</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>(2026.08.19.) 전주덕진 행복주택 예비입주자 모집</t>
+          <t>[경기남부] 26년 3차 청년 매입임대주택 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020579&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020688&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>오늘 마감</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>완주군</t>
+          <t>시흥시</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>(2026.08.19.)완주삼봉(A-1,A-3BL) 행복주택 자격완화 예비입주자 모집</t>
+          <t>[경기남부] 26년 3차 청년 매입임대주택 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020580&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020621&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>오늘 마감</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>구로구</t>
+          <t>평택시</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>기숙사형 청년주택(개봉동) 2026학년도 2학기 상시 입사생 모집 공고</t>
+          <t>[경기남부] 신혼·신생아 매입임대주택Ⅰ 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>20260820</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>20260906</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://happydorm.or.kr/gaebong/ko/index</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020687&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>서귀포시</t>
+          <t>여주시</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>제주지역 행복주택 예비입주자 모집(2026.08.18.)</t>
+          <t>[경기남부] 신혼·신생아 매입임대주택Ⅰ 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020582&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020628&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -831,12 +831,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>안성시</t>
+          <t>평택시</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>[경기 안성시] 26년 2차 기숙사형 청년주택 예비입주자 모집공고</t>
+          <t>[경기남부] 신혼·신생아 매입임대주택Ⅱ(전세형) 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -856,15 +856,15 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020618&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020629&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
@@ -876,12 +876,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>안산시 단원구</t>
+          <t>부천시 오정구</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>[경기남부] 26년 3차 청년 매입임대주택 예비입주자 모집공고</t>
+          <t>[인천지역본부] 26년 6차 청년 매입임대주택 예비입주자 모집공고(인천,부천)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -901,15 +901,15 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020621&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020693&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
@@ -921,12 +921,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>수원시 팔달구</t>
+          <t>부천시 원미구</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>[경기남부] 신혼·신생아 매입임대주택Ⅰ 예비입주자 모집공고</t>
+          <t>[인천지역본부] 26년 6차 청년 매입임대주택 예비입주자 모집공고(인천,부천)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -946,15 +946,15 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020628&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020630&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
@@ -964,10 +964,14 @@
           <t>경기</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>부천시 원미구</t>
+        </is>
+      </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>[경기남부] 신혼·신생아 매입임대주택Ⅱ(전세형) 예비입주자 모집공고</t>
+          <t>[인천지역본부]26년 6차 신혼·신생아Ⅰ 예비입주자 모집공고(인천,부천)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -987,15 +991,15 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020629&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020634&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1016,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>[인천지역본부] 26년 6차 청년 매입임대주택 예비입주자 모집공고(인천,부천)</t>
+          <t>[인천지역본부]26년 6차 신혼·신생아Ⅱ(전세형) 예비입주자 모집공고(인천,부천)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1032,15 +1036,15 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020630&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020661&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
@@ -1057,7 +1061,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>[인천지역본부]26년 6차 신혼·신생아Ⅰ 예비입주자 모집공고(인천,부천)</t>
+          <t>[인천지역본부]26년 6차 신혼·신생아Ⅱ(전세형) 예비입주자 모집공고(인천,부천)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1077,32 +1081,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020634&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020633&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>대전</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>부천시 원미구</t>
+          <t>유성구</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>[인천지역본부]26년 6차 신혼·신생아Ⅱ(전세형) 예비입주자 모집공고(인천,부천)</t>
+          <t>[대전·충남] 2026년 2차 든든전세주택 입주자 모집공고(비분양전환형)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1122,32 +1126,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020661&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020620&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>부천시 원미구</t>
+          <t>사상구</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>[인천지역본부]26년 6차 신혼·신생아Ⅱ(전세형) 예비입주자 모집공고(인천,부천)</t>
+          <t>2026년 장기미임대 매입임대주택 (예비)입주자 모집 공고</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1167,32 +1171,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020633&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://www.bmc.busan.kr/board/view.do?boardId=BBS_0000004&amp;menuCd=DOM_000000101001003000&amp;orderBy=DATA_SID%20DESC&amp;paging=ok&amp;startPage=1&amp;dataSid=800624</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>대전</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>유성구</t>
+          <t>남동구</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>[대전·충남] 2026년 2차 든든전세주택 입주자 모집공고(비분양전환형)</t>
+          <t>[인천지역본부] 26년 6차 청년 매입임대주택 예비입주자 모집공고(인천,부천)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1212,32 +1216,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020620&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020693&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>사상구</t>
+          <t>미추홀구</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026년 장기미임대 매입임대주택 (예비)입주자 모집 공고</t>
+          <t>[인천지역본부] 26년 6차 청년 매입임대주택 예비입주자 모집공고(인천,부천)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1257,15 +1261,15 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.bmc.busan.kr/board/view.do?boardId=BBS_0000004&amp;menuCd=DOM_000000101001003000&amp;orderBy=DATA_SID%20DESC&amp;paging=ok&amp;startPage=1&amp;dataSid=800624</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020630&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
@@ -1277,12 +1281,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>연수구</t>
+          <t>제물포구</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>[인천지역본부] 26년 6차 청년 매입임대주택 예비입주자 모집공고(인천,부천)</t>
+          <t>[인천지역본부]26년 6차 신혼·신생아Ⅰ 예비입주자 모집공고(인천,부천)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1302,15 +1306,15 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020630&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020634&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
@@ -1322,12 +1326,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>남동구</t>
+          <t>제물포구</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>[인천지역본부]26년 6차 신혼·신생아Ⅰ 예비입주자 모집공고(인천,부천)</t>
+          <t>[인천지역본부]26년 6차 신혼·신생아Ⅱ(전세형) 예비입주자 모집공고(인천,부천)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1347,15 +1351,15 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020634&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020661&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1371,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>제물포구</t>
+          <t>부평구</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1392,42 +1396,42 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020661&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020633&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>서해구</t>
+          <t>익산시</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>[인천지역본부]26년 6차 신혼·신생아Ⅱ(전세형) 예비입주자 모집공고(인천,부천)</t>
+          <t>익산시(익산부송1, 익산동산)영구임대주택 입주자격완화 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260908</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1437,42 +1441,42 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020633&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020603&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>익산시</t>
+          <t>아산시</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>익산시(익산부송1, 익산동산)영구임대주택 입주자격완화 예비입주자 모집공고</t>
+          <t>[대전·충남] 2026년 2차 든든전세주택 입주자 모집공고(비분양전환형)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>20260908</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1482,42 +1486,42 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020603&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020620&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>아산시</t>
+          <t>진천군</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>[대전·충남] 2026년 2차 든든전세주택 입주자 모집공고(비분양전환형)</t>
+          <t>진천성석,진천이월,청주우암 행복주택(입주자격완화) 예비입주자 추가모집</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260908</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1527,15 +1531,15 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020620&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020676&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
@@ -1572,15 +1576,15 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020676&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020672&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
@@ -1617,15 +1621,15 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020672&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020646&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1646,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>진천성석,진천이월,청주우암 행복주택(입주자격완화) 예비입주자 추가모집</t>
+          <t>진천이월 국민임대주택 예비입주자 모집(소득 및 자산요건배제, 무주택요건 완화)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1662,15 +1666,15 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020646&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020648&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
@@ -1682,17 +1686,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>진천군</t>
+          <t>청주시 흥덕구</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>진천이월 국민임대주택 예비입주자 모집(소득 및 자산요건배제, 무주택요건 완화)</t>
+          <t>청주산단1,청주산단2 행복주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1707,15 +1711,15 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020648&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020685&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
@@ -1752,15 +1756,15 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020685&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020671&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
@@ -1797,77 +1801,77 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020671&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020647&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>청주시 흥덕구</t>
+          <t>춘천시</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>청주산단1,청주산단2 행복주택 예비입주자 모집</t>
+          <t>춘천 산수빌 국민임대아파트 예비 입주자 모집안내</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>20260908</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020647&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://www.gdco.co.kr/customer/notice_view.php?intSeq=5805&amp;strBoardID=NOTI&amp;page=1&amp;pageSize=10</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-4</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>춘천시</t>
+          <t>고령군</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>춘천 산수빌 국민임대아파트 예비 입주자 모집안내</t>
+          <t>고령디오팰리스 국민임대주택 입주자격완화 예비입주자 모집</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1877,7 +1881,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260908</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1887,42 +1891,38 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.gdco.co.kr/customer/notice_view.php?intSeq=5805&amp;strBoardID=NOTI&amp;page=1&amp;pageSize=10</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020615&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-4</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>경북</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>고령군</t>
-        </is>
-      </c>
+          <t>세종</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
-          <t>고령디오팰리스 국민임대주택 입주자격완화 예비입주자 모집</t>
+          <t>2026년 세종시 영구임대주택(도램마을7‧8단지) 입주자 및 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>20260908</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1932,15 +1932,15 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020615&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://www.sjfmc.or.kr/kor/sub02_01/cop/bbs/BBSMSTR_000000000013/selectBoardArticle.do?nttId=12843</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-4</t>
         </is>
       </c>
     </row>
@@ -1953,7 +1953,7 @@
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026년 세종시 영구임대주택(도램마을7‧8단지) 입주자 및 예비입주자 모집 공고</t>
+          <t>세종 신흥사랑주택 입주자 15차 모집 공고</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1973,38 +1973,42 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.sjfmc.or.kr/kor/sub02_01/cop/bbs/BBSMSTR_000000000013/selectBoardArticle.do?nttId=12843</t>
+          <t>https://www.sjfmc.or.kr/kor/sub02_01/cop/bbs/BBSMSTR_000000000013/selectBoardArticle.do?nttId=12845&amp;kind=&amp;mno=sitemap_02&amp;pageIndex=1&amp;searchCnd=0&amp;searchWrd=%EC%9E%85%EC%A3%BC%EC%9E%90+%EB%AA%A8%EC%A7%91</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-4</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>세종</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr"/>
+          <t>제주</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>서귀포시</t>
+        </is>
+      </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>세종 신흥사랑주택 입주자 15차 모집 공고</t>
+          <t>[제주지역본부] 신혼.신생아 매입임대주택Ⅰ 예비입주자 모집 공고 (서귀포시)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2014,15 +2018,15 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.sjfmc.or.kr/kor/sub02_01/cop/bbs/BBSMSTR_000000000013/selectBoardArticle.do?nttId=12845&amp;kind=&amp;mno=sitemap_02&amp;pageIndex=1&amp;searchCnd=0&amp;searchWrd=%EC%9E%85%EC%A3%BC%EC%9E%90+%EB%AA%A8%EC%A7%91</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020622&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-4</t>
         </is>
       </c>
     </row>
@@ -2034,12 +2038,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>서귀포시</t>
+          <t>제주시</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>[제주지역본부] 신혼.신생아 매입임대주택Ⅰ 예비입주자 모집 공고 (서귀포시)</t>
+          <t>[제주지역본부] 신혼.신생아 매입임대주택Ⅰ 예비입주자 모집 공고 (제주시)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2063,56 +2067,56 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-4</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>제주시</t>
+          <t>동해시</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>[제주지역본부] 신혼.신생아 매입임대주택Ⅰ 예비입주자 모집 공고 (제주시)</t>
+          <t>동해천곡 고령자복지주택(영구임대) 입주자 모집</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020622&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020609&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
@@ -2129,12 +2133,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>동해천곡 고령자복지주택(영구임대) 입주자 모집</t>
+          <t>동해천곡 고령자복지주택(행복주택) 입주자 모집</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2149,15 +2153,15 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020609&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020610&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
@@ -2174,7 +2178,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>동해천곡 고령자복지주택(행복주택) 입주자 모집</t>
+          <t>동해천곡(고령자) 행복주택 입주자 모집</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2194,42 +2198,42 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020610&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020611&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>동해시</t>
+          <t>김포시</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>동해천곡(고령자) 행복주택 입주자 모집</t>
+          <t>김포한강 Ac-05블록 10년 공공임대주택(리츠) 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>10년임대</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2239,15 +2243,15 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020611&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=0000061160&amp;ccrCnntSysDsCd=02&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
@@ -2259,22 +2263,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>김포시</t>
+          <t>안산시 단원구</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>김포한강 Ac-05블록 10년 공공임대주택(리츠) 예비입주자 모집 공고</t>
+          <t>안산 선부동 행복주택 예비입주자(청년) 모집 공고</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>10년임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260826</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2284,42 +2288,42 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=0000061160&amp;ccrCnntSysDsCd=02&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.ansanuc.net</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>안산시 단원구</t>
+          <t>김해시</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>안산 선부동 행복주택 예비입주자(청년) 모집 공고</t>
+          <t>김해구산1 영구임대주택 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2329,32 +2333,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://apply.ansanuc.net</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020500&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>김해시</t>
+          <t>안동시</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>김해구산1 영구임대주택 예비입주자 모집 공고</t>
+          <t>[안동옥동2] 영구임대주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2374,42 +2378,42 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020500&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020584&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>안동시</t>
+          <t>달서구</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>[안동옥동2] 영구임대주택 예비입주자 모집</t>
+          <t>대구가람1단지 50년 공공임대 예비입주자 모집</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>50년임대</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2419,42 +2423,42 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020584&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020573&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>달서구</t>
+          <t>정읍시</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>대구가람1단지 50년 공공임대 예비입주자 모집</t>
+          <t>정읍시(정읍수성1)영구임대주택 입주자격완화 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>50년임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2464,15 +2468,15 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020573&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020666&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
@@ -2509,42 +2513,42 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020666&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020639&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>정읍시</t>
+          <t>제주시</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>정읍시(정읍수성1)영구임대주택 입주자격완화 예비입주자 모집공고</t>
+          <t>2026년 제주특별자치도개발공사 일반 매입임대주택 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2554,15 +2558,15 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020639&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://www.jpdc.co.kr/open/news/notice.htm?act=view&amp;seq=24135</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
@@ -2579,7 +2583,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026년 제주특별자치도개발공사 일반 매입임대주택 예비입주자 모집 공고</t>
+          <t>제주특별자치도개발공사 다자녀 매입임대주택 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2599,60 +2603,60 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.jpdc.co.kr/open/news/notice.htm?act=view&amp;seq=24135</t>
+          <t>https://www.jpdc.co.kr/open/news/notice.htm?act=view&amp;seq=24134</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>서귀포시</t>
+          <t>남원시</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>제주특별자치도개발공사 다자녀 매입임대주택 예비입주자 모집 공고</t>
+          <t>남원노암 공공임대 50년 예비입주자 모집</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>50년임대</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.jpdc.co.kr/open/news/notice.htm?act=view&amp;seq=24134</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020681&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-9</t>
         </is>
       </c>
     </row>
@@ -2664,12 +2668,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>남원시</t>
+          <t>익산시</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>남원노암 공공임대 50년 예비입주자 모집</t>
+          <t>익산부송3단지 50년 공공임대 예비입주자 모집</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2679,7 +2683,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2689,15 +2693,15 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020681&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020624&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>D-11</t>
+          <t>D-9</t>
         </is>
       </c>
     </row>
@@ -2714,62 +2718,62 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>익산부송3단지 50년 공공임대 예비입주자 모집</t>
+          <t>익산시 국민임대주택 예비입주자 모집 공고(26.09.03)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>50년임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
           <t>20260915</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>20260915</t>
-        </is>
-      </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020624&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020636&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>D-11</t>
+          <t>D-9</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>익산시</t>
+          <t>천안시 서북구</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>익산시 국민임대주택 예비입주자 모집 공고(26.09.03)</t>
+          <t>2026년 하반기 충남형 행복주택 매입임대 예비입주자 모집(천안, 보령, 서산)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2779,15 +2783,15 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020636&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.cndc.kr/</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>D-11</t>
+          <t>D-9</t>
         </is>
       </c>
     </row>
@@ -2799,12 +2803,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>천안시 서북구</t>
+          <t>예산군</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026년 하반기 충남형 행복주택 매입임대 예비입주자 모집(천안, 보령, 서산)</t>
+          <t>2026년 하반기 충남형 행복주택(꿈비채) 예비입주자 모집 공고문(당진, 천안, 예산)</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2828,56 +2832,56 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>D-11</t>
+          <t>D-9</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>예산군</t>
+          <t>춘천시</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026년 하반기 충남형 행복주택(꿈비채) 예비입주자 모집 공고문(당진, 천안, 예산)</t>
+          <t>[강원지역본부] 26년 3차 신혼신생아1 매입임대주택 예비자 모집공고</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260916</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://apply.cndc.kr/</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020675&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>D-11</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2893,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>춘천시</t>
+          <t>강릉시</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>[강원지역본부] 26년 3차 신혼신생아1 매입임대주택 예비자 모집공고</t>
+          <t>[강원지역본부] 26년 3차 신혼신생아2(전세형) 매입임대주택 예비자 모집공고</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2914,15 +2918,15 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020675&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020679&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
@@ -2934,12 +2938,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>강릉시</t>
+          <t>춘천시</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>[강원지역본부] 26년 3차 신혼신생아2(전세형) 매입임대주택 예비자 모집공고</t>
+          <t>[강원지역본부] 26년 3차 청년 매입임대주택 예비자 모집공고</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2959,37 +2963,37 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020679&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020673&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>춘천시</t>
+          <t>양산시</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>[강원지역본부] 26년 3차 청년 매입임대주택 예비자 모집공고</t>
+          <t>양산사송 A-8BL 영구임대주택 입주자격완화 예비입주자 모집</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3004,87 +3008,87 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020673&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020658&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>양산시</t>
+          <t>군산시</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>양산사송 A-8BL 영구임대주택 입주자격완화 예비입주자 모집</t>
+          <t>군산시 국민임대주택 예비입주자 모집 공고(26.09.03)</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260916</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>20260916</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020658&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020663&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-11</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>군산시</t>
+          <t>서산시</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>군산시 국민임대주택 예비입주자 모집 공고(26.09.03)</t>
+          <t>서산석림3단지 50년공공임대주택 예비입주자 모집공고(2026.09.01.)</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>50년임대</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>20260916</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -3094,60 +3098,60 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020663&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020657&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>D-13</t>
+          <t>D-11</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>서산시</t>
+          <t>부천시 원미구</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>서산석림3단지 50년공공임대주택 예비입주자 모집공고(2026.09.01.)</t>
+          <t>부천시 영구임대주택 예비입주자 모집 (중동한라1, 중동덕유1)</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>50년임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260916</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>20260917</t>
+          <t>20260918</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020657&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020678&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>D-13</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
@@ -3188,56 +3192,56 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>포항시 북구</t>
+          <t>서귀포시</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>포항창포 영구임대아파트 예비입주자 모집</t>
+          <t>[제주지역본부] 다자녀 매입임대주택 예비입주자 모집 공고(서귀포시)</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260918</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020651&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020691&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>D-17</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3258,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>포항학산 영구임대아파트 예비입주자 모집</t>
+          <t>포항창포 영구임대아파트 예비입주자 모집</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3274,15 +3278,15 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020650&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020651&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H64" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>D-17</t>
+          <t>D-15</t>
         </is>
       </c>
     </row>
@@ -3294,368 +3298,368 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>경주시</t>
+          <t>포항시 북구</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>경주시, 영천시, 포항시 부도매입(국민임대)주택 입주자격완화 모집공고</t>
+          <t>포항학산 영구임대아파트 예비입주자 모집</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>20260922</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020635&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020650&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>D-18</t>
+          <t>D-15</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>횡성군</t>
+          <t>경주시</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>강원횡성 통합공공임대주택 입주자 모집</t>
+          <t>경주시, 영천시, 포항시 부도매입(국민임대)주택 입주자격완화 모집공고</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>통합공공임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>20260923</t>
+          <t>20260922</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020627&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=48&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020635&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>D-19</t>
+          <t>D-16</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>경산시</t>
+          <t>횡성군</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>대구혁신10, 경산하양3 행복주택 입주자격완화 선계약 후검증 동호지정 입주자 모집</t>
+          <t>강원횡성 통합공공임대주택 입주자 모집</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>통합공공임대</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260923</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020682&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020627&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=48&amp;mi=1026</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>D-25</t>
+          <t>D-17</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>동구</t>
+          <t>익산시</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>대구혁신10, 경산하양3 행복주택 입주자격완화 선계약 후검증 동호지정 입주자 모집</t>
+          <t>익산한스빌 국민임대주택 예비입주자 자격완화 모집 공고</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260922</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260923</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020682&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020694&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>D-25</t>
+          <t>D-17</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>북구</t>
+          <t>경산시</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>부산만덕5 2블록 10년 분양전환공공임대주택(e편한세상 금정산) 예비입주자 모집공고</t>
+          <t>대구혁신10, 경산하양3 행복주택 입주자격완화 선계약 후검증 동호지정 입주자 모집</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>10년임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
+          <t>20260928</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
           <t>20260929</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>20260930</t>
-        </is>
-      </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=0000061163&amp;ccrCnntSysDsCd=02&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020682&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>D-26</t>
+          <t>D-23</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>경북</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr"/>
+          <t>대구</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>동구</t>
+        </is>
+      </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>[경북 포항,경주,영천] 일반 매입임대 입주자 모집공고</t>
+          <t>대구혁신10, 경산하양3 행복주택 입주자격완화 선계약 후검증 동호지정 입주자 모집</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>20260908</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020654&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020682&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>D-27</t>
+          <t>D-23</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>영천시</t>
+          <t>북구</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>[경북 포항,경주,영천] 일반 매입임대 입주자 모집공고</t>
+          <t>부산만덕5 2블록 10년 분양전환공공임대주택(e편한세상 금정산) 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>10년임대</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>20260908</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020601&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=0000061163&amp;ccrCnntSysDsCd=02&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>D-27</t>
+          <t>D-24</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>충북</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>청주시 서원구</t>
-        </is>
-      </c>
+          <t>경북</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr">
         <is>
-          <t>청주산남2-1 영구임대주택 예비입주자 모집 공고(2026.08.28)</t>
+          <t>[경북 포항,경주,영천] 일반 매입임대 입주자 모집공고</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260908</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020625&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020654&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>D-28</t>
+          <t>D-25</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>당진시</t>
+          <t>포항시 남구</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>[청년신혼부부매입임대리츠주택] 충남당진 송산청광플러스원 입주자격완화 상시모집</t>
+          <t>[경북 포항,경주,영천] 일반 매입임대 입주자 모집공고</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3665,205 +3669,205 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>20260810</t>
+          <t>20260908</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020529&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020601&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>D-41</t>
+          <t>D-25</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>양산시</t>
+          <t>청주시 서원구</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>양산 사송A-4BL 국민임대주택(29A형)선착순 동호지정 모집(입주자격완화, 선계약 후검증)</t>
+          <t>청주산남2-1 영구임대주택 예비입주자 모집 공고(2026.08.28)</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>20260813</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>20261029</t>
+          <t>20261002</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020495&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020625&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>55</v>
+        <v>26</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>D-55</t>
+          <t>D-26</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>군산시</t>
+          <t>당진시</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>군산신역세권A3(내흥3) 영구임대주택 입주자 추가모집</t>
+          <t>[청년신혼부부매입임대리츠주택] 충남당진 송산청광플러스원 입주자격완화 상시모집</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260810</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>20261030</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019841&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020529&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H75" t="n">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>D-56</t>
+          <t>D-39</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>칠곡군</t>
+          <t>양산시</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2026년 칠곡군 천원주택(신혼·신생아 매입임대주택Ⅰ) 예비입주자 모집 공고</t>
+          <t>양산 사송A-4BL 국민임대주택(29A형)선착순 동호지정 모집(입주자격완화, 선계약 후검증)</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>20260728</t>
+          <t>20260813</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>20261130</t>
+          <t>20261029</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=e54448a5-4c8c-4c3d-bfcf-bc465f677408&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020495&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H76" t="n">
-        <v>87</v>
+        <v>53</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>D-87</t>
+          <t>D-53</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>칠곡군</t>
+          <t>군산시</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2026년 칠곡군 천원주택(청년 매입임대주택) 입주자 및 예비입주자 모집 공고</t>
+          <t>군산신역세권A3(내흥3) 영구임대주택 입주자 추가모집</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>20260728</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>20261130</t>
+          <t>20261030</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=2e8989e9-02ae-48be-9591-f3c4c8e7fa39&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019841&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>87</v>
+        <v>54</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>D-87</t>
+          <t>D-54</t>
         </is>
       </c>
     </row>
@@ -3875,126 +3879,130 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>포항시 남구</t>
+          <t>칠곡군</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>포항블루밸리 행복주택 선착순 동호지정 상시모집(입주자격 완화, 통합공임 일반계층 추가, 선계약 후검증)</t>
+          <t>2026년 칠곡군 천원주택(신혼·신생아 매입임대주택Ⅰ) 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>20260707</t>
+          <t>20260728</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>20261222</t>
+          <t>20261130</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020042&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=e54448a5-4c8c-4c3d-bfcf-bc465f677408&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
         </is>
       </c>
       <c r="H78" t="n">
-        <v>109</v>
+        <v>85</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>D-109</t>
+          <t>D-85</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>삼척시</t>
+          <t>칠곡군</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>삼척시·정선군 국민임대 예비입주자 상시모집(26.6.10)</t>
+          <t>2026년 칠곡군 천원주택(청년 매입임대주택) 입주자 및 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>20260624</t>
+          <t>20260728</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>20261230</t>
+          <t>20261130</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020090&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=2e8989e9-02ae-48be-9591-f3c4c8e7fa39&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
         </is>
       </c>
       <c r="H79" t="n">
-        <v>117</v>
+        <v>85</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>D-117</t>
+          <t>D-85</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>강원</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr"/>
+          <t>경북</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>포항시 남구</t>
+        </is>
+      </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>포항블루밸리 행복주택 선착순 동호지정 상시모집(입주자격 완화, 통합공임 일반계층 추가, 선계약 후검증)</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260707</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261222</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020042&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H80" t="n">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>D-118</t>
+          <t>D-107</t>
         </is>
       </c>
     </row>
@@ -4004,38 +4012,42 @@
           <t>강원</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr"/>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>삼척시</t>
+        </is>
+      </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>삼척시·정선군 국민임대 예비입주자 상시모집(26.6.10)</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260624</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261230</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020090&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H81" t="n">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>D-118</t>
+          <t>D-115</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4060,7 @@
       <c r="B82" t="inlineStr"/>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4068,15 +4080,15 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H82" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>D-118</t>
+          <t>D-116</t>
         </is>
       </c>
     </row>
@@ -4089,7 +4101,7 @@
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4099,7 +4111,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -4109,15 +4121,15 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H83" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>D-118</t>
+          <t>D-116</t>
         </is>
       </c>
     </row>
@@ -4127,24 +4139,20 @@
           <t>강원</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>동해시</t>
-        </is>
-      </c>
+      <c r="B84" t="inlineStr"/>
       <c r="C84" t="inlineStr">
         <is>
-          <t>동해유성,태백철암장미 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>20260212</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -4154,15 +4162,15 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019312&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H84" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>D-118</t>
+          <t>D-116</t>
         </is>
       </c>
     </row>
@@ -4172,24 +4180,20 @@
           <t>강원</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>동해시</t>
-        </is>
-      </c>
+      <c r="B85" t="inlineStr"/>
       <c r="C85" t="inlineStr">
         <is>
-          <t>동해유성,태백철암장미 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>20260212</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -4199,15 +4203,15 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019308&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H85" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>D-118</t>
+          <t>D-116</t>
         </is>
       </c>
     </row>
@@ -4219,12 +4223,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>태백시</t>
+          <t>동해시</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>태백궁전 국민임대 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
+          <t>동해유성,태백철암장미 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4244,38 +4248,42 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019307&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019312&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H86" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>D-118</t>
+          <t>D-116</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>경기</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr"/>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>동해시</t>
+        </is>
+      </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>동해유성,태백철암장미 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260212</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -4285,38 +4293,42 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019308&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H87" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>D-118</t>
+          <t>D-116</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>경기</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr"/>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>태백시</t>
+        </is>
+      </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>태백궁전 국민임대 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260212</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -4326,15 +4338,15 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019307&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H88" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>D-118</t>
+          <t>D-116</t>
         </is>
       </c>
     </row>
@@ -4347,7 +4359,7 @@
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -4367,15 +4379,15 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H89" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>D-118</t>
+          <t>D-116</t>
         </is>
       </c>
     </row>
@@ -4388,7 +4400,7 @@
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -4398,7 +4410,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -4408,28 +4420,28 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H90" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>D-118</t>
+          <t>D-116</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -4449,28 +4461,28 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H91" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>D-118</t>
+          <t>D-116</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -4480,7 +4492,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -4490,15 +4502,15 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H92" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>D-118</t>
+          <t>D-116</t>
         </is>
       </c>
     </row>
@@ -4511,7 +4523,7 @@
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -4531,15 +4543,15 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H93" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>D-118</t>
+          <t>D-116</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4564,7 @@
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -4562,7 +4574,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -4572,28 +4584,28 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H94" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>D-118</t>
+          <t>D-116</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -4613,28 +4625,28 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H95" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>D-118</t>
+          <t>D-116</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -4644,7 +4656,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -4654,15 +4666,15 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H96" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>D-118</t>
+          <t>D-116</t>
         </is>
       </c>
     </row>
@@ -4675,7 +4687,7 @@
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -4695,15 +4707,15 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H97" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>D-118</t>
+          <t>D-116</t>
         </is>
       </c>
     </row>
@@ -4716,7 +4728,7 @@
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -4726,7 +4738,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -4736,28 +4748,28 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H98" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>D-118</t>
+          <t>D-116</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -4777,28 +4789,28 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H99" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>D-118</t>
+          <t>D-116</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -4808,7 +4820,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -4818,15 +4830,15 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H100" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>D-118</t>
+          <t>D-116</t>
         </is>
       </c>
     </row>
@@ -4839,7 +4851,7 @@
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -4859,15 +4871,15 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H101" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>D-118</t>
+          <t>D-116</t>
         </is>
       </c>
     </row>
@@ -4880,7 +4892,7 @@
       <c r="B102" t="inlineStr"/>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -4890,7 +4902,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -4900,28 +4912,28 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H102" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>D-118</t>
+          <t>D-116</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>대전</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -4941,28 +4953,28 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H103" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>D-118</t>
+          <t>D-116</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>대전</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -4972,7 +4984,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4982,15 +4994,15 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H104" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>D-118</t>
+          <t>D-116</t>
         </is>
       </c>
     </row>
@@ -5003,7 +5015,7 @@
       <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -5023,15 +5035,15 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H105" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>D-118</t>
+          <t>D-116</t>
         </is>
       </c>
     </row>
@@ -5044,7 +5056,7 @@
       <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -5054,7 +5066,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -5064,28 +5076,28 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H106" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>D-118</t>
+          <t>D-116</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>대전</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -5105,28 +5117,28 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H107" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>D-118</t>
+          <t>D-116</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>대전</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -5136,7 +5148,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -5146,15 +5158,15 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H108" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>D-118</t>
+          <t>D-116</t>
         </is>
       </c>
     </row>
@@ -5167,7 +5179,7 @@
       <c r="B109" t="inlineStr"/>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -5187,15 +5199,15 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H109" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>D-118</t>
+          <t>D-116</t>
         </is>
       </c>
     </row>
@@ -5208,7 +5220,7 @@
       <c r="B110" t="inlineStr"/>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -5218,7 +5230,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -5228,28 +5240,28 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H110" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>D-118</t>
+          <t>D-116</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -5269,28 +5281,28 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H111" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>D-118</t>
+          <t>D-116</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -5300,7 +5312,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -5310,15 +5322,15 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H112" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>D-118</t>
+          <t>D-116</t>
         </is>
       </c>
     </row>
@@ -5331,7 +5343,7 @@
       <c r="B113" t="inlineStr"/>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -5351,15 +5363,15 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H113" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>D-118</t>
+          <t>D-116</t>
         </is>
       </c>
     </row>
@@ -5372,7 +5384,7 @@
       <c r="B114" t="inlineStr"/>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -5382,7 +5394,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -5392,28 +5404,28 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H114" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>D-118</t>
+          <t>D-116</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>세종</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B115" t="inlineStr"/>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -5433,28 +5445,28 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H115" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>D-118</t>
+          <t>D-116</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>세종</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -5464,7 +5476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -5474,15 +5486,15 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H116" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>D-118</t>
+          <t>D-116</t>
         </is>
       </c>
     </row>
@@ -5495,7 +5507,7 @@
       <c r="B117" t="inlineStr"/>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -5515,15 +5527,15 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H117" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>D-118</t>
+          <t>D-116</t>
         </is>
       </c>
     </row>
@@ -5536,7 +5548,7 @@
       <c r="B118" t="inlineStr"/>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -5546,7 +5558,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -5556,28 +5568,28 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H118" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>D-118</t>
+          <t>D-116</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>울산</t>
+          <t>세종</t>
         </is>
       </c>
       <c r="B119" t="inlineStr"/>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -5597,28 +5609,28 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H119" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>D-118</t>
+          <t>D-116</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>울산</t>
+          <t>세종</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -5628,7 +5640,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -5638,15 +5650,15 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H120" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>D-118</t>
+          <t>D-116</t>
         </is>
       </c>
     </row>
@@ -5659,7 +5671,7 @@
       <c r="B121" t="inlineStr"/>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -5679,15 +5691,15 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H121" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>D-118</t>
+          <t>D-116</t>
         </is>
       </c>
     </row>
@@ -5700,7 +5712,7 @@
       <c r="B122" t="inlineStr"/>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -5710,7 +5722,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -5720,28 +5732,28 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H122" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>D-118</t>
+          <t>D-116</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>울산</t>
         </is>
       </c>
       <c r="B123" t="inlineStr"/>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -5761,28 +5773,28 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H123" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>D-118</t>
+          <t>D-116</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>울산</t>
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -5792,7 +5804,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -5802,15 +5814,15 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H124" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>D-118</t>
+          <t>D-116</t>
         </is>
       </c>
     </row>
@@ -5823,7 +5835,7 @@
       <c r="B125" t="inlineStr"/>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -5843,15 +5855,15 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H125" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>D-118</t>
+          <t>D-116</t>
         </is>
       </c>
     </row>
@@ -5864,7 +5876,7 @@
       <c r="B126" t="inlineStr"/>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -5874,7 +5886,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -5884,28 +5896,28 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H126" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>D-118</t>
+          <t>D-116</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B127" t="inlineStr"/>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -5925,28 +5937,28 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H127" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>D-118</t>
+          <t>D-116</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B128" t="inlineStr"/>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -5956,7 +5968,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -5966,15 +5978,15 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H128" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>D-118</t>
+          <t>D-116</t>
         </is>
       </c>
     </row>
@@ -5987,7 +5999,7 @@
       <c r="B129" t="inlineStr"/>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -6007,15 +6019,15 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H129" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>D-118</t>
+          <t>D-116</t>
         </is>
       </c>
     </row>
@@ -6028,7 +6040,7 @@
       <c r="B130" t="inlineStr"/>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -6038,7 +6050,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -6048,15 +6060,15 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H130" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>D-118</t>
+          <t>D-116</t>
         </is>
       </c>
     </row>
@@ -6066,24 +6078,20 @@
           <t>전북</t>
         </is>
       </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>김제시</t>
-        </is>
-      </c>
+      <c r="B131" t="inlineStr"/>
       <c r="C131" t="inlineStr">
         <is>
-          <t>김제검산1단지 영구임대주택 예비입주자 모집 공고(상시모집)</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>20260101</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -6093,15 +6101,15 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019412&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H131" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>D-118</t>
+          <t>D-116</t>
         </is>
       </c>
     </row>
@@ -6111,24 +6119,20 @@
           <t>전북</t>
         </is>
       </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>남원시</t>
-        </is>
-      </c>
+      <c r="B132" t="inlineStr"/>
       <c r="C132" t="inlineStr">
         <is>
-          <t>남원노암 공공임대 50년 예비입주자 모집</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>50년임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -6138,15 +6142,15 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020623&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H132" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>D-118</t>
+          <t>D-116</t>
         </is>
       </c>
     </row>
@@ -6158,12 +6162,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>전주시 완산구</t>
+          <t>김제시</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>전주시(전주평화1,전주평화4) 영구임대주택 예비입주자 모집 공고(공고일:2026.02.10.)</t>
+          <t>김제검산1단지 영구임대주택 예비입주자 모집 공고(상시모집)</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -6173,7 +6177,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>20260303</t>
+          <t>20260101</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -6183,38 +6187,42 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019241&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019412&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H133" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>D-118</t>
+          <t>D-116</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>제주</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr"/>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>남원시</t>
+        </is>
+      </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>남원노암 공공임대 50년 예비입주자 모집</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>50년임대</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -6224,38 +6232,42 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020623&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H134" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>D-118</t>
+          <t>D-116</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>제주</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr"/>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>전주시 완산구</t>
+        </is>
+      </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>전주시(전주평화1,전주평화4) 영구임대주택 예비입주자 모집 공고(공고일:2026.02.10.)</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260303</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -6265,15 +6277,15 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019241&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H135" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>D-118</t>
+          <t>D-116</t>
         </is>
       </c>
     </row>
@@ -6286,7 +6298,7 @@
       <c r="B136" t="inlineStr"/>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -6306,15 +6318,15 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H136" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>D-118</t>
+          <t>D-116</t>
         </is>
       </c>
     </row>
@@ -6327,7 +6339,7 @@
       <c r="B137" t="inlineStr"/>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -6337,7 +6349,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -6347,28 +6359,28 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H137" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>D-118</t>
+          <t>D-116</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -6388,28 +6400,28 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H138" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>D-118</t>
+          <t>D-116</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -6419,7 +6431,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -6429,15 +6441,15 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H139" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>D-118</t>
+          <t>D-116</t>
         </is>
       </c>
     </row>
@@ -6450,7 +6462,7 @@
       <c r="B140" t="inlineStr"/>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -6470,15 +6482,15 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H140" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>D-118</t>
+          <t>D-116</t>
         </is>
       </c>
     </row>
@@ -6491,7 +6503,7 @@
       <c r="B141" t="inlineStr"/>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -6501,7 +6513,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -6511,15 +6523,15 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H141" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>D-118</t>
+          <t>D-116</t>
         </is>
       </c>
     </row>
@@ -6529,24 +6541,20 @@
           <t>충남</t>
         </is>
       </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>당진시</t>
-        </is>
-      </c>
+      <c r="B142" t="inlineStr"/>
       <c r="C142" t="inlineStr">
         <is>
-          <t>[청년신혼부부매입임대리츠주택] 충남당진 송산청광플러스원 입주자격완화 상시모집</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>20260316</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -6556,28 +6564,28 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019433&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H142" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>D-118</t>
+          <t>D-116</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B143" t="inlineStr"/>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -6587,7 +6595,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -6597,38 +6605,42 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H143" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>D-118</t>
+          <t>D-116</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>충북</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr"/>
+          <t>충남</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>당진시</t>
+        </is>
+      </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>[청년신혼부부매입임대리츠주택] 충남당진 송산청광플러스원 입주자격완화 상시모집</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260316</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -6638,15 +6650,15 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019433&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H144" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>D-118</t>
+          <t>D-116</t>
         </is>
       </c>
     </row>
@@ -6659,7 +6671,7 @@
       <c r="B145" t="inlineStr"/>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -6679,15 +6691,15 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H145" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>D-118</t>
+          <t>D-116</t>
         </is>
       </c>
     </row>
@@ -6700,7 +6712,7 @@
       <c r="B146" t="inlineStr"/>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -6710,7 +6722,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -6720,122 +6732,114 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H146" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>D-118</t>
+          <t>D-116</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>강원</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>삼척시</t>
-        </is>
-      </c>
+          <t>충북</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr"/>
       <c r="C147" t="inlineStr">
         <is>
-          <t>삼척도계·정선신동 국민임대주택 예비입주자 입주자격완화 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>20270129</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020581&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H147" t="n">
-        <v>147</v>
+        <v>116</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>D-147</t>
+          <t>D-116</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>전북</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>군산시</t>
-        </is>
-      </c>
+          <t>충북</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr"/>
       <c r="C148" t="inlineStr">
         <is>
-          <t>군산시 국민임대주택 입주자 선착순 상시 모집(경암부향 등 7개 단지)</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>20260812</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>20270731</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020453&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H148" t="n">
-        <v>330</v>
+        <v>116</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>D-330</t>
+          <t>D-116</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>울산</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>울주군</t>
+          <t>삼척시</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>울산광역시 국민임대주택 예비입주자 정례모집 공고(2025.09.15.)</t>
+          <t>삼척도계·정선신동 국민임대주택 예비입주자 입주자격완화 공고</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -6845,70 +6849,160 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>20250929</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>20291001</t>
+          <t>20270129</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300018799&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020581&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H149" t="n">
-        <v>1123</v>
+        <v>145</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>D-1123</t>
+          <t>D-145</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>군산시</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>군산시 국민임대주택 입주자 선착순 상시 모집(경암부향 등 7개 단지)</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>국민임대</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>20260812</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>20270731</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020453&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H150" t="n">
+        <v>328</v>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>D-328</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
           <t>울산</t>
         </is>
       </c>
-      <c r="B150" t="inlineStr">
+      <c r="B151" t="inlineStr">
         <is>
           <t>울주군</t>
         </is>
       </c>
-      <c r="C150" t="inlineStr">
+      <c r="C151" t="inlineStr">
         <is>
           <t>울산광역시 국민임대주택 예비입주자 정례모집 공고(2025.09.15.)</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr">
+      <c r="D151" t="inlineStr">
         <is>
           <t>국민임대</t>
         </is>
       </c>
-      <c r="E150" t="inlineStr">
+      <c r="E151" t="inlineStr">
         <is>
           <t>20250929</t>
         </is>
       </c>
-      <c r="F150" t="inlineStr">
+      <c r="F151" t="inlineStr">
         <is>
           <t>20291001</t>
         </is>
       </c>
-      <c r="G150" t="inlineStr">
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300018799&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H151" t="n">
+        <v>1121</v>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>D-1121</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>울산</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>울주군</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>울산광역시 국민임대주택 예비입주자 정례모집 공고(2025.09.15.)</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>국민임대</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>20250929</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>20291001</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
         <is>
           <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300018780&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
-      <c r="H150" t="n">
-        <v>1123</v>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>D-1123</t>
+      <c r="H152" t="n">
+        <v>1121</v>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>D-1121</t>
         </is>
       </c>
     </row>

--- a/housing_notices.xlsx
+++ b/housing_notices.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I152"/>
+  <dimension ref="A1:I151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,17 +466,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>구로구</t>
+          <t>서귀포시</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>기숙사형 청년주택(개봉동) 2026학년도 2학기 상시 입사생 모집 공고</t>
+          <t>제주지역 행복주택 예비입주자 모집(2026.08.18.)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -486,17 +486,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>20260820</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>20260906</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://happydorm.or.kr/gaebong/ko/index</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020582&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -511,45 +511,45 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>서귀포시</t>
+          <t>안산시 단원구</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>제주지역 행복주택 예비입주자 모집(2026.08.18.)</t>
+          <t>[경기 군포·안산·안성·화성시] 26년 2차 기숙사형 청년주택 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020582&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020689&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
@@ -561,12 +561,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>안산시 단원구</t>
+          <t>안성시</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>[경기 군포·안산·안성·화성시] 26년 2차 기숙사형 청년주택 예비입주자 모집공고</t>
+          <t>[경기 안성시] 26년 2차 기숙사형 청년주택 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -586,15 +586,15 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020689&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020618&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
@@ -606,12 +606,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>안성시</t>
+          <t>이천시</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>[경기 안성시] 26년 2차 기숙사형 청년주택 예비입주자 모집공고</t>
+          <t>[경기남부] 26년 3차 청년 매입임대주택 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -631,15 +631,15 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020618&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020688&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
@@ -651,7 +651,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>이천시</t>
+          <t>시흥시</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -676,15 +676,15 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020688&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020621&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
@@ -696,12 +696,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>시흥시</t>
+          <t>평택시</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>[경기남부] 26년 3차 청년 매입임대주택 예비입주자 모집공고</t>
+          <t>[경기남부] 신혼·신생아 매입임대주택Ⅰ 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -721,15 +721,15 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020621&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020687&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>평택시</t>
+          <t>여주시</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -766,15 +766,15 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020687&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020628&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
@@ -786,12 +786,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>여주시</t>
+          <t>평택시</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>[경기남부] 신혼·신생아 매입임대주택Ⅰ 예비입주자 모집공고</t>
+          <t>[경기남부] 신혼·신생아 매입임대주택Ⅱ(전세형) 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -811,15 +811,15 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020628&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020629&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>평택시</t>
+          <t>부천시 오정구</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>[경기남부] 신혼·신생아 매입임대주택Ⅱ(전세형) 예비입주자 모집공고</t>
+          <t>[인천지역본부] 26년 6차 청년 매입임대주택 예비입주자 모집공고(인천,부천)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -856,15 +856,15 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020629&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020693&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>부천시 오정구</t>
+          <t>부천시 원미구</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -901,15 +901,15 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020693&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020630&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>[인천지역본부] 26년 6차 청년 매입임대주택 예비입주자 모집공고(인천,부천)</t>
+          <t>[인천지역본부]26년 6차 신혼·신생아Ⅰ 예비입주자 모집공고(인천,부천)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -946,15 +946,15 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020630&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020634&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>[인천지역본부]26년 6차 신혼·신생아Ⅰ 예비입주자 모집공고(인천,부천)</t>
+          <t>[인천지역본부]26년 6차 신혼·신생아Ⅱ(전세형) 예비입주자 모집공고(인천,부천)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -991,15 +991,15 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020634&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020661&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
@@ -1036,32 +1036,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020661&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020633&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>대전</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>부천시 원미구</t>
+          <t>유성구</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>[인천지역본부]26년 6차 신혼·신생아Ⅱ(전세형) 예비입주자 모집공고(인천,부천)</t>
+          <t>[대전·충남] 2026년 2차 든든전세주택 입주자 모집공고(비분양전환형)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1081,32 +1081,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020633&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020620&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>대전</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>유성구</t>
+          <t>사상구</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>[대전·충남] 2026년 2차 든든전세주택 입주자 모집공고(비분양전환형)</t>
+          <t>2026년 장기미임대 매입임대주택 (예비)입주자 모집 공고</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020620&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://www.bmc.busan.kr/board/view.do?boardId=BBS_0000004&amp;menuCd=DOM_000000101001003000&amp;orderBy=DATA_SID%20DESC&amp;paging=ok&amp;startPage=1&amp;dataSid=800624</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>사상구</t>
+          <t>남동구</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026년 장기미임대 매입임대주택 (예비)입주자 모집 공고</t>
+          <t>[인천지역본부] 26년 6차 청년 매입임대주택 예비입주자 모집공고(인천,부천)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1171,15 +1171,15 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.bmc.busan.kr/board/view.do?boardId=BBS_0000004&amp;menuCd=DOM_000000101001003000&amp;orderBy=DATA_SID%20DESC&amp;paging=ok&amp;startPage=1&amp;dataSid=800624</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020693&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>남동구</t>
+          <t>미추홀구</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1216,15 +1216,15 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020693&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020630&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
@@ -1236,12 +1236,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>미추홀구</t>
+          <t>제물포구</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>[인천지역본부] 26년 6차 청년 매입임대주택 예비입주자 모집공고(인천,부천)</t>
+          <t>[인천지역본부]26년 6차 신혼·신생아Ⅰ 예비입주자 모집공고(인천,부천)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1261,15 +1261,15 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020630&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020634&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
@@ -1286,7 +1286,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>[인천지역본부]26년 6차 신혼·신생아Ⅰ 예비입주자 모집공고(인천,부천)</t>
+          <t>[인천지역본부]26년 6차 신혼·신생아Ⅱ(전세형) 예비입주자 모집공고(인천,부천)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1306,15 +1306,15 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020634&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020661&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>제물포구</t>
+          <t>부평구</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1351,42 +1351,42 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020661&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020633&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>부평구</t>
+          <t>익산시</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>[인천지역본부]26년 6차 신혼·신생아Ⅱ(전세형) 예비입주자 모집공고(인천,부천)</t>
+          <t>익산시(익산부송1, 익산동산)영구임대주택 입주자격완화 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260908</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1396,42 +1396,42 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020633&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020603&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>익산시</t>
+          <t>아산시</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>익산시(익산부송1, 익산동산)영구임대주택 입주자격완화 예비입주자 모집공고</t>
+          <t>[대전·충남] 2026년 2차 든든전세주택 입주자 모집공고(비분양전환형)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>20260908</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1441,42 +1441,42 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020603&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020620&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>아산시</t>
+          <t>진천군</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>[대전·충남] 2026년 2차 든든전세주택 입주자 모집공고(비분양전환형)</t>
+          <t>진천성석,진천이월,청주우암 행복주택(입주자격완화) 예비입주자 추가모집</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260908</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1486,15 +1486,15 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020620&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020676&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
@@ -1531,15 +1531,15 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020676&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020672&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
@@ -1576,15 +1576,15 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020672&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020646&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
@@ -1601,12 +1601,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>진천성석,진천이월,청주우암 행복주택(입주자격완화) 예비입주자 추가모집</t>
+          <t>진천이월 국민임대주택 예비입주자 모집(소득 및 자산요건배제, 무주택요건 완화)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1621,15 +1621,15 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020646&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020648&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
@@ -1641,17 +1641,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>진천군</t>
+          <t>청주시 흥덕구</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>진천이월 국민임대주택 예비입주자 모집(소득 및 자산요건배제, 무주택요건 완화)</t>
+          <t>청주산단1,청주산단2 행복주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1666,15 +1666,15 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020648&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020685&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
@@ -1711,15 +1711,15 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020685&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020671&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
@@ -1756,52 +1756,52 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020671&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020647&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>청주시 흥덕구</t>
+          <t>춘천시</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>청주산단1,청주산단2 행복주택 예비입주자 모집</t>
+          <t>춘천 산수빌 국민임대아파트 예비 입주자 모집안내</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>20260908</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020647&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://www.gdco.co.kr/customer/notice_view.php?intSeq=5805&amp;strBoardID=NOTI&amp;page=1&amp;pageSize=10</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -1816,17 +1816,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>춘천시</t>
+          <t>고령군</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>춘천 산수빌 국민임대아파트 예비 입주자 모집안내</t>
+          <t>고령디오팰리스 국민임대주택 입주자격완화 예비입주자 모집</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260908</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1846,42 +1846,38 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.gdco.co.kr/customer/notice_view.php?intSeq=5805&amp;strBoardID=NOTI&amp;page=1&amp;pageSize=10</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020615&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>D-4</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>경북</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>고령군</t>
-        </is>
-      </c>
+          <t>세종</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
         <is>
-          <t>고령디오팰리스 국민임대주택 입주자격완화 예비입주자 모집</t>
+          <t>2026년 세종시 영구임대주택(도램마을7‧8단지) 입주자 및 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>20260908</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1891,15 +1887,15 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020615&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://www.sjfmc.or.kr/kor/sub02_01/cop/bbs/BBSMSTR_000000000013/selectBoardArticle.do?nttId=12843</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>D-4</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1908,7 @@
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026년 세종시 영구임대주택(도램마을7‧8단지) 입주자 및 예비입주자 모집 공고</t>
+          <t>세종 신흥사랑주택 입주자 15차 모집 공고</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1932,38 +1928,42 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.sjfmc.or.kr/kor/sub02_01/cop/bbs/BBSMSTR_000000000013/selectBoardArticle.do?nttId=12843</t>
+          <t>https://www.sjfmc.or.kr/kor/sub02_01/cop/bbs/BBSMSTR_000000000013/selectBoardArticle.do?nttId=12845&amp;kind=&amp;mno=sitemap_02&amp;pageIndex=1&amp;searchCnd=0&amp;searchWrd=%EC%9E%85%EC%A3%BC%EC%9E%90+%EB%AA%A8%EC%A7%91</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>D-4</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>세종</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr"/>
+          <t>제주</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>서귀포시</t>
+        </is>
+      </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>세종 신흥사랑주택 입주자 15차 모집 공고</t>
+          <t>[제주지역본부] 신혼.신생아 매입임대주택Ⅰ 예비입주자 모집 공고 (서귀포시)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1973,15 +1973,15 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.sjfmc.or.kr/kor/sub02_01/cop/bbs/BBSMSTR_000000000013/selectBoardArticle.do?nttId=12845&amp;kind=&amp;mno=sitemap_02&amp;pageIndex=1&amp;searchCnd=0&amp;searchWrd=%EC%9E%85%EC%A3%BC%EC%9E%90+%EB%AA%A8%EC%A7%91</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020622&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>D-4</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
@@ -1993,12 +1993,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>서귀포시</t>
+          <t>제주시</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>[제주지역본부] 신혼.신생아 매입임대주택Ⅰ 예비입주자 모집 공고 (서귀포시)</t>
+          <t>[제주지역본부] 신혼.신생아 매입임대주택Ⅰ 예비입주자 모집 공고 (제주시)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2022,48 +2022,48 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>D-4</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>제주시</t>
+          <t>동해시</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>[제주지역본부] 신혼.신생아 매입임대주택Ⅰ 예비입주자 모집 공고 (제주시)</t>
+          <t>동해천곡 고령자복지주택(영구임대) 입주자 모집</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020622&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020609&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H37" t="n">
@@ -2088,12 +2088,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>동해천곡 고령자복지주택(영구임대) 입주자 모집</t>
+          <t>동해천곡 고령자복지주택(행복주택) 입주자 모집</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2108,15 +2108,15 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020609&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020610&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-4</t>
         </is>
       </c>
     </row>
@@ -2133,7 +2133,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>동해천곡 고령자복지주택(행복주택) 입주자 모집</t>
+          <t>동해천곡(고령자) 행복주택 입주자 모집</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2153,42 +2153,42 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020610&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020611&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-4</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>동해시</t>
+          <t>김포시</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>동해천곡(고령자) 행복주택 입주자 모집</t>
+          <t>김포한강 Ac-05블록 10년 공공임대주택(리츠) 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>10년임대</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2198,15 +2198,15 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020611&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=0000061160&amp;ccrCnntSysDsCd=02&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-4</t>
         </is>
       </c>
     </row>
@@ -2218,22 +2218,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>김포시</t>
+          <t>안산시 단원구</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>김포한강 Ac-05블록 10년 공공임대주택(리츠) 예비입주자 모집 공고</t>
+          <t>안산 선부동 행복주택 예비입주자(청년) 모집 공고</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>10년임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260826</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2243,42 +2243,42 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=0000061160&amp;ccrCnntSysDsCd=02&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.ansanuc.net</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-4</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>안산시 단원구</t>
+          <t>김해시</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>안산 선부동 행복주택 예비입주자(청년) 모집 공고</t>
+          <t>김해구산1 영구임대주택 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2288,32 +2288,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://apply.ansanuc.net</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020500&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-4</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>김해시</t>
+          <t>안동시</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>김해구산1 영구임대주택 예비입주자 모집 공고</t>
+          <t>[안동옥동2] 영구임대주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2333,42 +2333,42 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020500&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020584&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-4</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>안동시</t>
+          <t>달서구</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>[안동옥동2] 영구임대주택 예비입주자 모집</t>
+          <t>대구가람1단지 50년 공공임대 예비입주자 모집</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>50년임대</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2378,42 +2378,42 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020584&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020573&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-4</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>달서구</t>
+          <t>정읍시</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>대구가람1단지 50년 공공임대 예비입주자 모집</t>
+          <t>정읍시(정읍수성1)영구임대주택 입주자격완화 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>50년임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2423,15 +2423,15 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020573&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020666&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-4</t>
         </is>
       </c>
     </row>
@@ -2468,42 +2468,42 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020666&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020639&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-4</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>정읍시</t>
+          <t>제주시</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>정읍시(정읍수성1)영구임대주택 입주자격완화 예비입주자 모집공고</t>
+          <t>2026년 제주특별자치도개발공사 일반 매입임대주택 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2513,15 +2513,15 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020639&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://www.jpdc.co.kr/open/news/notice.htm?act=view&amp;seq=24135</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-4</t>
         </is>
       </c>
     </row>
@@ -2533,12 +2533,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>제주시</t>
+          <t>서귀포시</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026년 제주특별자치도개발공사 일반 매입임대주택 예비입주자 모집 공고</t>
+          <t>제주특별자치도개발공사 다자녀 매입임대주택 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2558,60 +2558,60 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.jpdc.co.kr/open/news/notice.htm?act=view&amp;seq=24135</t>
+          <t>https://www.jpdc.co.kr/open/news/notice.htm?act=view&amp;seq=24134</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-4</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>서귀포시</t>
+          <t>남원시</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>제주특별자치도개발공사 다자녀 매입임대주택 예비입주자 모집 공고</t>
+          <t>남원노암 공공임대 50년 예비입주자 모집</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>50년임대</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.jpdc.co.kr/open/news/notice.htm?act=view&amp;seq=24134</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020681&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-8</t>
         </is>
       </c>
     </row>
@@ -2623,12 +2623,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>남원시</t>
+          <t>익산시</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>남원노암 공공임대 50년 예비입주자 모집</t>
+          <t>익산부송3단지 50년 공공임대 예비입주자 모집</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2648,15 +2648,15 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020681&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020624&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>D-9</t>
+          <t>D-8</t>
         </is>
       </c>
     </row>
@@ -2673,62 +2673,62 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>익산부송3단지 50년 공공임대 예비입주자 모집</t>
+          <t>익산시 국민임대주택 예비입주자 모집 공고(26.09.03)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>50년임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
           <t>20260915</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>20260915</t>
-        </is>
-      </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020624&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020636&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>D-9</t>
+          <t>D-8</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>익산시</t>
+          <t>천안시 서북구</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>익산시 국민임대주택 예비입주자 모집 공고(26.09.03)</t>
+          <t>2026년 하반기 충남형 행복주택 매입임대 예비입주자 모집(천안, 보령, 서산)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2738,15 +2738,15 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020636&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.cndc.kr/</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>D-9</t>
+          <t>D-8</t>
         </is>
       </c>
     </row>
@@ -2758,12 +2758,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>천안시 서북구</t>
+          <t>예산군</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026년 하반기 충남형 행복주택 매입임대 예비입주자 모집(천안, 보령, 서산)</t>
+          <t>2026년 하반기 충남형 행복주택(꿈비채) 예비입주자 모집 공고문(당진, 천안, 예산)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2787,48 +2787,48 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>D-9</t>
+          <t>D-8</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>예산군</t>
+          <t>춘천시</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026년 하반기 충남형 행복주택(꿈비채) 예비입주자 모집 공고문(당진, 천안, 예산)</t>
+          <t>[강원지역본부] 26년 3차 신혼신생아1 매입임대주택 예비자 모집공고</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260916</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://apply.cndc.kr/</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020675&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H54" t="n">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>춘천시</t>
+          <t>강릉시</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>[강원지역본부] 26년 3차 신혼신생아1 매입임대주택 예비자 모집공고</t>
+          <t>[강원지역본부] 26년 3차 신혼신생아2(전세형) 매입임대주택 예비자 모집공고</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2873,15 +2873,15 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020675&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020679&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>D-9</t>
         </is>
       </c>
     </row>
@@ -2893,12 +2893,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>강릉시</t>
+          <t>춘천시</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>[강원지역본부] 26년 3차 신혼신생아2(전세형) 매입임대주택 예비자 모집공고</t>
+          <t>[강원지역본부] 26년 3차 청년 매입임대주택 예비자 모집공고</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2918,37 +2918,37 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020679&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020673&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>D-9</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>춘천시</t>
+          <t>양산시</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>[강원지역본부] 26년 3차 청년 매입임대주택 예비자 모집공고</t>
+          <t>양산사송 A-8BL 영구임대주택 입주자격완화 예비입주자 모집</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2963,52 +2963,52 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020673&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020658&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>D-9</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>양산시</t>
+          <t>군산시</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>양산사송 A-8BL 영구임대주택 입주자격완화 예비입주자 모집</t>
+          <t>군산시 국민임대주택 예비입주자 모집 공고(26.09.03)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260916</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>20260916</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020658&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020663&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H58" t="n">
@@ -3023,27 +3023,27 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>군산시</t>
+          <t>서산시</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>군산시 국민임대주택 예비입주자 모집 공고(26.09.03)</t>
+          <t>서산석림3단지 50년공공임대주택 예비입주자 모집공고(2026.09.01.)</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>50년임대</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>20260916</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -3053,52 +3053,52 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020663&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020657&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>D-11</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>서산시</t>
+          <t>부천시 원미구</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>서산석림3단지 50년공공임대주택 예비입주자 모집공고(2026.09.01.)</t>
+          <t>부천시 영구임대주택 예비입주자 모집 (중동한라1, 중동덕유1)</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>50년임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260916</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>20260917</t>
+          <t>20260918</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020657&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020678&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H60" t="n">
@@ -3118,22 +3118,22 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>부천시 원미구</t>
+          <t>안산시 단원구</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>부천시 영구임대주택 예비입주자 모집 (중동한라1, 중동덕유1)</t>
+          <t>안산 선부동 행복주택 예비입주자(주거급여)모집 공고</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>20260916</t>
+          <t>20260903</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -3143,42 +3143,42 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020678&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://www.ansanuc.net/homenew/12286/20328/bbsList.do</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-11</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>안산시 단원구</t>
+          <t>서귀포시</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>안산 선부동 행복주택 예비입주자(주거급여)모집 공고</t>
+          <t>[제주지역본부] 다자녀 매입임대주택 예비입주자 모집 공고(서귀포시)</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>20260903</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3188,60 +3188,60 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.ansanuc.net/homenew/12286/20328/bbsList.do</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020691&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-11</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>서귀포시</t>
+          <t>포항시 북구</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>[제주지역본부] 다자녀 매입임대주택 예비입주자 모집 공고(서귀포시)</t>
+          <t>포항창포 영구임대아파트 예비입주자 모집</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>20260917</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020691&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020651&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-14</t>
         </is>
       </c>
     </row>
@@ -3258,7 +3258,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>포항창포 영구임대아파트 예비입주자 모집</t>
+          <t>포항학산 영구임대아파트 예비입주자 모집</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3278,15 +3278,15 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020651&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020650&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H64" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>D-15</t>
+          <t>D-14</t>
         </is>
       </c>
     </row>
@@ -3298,32 +3298,32 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>포항시 북구</t>
+          <t>경주시</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>포항학산 영구임대아파트 예비입주자 모집</t>
+          <t>경주시, 영천시, 포항시 부도매입(국민임대)주택 입주자격완화 모집공고</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260922</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020650&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020635&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H65" t="n">
@@ -3338,37 +3338,37 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>경주시</t>
+          <t>횡성군</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>경주시, 영천시, 포항시 부도매입(국민임대)주택 입주자격완화 모집공고</t>
+          <t>강원횡성 통합공공임대주택 입주자 모집</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>통합공공임대</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>20260922</t>
+          <t>20260923</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020635&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020627&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=48&amp;mi=1026</t>
         </is>
       </c>
       <c r="H66" t="n">
@@ -3383,27 +3383,27 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>횡성군</t>
+          <t>익산시</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>강원횡성 통합공공임대주택 입주자 모집</t>
+          <t>익산한스빌 국민임대주택 예비입주자 자격완화 모집 공고</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>통합공공임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260922</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -3413,72 +3413,72 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020627&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=48&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020694&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>D-17</t>
+          <t>D-16</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>익산시</t>
+          <t>경산시</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>익산한스빌 국민임대주택 예비입주자 자격완화 모집 공고</t>
+          <t>대구혁신10, 경산하양3 행복주택 입주자격완화 선계약 후검증 동호지정 입주자 모집</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>20260922</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>20260923</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020694&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020682&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>D-17</t>
+          <t>D-22</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>경산시</t>
+          <t>동구</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3507,48 +3507,48 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>D-23</t>
+          <t>D-22</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>동구</t>
+          <t>북구</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>대구혁신10, 경산하양3 행복주택 입주자격완화 선계약 후검증 동호지정 입주자 모집</t>
+          <t>부산만덕5 2블록 10년 분양전환공공임대주택(e편한세상 금정산) 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>10년임대</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020682&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=0000061163&amp;ccrCnntSysDsCd=02&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H70" t="n">
@@ -3563,37 +3563,33 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>부산</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>북구</t>
-        </is>
-      </c>
+          <t>경북</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr">
         <is>
-          <t>부산만덕5 2블록 10년 분양전환공공임대주택(e편한세상 금정산) 예비입주자 모집공고</t>
+          <t>[경북 포항,경주,영천] 일반 매입임대 입주자 모집공고</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>10년임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260908</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=0000061163&amp;ccrCnntSysDsCd=02&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020654&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H71" t="n">
@@ -3611,7 +3607,11 @@
           <t>경북</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr"/>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>포항시 남구</t>
+        </is>
+      </c>
       <c r="C72" t="inlineStr">
         <is>
           <t>[경북 포항,경주,영천] 일반 매입임대 입주자 모집공고</t>
@@ -3634,52 +3634,52 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020654&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020601&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>D-25</t>
+          <t>D-24</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>포항시 남구</t>
+          <t>청주시 서원구</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>[경북 포항,경주,영천] 일반 매입임대 입주자 모집공고</t>
+          <t>청주산남2-1 영구임대주택 예비입주자 모집 공고(2026.08.28)</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>20260908</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20261002</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020601&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020625&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H73" t="n">
@@ -3694,127 +3694,127 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>청주시 서원구</t>
+          <t>당진시</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>청주산남2-1 영구임대주택 예비입주자 모집 공고(2026.08.28)</t>
+          <t>[청년신혼부부매입임대리츠주택] 충남당진 송산청광플러스원 입주자격완화 상시모집</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260810</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020625&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020529&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>D-26</t>
+          <t>D-38</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>당진시</t>
+          <t>양산시</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>[청년신혼부부매입임대리츠주택] 충남당진 송산청광플러스원 입주자격완화 상시모집</t>
+          <t>양산 사송A-4BL 국민임대주택(29A형)선착순 동호지정 모집(입주자격완화, 선계약 후검증)</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>20260810</t>
+          <t>20260813</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261029</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020529&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020495&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H75" t="n">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>D-39</t>
+          <t>D-52</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>양산시</t>
+          <t>군산시</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>양산 사송A-4BL 국민임대주택(29A형)선착순 동호지정 모집(입주자격완화, 선계약 후검증)</t>
+          <t>군산신역세권A3(내흥3) 영구임대주택 입주자 추가모집</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>20260813</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>20261029</t>
+          <t>20261030</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020495&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019841&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H76" t="n">
@@ -3829,45 +3829,45 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>군산시</t>
+          <t>칠곡군</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>군산신역세권A3(내흥3) 영구임대주택 입주자 추가모집</t>
+          <t>2026년 칠곡군 천원주택(신혼·신생아 매입임대주택Ⅰ) 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260728</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>20261030</t>
+          <t>20261130</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019841&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=e54448a5-4c8c-4c3d-bfcf-bc465f677408&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>54</v>
+        <v>84</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>D-54</t>
+          <t>D-84</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2026년 칠곡군 천원주택(신혼·신생아 매입임대주택Ⅰ) 예비입주자 모집 공고</t>
+          <t>2026년 칠곡군 천원주택(청년 매입임대주택) 입주자 및 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -3904,15 +3904,15 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=e54448a5-4c8c-4c3d-bfcf-bc465f677408&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
+          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=2e8989e9-02ae-48be-9591-f3c4c8e7fa39&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
         </is>
       </c>
       <c r="H78" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>D-85</t>
+          <t>D-84</t>
         </is>
       </c>
     </row>
@@ -3924,85 +3924,85 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>칠곡군</t>
+          <t>포항시 남구</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2026년 칠곡군 천원주택(청년 매입임대주택) 입주자 및 예비입주자 모집 공고</t>
+          <t>포항블루밸리 행복주택 선착순 동호지정 상시모집(입주자격 완화, 통합공임 일반계층 추가, 선계약 후검증)</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>20260728</t>
+          <t>20260707</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>20261130</t>
+          <t>20261222</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=2e8989e9-02ae-48be-9591-f3c4c8e7fa39&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020042&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H79" t="n">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>D-85</t>
+          <t>D-106</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>포항시 남구</t>
+          <t>삼척시</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>포항블루밸리 행복주택 선착순 동호지정 상시모집(입주자격 완화, 통합공임 일반계층 추가, 선계약 후검증)</t>
+          <t>삼척시·정선군 국민임대 예비입주자 상시모집(26.6.10)</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>20260707</t>
+          <t>20260624</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>20261222</t>
+          <t>20261230</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020042&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020090&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H80" t="n">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>D-107</t>
+          <t>D-114</t>
         </is>
       </c>
     </row>
@@ -4012,34 +4012,30 @@
           <t>강원</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>삼척시</t>
-        </is>
-      </c>
+      <c r="B81" t="inlineStr"/>
       <c r="C81" t="inlineStr">
         <is>
-          <t>삼척시·정선군 국민임대 예비입주자 상시모집(26.6.10)</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>20260624</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>20261230</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020090&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H81" t="n">
@@ -4060,7 +4056,7 @@
       <c r="B82" t="inlineStr"/>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4080,15 +4076,15 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H82" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>D-116</t>
+          <t>D-115</t>
         </is>
       </c>
     </row>
@@ -4101,7 +4097,7 @@
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4121,15 +4117,15 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H83" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>D-116</t>
+          <t>D-115</t>
         </is>
       </c>
     </row>
@@ -4142,7 +4138,7 @@
       <c r="B84" t="inlineStr"/>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4152,7 +4148,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -4162,15 +4158,15 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H84" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>D-116</t>
+          <t>D-115</t>
         </is>
       </c>
     </row>
@@ -4180,20 +4176,24 @@
           <t>강원</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr"/>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>동해시</t>
+        </is>
+      </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>동해유성,태백철암장미 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260212</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -4203,15 +4203,15 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019312&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H85" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>D-116</t>
+          <t>D-115</t>
         </is>
       </c>
     </row>
@@ -4248,15 +4248,15 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019312&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019308&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H86" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>D-116</t>
+          <t>D-115</t>
         </is>
       </c>
     </row>
@@ -4268,12 +4268,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>동해시</t>
+          <t>태백시</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>동해유성,태백철암장미 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
+          <t>태백궁전 국민임대 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -4293,42 +4293,38 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019308&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019307&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H87" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>D-116</t>
+          <t>D-115</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>강원</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>태백시</t>
-        </is>
-      </c>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr"/>
       <c r="C88" t="inlineStr">
         <is>
-          <t>태백궁전 국민임대 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>20260212</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -4338,15 +4334,15 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019307&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H88" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>D-116</t>
+          <t>D-115</t>
         </is>
       </c>
     </row>
@@ -4359,7 +4355,7 @@
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -4379,15 +4375,15 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H89" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>D-116</t>
+          <t>D-115</t>
         </is>
       </c>
     </row>
@@ -4400,7 +4396,7 @@
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -4420,15 +4416,15 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H90" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>D-116</t>
+          <t>D-115</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4437,7 @@
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -4451,7 +4447,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -4461,28 +4457,28 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H91" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>D-116</t>
+          <t>D-115</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -4492,7 +4488,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -4502,15 +4498,15 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H92" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>D-116</t>
+          <t>D-115</t>
         </is>
       </c>
     </row>
@@ -4523,7 +4519,7 @@
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -4543,15 +4539,15 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H93" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>D-116</t>
+          <t>D-115</t>
         </is>
       </c>
     </row>
@@ -4564,7 +4560,7 @@
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -4584,15 +4580,15 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H94" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>D-116</t>
+          <t>D-115</t>
         </is>
       </c>
     </row>
@@ -4605,7 +4601,7 @@
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -4615,7 +4611,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -4625,28 +4621,28 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H95" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>D-116</t>
+          <t>D-115</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -4656,7 +4652,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -4666,15 +4662,15 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H96" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>D-116</t>
+          <t>D-115</t>
         </is>
       </c>
     </row>
@@ -4687,7 +4683,7 @@
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -4707,15 +4703,15 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H97" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>D-116</t>
+          <t>D-115</t>
         </is>
       </c>
     </row>
@@ -4728,7 +4724,7 @@
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -4748,15 +4744,15 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H98" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>D-116</t>
+          <t>D-115</t>
         </is>
       </c>
     </row>
@@ -4769,7 +4765,7 @@
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -4779,7 +4775,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -4789,28 +4785,28 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H99" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>D-116</t>
+          <t>D-115</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -4820,7 +4816,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -4830,15 +4826,15 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H100" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>D-116</t>
+          <t>D-115</t>
         </is>
       </c>
     </row>
@@ -4851,7 +4847,7 @@
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -4871,15 +4867,15 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H101" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>D-116</t>
+          <t>D-115</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4888,7 @@
       <c r="B102" t="inlineStr"/>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -4912,15 +4908,15 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H102" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>D-116</t>
+          <t>D-115</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4929,7 @@
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -4943,7 +4939,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4953,28 +4949,28 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H103" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>D-116</t>
+          <t>D-115</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>대전</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -4984,7 +4980,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4994,15 +4990,15 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H104" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>D-116</t>
+          <t>D-115</t>
         </is>
       </c>
     </row>
@@ -5015,7 +5011,7 @@
       <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -5035,15 +5031,15 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H105" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>D-116</t>
+          <t>D-115</t>
         </is>
       </c>
     </row>
@@ -5056,7 +5052,7 @@
       <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -5076,15 +5072,15 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H106" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>D-116</t>
+          <t>D-115</t>
         </is>
       </c>
     </row>
@@ -5097,7 +5093,7 @@
       <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -5107,7 +5103,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -5117,28 +5113,28 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H107" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>D-116</t>
+          <t>D-115</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>대전</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -5148,7 +5144,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -5158,15 +5154,15 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H108" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>D-116</t>
+          <t>D-115</t>
         </is>
       </c>
     </row>
@@ -5179,7 +5175,7 @@
       <c r="B109" t="inlineStr"/>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -5199,15 +5195,15 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H109" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>D-116</t>
+          <t>D-115</t>
         </is>
       </c>
     </row>
@@ -5220,7 +5216,7 @@
       <c r="B110" t="inlineStr"/>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -5240,15 +5236,15 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H110" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>D-116</t>
+          <t>D-115</t>
         </is>
       </c>
     </row>
@@ -5261,7 +5257,7 @@
       <c r="B111" t="inlineStr"/>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -5271,7 +5267,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -5281,28 +5277,28 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H111" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>D-116</t>
+          <t>D-115</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -5312,7 +5308,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -5322,15 +5318,15 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H112" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>D-116</t>
+          <t>D-115</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5339,7 @@
       <c r="B113" t="inlineStr"/>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -5363,15 +5359,15 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H113" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>D-116</t>
+          <t>D-115</t>
         </is>
       </c>
     </row>
@@ -5384,7 +5380,7 @@
       <c r="B114" t="inlineStr"/>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -5404,15 +5400,15 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H114" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>D-116</t>
+          <t>D-115</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5421,7 @@
       <c r="B115" t="inlineStr"/>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -5435,7 +5431,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -5445,28 +5441,28 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H115" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>D-116</t>
+          <t>D-115</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>세종</t>
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -5476,7 +5472,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -5486,15 +5482,15 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H116" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>D-116</t>
+          <t>D-115</t>
         </is>
       </c>
     </row>
@@ -5507,7 +5503,7 @@
       <c r="B117" t="inlineStr"/>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -5527,15 +5523,15 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H117" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>D-116</t>
+          <t>D-115</t>
         </is>
       </c>
     </row>
@@ -5548,7 +5544,7 @@
       <c r="B118" t="inlineStr"/>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -5568,15 +5564,15 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H118" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>D-116</t>
+          <t>D-115</t>
         </is>
       </c>
     </row>
@@ -5589,7 +5585,7 @@
       <c r="B119" t="inlineStr"/>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -5599,7 +5595,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -5609,28 +5605,28 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H119" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>D-116</t>
+          <t>D-115</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>세종</t>
+          <t>울산</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -5640,7 +5636,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -5650,15 +5646,15 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H120" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>D-116</t>
+          <t>D-115</t>
         </is>
       </c>
     </row>
@@ -5671,7 +5667,7 @@
       <c r="B121" t="inlineStr"/>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -5691,15 +5687,15 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H121" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>D-116</t>
+          <t>D-115</t>
         </is>
       </c>
     </row>
@@ -5712,7 +5708,7 @@
       <c r="B122" t="inlineStr"/>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -5732,15 +5728,15 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H122" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>D-116</t>
+          <t>D-115</t>
         </is>
       </c>
     </row>
@@ -5753,7 +5749,7 @@
       <c r="B123" t="inlineStr"/>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -5763,7 +5759,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -5773,28 +5769,28 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H123" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>D-116</t>
+          <t>D-115</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>울산</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -5804,7 +5800,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -5814,15 +5810,15 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H124" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>D-116</t>
+          <t>D-115</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5831,7 @@
       <c r="B125" t="inlineStr"/>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -5855,15 +5851,15 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H125" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>D-116</t>
+          <t>D-115</t>
         </is>
       </c>
     </row>
@@ -5876,7 +5872,7 @@
       <c r="B126" t="inlineStr"/>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -5896,15 +5892,15 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H126" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>D-116</t>
+          <t>D-115</t>
         </is>
       </c>
     </row>
@@ -5917,7 +5913,7 @@
       <c r="B127" t="inlineStr"/>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -5927,7 +5923,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -5937,28 +5933,28 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H127" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>D-116</t>
+          <t>D-115</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B128" t="inlineStr"/>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -5968,7 +5964,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -5978,15 +5974,15 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H128" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>D-116</t>
+          <t>D-115</t>
         </is>
       </c>
     </row>
@@ -5999,7 +5995,7 @@
       <c r="B129" t="inlineStr"/>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -6019,15 +6015,15 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H129" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>D-116</t>
+          <t>D-115</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6036,7 @@
       <c r="B130" t="inlineStr"/>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -6060,15 +6056,15 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H130" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>D-116</t>
+          <t>D-115</t>
         </is>
       </c>
     </row>
@@ -6081,7 +6077,7 @@
       <c r="B131" t="inlineStr"/>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -6091,7 +6087,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -6101,15 +6097,15 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H131" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>D-116</t>
+          <t>D-115</t>
         </is>
       </c>
     </row>
@@ -6119,20 +6115,24 @@
           <t>전북</t>
         </is>
       </c>
-      <c r="B132" t="inlineStr"/>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>김제시</t>
+        </is>
+      </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>김제검산1단지 영구임대주택 예비입주자 모집 공고(상시모집)</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260101</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -6142,15 +6142,15 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019412&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H132" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>D-116</t>
+          <t>D-115</t>
         </is>
       </c>
     </row>
@@ -6162,22 +6162,22 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>김제시</t>
+          <t>남원시</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>김제검산1단지 영구임대주택 예비입주자 모집 공고(상시모집)</t>
+          <t>남원노암 공공임대 50년 예비입주자 모집</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>50년임대</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>20260101</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -6187,15 +6187,15 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019412&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020623&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H133" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>D-116</t>
+          <t>D-115</t>
         </is>
       </c>
     </row>
@@ -6207,22 +6207,22 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>남원시</t>
+          <t>전주시 완산구</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>남원노암 공공임대 50년 예비입주자 모집</t>
+          <t>전주시(전주평화1,전주평화4) 영구임대주택 예비입주자 모집 공고(공고일:2026.02.10.)</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>50년임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260303</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -6232,42 +6232,38 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020623&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019241&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H134" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>D-116</t>
+          <t>D-115</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>전북</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>전주시 완산구</t>
-        </is>
-      </c>
+          <t>제주</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr"/>
       <c r="C135" t="inlineStr">
         <is>
-          <t>전주시(전주평화1,전주평화4) 영구임대주택 예비입주자 모집 공고(공고일:2026.02.10.)</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>20260303</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -6277,15 +6273,15 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019241&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H135" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>D-116</t>
+          <t>D-115</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6294,7 @@
       <c r="B136" t="inlineStr"/>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -6318,15 +6314,15 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H136" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>D-116</t>
+          <t>D-115</t>
         </is>
       </c>
     </row>
@@ -6339,7 +6335,7 @@
       <c r="B137" t="inlineStr"/>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -6359,15 +6355,15 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H137" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>D-116</t>
+          <t>D-115</t>
         </is>
       </c>
     </row>
@@ -6380,7 +6376,7 @@
       <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -6390,7 +6386,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -6400,28 +6396,28 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H138" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>D-116</t>
+          <t>D-115</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -6431,7 +6427,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -6441,15 +6437,15 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H139" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>D-116</t>
+          <t>D-115</t>
         </is>
       </c>
     </row>
@@ -6462,7 +6458,7 @@
       <c r="B140" t="inlineStr"/>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -6482,15 +6478,15 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H140" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>D-116</t>
+          <t>D-115</t>
         </is>
       </c>
     </row>
@@ -6503,7 +6499,7 @@
       <c r="B141" t="inlineStr"/>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -6523,15 +6519,15 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H141" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>D-116</t>
+          <t>D-115</t>
         </is>
       </c>
     </row>
@@ -6544,7 +6540,7 @@
       <c r="B142" t="inlineStr"/>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -6554,7 +6550,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -6564,15 +6560,15 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H142" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>D-116</t>
+          <t>D-115</t>
         </is>
       </c>
     </row>
@@ -6582,20 +6578,24 @@
           <t>충남</t>
         </is>
       </c>
-      <c r="B143" t="inlineStr"/>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>당진시</t>
+        </is>
+      </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>[청년신혼부부매입임대리츠주택] 충남당진 송산청광플러스원 입주자격완화 상시모집</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260316</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -6605,42 +6605,38 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019433&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H143" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>D-116</t>
+          <t>D-115</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>충남</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>당진시</t>
-        </is>
-      </c>
+          <t>충북</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr"/>
       <c r="C144" t="inlineStr">
         <is>
-          <t>[청년신혼부부매입임대리츠주택] 충남당진 송산청광플러스원 입주자격완화 상시모집</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>20260316</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -6650,15 +6646,15 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019433&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H144" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>D-116</t>
+          <t>D-115</t>
         </is>
       </c>
     </row>
@@ -6671,7 +6667,7 @@
       <c r="B145" t="inlineStr"/>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -6691,15 +6687,15 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H145" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>D-116</t>
+          <t>D-115</t>
         </is>
       </c>
     </row>
@@ -6712,7 +6708,7 @@
       <c r="B146" t="inlineStr"/>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -6732,15 +6728,15 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H146" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>D-116</t>
+          <t>D-115</t>
         </is>
       </c>
     </row>
@@ -6753,7 +6749,7 @@
       <c r="B147" t="inlineStr"/>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -6763,7 +6759,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -6773,73 +6769,77 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H147" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>D-116</t>
+          <t>D-115</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>충북</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr"/>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>삼척시</t>
+        </is>
+      </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>삼척도계·정선신동 국민임대주택 예비입주자 입주자격완화 공고</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20270129</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020581&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H148" t="n">
-        <v>116</v>
+        <v>144</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>D-116</t>
+          <t>D-144</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>삼척시</t>
+          <t>군산시</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>삼척도계·정선신동 국민임대주택 예비입주자 입주자격완화 공고</t>
+          <t>군산시 국민임대주택 입주자 선착순 상시 모집(경암부향 등 7개 단지)</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -6849,42 +6849,42 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260812</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>20270129</t>
+          <t>20270731</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020581&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020453&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H149" t="n">
-        <v>145</v>
+        <v>327</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>D-145</t>
+          <t>D-327</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>울산</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>군산시</t>
+          <t>울주군</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>군산시 국민임대주택 입주자 선착순 상시 모집(경암부향 등 7개 단지)</t>
+          <t>울산광역시 국민임대주택 예비입주자 정례모집 공고(2025.09.15.)</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -6894,25 +6894,25 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>20260812</t>
+          <t>20250929</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>20270731</t>
+          <t>20291001</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020453&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300018799&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H150" t="n">
-        <v>328</v>
+        <v>1120</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>D-328</t>
+          <t>D-1120</t>
         </is>
       </c>
     </row>
@@ -6949,60 +6949,15 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300018799&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300018780&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H151" t="n">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>D-1121</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>울산</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>울주군</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>울산광역시 국민임대주택 예비입주자 정례모집 공고(2025.09.15.)</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>국민임대</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>20250929</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>20291001</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300018780&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
-        </is>
-      </c>
-      <c r="H152" t="n">
-        <v>1121</v>
-      </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>D-1121</t>
+          <t>D-1120</t>
         </is>
       </c>
     </row>

--- a/housing_notices.xlsx
+++ b/housing_notices.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I151"/>
+  <dimension ref="A1:I164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,45 +466,45 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>서귀포시</t>
+          <t>화성시 효행구</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>제주지역 행복주택 예비입주자 모집(2026.08.18.)</t>
+          <t>[경기 군포·안산·안성·화성시] 26년 2차 기숙사형 청년주택 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020582&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020689&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>오늘 마감</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
@@ -516,12 +516,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>안산시 단원구</t>
+          <t>안성시</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>[경기 군포·안산·안성·화성시] 26년 2차 기숙사형 청년주택 예비입주자 모집공고</t>
+          <t>[경기 안성시] 26년 2차 기숙사형 청년주택 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -541,15 +541,15 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020689&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020618&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
@@ -561,12 +561,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>안성시</t>
+          <t>수원시 권선구</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>[경기 안성시] 26년 2차 기숙사형 청년주택 예비입주자 모집공고</t>
+          <t>[경기남부] 26년 3차 청년 매입임대주택 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -586,15 +586,15 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020618&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020688&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
@@ -606,7 +606,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>이천시</t>
+          <t>수원시 팔달구</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -631,15 +631,15 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020688&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020621&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
@@ -649,14 +649,10 @@
           <t>경기</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>시흥시</t>
-        </is>
-      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>[경기남부] 26년 3차 청년 매입임대주택 예비입주자 모집공고</t>
+          <t>[경기남부] 신혼·신생아 매입임대주택Ⅰ 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -676,15 +672,15 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020621&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020687&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
@@ -696,7 +692,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>평택시</t>
+          <t>여주시</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -721,15 +717,15 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020687&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020628&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
@@ -741,12 +737,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>여주시</t>
+          <t>오산시</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>[경기남부] 신혼·신생아 매입임대주택Ⅰ 예비입주자 모집공고</t>
+          <t>[경기남부] 신혼·신생아 매입임대주택Ⅱ(전세형) 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -766,15 +762,15 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020628&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020629&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
@@ -786,12 +782,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>평택시</t>
+          <t>부천시 오정구</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>[경기남부] 신혼·신생아 매입임대주택Ⅱ(전세형) 예비입주자 모집공고</t>
+          <t>[인천지역본부] 26년 6차 청년 매입임대주택 예비입주자 모집공고(인천,부천)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -811,15 +807,15 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020629&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020693&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
@@ -831,7 +827,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>부천시 오정구</t>
+          <t>부천시 원미구</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -856,15 +852,15 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020693&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020630&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
@@ -881,7 +877,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>[인천지역본부] 26년 6차 청년 매입임대주택 예비입주자 모집공고(인천,부천)</t>
+          <t>[인천지역본부]26년 6차 신혼·신생아Ⅰ 예비입주자 모집공고(인천,부천)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -901,15 +897,15 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020630&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020634&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
@@ -926,7 +922,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>[인천지역본부]26년 6차 신혼·신생아Ⅰ 예비입주자 모집공고(인천,부천)</t>
+          <t>[인천지역본부]26년 6차 신혼·신생아Ⅱ(전세형) 예비입주자 모집공고(인천,부천)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -946,15 +942,15 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020634&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020661&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
@@ -991,32 +987,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020661&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020633&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>대전</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>부천시 원미구</t>
+          <t>유성구</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>[인천지역본부]26년 6차 신혼·신생아Ⅱ(전세형) 예비입주자 모집공고(인천,부천)</t>
+          <t>[대전·충남] 2026년 2차 든든전세주택 입주자 모집공고(비분양전환형)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1036,32 +1032,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020633&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020620&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>대전</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>유성구</t>
+          <t>사상구</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>[대전·충남] 2026년 2차 든든전세주택 입주자 모집공고(비분양전환형)</t>
+          <t>2026년 장기미임대 매입임대주택 (예비)입주자 모집 공고</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1081,32 +1077,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020620&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://www.bmc.busan.kr/board/view.do?boardId=BBS_0000004&amp;menuCd=DOM_000000101001003000&amp;orderBy=DATA_SID%20DESC&amp;paging=ok&amp;startPage=1&amp;dataSid=800624</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>사상구</t>
+          <t>남동구</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026년 장기미임대 매입임대주택 (예비)입주자 모집 공고</t>
+          <t>[인천지역본부] 26년 6차 청년 매입임대주택 예비입주자 모집공고(인천,부천)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1126,15 +1122,15 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.bmc.busan.kr/board/view.do?boardId=BBS_0000004&amp;menuCd=DOM_000000101001003000&amp;orderBy=DATA_SID%20DESC&amp;paging=ok&amp;startPage=1&amp;dataSid=800624</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020693&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
@@ -1146,7 +1142,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>남동구</t>
+          <t>미추홀구</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1171,15 +1167,15 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020693&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020630&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
@@ -1196,7 +1192,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>[인천지역본부] 26년 6차 청년 매입임대주택 예비입주자 모집공고(인천,부천)</t>
+          <t>[인천지역본부]26년 6차 신혼·신생아Ⅰ 예비입주자 모집공고(인천,부천)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1216,15 +1212,15 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020630&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020634&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
@@ -1236,12 +1232,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>제물포구</t>
+          <t>부평구</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>[인천지역본부]26년 6차 신혼·신생아Ⅰ 예비입주자 모집공고(인천,부천)</t>
+          <t>[인천지역본부]26년 6차 신혼·신생아Ⅱ(전세형) 예비입주자 모집공고(인천,부천)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1261,15 +1257,15 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020634&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020661&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
@@ -1306,42 +1302,42 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020661&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020633&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>부평구</t>
+          <t>익산시</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>[인천지역본부]26년 6차 신혼·신생아Ⅱ(전세형) 예비입주자 모집공고(인천,부천)</t>
+          <t>익산시(익산부송1, 익산동산)영구임대주택 입주자격완화 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260908</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1351,42 +1347,42 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020633&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020603&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>익산시</t>
+          <t>아산시</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>익산시(익산부송1, 익산동산)영구임대주택 입주자격완화 예비입주자 모집공고</t>
+          <t>[대전·충남] 2026년 2차 든든전세주택 입주자 모집공고(비분양전환형)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>20260908</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1396,42 +1392,42 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020603&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020620&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>아산시</t>
+          <t>진천군</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>[대전·충남] 2026년 2차 든든전세주택 입주자 모집공고(비분양전환형)</t>
+          <t>진천성석,진천이월,청주우암 행복주택(입주자격완화) 예비입주자 추가모집</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260908</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1441,15 +1437,15 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020620&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020676&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
@@ -1486,15 +1482,15 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020676&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020672&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
@@ -1531,15 +1527,15 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020672&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020646&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1552,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>진천성석,진천이월,청주우암 행복주택(입주자격완화) 예비입주자 추가모집</t>
+          <t>진천이월 국민임대주택 예비입주자 모집(소득 및 자산요건배제, 무주택요건 완화)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1576,15 +1572,15 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020646&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020648&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
@@ -1596,17 +1592,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>진천군</t>
+          <t>청주시 흥덕구</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>진천이월 국민임대주택 예비입주자 모집(소득 및 자산요건배제, 무주택요건 완화)</t>
+          <t>청주산단1,청주산단2 행복주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1621,15 +1617,15 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020648&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020685&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
@@ -1666,15 +1662,15 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020685&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020671&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
@@ -1711,52 +1707,52 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020671&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020647&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>청주시 흥덕구</t>
+          <t>춘천시</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>청주산단1,청주산단2 행복주택 예비입주자 모집</t>
+          <t>춘천 산수빌 국민임대아파트 예비 입주자 모집안내</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>20260908</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020647&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://www.gdco.co.kr/customer/notice_view.php?intSeq=5805&amp;strBoardID=NOTI&amp;page=1&amp;pageSize=10</t>
         </is>
       </c>
       <c r="H30" t="n">
@@ -1771,17 +1767,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>춘천시</t>
+          <t>고령군</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>춘천 산수빌 국민임대아파트 예비 입주자 모집안내</t>
+          <t>고령디오팰리스 국민임대주택 입주자격완화 예비입주자 모집</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1791,7 +1787,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260908</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1801,42 +1797,38 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.gdco.co.kr/customer/notice_view.php?intSeq=5805&amp;strBoardID=NOTI&amp;page=1&amp;pageSize=10</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020615&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>경북</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>고령군</t>
-        </is>
-      </c>
+          <t>세종</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
-          <t>고령디오팰리스 국민임대주택 입주자격완화 예비입주자 모집</t>
+          <t>2026년 세종시 영구임대주택(도램마을7‧8단지) 입주자 및 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>20260908</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1846,15 +1838,15 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020615&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://www.sjfmc.or.kr/kor/sub02_01/cop/bbs/BBSMSTR_000000000013/selectBoardArticle.do?nttId=12843</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1859,7 @@
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026년 세종시 영구임대주택(도램마을7‧8단지) 입주자 및 예비입주자 모집 공고</t>
+          <t>세종 신흥사랑주택 입주자 15차 모집 공고</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1887,38 +1879,42 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.sjfmc.or.kr/kor/sub02_01/cop/bbs/BBSMSTR_000000000013/selectBoardArticle.do?nttId=12843</t>
+          <t>https://www.sjfmc.or.kr/kor/sub02_01/cop/bbs/BBSMSTR_000000000013/selectBoardArticle.do?nttId=12845&amp;kind=&amp;mno=sitemap_02&amp;pageIndex=1&amp;searchCnd=0&amp;searchWrd=%EC%9E%85%EC%A3%BC%EC%9E%90+%EB%AA%A8%EC%A7%91</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>세종</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr"/>
+          <t>제주</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>서귀포시</t>
+        </is>
+      </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>세종 신흥사랑주택 입주자 15차 모집 공고</t>
+          <t>[제주지역본부] 신혼.신생아 매입임대주택Ⅰ 예비입주자 모집 공고 (서귀포시)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1928,15 +1924,15 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.sjfmc.or.kr/kor/sub02_01/cop/bbs/BBSMSTR_000000000013/selectBoardArticle.do?nttId=12845&amp;kind=&amp;mno=sitemap_02&amp;pageIndex=1&amp;searchCnd=0&amp;searchWrd=%EC%9E%85%EC%A3%BC%EC%9E%90+%EB%AA%A8%EC%A7%91</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020622&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
@@ -1948,12 +1944,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>서귀포시</t>
+          <t>제주시</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>[제주지역본부] 신혼.신생아 매입임대주택Ⅰ 예비입주자 모집 공고 (서귀포시)</t>
+          <t>[제주지역본부] 신혼.신생아 매입임대주택Ⅰ 예비입주자 모집 공고 (제주시)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1977,48 +1973,48 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>제주시</t>
+          <t>동해시</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>[제주지역본부] 신혼.신생아 매입임대주택Ⅰ 예비입주자 모집 공고 (제주시)</t>
+          <t>동해천곡 고령자복지주택(영구임대) 입주자 모집</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020622&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020609&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H36" t="n">
@@ -2043,12 +2039,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>동해천곡 고령자복지주택(영구임대) 입주자 모집</t>
+          <t>동해천곡 고령자복지주택(행복주택) 입주자 모집</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2063,15 +2059,15 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020609&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020610&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>D-4</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2084,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>동해천곡 고령자복지주택(행복주택) 입주자 모집</t>
+          <t>동해천곡(고령자) 행복주택 입주자 모집</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2108,42 +2104,42 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020610&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020611&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>D-4</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>동해시</t>
+          <t>김포시</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>동해천곡(고령자) 행복주택 입주자 모집</t>
+          <t>김포한강 Ac-05블록 10년 공공임대주택(리츠) 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>10년임대</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2153,15 +2149,15 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020611&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=0000061160&amp;ccrCnntSysDsCd=02&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>D-4</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
@@ -2173,22 +2169,22 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>김포시</t>
+          <t>안산시 단원구</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>김포한강 Ac-05블록 10년 공공임대주택(리츠) 예비입주자 모집 공고</t>
+          <t>안산 선부동 행복주택 예비입주자(청년) 모집 공고</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>10년임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260826</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2198,42 +2194,42 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=0000061160&amp;ccrCnntSysDsCd=02&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.ansanuc.net</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>D-4</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>안산시 단원구</t>
+          <t>김해시</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>안산 선부동 행복주택 예비입주자(청년) 모집 공고</t>
+          <t>김해구산1 영구임대주택 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2243,32 +2239,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://apply.ansanuc.net</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020500&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>D-4</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>김해시</t>
+          <t>안동시</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>김해구산1 영구임대주택 예비입주자 모집 공고</t>
+          <t>[안동옥동2] 영구임대주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2288,42 +2284,42 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020500&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020584&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>D-4</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>안동시</t>
+          <t>달서구</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>[안동옥동2] 영구임대주택 예비입주자 모집</t>
+          <t>대구가람1단지 50년 공공임대 예비입주자 모집</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>50년임대</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2333,42 +2329,42 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020584&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020573&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>D-4</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>달서구</t>
+          <t>정읍시</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>대구가람1단지 50년 공공임대 예비입주자 모집</t>
+          <t>정읍시(정읍수성1)영구임대주택 입주자격완화 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>50년임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2378,15 +2374,15 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020573&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020666&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>D-4</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
@@ -2423,42 +2419,42 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020666&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020639&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>D-4</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>정읍시</t>
+          <t>제주시</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>정읍시(정읍수성1)영구임대주택 입주자격완화 예비입주자 모집공고</t>
+          <t>2026년 제주특별자치도개발공사 일반 매입임대주택 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2468,15 +2464,15 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020639&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://www.jpdc.co.kr/open/news/notice.htm?act=view&amp;seq=24135</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>D-4</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
@@ -2488,12 +2484,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>제주시</t>
+          <t>서귀포시</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026년 제주특별자치도개발공사 일반 매입임대주택 예비입주자 모집 공고</t>
+          <t>제주특별자치도개발공사 다자녀 매입임대주택 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2513,60 +2509,60 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.jpdc.co.kr/open/news/notice.htm?act=view&amp;seq=24135</t>
+          <t>https://www.jpdc.co.kr/open/news/notice.htm?act=view&amp;seq=24134</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>D-4</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>서귀포시</t>
+          <t>남원시</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>제주특별자치도개발공사 다자녀 매입임대주택 예비입주자 모집 공고</t>
+          <t>남원노암 공공임대 50년 예비입주자 모집</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>50년임대</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.jpdc.co.kr/open/news/notice.htm?act=view&amp;seq=24134</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020681&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>D-4</t>
+          <t>D-7</t>
         </is>
       </c>
     </row>
@@ -2578,12 +2574,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>남원시</t>
+          <t>익산시</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>남원노암 공공임대 50년 예비입주자 모집</t>
+          <t>익산부송3단지 50년 공공임대 예비입주자 모집</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2593,7 +2589,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2603,15 +2599,15 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020681&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020624&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-7</t>
         </is>
       </c>
     </row>
@@ -2628,62 +2624,62 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>익산부송3단지 50년 공공임대 예비입주자 모집</t>
+          <t>익산시 국민임대주택 예비입주자 모집 공고(26.09.03)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>50년임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
           <t>20260915</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>20260915</t>
-        </is>
-      </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020624&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020636&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-7</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>익산시</t>
+          <t>천안시 서북구</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>익산시 국민임대주택 예비입주자 모집 공고(26.09.03)</t>
+          <t>2026년 하반기 충남형 행복주택 매입임대 예비입주자 모집(천안, 보령, 서산)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2693,15 +2689,15 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020636&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.cndc.kr/</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-7</t>
         </is>
       </c>
     </row>
@@ -2713,12 +2709,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>천안시 서북구</t>
+          <t>예산군</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026년 하반기 충남형 행복주택 매입임대 예비입주자 모집(천안, 보령, 서산)</t>
+          <t>2026년 하반기 충남형 행복주택(꿈비채) 예비입주자 모집 공고문(당진, 천안, 예산)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2742,48 +2738,48 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-7</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>예산군</t>
+          <t>춘천시</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026년 하반기 충남형 행복주택(꿈비채) 예비입주자 모집 공고문(당진, 천안, 예산)</t>
+          <t>[강원지역본부] 26년 3차 신혼신생아1 매입임대주택 예비자 모집공고</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260916</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://apply.cndc.kr/</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020675&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H53" t="n">
@@ -2803,12 +2799,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>춘천시</t>
+          <t>강릉시</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>[강원지역본부] 26년 3차 신혼신생아1 매입임대주택 예비자 모집공고</t>
+          <t>[강원지역본부] 26년 3차 신혼신생아2(전세형) 매입임대주택 예비자 모집공고</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2828,15 +2824,15 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020675&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020679&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>D-9</t>
+          <t>D-8</t>
         </is>
       </c>
     </row>
@@ -2848,12 +2844,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>강릉시</t>
+          <t>춘천시</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>[강원지역본부] 26년 3차 신혼신생아2(전세형) 매입임대주택 예비자 모집공고</t>
+          <t>[강원지역본부] 26년 3차 청년 매입임대주택 예비자 모집공고</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2873,37 +2869,37 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020679&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020673&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>D-9</t>
+          <t>D-8</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>춘천시</t>
+          <t>양산시</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>[강원지역본부] 26년 3차 청년 매입임대주택 예비자 모집공고</t>
+          <t>양산사송 A-8BL 영구임대주택 입주자격완화 예비입주자 모집</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2918,52 +2914,52 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020673&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020658&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>D-9</t>
+          <t>D-8</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>양산시</t>
+          <t>군산시</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>양산사송 A-8BL 영구임대주택 입주자격완화 예비입주자 모집</t>
+          <t>군산시 국민임대주택 예비입주자 모집 공고(26.09.03)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260916</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>20260916</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020658&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020663&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H57" t="n">
@@ -2983,12 +2979,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>군산시</t>
+          <t>김제시</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>군산시 국민임대주택 예비입주자 모집 공고(26.09.03)</t>
+          <t>김제하동 국민임대주택 모집공고</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2998,7 +2994,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>20260916</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -3008,15 +3004,15 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020663&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020701&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>D-9</t>
         </is>
       </c>
     </row>
@@ -3057,11 +3053,11 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>D-9</t>
         </is>
       </c>
     </row>
@@ -3102,11 +3098,11 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>D-11</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
@@ -3147,11 +3143,11 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>D-11</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
@@ -3192,38 +3188,34 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>D-11</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>경북</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>포항시 북구</t>
-        </is>
-      </c>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr">
         <is>
-          <t>포항창포 영구임대아파트 예비입주자 모집</t>
+          <t>[경기남부] 용인시 신혼·신생아 매입임대주택Ⅱ(전세형) 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3233,42 +3225,38 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020651&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020702&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>D-13</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>경북</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>포항시 북구</t>
-        </is>
-      </c>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr">
         <is>
-          <t>포항학산 영구임대아파트 예비입주자 모집</t>
+          <t>[경기남부] 용인시 청년 매입임대주택 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3278,478 +3266,482 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020650&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020699&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H64" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>D-13</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>경주시</t>
+          <t>평택시</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>경주시, 영천시, 포항시 부도매입(국민임대)주택 입주자격완화 모집공고</t>
+          <t>[경기남부] 화성시·평택시 신혼·신생아 매입임대주택Ⅱ(전세형) 예비입주자 [후순번] 모집공고</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>20260922</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020635&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020703&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>D-15</t>
+          <t>D-13</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>횡성군</t>
+          <t>포항시 북구</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>강원횡성 통합공공임대주택 입주자 모집</t>
+          <t>포항창포 영구임대아파트 예비입주자 모집</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>통합공공임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
           <t>20260921</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>20260923</t>
-        </is>
-      </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020627&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=48&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020651&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>D-16</t>
+          <t>D-13</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>익산시</t>
+          <t>포항시 북구</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>익산한스빌 국민임대주택 예비입주자 자격완화 모집 공고</t>
+          <t>포항학산 영구임대아파트 예비입주자 모집</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>20260922</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>20260923</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020694&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020650&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>D-16</t>
+          <t>D-13</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>경산시</t>
+          <t>부천시 오정구</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>대구혁신10, 경산하양3 행복주택 입주자격완화 선계약 후검증 동호지정 입주자 모집</t>
+          <t>2026년 9월 부천시 국민임대주택 예비입주자 모집 공고(2026.09.07)</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260922</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020682&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020652&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>D-22</t>
+          <t>D-14</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>동구</t>
+          <t>경주시</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>대구혁신10, 경산하양3 행복주택 입주자격완화 선계약 후검증 동호지정 입주자 모집</t>
+          <t>경주시, 영천시, 포항시 부도매입(국민임대)주택 입주자격완화 모집공고</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260922</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020682&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020635&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>D-22</t>
+          <t>D-14</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>북구</t>
+          <t>남동구</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>부산만덕5 2블록 10년 분양전환공공임대주택(e편한세상 금정산) 예비입주자 모집공고</t>
+          <t>26년 9월 인천시 남동구 국민임대주택 예비입주자 모집 공고(2026.09.07)</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>10년임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20260922</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=0000061163&amp;ccrCnntSysDsCd=02&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020619&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>D-23</t>
+          <t>D-14</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>경북</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr"/>
+          <t>인천</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>옹진군</t>
+        </is>
+      </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>[경북 포항,경주,영천] 일반 매입임대 입주자 모집공고</t>
+          <t>인천옹진백령 국민임대주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>20260908</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20260922</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020654&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020578&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>D-24</t>
+          <t>D-14</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>포항시 남구</t>
+          <t>옹진군</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>[경북 포항,경주,영천] 일반 매입임대 입주자 모집공고</t>
+          <t>인천옹진연평 국민임대주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>20260908</t>
+          <t>20260922</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20260922</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020601&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020697&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>D-24</t>
+          <t>D-14</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>청주시 서원구</t>
+          <t>횡성군</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>청주산남2-1 영구임대주택 예비입주자 모집 공고(2026.08.28)</t>
+          <t>강원횡성 통합공공임대주택 입주자 모집</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>통합공공임대</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20260923</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020625&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020627&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=48&amp;mi=1026</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>D-25</t>
+          <t>D-15</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>당진시</t>
+          <t>김포시</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>[청년신혼부부매입임대리츠주택] 충남당진 송산청광플러스원 입주자격완화 상시모집</t>
+          <t>김포시 국민임대주택 예비입주자 모집(2026.09.07)</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>20260810</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20260923</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020529&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020659&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>D-38</t>
+          <t>D-15</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>양산시</t>
+          <t>익산시</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>양산 사송A-4BL 국민임대주택(29A형)선착순 동호지정 모집(입주자격완화, 선계약 후검증)</t>
+          <t>익산한스빌 국민임대주택 예비입주자 자격완화 모집 공고</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -3759,222 +3751,222 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>20260813</t>
+          <t>20260922</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>20261029</t>
+          <t>20260923</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020495&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020694&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H75" t="n">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>D-52</t>
+          <t>D-15</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>군산시</t>
+          <t>경산시</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>군산신역세권A3(내흥3) 영구임대주택 입주자 추가모집</t>
+          <t>대구혁신10, 경산하양3 행복주택 입주자격완화 선계약 후검증 동호지정 입주자 모집</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>20261030</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019841&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020682&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H76" t="n">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>D-53</t>
+          <t>D-21</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>칠곡군</t>
+          <t>동구</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2026년 칠곡군 천원주택(신혼·신생아 매입임대주택Ⅰ) 예비입주자 모집 공고</t>
+          <t>대구혁신10, 경산하양3 행복주택 입주자격완화 선계약 후검증 동호지정 입주자 모집</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>20260728</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>20261130</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=e54448a5-4c8c-4c3d-bfcf-bc465f677408&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020682&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>84</v>
+        <v>21</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>D-84</t>
+          <t>D-21</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>칠곡군</t>
+          <t>김포시</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2026년 칠곡군 천원주택(청년 매입임대주택) 입주자 및 예비입주자 모집 공고</t>
+          <t>김포지역 국민임대주택 예비입주자 모집 공고(26.09.07.)</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>20260728</t>
+          <t>20260918</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>20261130</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=2e8989e9-02ae-48be-9591-f3c4c8e7fa39&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020704&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H78" t="n">
-        <v>84</v>
+        <v>22</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>D-84</t>
+          <t>D-22</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>포항시 남구</t>
+          <t>김포시</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>포항블루밸리 행복주택 선착순 동호지정 상시모집(입주자격 완화, 통합공임 일반계층 추가, 선계약 후검증)</t>
+          <t>김포지역 국민임대주택 예비입주자 모집 공고(26.09.07.)</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>20260707</t>
+          <t>20260918</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>20261222</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020042&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020662&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H79" t="n">
-        <v>106</v>
+        <v>22</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>D-106</t>
+          <t>D-22</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>삼척시</t>
+          <t>안성시</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>삼척시·정선군 국민임대 예비입주자 상시모집(26.6.10)</t>
+          <t>안성금화 국민임대 입주자격완화 예비입주자 모집공고(2026.09.07)</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -3984,296 +3976,308 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>20260624</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>20261230</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020090&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020695&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H80" t="n">
-        <v>114</v>
+        <v>22</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>D-114</t>
+          <t>D-22</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>강원</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr"/>
+          <t>부산</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>북구</t>
+        </is>
+      </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>부산만덕5 2블록 10년 분양전환공공임대주택(e편한세상 금정산) 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>10년임대</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=0000061163&amp;ccrCnntSysDsCd=02&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H81" t="n">
-        <v>115</v>
+        <v>22</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>D-115</t>
+          <t>D-22</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>강원</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr"/>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>남양주시</t>
+        </is>
+      </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>남양주마석2단지 국민임대주택 예비입주자 모집공고(2026.9.7.)</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020668&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H82" t="n">
-        <v>115</v>
+        <v>23</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>D-115</t>
+          <t>D-23</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>[경북 포항,경주,영천] 일반 매입임대 입주자 모집공고</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260908</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020654&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H83" t="n">
-        <v>115</v>
+        <v>23</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>D-115</t>
+          <t>D-23</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>강원</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr"/>
+          <t>경북</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>포항시 남구</t>
+        </is>
+      </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>[경북 포항,경주,영천] 일반 매입임대 입주자 모집공고</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260908</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020601&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H84" t="n">
-        <v>115</v>
+        <v>23</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>D-115</t>
+          <t>D-23</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>동해시</t>
+          <t>청주시 서원구</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>동해유성,태백철암장미 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
+          <t>청주산남2-1 영구임대주택 예비입주자 모집 공고(2026.08.28)</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>20260212</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261002</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019312&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020625&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H85" t="n">
-        <v>115</v>
+        <v>24</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>D-115</t>
+          <t>D-24</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>동해시</t>
+          <t>당진시</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>동해유성,태백철암장미 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
+          <t>[청년신혼부부매입임대리츠주택] 충남당진 송산청광플러스원 입주자격완화 상시모집</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>20260212</t>
+          <t>20260810</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019308&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020529&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H86" t="n">
-        <v>115</v>
+        <v>37</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>D-115</t>
+          <t>D-37</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>태백시</t>
+          <t>양산시</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>태백궁전 국민임대 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
+          <t>양산 사송A-4BL 국민임대주택(29A형)선착순 동호지정 모집(입주자격완화, 선계약 후검증)</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -4283,243 +4287,263 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>20260212</t>
+          <t>20260813</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261029</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019307&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020495&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H87" t="n">
-        <v>115</v>
+        <v>51</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>D-115</t>
+          <t>D-51</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>경기</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr"/>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>군산시</t>
+        </is>
+      </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>군산신역세권A3(내흥3) 영구임대주택 입주자 추가모집</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261030</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019841&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H88" t="n">
-        <v>115</v>
+        <v>52</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>D-115</t>
+          <t>D-52</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>경기</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr"/>
+          <t>경북</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>칠곡군</t>
+        </is>
+      </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 칠곡군 천원주택(신혼·신생아 매입임대주택Ⅰ) 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260728</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261130</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=e54448a5-4c8c-4c3d-bfcf-bc465f677408&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
         </is>
       </c>
       <c r="H89" t="n">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>D-115</t>
+          <t>D-83</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>경기</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr"/>
+          <t>경북</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>칠곡군</t>
+        </is>
+      </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 칠곡군 천원주택(청년 매입임대주택) 입주자 및 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260728</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261130</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=2e8989e9-02ae-48be-9591-f3c4c8e7fa39&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
         </is>
       </c>
       <c r="H90" t="n">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>D-115</t>
+          <t>D-83</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>경기</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr"/>
+          <t>경북</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>포항시 남구</t>
+        </is>
+      </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>포항블루밸리 행복주택 선착순 동호지정 상시모집(입주자격 완화, 통합공임 일반계층 추가, 선계약 후검증)</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260707</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261222</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020042&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H91" t="n">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>D-115</t>
+          <t>D-105</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr"/>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>삼척시</t>
+        </is>
+      </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>삼척시·정선군 국민임대 예비입주자 상시모집(26.6.10)</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260624</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261230</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020090&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H92" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>D-115</t>
+          <t>D-113</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -4539,28 +4563,28 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H93" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>D-115</t>
+          <t>D-114</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -4580,28 +4604,28 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H94" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>D-115</t>
+          <t>D-114</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -4611,7 +4635,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -4621,28 +4645,28 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H95" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>D-115</t>
+          <t>D-114</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -4652,7 +4676,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -4662,38 +4686,42 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H96" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>D-115</t>
+          <t>D-114</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>경북</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr"/>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>동해시</t>
+        </is>
+      </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>동해유성,태백철암장미 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260212</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -4703,38 +4731,42 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019312&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H97" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>D-115</t>
+          <t>D-114</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>경북</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr"/>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>동해시</t>
+        </is>
+      </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>동해유성,태백철암장미 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260212</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -4744,38 +4776,42 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019308&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H98" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>D-115</t>
+          <t>D-114</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>경북</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr"/>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>태백시</t>
+        </is>
+      </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>태백궁전 국민임대 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260212</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -4785,22 +4821,22 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019307&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H99" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>D-115</t>
+          <t>D-114</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
@@ -4830,18 +4866,18 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>D-115</t>
+          <t>D-114</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
@@ -4871,18 +4907,18 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>D-115</t>
+          <t>D-114</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
@@ -4912,18 +4948,18 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>D-115</t>
+          <t>D-114</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
@@ -4953,18 +4989,18 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>D-115</t>
+          <t>D-114</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>대전</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
@@ -4994,18 +5030,18 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>D-115</t>
+          <t>D-114</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>대전</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
@@ -5035,18 +5071,18 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>D-115</t>
+          <t>D-114</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>대전</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B106" t="inlineStr"/>
@@ -5076,18 +5112,18 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>D-115</t>
+          <t>D-114</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>대전</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
@@ -5117,18 +5153,18 @@
         </is>
       </c>
       <c r="H107" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>D-115</t>
+          <t>D-114</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
@@ -5158,18 +5194,18 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>D-115</t>
+          <t>D-114</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
@@ -5199,18 +5235,18 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>D-115</t>
+          <t>D-114</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B110" t="inlineStr"/>
@@ -5240,18 +5276,18 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>D-115</t>
+          <t>D-114</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
@@ -5281,18 +5317,18 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>D-115</t>
+          <t>D-114</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
@@ -5322,18 +5358,18 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>D-115</t>
+          <t>D-114</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
@@ -5363,18 +5399,18 @@
         </is>
       </c>
       <c r="H113" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>D-115</t>
+          <t>D-114</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B114" t="inlineStr"/>
@@ -5404,18 +5440,18 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>D-115</t>
+          <t>D-114</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B115" t="inlineStr"/>
@@ -5445,18 +5481,18 @@
         </is>
       </c>
       <c r="H115" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>D-115</t>
+          <t>D-114</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>세종</t>
+          <t>대전</t>
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
@@ -5486,18 +5522,18 @@
         </is>
       </c>
       <c r="H116" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>D-115</t>
+          <t>D-114</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>세종</t>
+          <t>대전</t>
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
@@ -5527,18 +5563,18 @@
         </is>
       </c>
       <c r="H117" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>D-115</t>
+          <t>D-114</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>세종</t>
+          <t>대전</t>
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
@@ -5568,18 +5604,18 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>D-115</t>
+          <t>D-114</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>세종</t>
+          <t>대전</t>
         </is>
       </c>
       <c r="B119" t="inlineStr"/>
@@ -5609,18 +5645,18 @@
         </is>
       </c>
       <c r="H119" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>D-115</t>
+          <t>D-114</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>울산</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
@@ -5650,18 +5686,18 @@
         </is>
       </c>
       <c r="H120" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>D-115</t>
+          <t>D-114</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>울산</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
@@ -5691,18 +5727,18 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>D-115</t>
+          <t>D-114</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>울산</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B122" t="inlineStr"/>
@@ -5732,18 +5768,18 @@
         </is>
       </c>
       <c r="H122" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>D-115</t>
+          <t>D-114</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>울산</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B123" t="inlineStr"/>
@@ -5773,18 +5809,18 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>D-115</t>
+          <t>D-114</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
@@ -5814,18 +5850,18 @@
         </is>
       </c>
       <c r="H124" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>D-115</t>
+          <t>D-114</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B125" t="inlineStr"/>
@@ -5855,18 +5891,18 @@
         </is>
       </c>
       <c r="H125" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>D-115</t>
+          <t>D-114</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
@@ -5896,18 +5932,18 @@
         </is>
       </c>
       <c r="H126" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>D-115</t>
+          <t>D-114</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B127" t="inlineStr"/>
@@ -5937,18 +5973,18 @@
         </is>
       </c>
       <c r="H127" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>D-115</t>
+          <t>D-114</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>세종</t>
         </is>
       </c>
       <c r="B128" t="inlineStr"/>
@@ -5978,18 +6014,18 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>D-115</t>
+          <t>D-114</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>세종</t>
         </is>
       </c>
       <c r="B129" t="inlineStr"/>
@@ -6019,18 +6055,18 @@
         </is>
       </c>
       <c r="H129" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>D-115</t>
+          <t>D-114</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>세종</t>
         </is>
       </c>
       <c r="B130" t="inlineStr"/>
@@ -6060,18 +6096,18 @@
         </is>
       </c>
       <c r="H130" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>D-115</t>
+          <t>D-114</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>세종</t>
         </is>
       </c>
       <c r="B131" t="inlineStr"/>
@@ -6101,38 +6137,34 @@
         </is>
       </c>
       <c r="H131" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>D-115</t>
+          <t>D-114</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>전북</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>김제시</t>
-        </is>
-      </c>
+          <t>울산</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr"/>
       <c r="C132" t="inlineStr">
         <is>
-          <t>김제검산1단지 영구임대주택 예비입주자 모집 공고(상시모집)</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>20260101</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -6142,42 +6174,38 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019412&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H132" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>D-115</t>
+          <t>D-114</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>전북</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>남원시</t>
-        </is>
-      </c>
+          <t>울산</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr"/>
       <c r="C133" t="inlineStr">
         <is>
-          <t>남원노암 공공임대 50년 예비입주자 모집</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>50년임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -6187,42 +6215,38 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020623&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H133" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>D-115</t>
+          <t>D-114</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>전북</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>전주시 완산구</t>
-        </is>
-      </c>
+          <t>울산</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr"/>
       <c r="C134" t="inlineStr">
         <is>
-          <t>전주시(전주평화1,전주평화4) 영구임대주택 예비입주자 모집 공고(공고일:2026.02.10.)</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>20260303</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -6232,28 +6256,28 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019241&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H134" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>D-115</t>
+          <t>D-114</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>울산</t>
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -6263,7 +6287,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -6273,28 +6297,28 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H135" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>D-115</t>
+          <t>D-114</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B136" t="inlineStr"/>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -6314,28 +6338,28 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H136" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>D-115</t>
+          <t>D-114</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B137" t="inlineStr"/>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -6355,28 +6379,28 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H137" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>D-115</t>
+          <t>D-114</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -6386,7 +6410,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -6396,28 +6420,28 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H138" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>D-115</t>
+          <t>D-114</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -6427,7 +6451,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -6437,28 +6461,28 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H139" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>D-115</t>
+          <t>D-114</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B140" t="inlineStr"/>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -6478,28 +6502,28 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H140" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>D-115</t>
+          <t>D-114</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B141" t="inlineStr"/>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -6519,28 +6543,28 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H141" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>D-115</t>
+          <t>D-114</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B142" t="inlineStr"/>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -6550,7 +6574,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -6560,42 +6584,38 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H142" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>D-115</t>
+          <t>D-114</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>충남</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>당진시</t>
-        </is>
-      </c>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr"/>
       <c r="C143" t="inlineStr">
         <is>
-          <t>[청년신혼부부매입임대리츠주택] 충남당진 송산청광플러스원 입주자격완화 상시모집</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>20260316</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -6605,38 +6625,42 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019433&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H143" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>D-115</t>
+          <t>D-114</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>충북</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr"/>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>김제시</t>
+        </is>
+      </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>김제검산1단지 영구임대주택 예비입주자 모집 공고(상시모집)</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260101</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -6646,38 +6670,42 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019412&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H144" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>D-115</t>
+          <t>D-114</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>충북</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr"/>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>남원시</t>
+        </is>
+      </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>남원노암 공공임대 50년 예비입주자 모집</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>50년임대</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -6687,38 +6715,42 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020623&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H145" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>D-115</t>
+          <t>D-114</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>충북</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr"/>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>남원시</t>
+        </is>
+      </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>남원노암단지 영구임대주택 입주자격완화 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -6728,38 +6760,42 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020649&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H146" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>D-115</t>
+          <t>D-114</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>충북</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr"/>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>전주시 완산구</t>
+        </is>
+      </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>전주시(전주평화1,전주평화4) 영구임대주택 예비입주자 모집 공고(공고일:2026.02.10.)</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260303</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -6769,195 +6805,732 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019241&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H147" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>D-115</t>
+          <t>D-114</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>강원</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>삼척시</t>
-        </is>
-      </c>
+          <t>제주</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr"/>
       <c r="C148" t="inlineStr">
         <is>
-          <t>삼척도계·정선신동 국민임대주택 예비입주자 입주자격완화 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>20270129</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020581&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H148" t="n">
-        <v>144</v>
+        <v>114</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>D-144</t>
+          <t>D-114</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>전북</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>군산시</t>
-        </is>
-      </c>
+          <t>제주</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr"/>
       <c r="C149" t="inlineStr">
         <is>
-          <t>군산시 국민임대주택 입주자 선착순 상시 모집(경암부향 등 7개 단지)</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>20260812</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>20270731</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020453&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H149" t="n">
-        <v>327</v>
+        <v>114</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>D-327</t>
+          <t>D-114</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>울산</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>울주군</t>
-        </is>
-      </c>
+          <t>제주</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr"/>
       <c r="C150" t="inlineStr">
         <is>
-          <t>울산광역시 국민임대주택 예비입주자 정례모집 공고(2025.09.15.)</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>20250929</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>20291001</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300018799&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H150" t="n">
-        <v>1120</v>
+        <v>114</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>D-1120</t>
+          <t>D-114</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
+          <t>제주</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr"/>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>20260224</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H151" t="n">
+        <v>114</v>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>D-114</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>충남</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr"/>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H152" t="n">
+        <v>114</v>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>D-114</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>충남</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr"/>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H153" t="n">
+        <v>114</v>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>D-114</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>충남</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr"/>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H154" t="n">
+        <v>114</v>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>D-114</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>충남</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr"/>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>20260224</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H155" t="n">
+        <v>114</v>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>D-114</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>충남</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>당진시</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>[청년신혼부부매입임대리츠주택] 충남당진 송산청광플러스원 입주자격완화 상시모집</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>매입임대</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>20260316</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019433&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H156" t="n">
+        <v>114</v>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>D-114</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>충북</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr"/>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H157" t="n">
+        <v>114</v>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>D-114</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>충북</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr"/>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H158" t="n">
+        <v>114</v>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>D-114</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>충북</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr"/>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H159" t="n">
+        <v>114</v>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>D-114</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>충북</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr"/>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>20260224</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H160" t="n">
+        <v>114</v>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>D-114</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>삼척시</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>삼척도계·정선신동 국민임대주택 예비입주자 입주자격완화 공고</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>국민임대</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>20270129</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020581&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H161" t="n">
+        <v>143</v>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>D-143</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>군산시</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>군산시 국민임대주택 입주자 선착순 상시 모집(경암부향 등 7개 단지)</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>국민임대</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>20260812</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>20270731</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020453&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H162" t="n">
+        <v>326</v>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>D-326</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
           <t>울산</t>
         </is>
       </c>
-      <c r="B151" t="inlineStr">
+      <c r="B163" t="inlineStr">
         <is>
           <t>울주군</t>
         </is>
       </c>
-      <c r="C151" t="inlineStr">
+      <c r="C163" t="inlineStr">
         <is>
           <t>울산광역시 국민임대주택 예비입주자 정례모집 공고(2025.09.15.)</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr">
+      <c r="D163" t="inlineStr">
         <is>
           <t>국민임대</t>
         </is>
       </c>
-      <c r="E151" t="inlineStr">
+      <c r="E163" t="inlineStr">
         <is>
           <t>20250929</t>
         </is>
       </c>
-      <c r="F151" t="inlineStr">
+      <c r="F163" t="inlineStr">
         <is>
           <t>20291001</t>
         </is>
       </c>
-      <c r="G151" t="inlineStr">
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300018799&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H163" t="n">
+        <v>1119</v>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>D-1119</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>울산</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>울주군</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>울산광역시 국민임대주택 예비입주자 정례모집 공고(2025.09.15.)</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>국민임대</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>20250929</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>20291001</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
         <is>
           <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300018780&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
-      <c r="H151" t="n">
-        <v>1120</v>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>D-1120</t>
+      <c r="H164" t="n">
+        <v>1119</v>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>D-1119</t>
         </is>
       </c>
     </row>

--- a/housing_notices.xlsx
+++ b/housing_notices.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I164"/>
+  <dimension ref="A1:I142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,112 +466,108 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>화성시 효행구</t>
+          <t>춘천시</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>[경기 군포·안산·안성·화성시] 26년 2차 기숙사형 청년주택 예비입주자 모집공고</t>
+          <t>춘천 산수빌 국민임대아파트 예비 입주자 모집안내</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020689&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://www.gdco.co.kr/customer/notice_view.php?intSeq=5805&amp;strBoardID=NOTI&amp;page=1&amp;pageSize=10</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>오늘 마감</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>안성시</t>
+          <t>고령군</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>[경기 안성시] 26년 2차 기숙사형 청년주택 예비입주자 모집공고</t>
+          <t>고령디오팰리스 국민임대주택 입주자격완화 예비입주자 모집</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260908</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020618&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020615&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>오늘 마감</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>경기</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>수원시 권선구</t>
-        </is>
-      </c>
+          <t>세종</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>[경기남부] 26년 3차 청년 매입임대주택 예비입주자 모집공고</t>
+          <t>2026년 세종시 영구임대주택(도램마을7‧8단지) 입주자 및 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -581,42 +577,38 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020688&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://www.sjfmc.or.kr/kor/sub02_01/cop/bbs/BBSMSTR_000000000013/selectBoardArticle.do?nttId=12843</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>오늘 마감</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>경기</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>수원시 팔달구</t>
-        </is>
-      </c>
+          <t>세종</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>[경기남부] 26년 3차 청년 매입임대주택 예비입주자 모집공고</t>
+          <t>세종 신흥사랑주택 입주자 15차 모집 공고</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -626,33 +618,37 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020621&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://www.sjfmc.or.kr/kor/sub02_01/cop/bbs/BBSMSTR_000000000013/selectBoardArticle.do?nttId=12845&amp;kind=&amp;mno=sitemap_02&amp;pageIndex=1&amp;searchCnd=0&amp;searchWrd=%EC%9E%85%EC%A3%BC%EC%9E%90+%EB%AA%A8%EC%A7%91</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>오늘 마감</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>경기</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
+          <t>제주</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>서귀포시</t>
+        </is>
+      </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>[경기남부] 신혼·신생아 매입임대주택Ⅰ 예비입주자 모집공고</t>
+          <t>[제주지역본부] 신혼.신생아 매입임대주택Ⅰ 예비입주자 모집 공고 (서귀포시)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -662,42 +658,42 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020687&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020622&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>오늘 마감</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>여주시</t>
+          <t>제주시</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>[경기남부] 신혼·신생아 매입임대주택Ⅰ 예비입주자 모집공고</t>
+          <t>[제주지역본부] 신혼.신생아 매입임대주택Ⅰ 예비입주자 모집 공고 (제주시)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -707,47 +703,47 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020628&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020622&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>오늘 마감</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>오산시</t>
+          <t>동해시</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>[경기남부] 신혼·신생아 매입임대주택Ⅱ(전세형) 예비입주자 모집공고</t>
+          <t>동해천곡 고령자복지주택(영구임대) 입주자 모집</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -757,12 +753,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020629&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020609&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -777,22 +773,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>부천시 오정구</t>
+          <t>동해시</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>[인천지역본부] 26년 6차 청년 매입임대주택 예비입주자 모집공고(인천,부천)</t>
+          <t>동해천곡 고령자복지주택(행복주택) 입주자 모집</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -802,12 +798,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020693&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020610&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -822,22 +818,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>부천시 원미구</t>
+          <t>동해시</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>[인천지역본부] 26년 6차 청년 매입임대주택 예비입주자 모집공고(인천,부천)</t>
+          <t>동해천곡(고령자) 행복주택 입주자 모집</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -847,12 +843,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020630&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020611&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -872,32 +868,32 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>부천시 원미구</t>
+          <t>김포시</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>[인천지역본부]26년 6차 신혼·신생아Ⅰ 예비입주자 모집공고(인천,부천)</t>
+          <t>김포한강 Ac-05블록 10년 공공임대주택(리츠) 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>10년임대</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020634&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=0000061160&amp;ccrCnntSysDsCd=02&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -917,32 +913,32 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>부천시 원미구</t>
+          <t>안산시 단원구</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>[인천지역본부]26년 6차 신혼·신생아Ⅱ(전세형) 예비입주자 모집공고(인천,부천)</t>
+          <t>안산 선부동 행복주택 예비입주자(청년) 모집 공고</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260826</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020661&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.ansanuc.net</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -957,22 +953,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>부천시 원미구</t>
+          <t>김해시</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>[인천지역본부]26년 6차 신혼·신생아Ⅱ(전세형) 예비입주자 모집공고(인천,부천)</t>
+          <t>김해구산1 영구임대주택 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -982,12 +978,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020633&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020500&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -1002,22 +998,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>대전</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>유성구</t>
+          <t>안동시</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>[대전·충남] 2026년 2차 든든전세주택 입주자 모집공고(비분양전환형)</t>
+          <t>[안동옥동2] 영구임대주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1027,12 +1023,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020620&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020584&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -1047,37 +1043,37 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>사상구</t>
+          <t>달서구</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026년 장기미임대 매입임대주택 (예비)입주자 모집 공고</t>
+          <t>대구가람1단지 50년 공공임대 예비입주자 모집</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>50년임대</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.bmc.busan.kr/board/view.do?boardId=BBS_0000004&amp;menuCd=DOM_000000101001003000&amp;orderBy=DATA_SID%20DESC&amp;paging=ok&amp;startPage=1&amp;dataSid=800624</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020573&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -1092,37 +1088,37 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>남동구</t>
+          <t>정읍시</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>[인천지역본부] 26년 6차 청년 매입임대주택 예비입주자 모집공고(인천,부천)</t>
+          <t>정읍시(정읍수성1)영구임대주택 입주자격완화 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020693&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020666&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -1137,37 +1133,37 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>미추홀구</t>
+          <t>정읍시</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>[인천지역본부] 26년 6차 청년 매입임대주택 예비입주자 모집공고(인천,부천)</t>
+          <t>정읍시(정읍수성1)영구임대주택 입주자격완화 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020630&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020639&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -1182,17 +1178,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>미추홀구</t>
+          <t>제주시</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>[인천지역본부]26년 6차 신혼·신생아Ⅰ 예비입주자 모집공고(인천,부천)</t>
+          <t>2026년 제주특별자치도개발공사 일반 매입임대주택 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1202,17 +1198,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020634&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://www.jpdc.co.kr/open/news/notice.htm?act=view&amp;seq=24135</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -1227,17 +1223,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>부평구</t>
+          <t>서귀포시</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>[인천지역본부]26년 6차 신혼·신생아Ⅱ(전세형) 예비입주자 모집공고(인천,부천)</t>
+          <t>제주특별자치도개발공사 다자녀 매입임대주택 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1247,17 +1243,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020661&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://www.jpdc.co.kr/open/news/notice.htm?act=view&amp;seq=24134</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -1272,17 +1268,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>제물포구</t>
+          <t>김제시</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>[인천지역본부]26년 6차 신혼·신생아Ⅱ(전세형) 예비입주자 모집공고(인천,부천)</t>
+          <t>2026년 한부모주거지원사업 매입주택 입주자 모집</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1292,25 +1288,25 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260901</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020633&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://www.gimje.go.kr/board/list.gimje?boardId=BBS_0000027&amp;listRow=10&amp;listCel=1&amp;menuCd=DOM_000000104001000000&amp;orderBy=REGISTER_DATE%20DESC&amp;paging=ok&amp;categoryCode1=DEPART01,DEPART2005_1,DEPART02,DEPART03,DEPART06,DEPART07,DEPART08,DEPART09,DEPART11,DEPART22,DEPART15,DEPART13,DEPART10,DEPART42,DEPAR</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
@@ -1322,147 +1318,147 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>익산시</t>
+          <t>남원시</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>익산시(익산부송1, 익산동산)영구임대주택 입주자격완화 예비입주자 모집공고</t>
+          <t>남원노암 공공임대 50년 예비입주자 모집</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>50년임대</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>20260908</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020603&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020681&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>아산시</t>
+          <t>익산시</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>[대전·충남] 2026년 2차 든든전세주택 입주자 모집공고(비분양전환형)</t>
+          <t>익산부송3단지 50년 공공임대 예비입주자 모집</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>50년임대</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020620&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020624&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>진천군</t>
+          <t>익산시</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>진천성석,진천이월,청주우암 행복주택(입주자격완화) 예비입주자 추가모집</t>
+          <t>익산시 국민임대주택 예비입주자 모집 공고(26.09.03)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>20260908</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020676&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020636&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>진천군</t>
+          <t>천안시 서북구</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>진천성석,진천이월,청주우암 행복주택(입주자격완화) 예비입주자 추가모집</t>
+          <t>2026년 하반기 충남형 행복주택 매입임대 예비입주자 모집(천안, 보령, 서산)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1472,42 +1468,42 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>20260908</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020672&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.cndc.kr/</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>진천군</t>
+          <t>예산군</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>진천성석,진천이월,청주우암 행복주택(입주자격완화) 예비입주자 추가모집</t>
+          <t>2026년 하반기 충남형 행복주택(꿈비채) 예비입주자 모집 공고문(당진, 천안, 예산)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1517,222 +1513,222 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>20260908</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020646&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.cndc.kr/</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>진천군</t>
+          <t>춘천시</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>진천이월 국민임대주택 예비입주자 모집(소득 및 자산요건배제, 무주택요건 완화)</t>
+          <t>[강원지역본부] 26년 3차 신혼신생아1 매입임대주택 예비자 모집공고</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>20260908</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260916</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020648&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020675&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>D-6</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>청주시 흥덕구</t>
+          <t>강릉시</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>청주산단1,청주산단2 행복주택 예비입주자 모집</t>
+          <t>[강원지역본부] 26년 3차 신혼신생아2(전세형) 매입임대주택 예비자 모집공고</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>20260908</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260916</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020685&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020679&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>D-6</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>청주시 흥덕구</t>
+          <t>춘천시</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>청주산단1,청주산단2 행복주택 예비입주자 모집</t>
+          <t>[강원지역본부] 26년 3차 청년 매입임대주택 예비자 모집공고</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>20260908</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260916</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020671&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020673&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>D-6</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>청주시 흥덕구</t>
+          <t>양산시</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>청주산단1,청주산단2 행복주택 예비입주자 모집</t>
+          <t>양산사송 A-8BL 영구임대주택 입주자격완화 예비입주자 모집</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>20260908</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260916</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020647&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020658&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>D-6</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>춘천시</t>
+          <t>군산시</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>춘천 산수빌 국민임대아파트 예비 입주자 모집안내</t>
+          <t>군산시 국민임대주택 예비입주자 모집 공고(26.09.03)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1742,42 +1738,42 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260916</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.gdco.co.kr/customer/notice_view.php?intSeq=5805&amp;strBoardID=NOTI&amp;page=1&amp;pageSize=10</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020663&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>D-7</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>고령군</t>
+          <t>김제시</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>고령디오팰리스 국민임대주택 입주자격완화 예비입주자 모집</t>
+          <t>김제하동 국민임대주택 모집공고</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1787,79 +1783,87 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>20260908</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020615&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020701&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>D-7</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>세종</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr"/>
+          <t>충남</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>서산시</t>
+        </is>
+      </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026년 세종시 영구임대주택(도램마을7‧8단지) 입주자 및 예비입주자 모집 공고</t>
+          <t>서산석림3단지 50년공공임대주택 예비입주자 모집공고(2026.09.01.)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>50년임대</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.sjfmc.or.kr/kor/sub02_01/cop/bbs/BBSMSTR_000000000013/selectBoardArticle.do?nttId=12843</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020657&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>D-7</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>세종</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr"/>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>부천시 원미구</t>
+        </is>
+      </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>세종 신흥사랑주택 입주자 15차 모집 공고</t>
+          <t>부천시 영구임대주택 예비입주자 모집 (중동한라1, 중동덕유1)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1869,70 +1873,70 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260916</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260918</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.sjfmc.or.kr/kor/sub02_01/cop/bbs/BBSMSTR_000000000013/selectBoardArticle.do?nttId=12845&amp;kind=&amp;mno=sitemap_02&amp;pageIndex=1&amp;searchCnd=0&amp;searchWrd=%EC%9E%85%EC%A3%BC%EC%9E%90+%EB%AA%A8%EC%A7%91</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020678&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>D-8</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>서귀포시</t>
+          <t>안산시 단원구</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>[제주지역본부] 신혼.신생아 매입임대주택Ⅰ 예비입주자 모집 공고 (서귀포시)</t>
+          <t>안산 선부동 행복주택 예비입주자(주거급여)모집 공고</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260903</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260918</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020622&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://www.ansanuc.net/homenew/12286/20328/bbsList.do</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>D-8</t>
         </is>
       </c>
     </row>
@@ -1944,12 +1948,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>제주시</t>
+          <t>서귀포시</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>[제주지역본부] 신혼.신생아 매입임대주택Ⅰ 예비입주자 모집 공고 (제주시)</t>
+          <t>[제주지역본부] 다자녀 매입임대주택 예비입주자 모집 공고(서귀포시)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1959,672 +1963,656 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260918</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020622&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020691&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>D-8</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>강원</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>동해시</t>
-        </is>
-      </c>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
-          <t>동해천곡 고령자복지주택(영구임대) 입주자 모집</t>
+          <t>[경기남부] 용인시 신혼·신생아 매입임대주택Ⅱ(전세형) 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020609&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020702&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-11</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>강원</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>동해시</t>
-        </is>
-      </c>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
-          <t>동해천곡 고령자복지주택(행복주택) 입주자 모집</t>
+          <t>[경기남부] 용인시 청년 매입임대주택 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020610&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020699&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-11</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>강원</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>동해시</t>
-        </is>
-      </c>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>동해천곡(고령자) 행복주택 입주자 모집</t>
+          <t>[경기남부] 화성시·평택시 신혼·신생아 매입임대주택Ⅱ(전세형) 예비입주자 [후순번] 모집공고</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020611&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020703&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-11</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>김포시</t>
+          <t>포항시 북구</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>김포한강 Ac-05블록 10년 공공임대주택(리츠) 예비입주자 모집 공고</t>
+          <t>포항창포 영구임대아파트 예비입주자 모집</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>10년임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=0000061160&amp;ccrCnntSysDsCd=02&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020651&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-11</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>안산시 단원구</t>
+          <t>포항시 북구</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>안산 선부동 행복주택 예비입주자(청년) 모집 공고</t>
+          <t>포항학산 영구임대아파트 예비입주자 모집</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://apply.ansanuc.net</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020650&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-11</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>김해시</t>
+          <t>부천시 오정구</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>김해구산1 영구임대주택 예비입주자 모집 공고</t>
+          <t>2026년 9월 부천시 국민임대주택 예비입주자 모집 공고(2026.09.07)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260922</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020500&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020652&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>경북</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>안동시</t>
-        </is>
-      </c>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
         <is>
-          <t>[안동옥동2] 영구임대주택 예비입주자 모집</t>
+          <t>26-4차 인천본부 든든전세주택 입주자 모집공고(인천, 부천)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260922</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020584&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020715&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>달서구</t>
+          <t>경주시</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>대구가람1단지 50년 공공임대 예비입주자 모집</t>
+          <t>경주시, 영천시, 포항시 부도매입(국민임대)주택 입주자격완화 모집공고</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>50년임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260922</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020573&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020635&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>정읍시</t>
+          <t>미추홀구</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>정읍시(정읍수성1)영구임대주택 입주자격완화 예비입주자 모집공고</t>
+          <t>26-4차 인천본부 든든전세주택 입주자 모집공고(인천, 부천)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260922</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020666&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020715&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>정읍시</t>
+          <t>남동구</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>정읍시(정읍수성1)영구임대주택 입주자격완화 예비입주자 모집공고</t>
+          <t>26년 9월 인천시 남동구 국민임대주택 예비입주자 모집 공고(2026.09.07)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260922</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020639&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020619&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>제주시</t>
+          <t>옹진군</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026년 제주특별자치도개발공사 일반 매입임대주택 예비입주자 모집 공고</t>
+          <t>인천옹진백령 국민임대주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260922</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.jpdc.co.kr/open/news/notice.htm?act=view&amp;seq=24135</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020578&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>서귀포시</t>
+          <t>옹진군</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>제주특별자치도개발공사 다자녀 매입임대주택 예비입주자 모집 공고</t>
+          <t>인천옹진연평 국민임대주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260922</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260922</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.jpdc.co.kr/open/news/notice.htm?act=view&amp;seq=24134</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020697&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>남원시</t>
+          <t>횡성군</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>남원노암 공공임대 50년 예비입주자 모집</t>
+          <t>강원횡성 통합공공임대주택 입주자 모집</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>50년임대</t>
+          <t>통합공공임대</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260923</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020681&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020627&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=48&amp;mi=1026</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-13</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>익산시</t>
+          <t>김포시</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>익산부송3단지 50년 공공임대 예비입주자 모집</t>
+          <t>김포시 국민임대주택 예비입주자 모집(2026.09.07)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>50년임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260923</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020624&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020659&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-13</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>익산시</t>
+          <t>화성시 효행구</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>익산시 국민임대주택 예비입주자 모집 공고(26.09.03)</t>
+          <t>화성서부권 국민임대주택 예비입주자 모집[입주자격완화]</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2634,87 +2622,87 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260923</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020636&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020686&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-13</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>천안시 서북구</t>
+          <t>익산시</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026년 하반기 충남형 행복주택 매입임대 예비입주자 모집(천안, 보령, 서산)</t>
+          <t>익산한스빌 국민임대주택 예비입주자 자격완화 모집 공고</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260922</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260923</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://apply.cndc.kr/</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020694&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-13</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>예산군</t>
+          <t>경산시</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026년 하반기 충남형 행복주택(꿈비채) 예비입주자 모집 공고문(당진, 천안, 예산)</t>
+          <t>대구혁신10, 경산하양3 행복주택 입주자격완화 선계약 후검증 동호지정 입주자 모집</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2724,267 +2712,267 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://apply.cndc.kr/</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020682&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-19</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>춘천시</t>
+          <t>동구</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>[강원지역본부] 26년 3차 신혼신생아1 매입임대주택 예비자 모집공고</t>
+          <t>대구혁신10, 경산하양3 행복주택 입주자격완화 선계약 후검증 동호지정 입주자 모집</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>20260916</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020675&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020682&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-19</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>강릉시</t>
+          <t>김포시</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>[강원지역본부] 26년 3차 신혼신생아2(전세형) 매입임대주택 예비자 모집공고</t>
+          <t>김포지역 국민임대주택 예비입주자 모집 공고(26.09.07.)</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260918</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>20260916</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020679&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020704&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-20</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>춘천시</t>
+          <t>김포시</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>[강원지역본부] 26년 3차 청년 매입임대주택 예비자 모집공고</t>
+          <t>김포지역 국민임대주택 예비입주자 모집 공고(26.09.07.)</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260918</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>20260916</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020673&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020662&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-20</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>양산시</t>
+          <t>안성시</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>양산사송 A-8BL 영구임대주택 입주자격완화 예비입주자 모집</t>
+          <t>안성금화 국민임대 입주자격완화 예비입주자 모집공고(2026.09.07)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>20260916</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020658&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020695&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-20</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>군산시</t>
+          <t>북구</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>군산시 국민임대주택 예비입주자 모집 공고(26.09.03)</t>
+          <t>부산만덕5 2블록 10년 분양전환공공임대주택(e편한세상 금정산) 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>10년임대</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>20260916</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>20260917</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020663&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=0000061163&amp;ccrCnntSysDsCd=02&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>D-9</t>
+          <t>D-20</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>김제시</t>
+          <t>남양주시</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>김제하동 국민임대주택 모집공고</t>
+          <t>남양주마석2단지 국민임대주택 예비입주자 모집공고(2026.9.7.)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2994,177 +2982,173 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>20260917</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020701&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020710&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>D-9</t>
+          <t>D-21</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>서산시</t>
+          <t>남양주시</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>서산석림3단지 50년공공임대주택 예비입주자 모집공고(2026.09.01.)</t>
+          <t>남양주마석2단지 국민임대주택 예비입주자 모집공고(2026.9.7.)</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>50년임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>20260917</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020657&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020668&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>D-9</t>
+          <t>D-21</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>부천시 원미구</t>
+          <t>김해시</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>부천시 영구임대주택 예비입주자 모집 (중동한라1, 중동덕유1)</t>
+          <t>[경남지역본부] 일반 매입임대주택 입주자 모집 공고(김해시, 밀양시)</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>20260916</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020678&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020706&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>D-21</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>경기</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>안산시 단원구</t>
-        </is>
-      </c>
+          <t>경북</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr">
         <is>
-          <t>안산 선부동 행복주택 예비입주자(주거급여)모집 공고</t>
+          <t>[경북 포항,경주,영천] 일반 매입임대 입주자 모집공고</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>20260903</t>
+          <t>20260908</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.ansanuc.net/homenew/12286/20328/bbsList.do</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020654&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>D-21</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>서귀포시</t>
+          <t>포항시 남구</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>[제주지역본부] 다자녀 매입임대주택 예비입주자 모집 공고(서귀포시)</t>
+          <t>[경북 포항,경주,영천] 일반 매입임대 입주자 모집공고</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3174,79 +3158,87 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>20260917</t>
+          <t>20260908</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020691&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020601&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>D-21</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>경기</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr"/>
+          <t>충북</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>청주시 서원구</t>
+        </is>
+      </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>[경기남부] 용인시 신혼·신생아 매입임대주택Ⅱ(전세형) 예비입주자 모집공고</t>
+          <t>청주산남2-1 영구임대주택 예비입주자 모집 공고(2026.08.28)</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>20260917</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20261002</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020702&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020625&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>D-13</t>
+          <t>D-22</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>경기</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr"/>
+          <t>충남</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>당진시</t>
+        </is>
+      </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>[경기남부] 용인시 청년 매입임대주택 예비입주자 모집공고</t>
+          <t>[청년신혼부부매입임대리츠주택] 충남당진 송산청광플러스원 입주자격완화 상시모집</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3256,87 +3248,87 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>20260917</t>
+          <t>20260810</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020699&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020529&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H64" t="n">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>D-13</t>
+          <t>D-35</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>평택시</t>
+          <t>양산시</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>[경기남부] 화성시·평택시 신혼·신생아 매입임대주택Ⅱ(전세형) 예비입주자 [후순번] 모집공고</t>
+          <t>양산 사송A-4BL 국민임대주택(29A형)선착순 동호지정 모집(입주자격완화, 선계약 후검증)</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>20260917</t>
+          <t>20260813</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20261029</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020703&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020495&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>D-13</t>
+          <t>D-49</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>포항시 북구</t>
+          <t>군산시</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>포항창포 영구임대아파트 예비입주자 모집</t>
+          <t>군산신역세권A3(내흥3) 영구임대주택 입주자 추가모집</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3346,25 +3338,25 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20261030</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020651&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019841&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>D-13</t>
+          <t>D-50</t>
         </is>
       </c>
     </row>
@@ -3376,85 +3368,85 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>포항시 북구</t>
+          <t>칠곡군</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>포항학산 영구임대아파트 예비입주자 모집</t>
+          <t>2026년 칠곡군 천원주택(신혼·신생아 매입임대주택Ⅰ) 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260728</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20261130</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020650&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=e54448a5-4c8c-4c3d-bfcf-bc465f677408&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>13</v>
+        <v>81</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>D-13</t>
+          <t>D-81</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>부천시 오정구</t>
+          <t>칠곡군</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026년 9월 부천시 국민임대주택 예비입주자 모집 공고(2026.09.07)</t>
+          <t>2026년 칠곡군 천원주택(청년 매입임대주택) 입주자 및 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260728</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>20260922</t>
+          <t>20261130</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020652&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=2e8989e9-02ae-48be-9591-f3c4c8e7fa39&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>14</v>
+        <v>81</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>D-81</t>
         </is>
       </c>
     </row>
@@ -3466,57 +3458,57 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>경주시</t>
+          <t>포항시 남구</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>경주시, 영천시, 포항시 부도매입(국민임대)주택 입주자격완화 모집공고</t>
+          <t>포항블루밸리 행복주택 선착순 동호지정 상시모집(입주자격 완화, 통합공임 일반계층 추가, 선계약 후검증)</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260707</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>20260922</t>
+          <t>20261222</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020635&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020042&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>14</v>
+        <v>103</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>D-103</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>남동구</t>
+          <t>삼척시</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>26년 9월 인천시 남동구 국민임대주택 예비입주자 모집 공고(2026.09.07)</t>
+          <t>삼척시·정선군 국민임대 예비입주자 상시모집(26.6.10)</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3526,115 +3518,107 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260624</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>20260922</t>
+          <t>20261230</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020619&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020090&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>14</v>
+        <v>111</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>D-111</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>인천</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>옹진군</t>
-        </is>
-      </c>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr">
         <is>
-          <t>인천옹진백령 국민임대주택 예비입주자 모집</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>20260922</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020578&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>14</v>
+        <v>112</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>D-112</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>인천</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>옹진군</t>
-        </is>
-      </c>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr">
         <is>
-          <t>인천옹진연평 국민임대주택 예비입주자 모집</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>20260922</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>20260922</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020697&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>14</v>
+        <v>112</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>D-112</t>
         </is>
       </c>
     </row>
@@ -3644,104 +3628,96 @@
           <t>강원</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>횡성군</t>
-        </is>
-      </c>
+      <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr">
         <is>
-          <t>강원횡성 통합공공임대주택 입주자 모집</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>통합공공임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>20260923</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020627&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=48&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>15</v>
+        <v>112</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>D-15</t>
+          <t>D-112</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>경기</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>김포시</t>
-        </is>
-      </c>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr"/>
       <c r="C74" t="inlineStr">
         <is>
-          <t>김포시 국민임대주택 예비입주자 모집(2026.09.07)</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>20260923</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020659&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>15</v>
+        <v>112</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>D-15</t>
+          <t>D-112</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>익산시</t>
+          <t>동해시</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>익산한스빌 국민임대주택 예비입주자 자격완화 모집 공고</t>
+          <t>동해유성,태백철암장미 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -3751,115 +3727,115 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>20260922</t>
+          <t>20260212</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>20260923</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020694&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019312&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H75" t="n">
-        <v>15</v>
+        <v>112</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>D-15</t>
+          <t>D-112</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>경산시</t>
+          <t>동해시</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>대구혁신10, 경산하양3 행복주택 입주자격완화 선계약 후검증 동호지정 입주자 모집</t>
+          <t>동해유성,태백철암장미 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260212</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020682&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019308&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H76" t="n">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>D-21</t>
+          <t>D-112</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>동구</t>
+          <t>태백시</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>대구혁신10, 경산하양3 행복주택 입주자격완화 선계약 후검증 동호지정 입주자 모집</t>
+          <t>태백궁전 국민임대 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260212</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020682&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019307&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>D-21</t>
+          <t>D-112</t>
         </is>
       </c>
     </row>
@@ -3869,42 +3845,38 @@
           <t>경기</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>김포시</t>
-        </is>
-      </c>
+      <c r="B78" t="inlineStr"/>
       <c r="C78" t="inlineStr">
         <is>
-          <t>김포지역 국민임대주택 예비입주자 모집 공고(26.09.07.)</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020704&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H78" t="n">
-        <v>22</v>
+        <v>112</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>D-22</t>
+          <t>D-112</t>
         </is>
       </c>
     </row>
@@ -3914,42 +3886,38 @@
           <t>경기</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>김포시</t>
-        </is>
-      </c>
+      <c r="B79" t="inlineStr"/>
       <c r="C79" t="inlineStr">
         <is>
-          <t>김포지역 국민임대주택 예비입주자 모집 공고(26.09.07.)</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020662&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H79" t="n">
-        <v>22</v>
+        <v>112</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>D-22</t>
+          <t>D-112</t>
         </is>
       </c>
     </row>
@@ -3959,398 +3927,366 @@
           <t>경기</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>안성시</t>
-        </is>
-      </c>
+      <c r="B80" t="inlineStr"/>
       <c r="C80" t="inlineStr">
         <is>
-          <t>안성금화 국민임대 입주자격완화 예비입주자 모집공고(2026.09.07)</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020695&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H80" t="n">
-        <v>22</v>
+        <v>112</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>D-22</t>
+          <t>D-112</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>부산</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>북구</t>
-        </is>
-      </c>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr"/>
       <c r="C81" t="inlineStr">
         <is>
-          <t>부산만덕5 2블록 10년 분양전환공공임대주택(e편한세상 금정산) 예비입주자 모집공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>10년임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=0000061163&amp;ccrCnntSysDsCd=02&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H81" t="n">
-        <v>22</v>
+        <v>112</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>D-22</t>
+          <t>D-112</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>경기</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>남양주시</t>
-        </is>
-      </c>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr"/>
       <c r="C82" t="inlineStr">
         <is>
-          <t>남양주마석2단지 국민임대주택 예비입주자 모집공고(2026.9.7.)</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020668&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H82" t="n">
-        <v>23</v>
+        <v>112</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>D-23</t>
+          <t>D-112</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="inlineStr">
         <is>
-          <t>[경북 포항,경주,영천] 일반 매입임대 입주자 모집공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>20260908</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020654&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H83" t="n">
-        <v>23</v>
+        <v>112</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>D-23</t>
+          <t>D-112</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>경북</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>포항시 남구</t>
-        </is>
-      </c>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr"/>
       <c r="C84" t="inlineStr">
         <is>
-          <t>[경북 포항,경주,영천] 일반 매입임대 입주자 모집공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>20260908</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020601&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H84" t="n">
-        <v>23</v>
+        <v>112</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>D-23</t>
+          <t>D-112</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>충북</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>청주시 서원구</t>
-        </is>
-      </c>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr"/>
       <c r="C85" t="inlineStr">
         <is>
-          <t>청주산남2-1 영구임대주택 예비입주자 모집 공고(2026.08.28)</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020625&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H85" t="n">
-        <v>24</v>
+        <v>112</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>D-24</t>
+          <t>D-112</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>충남</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>당진시</t>
-        </is>
-      </c>
+          <t>경북</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr"/>
       <c r="C86" t="inlineStr">
         <is>
-          <t>[청년신혼부부매입임대리츠주택] 충남당진 송산청광플러스원 입주자격완화 상시모집</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>20260810</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020529&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H86" t="n">
-        <v>37</v>
+        <v>112</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>D-37</t>
+          <t>D-112</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>양산시</t>
-        </is>
-      </c>
+          <t>경북</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr"/>
       <c r="C87" t="inlineStr">
         <is>
-          <t>양산 사송A-4BL 국민임대주택(29A형)선착순 동호지정 모집(입주자격완화, 선계약 후검증)</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>20260813</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>20261029</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020495&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H87" t="n">
-        <v>51</v>
+        <v>112</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>D-51</t>
+          <t>D-112</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>전북</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>군산시</t>
-        </is>
-      </c>
+          <t>경북</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr"/>
       <c r="C88" t="inlineStr">
         <is>
-          <t>군산신역세권A3(내흥3) 영구임대주택 입주자 추가모집</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>20261030</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019841&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H88" t="n">
-        <v>52</v>
+        <v>112</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>D-52</t>
+          <t>D-112</t>
         </is>
       </c>
     </row>
@@ -4360,190 +4296,174 @@
           <t>경북</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>칠곡군</t>
-        </is>
-      </c>
+      <c r="B89" t="inlineStr"/>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2026년 칠곡군 천원주택(신혼·신생아 매입임대주택Ⅰ) 예비입주자 모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>20260728</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>20261130</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=e54448a5-4c8c-4c3d-bfcf-bc465f677408&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H89" t="n">
-        <v>83</v>
+        <v>112</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>D-83</t>
+          <t>D-112</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>경북</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>칠곡군</t>
-        </is>
-      </c>
+          <t>대구</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr"/>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2026년 칠곡군 천원주택(청년 매입임대주택) 입주자 및 예비입주자 모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>20260728</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>20261130</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=2e8989e9-02ae-48be-9591-f3c4c8e7fa39&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H90" t="n">
-        <v>83</v>
+        <v>112</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>D-83</t>
+          <t>D-112</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>경북</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>포항시 남구</t>
-        </is>
-      </c>
+          <t>대구</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr"/>
       <c r="C91" t="inlineStr">
         <is>
-          <t>포항블루밸리 행복주택 선착순 동호지정 상시모집(입주자격 완화, 통합공임 일반계층 추가, 선계약 후검증)</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>20260707</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>20261222</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020042&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H91" t="n">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>D-105</t>
+          <t>D-112</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>강원</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>삼척시</t>
-        </is>
-      </c>
+          <t>대구</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr"/>
       <c r="C92" t="inlineStr">
         <is>
-          <t>삼척시·정선군 국민임대 예비입주자 상시모집(26.6.10)</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>20260624</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>20261230</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020090&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H92" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>D-113</t>
+          <t>D-112</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -4553,7 +4473,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -4563,28 +4483,28 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H93" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>D-114</t>
+          <t>D-112</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>대전</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -4604,28 +4524,28 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H94" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>D-114</t>
+          <t>D-112</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>대전</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -4645,28 +4565,28 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H95" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>D-114</t>
+          <t>D-112</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>대전</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -4676,7 +4596,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -4686,42 +4606,38 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H96" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>D-114</t>
+          <t>D-112</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>강원</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>동해시</t>
-        </is>
-      </c>
+          <t>대전</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr">
         <is>
-          <t>동해유성,태백철암장미 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>20260212</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -4731,42 +4647,38 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019312&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H97" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>D-114</t>
+          <t>D-112</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>강원</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>동해시</t>
-        </is>
-      </c>
+          <t>부산</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr"/>
       <c r="C98" t="inlineStr">
         <is>
-          <t>동해유성,태백철암장미 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>20260212</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -4776,42 +4688,38 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019308&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H98" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>D-114</t>
+          <t>D-112</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>강원</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>태백시</t>
-        </is>
-      </c>
+          <t>부산</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr">
         <is>
-          <t>태백궁전 국민임대 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>20260212</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -4821,28 +4729,28 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019307&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H99" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>D-114</t>
+          <t>D-112</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -4862,28 +4770,28 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H100" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>D-114</t>
+          <t>D-112</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -4893,7 +4801,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -4903,28 +4811,28 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H101" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>D-114</t>
+          <t>D-112</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -4944,28 +4852,28 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H102" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>D-114</t>
+          <t>D-112</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -4975,7 +4883,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4985,28 +4893,28 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H103" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>D-114</t>
+          <t>D-112</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -5026,28 +4934,28 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H104" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>D-114</t>
+          <t>D-112</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -5057,7 +4965,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -5067,28 +4975,28 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H105" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>D-114</t>
+          <t>D-112</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>세종</t>
         </is>
       </c>
       <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -5108,28 +5016,28 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H106" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>D-114</t>
+          <t>D-112</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>세종</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -5139,7 +5047,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -5149,28 +5057,28 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H107" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>D-114</t>
+          <t>D-112</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>세종</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -5190,28 +5098,28 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H108" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>D-114</t>
+          <t>D-112</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>세종</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -5221,7 +5129,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -5231,28 +5139,28 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H109" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>D-114</t>
+          <t>D-112</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>울산</t>
         </is>
       </c>
       <c r="B110" t="inlineStr"/>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -5272,28 +5180,28 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H110" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>D-114</t>
+          <t>D-112</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>울산</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -5303,7 +5211,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -5313,28 +5221,28 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H111" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>D-114</t>
+          <t>D-112</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>울산</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -5354,28 +5262,28 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H112" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>D-114</t>
+          <t>D-112</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>울산</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -5385,7 +5293,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -5395,28 +5303,28 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H113" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>D-114</t>
+          <t>D-112</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B114" t="inlineStr"/>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -5436,28 +5344,28 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H114" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>D-114</t>
+          <t>D-112</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B115" t="inlineStr"/>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -5467,7 +5375,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -5477,28 +5385,28 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H115" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>D-114</t>
+          <t>D-112</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>대전</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -5518,28 +5426,28 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H116" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>D-114</t>
+          <t>D-112</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>대전</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -5549,7 +5457,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -5559,28 +5467,28 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H117" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>D-114</t>
+          <t>D-112</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>대전</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -5600,28 +5508,28 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H118" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>D-114</t>
+          <t>D-112</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>대전</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B119" t="inlineStr"/>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -5631,7 +5539,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -5641,28 +5549,28 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H119" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>D-114</t>
+          <t>D-112</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -5682,28 +5590,28 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H120" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>D-114</t>
+          <t>D-112</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -5713,7 +5621,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -5723,38 +5631,42 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H121" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>D-114</t>
+          <t>D-112</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>부산</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr"/>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>김제시</t>
+        </is>
+      </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>김제검산1단지 영구임대주택 예비입주자 모집 공고(상시모집)</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260101</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -5764,38 +5676,42 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019412&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H122" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>D-114</t>
+          <t>D-112</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>부산</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr"/>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>남원시</t>
+        </is>
+      </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>남원노암 공공임대 50년 예비입주자 모집</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>50년임대</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -5805,38 +5721,42 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020623&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H123" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>D-114</t>
+          <t>D-112</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>서울</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr"/>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>남원시</t>
+        </is>
+      </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>남원노암단지 영구임대주택 입주자격완화 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -5846,38 +5766,42 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020649&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H124" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>D-114</t>
+          <t>D-112</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>서울</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr"/>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>전주시 완산구</t>
+        </is>
+      </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>전주시(전주평화1,전주평화4) 영구임대주택 예비입주자 모집 공고(공고일:2026.02.10.)</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260303</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -5887,28 +5811,28 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019241&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H125" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>D-114</t>
+          <t>D-112</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -5928,28 +5852,28 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H126" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>D-114</t>
+          <t>D-112</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="B127" t="inlineStr"/>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -5959,7 +5883,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -5969,28 +5893,28 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H127" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>D-114</t>
+          <t>D-112</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>세종</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="B128" t="inlineStr"/>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -6010,28 +5934,28 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H128" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>D-114</t>
+          <t>D-112</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>세종</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="B129" t="inlineStr"/>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -6041,7 +5965,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -6051,28 +5975,28 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H129" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>D-114</t>
+          <t>D-112</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>세종</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B130" t="inlineStr"/>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -6092,28 +6016,28 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H130" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>D-114</t>
+          <t>D-112</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>세종</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B131" t="inlineStr"/>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -6123,7 +6047,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -6133,28 +6057,28 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H131" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>D-114</t>
+          <t>D-112</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>울산</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B132" t="inlineStr"/>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -6174,28 +6098,28 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H132" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>D-114</t>
+          <t>D-112</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>울산</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B133" t="inlineStr"/>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -6205,7 +6129,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -6215,38 +6139,42 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H133" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>D-114</t>
+          <t>D-112</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>울산</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr"/>
+          <t>충남</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>당진시</t>
+        </is>
+      </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>[청년신혼부부매입임대리츠주택] 충남당진 송산청광플러스원 입주자격완화 상시모집</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260316</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -6256,28 +6184,28 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019433&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H134" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>D-114</t>
+          <t>D-112</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>울산</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -6287,7 +6215,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -6297,28 +6225,28 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H135" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>D-114</t>
+          <t>D-112</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B136" t="inlineStr"/>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -6338,28 +6266,28 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H136" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>D-114</t>
+          <t>D-112</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B137" t="inlineStr"/>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -6379,28 +6307,28 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H137" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>D-114</t>
+          <t>D-112</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -6410,7 +6338,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -6420,56 +6348,60 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H138" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>D-114</t>
+          <t>D-112</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>인천</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr"/>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>삼척시</t>
+        </is>
+      </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>삼척도계·정선신동 국민임대주택 예비입주자 입주자격완화 공고</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20270129</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020581&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H139" t="n">
-        <v>114</v>
+        <v>141</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>D-114</t>
+          <t>D-141</t>
         </is>
       </c>
     </row>
@@ -6479,1058 +6411,132 @@
           <t>전북</t>
         </is>
       </c>
-      <c r="B140" t="inlineStr"/>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>군산시</t>
+        </is>
+      </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>군산시 국민임대주택 입주자 선착순 상시 모집(경암부향 등 7개 단지)</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260812</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20270731</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020453&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H140" t="n">
-        <v>114</v>
+        <v>324</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>D-114</t>
+          <t>D-324</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>전북</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr"/>
+          <t>울산</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>울주군</t>
+        </is>
+      </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>울산광역시 국민임대주택 예비입주자 정례모집 공고(2025.09.15.)</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20250929</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20291001</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300018799&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H141" t="n">
-        <v>114</v>
+        <v>1117</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>D-114</t>
+          <t>D-1117</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>전북</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr"/>
+          <t>울산</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>울주군</t>
+        </is>
+      </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>울산광역시 국민임대주택 예비입주자 정례모집 공고(2025.09.15.)</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20250929</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20291001</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300018780&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H142" t="n">
-        <v>114</v>
+        <v>1117</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>D-114</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>전북</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr"/>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>전세임대</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>20260224</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>20261231</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
-        </is>
-      </c>
-      <c r="H143" t="n">
-        <v>114</v>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>D-114</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>전북</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>김제시</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>김제검산1단지 영구임대주택 예비입주자 모집 공고(상시모집)</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>영구임대</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>20261231</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019412&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
-        </is>
-      </c>
-      <c r="H144" t="n">
-        <v>114</v>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>D-114</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>전북</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>남원시</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>남원노암 공공임대 50년 예비입주자 모집</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>50년임대</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>20260921</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>20261231</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020623&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
-        </is>
-      </c>
-      <c r="H145" t="n">
-        <v>114</v>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>D-114</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>전북</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>남원시</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>남원노암단지 영구임대주택 입주자격완화 예비입주자 모집공고</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>영구임대</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>20260921</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>20261231</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020649&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
-        </is>
-      </c>
-      <c r="H146" t="n">
-        <v>114</v>
-      </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>D-114</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>전북</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>전주시 완산구</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>전주시(전주평화1,전주평화4) 영구임대주택 예비입주자 모집 공고(공고일:2026.02.10.)</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>영구임대</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>20260303</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>20261231</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019241&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
-        </is>
-      </c>
-      <c r="H147" t="n">
-        <v>114</v>
-      </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>D-114</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>제주</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr"/>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>전세임대</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>20260324</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>20261231</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
-        </is>
-      </c>
-      <c r="H148" t="n">
-        <v>114</v>
-      </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>D-114</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>제주</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr"/>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>전세임대</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>20260324</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>20261231</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
-        </is>
-      </c>
-      <c r="H149" t="n">
-        <v>114</v>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>D-114</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>제주</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr"/>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>전세임대</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>20260324</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>20261231</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
-        </is>
-      </c>
-      <c r="H150" t="n">
-        <v>114</v>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>D-114</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>제주</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr"/>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>전세임대</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>20260224</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>20261231</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
-        </is>
-      </c>
-      <c r="H151" t="n">
-        <v>114</v>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>D-114</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>충남</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr"/>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>전세임대</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>20260324</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>20261231</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
-        </is>
-      </c>
-      <c r="H152" t="n">
-        <v>114</v>
-      </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>D-114</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>충남</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr"/>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>전세임대</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>20260324</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>20261231</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
-        </is>
-      </c>
-      <c r="H153" t="n">
-        <v>114</v>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>D-114</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>충남</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr"/>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>전세임대</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>20260324</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>20261231</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
-        </is>
-      </c>
-      <c r="H154" t="n">
-        <v>114</v>
-      </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>D-114</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>충남</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr"/>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>전세임대</t>
-        </is>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>20260224</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>20261231</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
-        </is>
-      </c>
-      <c r="H155" t="n">
-        <v>114</v>
-      </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>D-114</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>충남</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>당진시</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>[청년신혼부부매입임대리츠주택] 충남당진 송산청광플러스원 입주자격완화 상시모집</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>매입임대</t>
-        </is>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>20260316</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>20261231</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019433&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
-        </is>
-      </c>
-      <c r="H156" t="n">
-        <v>114</v>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>D-114</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>충북</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr"/>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>전세임대</t>
-        </is>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>20260324</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>20261231</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
-        </is>
-      </c>
-      <c r="H157" t="n">
-        <v>114</v>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>D-114</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>충북</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr"/>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>전세임대</t>
-        </is>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>20260324</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>20261231</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
-        </is>
-      </c>
-      <c r="H158" t="n">
-        <v>114</v>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>D-114</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>충북</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr"/>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>전세임대</t>
-        </is>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>20260324</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>20261231</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
-        </is>
-      </c>
-      <c r="H159" t="n">
-        <v>114</v>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>D-114</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>충북</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr"/>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>전세임대</t>
-        </is>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>20260224</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>20261231</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
-        </is>
-      </c>
-      <c r="H160" t="n">
-        <v>114</v>
-      </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>D-114</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>강원</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>삼척시</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>삼척도계·정선신동 국민임대주택 예비입주자 입주자격완화 공고</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>국민임대</t>
-        </is>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>20260915</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>20270129</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020581&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
-        </is>
-      </c>
-      <c r="H161" t="n">
-        <v>143</v>
-      </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>D-143</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>전북</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>군산시</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>군산시 국민임대주택 입주자 선착순 상시 모집(경암부향 등 7개 단지)</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>국민임대</t>
-        </is>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>20260812</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>20270731</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020453&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
-        </is>
-      </c>
-      <c r="H162" t="n">
-        <v>326</v>
-      </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>D-326</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>울산</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>울주군</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>울산광역시 국민임대주택 예비입주자 정례모집 공고(2025.09.15.)</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>국민임대</t>
-        </is>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>20250929</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>20291001</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300018799&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
-        </is>
-      </c>
-      <c r="H163" t="n">
-        <v>1119</v>
-      </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>D-1119</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>울산</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>울주군</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>울산광역시 국민임대주택 예비입주자 정례모집 공고(2025.09.15.)</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>국민임대</t>
-        </is>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>20250929</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>20291001</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300018780&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
-        </is>
-      </c>
-      <c r="H164" t="n">
-        <v>1119</v>
-      </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>D-1119</t>
+          <t>D-1117</t>
         </is>
       </c>
     </row>

--- a/housing_notices.xlsx
+++ b/housing_notices.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I142"/>
+  <dimension ref="A1:I147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,32 +471,32 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>춘천시</t>
+          <t>동해시</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>춘천 산수빌 국민임대아파트 예비 입주자 모집안내</t>
+          <t>동해천곡 고령자복지주택(영구임대) 입주자 모집</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.gdco.co.kr/customer/notice_view.php?intSeq=5805&amp;strBoardID=NOTI&amp;page=1&amp;pageSize=10</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020609&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -511,37 +511,37 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>고령군</t>
+          <t>동해시</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>고령디오팰리스 국민임대주택 입주자격완화 예비입주자 모집</t>
+          <t>동해천곡 고령자복지주택(행복주택) 입주자 모집</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>20260908</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020615&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020610&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -556,18 +556,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>세종</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>동해시</t>
+        </is>
+      </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026년 세종시 영구임대주택(도램마을7‧8단지) 입주자 및 예비입주자 모집 공고</t>
+          <t>동해천곡(고령자) 행복주택 입주자 모집</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -577,12 +581,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.sjfmc.or.kr/kor/sub02_01/cop/bbs/BBSMSTR_000000000013/selectBoardArticle.do?nttId=12843</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020611&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -597,33 +601,37 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>세종</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>김포시</t>
+        </is>
+      </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>세종 신흥사랑주택 입주자 15차 모집 공고</t>
+          <t>김포한강 Ac-05블록 10년 공공임대주택(리츠) 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>10년임대</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.sjfmc.or.kr/kor/sub02_01/cop/bbs/BBSMSTR_000000000013/selectBoardArticle.do?nttId=12845&amp;kind=&amp;mno=sitemap_02&amp;pageIndex=1&amp;searchCnd=0&amp;searchWrd=%EC%9E%85%EC%A3%BC%EC%9E%90+%EB%AA%A8%EC%A7%91</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=0000061160&amp;ccrCnntSysDsCd=02&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -638,37 +646,37 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>서귀포시</t>
+          <t>안산시 단원구</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>[제주지역본부] 신혼.신생아 매입임대주택Ⅰ 예비입주자 모집 공고 (서귀포시)</t>
+          <t>안산 선부동 행복주택 예비입주자(청년) 모집 공고</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260826</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020622&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.ansanuc.net</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -683,37 +691,37 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>제주시</t>
+          <t>김해시</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>[제주지역본부] 신혼.신생아 매입임대주택Ⅰ 예비입주자 모집 공고 (제주시)</t>
+          <t>김해구산1 영구임대주택 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020622&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020500&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -728,17 +736,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>동해시</t>
+          <t>안동시</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>동해천곡 고령자복지주택(영구임대) 입주자 모집</t>
+          <t>[안동옥동2] 영구임대주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -758,42 +766,42 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020609&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020584&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>오늘 마감</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>동해시</t>
+          <t>달서구</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>동해천곡 고령자복지주택(행복주택) 입주자 모집</t>
+          <t>대구가람1단지 50년 공공임대 예비입주자 모집</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>50년임대</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -803,42 +811,42 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020610&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020573&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>오늘 마감</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>동해시</t>
+          <t>정읍시</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>동해천곡(고령자) 행복주택 입주자 모집</t>
+          <t>정읍시(정읍수성1)영구임대주택 입주자격완화 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -848,42 +856,42 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020611&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020666&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>오늘 마감</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>김포시</t>
+          <t>정읍시</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>김포한강 Ac-05블록 10년 공공임대주택(리츠) 예비입주자 모집 공고</t>
+          <t>정읍시(정읍수성1)영구임대주택 입주자격완화 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>10년임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -893,42 +901,42 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=0000061160&amp;ccrCnntSysDsCd=02&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020639&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>오늘 마감</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>안산시 단원구</t>
+          <t>서귀포시</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>안산 선부동 행복주택 예비입주자(청년) 모집 공고</t>
+          <t>2026년 제주특별자치도개발공사 일반 매입임대주택 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -938,42 +946,42 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://apply.ansanuc.net</t>
+          <t>https://www.jpdc.co.kr/open/news/notice.htm?act=view&amp;seq=24135</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>오늘 마감</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>김해시</t>
+          <t>제주시</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>김해구산1 영구임대주택 예비입주자 모집 공고</t>
+          <t>제주특별자치도개발공사 다자녀 매입임대주택 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -983,77 +991,77 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020500&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://www.jpdc.co.kr/open/news/notice.htm?act=view&amp;seq=24134</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>오늘 마감</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>안동시</t>
+          <t>김제시</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>[안동옥동2] 영구임대주택 예비입주자 모집</t>
+          <t>2026년 한부모주거지원사업 매입주택 입주자 모집</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260901</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020584&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://www.gimje.go.kr/board/list.gimje?boardId=BBS_0000027&amp;listRow=10&amp;listCel=1&amp;menuCd=DOM_000000104001000000&amp;orderBy=REGISTER_DATE%20DESC&amp;paging=ok&amp;categoryCode1=DEPART01,DEPART2005_1,DEPART02,DEPART03,DEPART06,DEPART07,DEPART08,DEPART09,DEPART11,DEPART22,DEPART15,DEPART13,DEPART10,DEPART42,DEPAR</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>D-4</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>달서구</t>
+          <t>남원시</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>대구가람1단지 50년 공공임대 예비입주자 모집</t>
+          <t>남원노암 공공임대 50년 예비입주자 모집</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1063,25 +1071,25 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020573&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020681&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>D-4</t>
         </is>
       </c>
     </row>
@@ -1093,40 +1101,40 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>정읍시</t>
+          <t>익산시</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>정읍시(정읍수성1)영구임대주택 입주자격완화 예비입주자 모집공고</t>
+          <t>익산부송3단지 50년 공공임대 예비입주자 모집</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>50년임대</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020666&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020624&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>D-4</t>
         </is>
       </c>
     </row>
@@ -1138,147 +1146,147 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>정읍시</t>
+          <t>익산시</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>정읍시(정읍수성1)영구임대주택 입주자격완화 예비입주자 모집공고</t>
+          <t>익산시 국민임대주택 예비입주자 모집 공고(26.09.03)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020639&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020636&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>D-4</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>제주시</t>
+          <t>천안시 서북구</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026년 제주특별자치도개발공사 일반 매입임대주택 예비입주자 모집 공고</t>
+          <t>2026년 하반기 충남형 행복주택 매입임대 예비입주자 모집(천안, 보령, 서산)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.jpdc.co.kr/open/news/notice.htm?act=view&amp;seq=24135</t>
+          <t>https://apply.cndc.kr/</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>D-4</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>서귀포시</t>
+          <t>예산군</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>제주특별자치도개발공사 다자녀 매입임대주택 예비입주자 모집 공고</t>
+          <t>2026년 하반기 충남형 행복주택(꿈비채) 예비입주자 모집 공고문(당진, 천안, 예산)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.jpdc.co.kr/open/news/notice.htm?act=view&amp;seq=24134</t>
+          <t>https://apply.cndc.kr/</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>D-4</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>김제시</t>
+          <t>춘천시</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026년 한부모주거지원사업 매입주택 입주자 모집</t>
+          <t>[강원지역본부] 26년 3차 신혼신생아1 매입임대주택 예비자 모집공고</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1288,17 +1296,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>20260901</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260916</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.gimje.go.kr/board/list.gimje?boardId=BBS_0000027&amp;listRow=10&amp;listCel=1&amp;menuCd=DOM_000000104001000000&amp;orderBy=REGISTER_DATE%20DESC&amp;paging=ok&amp;categoryCode1=DEPART01,DEPART2005_1,DEPART02,DEPART03,DEPART06,DEPART07,DEPART08,DEPART09,DEPART11,DEPART22,DEPART15,DEPART13,DEPART10,DEPART42,DEPAR</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020675&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -1313,22 +1321,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>남원시</t>
+          <t>강릉시</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>남원노암 공공임대 50년 예비입주자 모집</t>
+          <t>[강원지역본부] 26년 3차 신혼신생아2(전세형) 매입임대주택 예비자 모집공고</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>50년임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1338,12 +1346,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260916</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020681&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020679&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -1358,37 +1366,37 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>익산시</t>
+          <t>춘천시</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>익산부송3단지 50년 공공임대 예비입주자 모집</t>
+          <t>[강원지역본부] 26년 3차 청년 매입임대주택 예비자 모집공고</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>50년임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260916</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020624&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020673&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -1403,22 +1411,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>익산시</t>
+          <t>양산시</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>익산시 국민임대주택 예비입주자 모집 공고(26.09.03)</t>
+          <t>양산사송 A-8BL 영구임대주택 입주자격완화 예비입주자 모집</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1428,12 +1436,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260916</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020636&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020658&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -1448,127 +1456,127 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>천안시 서북구</t>
+          <t>군산시</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026년 하반기 충남형 행복주택 매입임대 예비입주자 모집(천안, 보령, 서산)</t>
+          <t>군산시 국민임대주택 예비입주자 모집 공고(26.09.03)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260916</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://apply.cndc.kr/</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020663&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-6</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>예산군</t>
+          <t>김제시</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026년 하반기 충남형 행복주택(꿈비채) 예비입주자 모집 공고문(당진, 천안, 예산)</t>
+          <t>김제하동 국민임대주택 모집공고</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://apply.cndc.kr/</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020701&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-6</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>춘천시</t>
+          <t>서산시</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>[강원지역본부] 26년 3차 신혼신생아1 매입임대주택 예비자 모집공고</t>
+          <t>서산석림3단지 50년공공임대주택 예비입주자 모집공고(2026.09.01.)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>50년임대</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>20260916</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020675&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020657&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -1583,287 +1591,275 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>강릉시</t>
+          <t>부천시 원미구</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>[강원지역본부] 26년 3차 신혼신생아2(전세형) 매입임대주택 예비자 모집공고</t>
+          <t>부천시 영구임대주택 예비입주자 모집 (중동한라1, 중동덕유1)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260916</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>20260916</t>
+          <t>20260918</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020679&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020678&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-7</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>춘천시</t>
+          <t>안산시 단원구</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>[강원지역본부] 26년 3차 청년 매입임대주택 예비자 모집공고</t>
+          <t>안산 선부동 행복주택 예비입주자(주거급여)모집 공고</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260903</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>20260916</t>
+          <t>20260918</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020673&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://www.ansanuc.net/homenew/12286/20328/bbsList.do</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-7</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>양산시</t>
+          <t>서귀포시</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>양산사송 A-8BL 영구임대주택 입주자격완화 예비입주자 모집</t>
+          <t>[제주지역본부] 다자녀 매입임대주택 예비입주자 모집 공고(서귀포시)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>20260916</t>
+          <t>20260918</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020658&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020691&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-7</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>전북</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>군산시</t>
-        </is>
-      </c>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
-          <t>군산시 국민임대주택 예비입주자 모집 공고(26.09.03)</t>
+          <t>[경기남부] 용인시 신혼·신생아 매입임대주택Ⅱ(전세형) 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>20260916</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>20260917</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020663&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020702&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>전북</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>김제시</t>
-        </is>
-      </c>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
-          <t>김제하동 국민임대주택 모집공고</t>
+          <t>[경기남부] 용인시 청년 매입임대주택 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>20260917</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020701&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020699&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>충남</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>서산시</t>
-        </is>
-      </c>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
-          <t>서산석림3단지 50년공공임대주택 예비입주자 모집공고(2026.09.01.)</t>
+          <t>[경기남부] 화성시·평택시 신혼·신생아 매입임대주택Ⅱ(전세형) 예비입주자 [후순번] 모집공고</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>50년임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>20260917</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020657&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020703&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>부천시 원미구</t>
+          <t>포항시 북구</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>부천시 영구임대주택 예비입주자 모집 (중동한라1, 중동덕유1)</t>
+          <t>포항창포 영구임대아파트 예비입주자 모집</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1873,115 +1869,115 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>20260916</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020678&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020651&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>안산시 단원구</t>
+          <t>포항시 북구</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>안산 선부동 행복주택 예비입주자(주거급여)모집 공고</t>
+          <t>포항학산 영구임대아파트 예비입주자 모집</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>20260903</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.ansanuc.net/homenew/12286/20328/bbsList.do</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020650&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>서귀포시</t>
+          <t>부천시 오정구</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>[제주지역본부] 다자녀 매입임대주택 예비입주자 모집 공고(서귀포시)</t>
+          <t>2026년 9월 부천시 국민임대주택 예비입주자 모집 공고(2026.09.07)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>20260917</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260922</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020691&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020652&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-11</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1990,7 @@
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
-          <t>[경기남부] 용인시 신혼·신생아 매입임대주택Ⅱ(전세형) 예비입주자 모집공고</t>
+          <t>26-4차 인천본부 든든전세주택 입주자 모집공고(인천, 부천)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2004,17 +2000,17 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>20260917</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260922</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020702&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020725&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H36" t="n">
@@ -2035,7 +2031,7 @@
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
-          <t>[경기남부] 용인시 청년 매입임대주택 예비입주자 모집공고</t>
+          <t>26-4차 인천본부 든든전세주택 입주자 모집공고(인천, 부천)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2045,17 +2041,17 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>20260917</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260922</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020699&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020715&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H37" t="n">
@@ -2070,33 +2066,37 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>경기</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr"/>
+          <t>경북</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>경주시</t>
+        </is>
+      </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>[경기남부] 화성시·평택시 신혼·신생아 매입임대주택Ⅱ(전세형) 예비입주자 [후순번] 모집공고</t>
+          <t>경주시, 영천시, 포항시 부도매입(국민임대)주택 입주자격완화 모집공고</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>20260917</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260922</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020703&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020635&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H38" t="n">
@@ -2111,37 +2111,37 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>포항시 북구</t>
+          <t>계양구</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>포항창포 영구임대아파트 예비입주자 모집</t>
+          <t>26-4차 인천본부 든든전세주택 입주자 모집공고(인천, 부천)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260922</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020651&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020725&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H39" t="n">
@@ -2156,37 +2156,37 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>포항시 북구</t>
+          <t>계양구</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>포항학산 영구임대아파트 예비입주자 모집</t>
+          <t>26-4차 인천본부 든든전세주택 입주자 모집공고(인천, 부천)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260922</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020650&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020715&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H40" t="n">
@@ -2201,17 +2201,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>부천시 오정구</t>
+          <t>남동구</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026년 9월 부천시 국민임대주택 예비입주자 모집 공고(2026.09.07)</t>
+          <t>26년 9월 인천시 남동구 국민임대주택 예비입주자 모집 공고(2026.09.07)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2231,33 +2231,37 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020652&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020619&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-11</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>경기</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr"/>
+          <t>인천</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>옹진군</t>
+        </is>
+      </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>26-4차 인천본부 든든전세주택 입주자 모집공고(인천, 부천)</t>
+          <t>인천옹진백령 국민임대주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2272,32 +2276,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020715&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020578&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-11</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>경주시</t>
+          <t>옹진군</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>경주시, 영천시, 포항시 부도매입(국민임대)주택 입주자격완화 모집공고</t>
+          <t>인천옹진연평 국민임대주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2307,7 +2311,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260922</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2317,37 +2321,37 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020635&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020697&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-11</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>미추홀구</t>
+          <t>횡성군</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>26-4차 인천본부 든든전세주택 입주자 모집공고(인천, 부천)</t>
+          <t>강원횡성 통합공공임대주택 입주자 모집</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>통합공공임대</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2357,12 +2361,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>20260922</t>
+          <t>20260923</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020715&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020627&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=48&amp;mi=1026</t>
         </is>
       </c>
       <c r="H44" t="n">
@@ -2377,17 +2381,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>남동구</t>
+          <t>김포시</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>26년 9월 인천시 남동구 국민임대주택 예비입주자 모집 공고(2026.09.07)</t>
+          <t>김포시 국민임대주택 예비입주자 모집(2026.09.07)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2402,12 +2406,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>20260922</t>
+          <t>20260923</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020619&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020659&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H45" t="n">
@@ -2422,17 +2426,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>옹진군</t>
+          <t>화성시 효행구</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>인천옹진백령 국민임대주택 예비입주자 모집</t>
+          <t>화성서부권 국민임대주택 예비입주자 모집[입주자격완화]</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2447,12 +2451,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>20260922</t>
+          <t>20260923</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020578&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020686&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H46" t="n">
@@ -2467,37 +2471,37 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>옹진군</t>
+          <t>통영시</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>인천옹진연평 국민임대주택 예비입주자 모집</t>
+          <t>[경남지역본부]26년 3차 분양전환형 든든전세주택 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>20260922</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>20260922</t>
+          <t>20260923</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020697&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020721&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H47" t="n">
@@ -2512,22 +2516,18 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>강원</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>횡성군</t>
-        </is>
-      </c>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
-          <t>강원횡성 통합공공임대주택 입주자 모집</t>
+          <t>[경남지역본부]26년 3차 비분양전환형 든든전세주택 입주자 모집 공고</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>통합공공임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2542,37 +2542,37 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020627&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=48&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020720&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>D-13</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>김포시</t>
+          <t>김해시</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>김포시 국민임대주택 예비입주자 모집(2026.09.07)</t>
+          <t>[경남지역본부]26년 3차 신혼·신생아매입임대Ⅰ 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2587,37 +2587,37 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020659&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020722&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>D-13</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>화성시 효행구</t>
+          <t>양산시</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>화성서부권 국민임대주택 예비입주자 모집[입주자격완화]</t>
+          <t>[경남지역본부]26년 3차 신혼·신생아매입임대Ⅱ(전세형) 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2632,42 +2632,42 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020686&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020723&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>D-13</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>익산시</t>
+          <t>양산시</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>익산한스빌 국민임대주택 예비입주자 자격완화 모집 공고</t>
+          <t>[경남지역본부]26년 3차 청년매입임대 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>20260922</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2677,77 +2677,77 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020694&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020717&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>D-13</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>경산시</t>
+          <t>함양군</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>대구혁신10, 경산하양3 행복주택 입주자격완화 선계약 후검증 동호지정 입주자 모집</t>
+          <t>경남 함양군 서하면 다자녀 매입임대주택 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260923</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020682&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020711&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>D-19</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>동구</t>
+          <t>김제시</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>대구혁신10, 경산하양3 행복주택 입주자격완화 선계약 후검증 동호지정 입주자 모집</t>
+          <t>(26.9.10)김제대검산, 정읍시기, 정읍첨단 행복주택 입주자격완화 예비자 모집 공고(소득·총자산요건 배제 및 무주택요건 완화)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2757,42 +2757,42 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260923</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020682&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020344&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>D-19</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>김포시</t>
+          <t>익산시</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>김포지역 국민임대주택 예비입주자 모집 공고(26.09.07.)</t>
+          <t>익산한스빌 국민임대주택 예비입주자 자격완화 모집 공고</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2802,92 +2802,92 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260922</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20260923</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020704&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020694&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>D-20</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>김포시</t>
+          <t>경산시</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>김포지역 국민임대주택 예비입주자 모집 공고(26.09.07.)</t>
+          <t>대구혁신10, 경산하양3 행복주택 입주자격완화 선계약 후검증 동호지정 입주자 모집</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020662&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020682&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>D-20</t>
+          <t>D-18</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>안성시</t>
+          <t>동구</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>안성금화 국민임대 입주자격완화 예비입주자 모집공고(2026.09.07)</t>
+          <t>대구혁신10, 경산하양3 행복주택 입주자격완화 선계약 후검증 동호지정 입주자 모집</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2897,47 +2897,47 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020695&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020682&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>D-20</t>
+          <t>D-18</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>북구</t>
+          <t>김포시</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>부산만덕5 2블록 10년 분양전환공공임대주택(e편한세상 금정산) 예비입주자 모집공고</t>
+          <t>김포지역 국민임대주택 예비입주자 모집 공고(26.09.07.)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>10년임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260918</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2947,15 +2947,15 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=0000061163&amp;ccrCnntSysDsCd=02&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020704&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>D-20</t>
+          <t>D-19</t>
         </is>
       </c>
     </row>
@@ -2967,12 +2967,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>남양주시</t>
+          <t>김포시</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>남양주마석2단지 국민임대주택 예비입주자 모집공고(2026.9.7.)</t>
+          <t>김포지역 국민임대주택 예비입주자 모집 공고(26.09.07.)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2982,25 +2982,25 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
+          <t>20260918</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
           <t>20260930</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>20261001</t>
-        </is>
-      </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020710&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020662&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>D-21</t>
+          <t>D-19</t>
         </is>
       </c>
     </row>
@@ -3012,12 +3012,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>남양주시</t>
+          <t>안성시</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>남양주마석2단지 국민임대주택 예비입주자 모집공고(2026.9.7.)</t>
+          <t>안성금화 국민임대 입주자격완화 예비입주자 모집공고(2026.09.07)</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3027,128 +3027,132 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
+          <t>20260928</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
           <t>20260930</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>20261001</t>
-        </is>
-      </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020668&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020695&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>D-21</t>
+          <t>D-19</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>김해시</t>
+          <t>의정부시</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>[경남지역본부] 일반 매입임대주택 입주자 모집 공고(김해시, 밀양시)</t>
+          <t>의정부송산3단지 공임50년 예비입주자 표준모집공고문</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>50년임대</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020706&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020670&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>D-21</t>
+          <t>D-19</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>경북</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr"/>
+          <t>부산</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>북구</t>
+        </is>
+      </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>[경북 포항,경주,영천] 일반 매입임대 입주자 모집공고</t>
+          <t>부산만덕5 2블록 10년 분양전환공공임대주택(e편한세상 금정산) 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>10년임대</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>20260908</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020654&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=0000061163&amp;ccrCnntSysDsCd=02&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>D-21</t>
+          <t>D-19</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>포항시 남구</t>
+          <t>포천시</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>[경북 포항,경주,영천] 일반 매입임대 입주자 모집공고</t>
+          <t>[경기북부] 2026년 하반기 일반 매입임대주택 입주자 모집공고</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3158,7 +3162,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>20260908</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3168,105 +3172,105 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020601&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020713&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>D-21</t>
+          <t>D-20</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>청주시 서원구</t>
+          <t>남양주시</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>청주산남2-1 영구임대주택 예비입주자 모집 공고(2026.08.28)</t>
+          <t>남양주마석2단지 국민임대주택 예비입주자 모집공고(2026.9.7.)</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020625&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020710&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>D-22</t>
+          <t>D-20</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>당진시</t>
+          <t>남양주시</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>[청년신혼부부매입임대리츠주택] 충남당진 송산청광플러스원 입주자격완화 상시모집</t>
+          <t>남양주마석2단지 국민임대주택 예비입주자 모집공고(2026.9.7.)</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>20260810</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020529&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020668&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H64" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>D-35</t>
+          <t>D-20</t>
         </is>
       </c>
     </row>
@@ -3278,85 +3282,85 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>양산시</t>
+          <t>김해시</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>양산 사송A-4BL 국민임대주택(29A형)선착순 동호지정 모집(입주자격완화, 선계약 후검증)</t>
+          <t>[경남지역본부] 일반 매입임대주택 입주자 모집 공고(김해시, 밀양시)</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>20260813</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>20261029</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020495&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020706&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>D-49</t>
+          <t>D-20</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>군산시</t>
+          <t>영천시</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>군산신역세권A3(내흥3) 영구임대주택 입주자 추가모집</t>
+          <t>[경북 포항,경주,영천] 일반 매입임대 입주자 모집공고</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260908</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>20261030</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019841&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020654&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>D-50</t>
+          <t>D-20</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3372,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>칠곡군</t>
+          <t>경주시</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026년 칠곡군 천원주택(신혼·신생아 매입임대주택Ⅰ) 예비입주자 모집 공고</t>
+          <t>[경북 포항,경주,영천] 일반 매입임대 입주자 모집공고</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3383,132 +3387,132 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>20260728</t>
+          <t>20260908</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>20261130</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=e54448a5-4c8c-4c3d-bfcf-bc465f677408&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020601&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>81</v>
+        <v>20</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>D-81</t>
+          <t>D-20</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>칠곡군</t>
+          <t>청주시 서원구</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026년 칠곡군 천원주택(청년 매입임대주택) 입주자 및 예비입주자 모집 공고</t>
+          <t>청주산남2-1 영구임대주택 예비입주자 모집 공고(2026.08.28)</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>20260728</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>20261130</t>
+          <t>20261002</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=2e8989e9-02ae-48be-9591-f3c4c8e7fa39&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020625&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>81</v>
+        <v>21</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>D-81</t>
+          <t>D-21</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>포항시 남구</t>
+          <t>당진시</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>포항블루밸리 행복주택 선착순 동호지정 상시모집(입주자격 완화, 통합공임 일반계층 추가, 선계약 후검증)</t>
+          <t>[청년신혼부부매입임대리츠주택] 충남당진 송산청광플러스원 입주자격완화 상시모집</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>20260707</t>
+          <t>20260810</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>20261222</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020042&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020529&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>103</v>
+        <v>34</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>D-103</t>
+          <t>D-34</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>삼척시</t>
+          <t>양산시</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>삼척시·정선군 국민임대 예비입주자 상시모집(26.6.10)</t>
+          <t>양산 사송A-4BL 국민임대주택(29A형)선착순 동호지정 모집(입주자격완화, 선계약 후검증)</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3518,189 +3522,205 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>20260624</t>
+          <t>20260813</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>20261230</t>
+          <t>20261029</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020090&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020495&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>111</v>
+        <v>48</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>D-111</t>
+          <t>D-48</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>강원</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr"/>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>군산시</t>
+        </is>
+      </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>군산신역세권A3(내흥3) 영구임대주택 입주자 추가모집</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261030</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019841&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>112</v>
+        <v>49</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>D-112</t>
+          <t>D-49</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>강원</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr"/>
+          <t>경북</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>칠곡군</t>
+        </is>
+      </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 칠곡군 천원주택(신혼·신생아 매입임대주택Ⅰ) 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260728</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261130</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=e54448a5-4c8c-4c3d-bfcf-bc465f677408&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>112</v>
+        <v>80</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>D-112</t>
+          <t>D-80</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>강원</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr"/>
+          <t>경북</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>칠곡군</t>
+        </is>
+      </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 칠곡군 천원주택(청년 매입임대주택) 입주자 및 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260728</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261130</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=2e8989e9-02ae-48be-9591-f3c4c8e7fa39&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>112</v>
+        <v>80</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>D-112</t>
+          <t>D-80</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>강원</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr"/>
+          <t>경북</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>포항시 남구</t>
+        </is>
+      </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>포항블루밸리 행복주택 선착순 동호지정 상시모집(입주자격 완화, 통합공임 일반계층 추가, 선계약 후검증)</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260707</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261222</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020042&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>D-112</t>
+          <t>D-102</t>
         </is>
       </c>
     </row>
@@ -3712,12 +3732,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>동해시</t>
+          <t>삼척시</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>동해유성,태백철암장미 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
+          <t>삼척시·정선군 국민임대 예비입주자 상시모집(26.6.10)</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -3727,25 +3747,25 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>20260212</t>
+          <t>20260624</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261230</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019312&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020090&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H75" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>D-112</t>
+          <t>D-110</t>
         </is>
       </c>
     </row>
@@ -3755,24 +3775,20 @@
           <t>강원</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>동해시</t>
-        </is>
-      </c>
+      <c r="B76" t="inlineStr"/>
       <c r="C76" t="inlineStr">
         <is>
-          <t>동해유성,태백철암장미 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>20260212</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3782,15 +3798,15 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019308&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H76" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>D-112</t>
+          <t>D-111</t>
         </is>
       </c>
     </row>
@@ -3800,24 +3816,20 @@
           <t>강원</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>태백시</t>
-        </is>
-      </c>
+      <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr">
         <is>
-          <t>태백궁전 국민임대 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>20260212</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3827,28 +3839,28 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019307&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>D-112</t>
+          <t>D-111</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -3868,28 +3880,28 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H78" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>D-112</t>
+          <t>D-111</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -3899,7 +3911,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3909,38 +3921,42 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H79" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>D-112</t>
+          <t>D-111</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>경기</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr"/>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>동해시</t>
+        </is>
+      </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>동해유성,태백철암장미 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260212</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3950,38 +3966,42 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019312&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H80" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>D-112</t>
+          <t>D-111</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>경기</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr"/>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>동해시</t>
+        </is>
+      </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>동해유성,태백철암장미 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260212</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3991,38 +4011,42 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019308&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H81" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>D-112</t>
+          <t>D-111</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr"/>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>태백시</t>
+        </is>
+      </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>태백궁전 국민임대 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260212</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -4032,28 +4056,28 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019307&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H82" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>D-112</t>
+          <t>D-111</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4073,28 +4097,28 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H83" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>D-112</t>
+          <t>D-111</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4114,28 +4138,28 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H84" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>D-112</t>
+          <t>D-111</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4145,7 +4169,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -4155,28 +4179,28 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H85" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>D-112</t>
+          <t>D-111</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4186,7 +4210,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -4196,28 +4220,28 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H86" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>D-112</t>
+          <t>D-111</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -4237,28 +4261,28 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H87" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>D-112</t>
+          <t>D-111</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -4278,28 +4302,28 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H88" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>D-112</t>
+          <t>D-111</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -4309,7 +4333,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -4319,28 +4343,28 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H89" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>D-112</t>
+          <t>D-111</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -4350,7 +4374,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -4360,28 +4384,28 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H90" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>D-112</t>
+          <t>D-111</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -4401,28 +4425,28 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H91" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>D-112</t>
+          <t>D-111</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -4442,28 +4466,28 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H92" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>D-112</t>
+          <t>D-111</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -4473,7 +4497,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -4483,28 +4507,28 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H93" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>D-112</t>
+          <t>D-111</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>대전</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -4514,7 +4538,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -4524,28 +4548,28 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H94" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>D-112</t>
+          <t>D-111</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>대전</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -4565,28 +4589,28 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H95" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>D-112</t>
+          <t>D-111</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>대전</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -4606,28 +4630,28 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H96" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>D-112</t>
+          <t>D-111</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>대전</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -4637,7 +4661,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -4647,28 +4671,28 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H97" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>D-112</t>
+          <t>D-111</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -4678,7 +4702,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -4688,28 +4712,28 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H98" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>D-112</t>
+          <t>D-111</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>대전</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -4729,28 +4753,28 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H99" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>D-112</t>
+          <t>D-111</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>대전</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -4770,28 +4794,28 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H100" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>D-112</t>
+          <t>D-111</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>대전</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -4801,7 +4825,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -4811,28 +4835,28 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H101" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>D-112</t>
+          <t>D-111</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>대전</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -4842,7 +4866,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -4852,28 +4876,28 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H102" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>D-112</t>
+          <t>D-111</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -4893,28 +4917,28 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H103" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>D-112</t>
+          <t>D-111</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -4934,28 +4958,28 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H104" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>D-112</t>
+          <t>D-111</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -4965,7 +4989,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4975,28 +4999,28 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H105" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>D-112</t>
+          <t>D-111</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>세종</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -5006,7 +5030,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -5016,28 +5040,28 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H106" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>D-112</t>
+          <t>D-111</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>세종</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -5057,28 +5081,28 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H107" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>D-112</t>
+          <t>D-111</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>세종</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -5098,28 +5122,28 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H108" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>D-112</t>
+          <t>D-111</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>세종</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -5129,7 +5153,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -5139,28 +5163,28 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H109" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>D-112</t>
+          <t>D-111</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>울산</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B110" t="inlineStr"/>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -5170,7 +5194,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -5180,28 +5204,28 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H110" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>D-112</t>
+          <t>D-111</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>울산</t>
+          <t>세종</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -5221,28 +5245,28 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H111" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>D-112</t>
+          <t>D-111</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>울산</t>
+          <t>세종</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -5262,28 +5286,28 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H112" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>D-112</t>
+          <t>D-111</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>울산</t>
+          <t>세종</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -5293,7 +5317,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -5303,28 +5327,28 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H113" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>D-112</t>
+          <t>D-111</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>세종</t>
         </is>
       </c>
       <c r="B114" t="inlineStr"/>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -5334,7 +5358,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -5344,28 +5368,28 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H114" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>D-112</t>
+          <t>D-111</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>울산</t>
         </is>
       </c>
       <c r="B115" t="inlineStr"/>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -5385,28 +5409,28 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H115" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>D-112</t>
+          <t>D-111</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>울산</t>
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -5426,28 +5450,28 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H116" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>D-112</t>
+          <t>D-111</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>울산</t>
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -5457,7 +5481,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -5467,28 +5491,28 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H117" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>D-112</t>
+          <t>D-111</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>울산</t>
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -5498,7 +5522,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -5508,28 +5532,28 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H118" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>D-112</t>
+          <t>D-111</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B119" t="inlineStr"/>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -5549,28 +5573,28 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H119" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>D-112</t>
+          <t>D-111</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -5590,28 +5614,28 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H120" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>D-112</t>
+          <t>D-111</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -5621,7 +5645,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -5631,42 +5655,38 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H121" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>D-112</t>
+          <t>D-111</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>전북</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>김제시</t>
-        </is>
-      </c>
+          <t>인천</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr"/>
       <c r="C122" t="inlineStr">
         <is>
-          <t>김제검산1단지 영구임대주택 예비입주자 모집 공고(상시모집)</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>20260101</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -5676,15 +5696,15 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019412&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H122" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>D-112</t>
+          <t>D-111</t>
         </is>
       </c>
     </row>
@@ -5694,24 +5714,20 @@
           <t>전북</t>
         </is>
       </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>남원시</t>
-        </is>
-      </c>
+      <c r="B123" t="inlineStr"/>
       <c r="C123" t="inlineStr">
         <is>
-          <t>남원노암 공공임대 50년 예비입주자 모집</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>50년임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -5721,15 +5737,15 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020623&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H123" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>D-112</t>
+          <t>D-111</t>
         </is>
       </c>
     </row>
@@ -5739,24 +5755,20 @@
           <t>전북</t>
         </is>
       </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>남원시</t>
-        </is>
-      </c>
+      <c r="B124" t="inlineStr"/>
       <c r="C124" t="inlineStr">
         <is>
-          <t>남원노암단지 영구임대주택 입주자격완화 예비입주자 모집공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -5766,15 +5778,15 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020649&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H124" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>D-112</t>
+          <t>D-111</t>
         </is>
       </c>
     </row>
@@ -5784,24 +5796,20 @@
           <t>전북</t>
         </is>
       </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>전주시 완산구</t>
-        </is>
-      </c>
+      <c r="B125" t="inlineStr"/>
       <c r="C125" t="inlineStr">
         <is>
-          <t>전주시(전주평화1,전주평화4) 영구임대주택 예비입주자 모집 공고(공고일:2026.02.10.)</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>20260303</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -5811,28 +5819,28 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019241&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H125" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>D-112</t>
+          <t>D-111</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -5842,7 +5850,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -5852,38 +5860,42 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H126" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>D-112</t>
+          <t>D-111</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>제주</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr"/>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>김제시</t>
+        </is>
+      </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>김제검산1단지 영구임대주택 예비입주자 모집 공고(상시모집)</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260101</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -5893,38 +5905,42 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019412&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H127" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>D-112</t>
+          <t>D-111</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>제주</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr"/>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>남원시</t>
+        </is>
+      </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>남원노암 공공임대 50년 예비입주자 모집</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>50년임대</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -5934,38 +5950,42 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020623&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H128" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>D-112</t>
+          <t>D-111</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>제주</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr"/>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>남원시</t>
+        </is>
+      </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>남원노암단지 영구임대주택 입주자격완화 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -5975,38 +5995,42 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020649&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H129" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>D-112</t>
+          <t>D-111</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>충남</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr"/>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>전주시 완산구</t>
+        </is>
+      </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>전주시(전주평화1,전주평화4) 영구임대주택 예비입주자 모집 공고(공고일:2026.02.10.)</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260303</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -6016,28 +6040,28 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019241&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H130" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>D-112</t>
+          <t>D-111</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="B131" t="inlineStr"/>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -6057,28 +6081,28 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H131" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>D-112</t>
+          <t>D-111</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="B132" t="inlineStr"/>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -6098,28 +6122,28 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H132" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>D-112</t>
+          <t>D-111</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="B133" t="inlineStr"/>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -6129,7 +6153,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -6139,42 +6163,38 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H133" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>D-112</t>
+          <t>D-111</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>충남</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>당진시</t>
-        </is>
-      </c>
+          <t>제주</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr"/>
       <c r="C134" t="inlineStr">
         <is>
-          <t>[청년신혼부부매입임대리츠주택] 충남당진 송산청광플러스원 입주자격완화 상시모집</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>20260316</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -6184,22 +6204,22 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019433&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H134" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>D-112</t>
+          <t>D-111</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
@@ -6229,18 +6249,18 @@
         </is>
       </c>
       <c r="H135" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>D-112</t>
+          <t>D-111</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B136" t="inlineStr"/>
@@ -6270,18 +6290,18 @@
         </is>
       </c>
       <c r="H136" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>D-112</t>
+          <t>D-111</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B137" t="inlineStr"/>
@@ -6311,18 +6331,18 @@
         </is>
       </c>
       <c r="H137" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>D-112</t>
+          <t>D-111</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
@@ -6352,191 +6372,400 @@
         </is>
       </c>
       <c r="H138" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>D-112</t>
+          <t>D-111</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>삼척시</t>
+          <t>당진시</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>삼척도계·정선신동 국민임대주택 예비입주자 입주자격완화 공고</t>
+          <t>[청년신혼부부매입임대리츠주택] 충남당진 송산청광플러스원 입주자격완화 상시모집</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260316</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>20270129</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020581&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019433&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H139" t="n">
-        <v>141</v>
+        <v>111</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>D-141</t>
+          <t>D-111</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>전북</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>군산시</t>
-        </is>
-      </c>
+          <t>충북</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr"/>
       <c r="C140" t="inlineStr">
         <is>
-          <t>군산시 국민임대주택 입주자 선착순 상시 모집(경암부향 등 7개 단지)</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>20260812</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>20270731</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020453&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H140" t="n">
-        <v>324</v>
+        <v>111</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>D-324</t>
+          <t>D-111</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>울산</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>울주군</t>
-        </is>
-      </c>
+          <t>충북</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr"/>
       <c r="C141" t="inlineStr">
         <is>
-          <t>울산광역시 국민임대주택 예비입주자 정례모집 공고(2025.09.15.)</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>20250929</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>20291001</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300018799&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H141" t="n">
-        <v>1117</v>
+        <v>111</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>D-1117</t>
+          <t>D-111</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
+          <t>충북</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr"/>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H142" t="n">
+        <v>111</v>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>D-111</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>충북</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr"/>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>20260224</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H143" t="n">
+        <v>111</v>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>D-111</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>삼척시</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>삼척도계·정선신동 국민임대주택 예비입주자 입주자격완화 공고</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>국민임대</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>20270129</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020581&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H144" t="n">
+        <v>140</v>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>D-140</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>군산시</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>군산시 국민임대주택 입주자 선착순 상시 모집(경암부향 등 7개 단지)</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>국민임대</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>20260812</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>20270731</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020453&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H145" t="n">
+        <v>323</v>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>D-323</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
           <t>울산</t>
         </is>
       </c>
-      <c r="B142" t="inlineStr">
+      <c r="B146" t="inlineStr">
         <is>
           <t>울주군</t>
         </is>
       </c>
-      <c r="C142" t="inlineStr">
+      <c r="C146" t="inlineStr">
         <is>
           <t>울산광역시 국민임대주택 예비입주자 정례모집 공고(2025.09.15.)</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr">
+      <c r="D146" t="inlineStr">
         <is>
           <t>국민임대</t>
         </is>
       </c>
-      <c r="E142" t="inlineStr">
+      <c r="E146" t="inlineStr">
         <is>
           <t>20250929</t>
         </is>
       </c>
-      <c r="F142" t="inlineStr">
+      <c r="F146" t="inlineStr">
         <is>
           <t>20291001</t>
         </is>
       </c>
-      <c r="G142" t="inlineStr">
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300018799&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H146" t="n">
+        <v>1116</v>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>D-1116</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>울산</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>울주군</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>울산광역시 국민임대주택 예비입주자 정례모집 공고(2025.09.15.)</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>국민임대</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>20250929</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>20291001</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
         <is>
           <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300018780&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
-      <c r="H142" t="n">
-        <v>1117</v>
-      </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>D-1117</t>
+      <c r="H147" t="n">
+        <v>1116</v>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>D-1116</t>
         </is>
       </c>
     </row>

--- a/housing_notices.xlsx
+++ b/housing_notices.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I147"/>
+  <dimension ref="A1:I136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,197 +466,197 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>동해시</t>
+          <t>김제시</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>동해천곡 고령자복지주택(영구임대) 입주자 모집</t>
+          <t>2026년 한부모주거지원사업 매입주택 입주자 모집</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260901</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020609&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://www.gimje.go.kr/board/list.gimje?boardId=BBS_0000027&amp;listRow=10&amp;listCel=1&amp;menuCd=DOM_000000104001000000&amp;orderBy=REGISTER_DATE%20DESC&amp;paging=ok&amp;categoryCode1=DEPART01,DEPART2005_1,DEPART02,DEPART03,DEPART06,DEPART07,DEPART08,DEPART09,DEPART11,DEPART22,DEPART15,DEPART13,DEPART10,DEPART42,DEPAR</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>오늘 마감</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>동해시</t>
+          <t>남원시</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>동해천곡 고령자복지주택(행복주택) 입주자 모집</t>
+          <t>남원노암 공공임대 50년 예비입주자 모집</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>50년임대</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020610&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020681&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>오늘 마감</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>동해시</t>
+          <t>익산시</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>동해천곡(고령자) 행복주택 입주자 모집</t>
+          <t>익산부송3단지 50년 공공임대 예비입주자 모집</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>50년임대</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020611&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020624&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>오늘 마감</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>김포시</t>
+          <t>익산시</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>김포한강 Ac-05블록 10년 공공임대주택(리츠) 예비입주자 모집 공고</t>
+          <t>익산시 국민임대주택 예비입주자 모집 공고(26.09.03)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>10년임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=0000061160&amp;ccrCnntSysDsCd=02&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020636&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>오늘 마감</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>안산시 단원구</t>
+          <t>천안시 서북구</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>안산 선부동 행복주택 예비입주자(청년) 모집 공고</t>
+          <t>2026년 하반기 충남형 행복주택 매입임대 예비입주자 모집(천안, 보령, 서산)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -666,222 +666,222 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://apply.ansanuc.net</t>
+          <t>https://apply.cndc.kr/</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>오늘 마감</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>김해시</t>
+          <t>예산군</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>김해구산1 영구임대주택 예비입주자 모집 공고</t>
+          <t>2026년 하반기 충남형 행복주택(꿈비채) 예비입주자 모집 공고문(당진, 천안, 예산)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020500&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.cndc.kr/</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>오늘 마감</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>안동시</t>
+          <t>춘천시</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>[안동옥동2] 영구임대주택 예비입주자 모집</t>
+          <t>[강원지역본부] 26년 3차 신혼신생아1 매입임대주택 예비자 모집공고</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260916</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020584&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020675&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>오늘 마감</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>달서구</t>
+          <t>강릉시</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>대구가람1단지 50년 공공임대 예비입주자 모집</t>
+          <t>[강원지역본부] 26년 3차 신혼신생아2(전세형) 매입임대주택 예비자 모집공고</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>50년임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260916</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020573&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020679&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>오늘 마감</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>정읍시</t>
+          <t>강릉시</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>정읍시(정읍수성1)영구임대주택 입주자격완화 예비입주자 모집공고</t>
+          <t>[강원지역본부] 26년 3차 청년 매입임대주택 예비자 모집공고</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260916</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020666&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020673&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>오늘 마감</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>정읍시</t>
+          <t>양산시</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>정읍시(정읍수성1)영구임대주택 입주자격완화 예비입주자 모집공고</t>
+          <t>양산사송 A-8BL 영구임대주택 입주자격완화 예비입주자 모집</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -891,197 +891,197 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260916</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020639&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020658&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>오늘 마감</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>서귀포시</t>
+          <t>군산시</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026년 제주특별자치도개발공사 일반 매입임대주택 예비입주자 모집 공고</t>
+          <t>군산시 국민임대주택 예비입주자 모집 공고(26.09.03)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260916</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.jpdc.co.kr/open/news/notice.htm?act=view&amp;seq=24135</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020663&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>오늘 마감</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>제주시</t>
+          <t>김제시</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>제주특별자치도개발공사 다자녀 매입임대주택 예비입주자 모집 공고</t>
+          <t>김제하동 국민임대주택 모집공고</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.jpdc.co.kr/open/news/notice.htm?act=view&amp;seq=24134</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020701&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>오늘 마감</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>김제시</t>
+          <t>서산시</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026년 한부모주거지원사업 매입주택 입주자 모집</t>
+          <t>서산석림3단지 50년공공임대주택 예비입주자 모집공고(2026.09.01.)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>50년임대</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>20260901</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.gimje.go.kr/board/list.gimje?boardId=BBS_0000027&amp;listRow=10&amp;listCel=1&amp;menuCd=DOM_000000104001000000&amp;orderBy=REGISTER_DATE%20DESC&amp;paging=ok&amp;categoryCode1=DEPART01,DEPART2005_1,DEPART02,DEPART03,DEPART06,DEPART07,DEPART08,DEPART09,DEPART11,DEPART22,DEPART15,DEPART13,DEPART10,DEPART42,DEPAR</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020657&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>D-4</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>남원시</t>
+          <t>부천시 원미구</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>남원노암 공공임대 50년 예비입주자 모집</t>
+          <t>부천시 영구임대주택 예비입주자 모집 (중동한라1, 중동덕유1)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>50년임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260916</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260918</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020681&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020678&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -1096,37 +1096,37 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>익산시</t>
+          <t>안산시 단원구</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>익산부송3단지 50년 공공임대 예비입주자 모집</t>
+          <t>안산 선부동 행복주택 예비입주자(주거급여)모집 공고</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>50년임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260903</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260918</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020624&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://www.ansanuc.net/homenew/12286/20328/bbsList.do</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -1141,37 +1141,37 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>익산시</t>
+          <t>서귀포시</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>익산시 국민임대주택 예비입주자 모집 공고(26.09.03)</t>
+          <t>[제주지역본부] 다자녀 매입임대주택 예비입주자 모집 공고(서귀포시)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260918</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020636&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020691&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -1186,107 +1186,99 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>충남</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>천안시 서북구</t>
-        </is>
-      </c>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026년 하반기 충남형 행복주택 매입임대 예비입주자 모집(천안, 보령, 서산)</t>
+          <t>[경기남부] 용인시 신혼·신생아 매입임대주택Ⅱ(전세형) 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://apply.cndc.kr/</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020702&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>D-4</t>
+          <t>D-7</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>충남</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>예산군</t>
-        </is>
-      </c>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026년 하반기 충남형 행복주택(꿈비채) 예비입주자 모집 공고문(당진, 천안, 예산)</t>
+          <t>[경기남부] 용인시 청년 매입임대주택 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://apply.cndc.kr/</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020699&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>D-4</t>
+          <t>D-7</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>춘천시</t>
+          <t>평택시</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>[강원지역본부] 26년 3차 신혼신생아1 매입임대주택 예비자 모집공고</t>
+          <t>[경기남부] 화성시·평택시 신혼·신생아 매입임대주택Ⅱ(전세형) 예비입주자 [후순번] 모집공고</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1296,47 +1288,47 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>20260916</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020675&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020703&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-7</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>강릉시</t>
+          <t>포항시 북구</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>[강원지역본부] 26년 3차 신혼신생아2(전세형) 매입임대주택 예비자 모집공고</t>
+          <t>포항창포 영구임대아파트 예비입주자 모집</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1346,42 +1338,42 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>20260916</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020679&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020651&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-7</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>춘천시</t>
+          <t>포항시 북구</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>[강원지역본부] 26년 3차 청년 매입임대주택 예비자 모집공고</t>
+          <t>포항학산 영구임대아파트 예비입주자 모집</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1391,177 +1383,169 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>20260916</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020673&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020650&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-7</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>양산시</t>
+          <t>부천시 오정구</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>양산사송 A-8BL 영구임대주택 입주자격완화 예비입주자 모집</t>
+          <t>2026년 9월 부천시 국민임대주택 예비입주자 모집 공고(2026.09.07)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>20260916</t>
+          <t>20260922</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020658&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020652&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-8</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>전북</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>군산시</t>
-        </is>
-      </c>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
-          <t>군산시 국민임대주택 예비입주자 모집 공고(26.09.03)</t>
+          <t>26-4차 인천본부 든든전세주택 입주자 모집공고(인천, 부천)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>20260916</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>20260917</t>
+          <t>20260922</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020663&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020725&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-8</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>전북</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>김제시</t>
-        </is>
-      </c>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
-          <t>김제하동 국민임대주택 모집공고</t>
+          <t>26-4차 인천본부 든든전세주택 입주자 모집공고(인천, 부천)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>20260917</t>
+          <t>20260922</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020701&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020715&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-8</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>서산시</t>
+          <t>경주시</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>서산석림3단지 50년공공임대주택 예비입주자 모집공고(2026.09.01.)</t>
+          <t>경주시, 영천시, 포항시 부도매입(국민임대)주택 입주자격완화 모집공고</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>50년임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1571,368 +1555,380 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>20260917</t>
+          <t>20260922</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020657&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020635&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-8</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>부천시 원미구</t>
+          <t>계양구</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>부천시 영구임대주택 예비입주자 모집 (중동한라1, 중동덕유1)</t>
+          <t>26-4차 인천본부 든든전세주택 입주자 모집공고(인천, 부천)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>20260916</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260922</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020678&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020725&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-8</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>안산시 단원구</t>
+          <t>계양구</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>안산 선부동 행복주택 예비입주자(주거급여)모집 공고</t>
+          <t>26-4차 인천본부 든든전세주택 입주자 모집공고(인천, 부천)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>20260903</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260922</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.ansanuc.net/homenew/12286/20328/bbsList.do</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020715&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-8</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>서귀포시</t>
+          <t>남동구</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>[제주지역본부] 다자녀 매입임대주택 예비입주자 모집 공고(서귀포시)</t>
+          <t>26년 9월 인천시 남동구 국민임대주택 예비입주자 모집 공고(2026.09.07)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>20260917</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260922</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020691&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020619&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-8</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>경기</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr"/>
+          <t>인천</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>옹진군</t>
+        </is>
+      </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>[경기남부] 용인시 신혼·신생아 매입임대주택Ⅱ(전세형) 예비입주자 모집공고</t>
+          <t>인천옹진백령 국민임대주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>20260917</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260922</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020702&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020578&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>D-8</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>경기</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr"/>
+          <t>인천</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>옹진군</t>
+        </is>
+      </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>[경기남부] 용인시 청년 매입임대주택 예비입주자 모집공고</t>
+          <t>인천옹진연평 국민임대주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>20260917</t>
+          <t>20260922</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260922</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020699&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020697&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>D-8</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>경기</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr"/>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>횡성군</t>
+        </is>
+      </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>[경기남부] 화성시·평택시 신혼·신생아 매입임대주택Ⅱ(전세형) 예비입주자 [후순번] 모집공고</t>
+          <t>강원횡성 통합공공임대주택 입주자 모집</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>통합공공임대</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>20260917</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260923</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020703&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020627&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=48&amp;mi=1026</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>D-9</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>포항시 북구</t>
+          <t>오산시</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>포항창포 영구임대아파트 예비입주자 모집</t>
+          <t>[온라인 접수 불가, 관할 주거복지지사 현장접수] 경기남부지역본부 2026년 일반 매입임대주택 입주자 모집공고</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260923</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020651&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020731&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>D-9</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>포항시 북구</t>
+          <t>김포시</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>포항학산 영구임대아파트 예비입주자 모집</t>
+          <t>김포시 국민임대주택 예비입주자 모집(2026.09.07)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260923</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020650&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020659&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>D-9</t>
         </is>
       </c>
     </row>
@@ -1944,12 +1940,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>부천시 오정구</t>
+          <t>화성시 효행구</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026년 9월 부천시 국민임대주택 예비입주자 모집 공고(2026.09.07)</t>
+          <t>화성서부권 국민임대주택 예비입주자 모집[입주자격완화]</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1964,33 +1960,37 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>20260922</t>
+          <t>20260923</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020652&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020686&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>D-11</t>
+          <t>D-9</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>경기</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr"/>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>통영시</t>
+        </is>
+      </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>26-4차 인천본부 든든전세주택 입주자 모집공고(인천, 부천)</t>
+          <t>[경남지역본부]26년 3차 분양전환형 든든전세주택 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2005,33 +2005,33 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>20260922</t>
+          <t>20260923</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020725&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020721&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>D-11</t>
+          <t>D-9</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
-          <t>26-4차 인천본부 든든전세주택 입주자 모집공고(인천, 부천)</t>
+          <t>[경남지역본부]26년 3차 비분양전환형 든든전세주택 입주자 모집 공고</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2046,82 +2046,78 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>20260922</t>
+          <t>20260923</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020715&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020720&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>D-11</t>
+          <t>D-9</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>경북</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>경주시</t>
-        </is>
-      </c>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>경주시, 영천시, 포항시 부도매입(국민임대)주택 입주자격완화 모집공고</t>
+          <t>[경남지역본부]26년 3차 신혼·신생아매입임대Ⅰ 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>20260922</t>
+          <t>20260923</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020635&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020722&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>D-11</t>
+          <t>D-9</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>계양구</t>
+          <t>양산시</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>26-4차 인천본부 든든전세주택 입주자 모집공고(인천, 부천)</t>
+          <t>[경남지역본부]26년 3차 신혼·신생아매입임대Ⅱ(전세형) 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2136,37 +2132,37 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>20260922</t>
+          <t>20260923</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020725&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020723&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>D-11</t>
+          <t>D-9</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>계양구</t>
+          <t>양산시</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>26-4차 인천본부 든든전세주택 입주자 모집공고(인천, 부천)</t>
+          <t>[경남지역본부]26년 3차 청년매입임대 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2181,87 +2177,87 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>20260922</t>
+          <t>20260923</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020715&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020717&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>D-11</t>
+          <t>D-9</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>남동구</t>
+          <t>함양군</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>26년 9월 인천시 남동구 국민임대주택 예비입주자 모집 공고(2026.09.07)</t>
+          <t>경남 함양군 서하면 다자녀 매입임대주택 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>20260922</t>
+          <t>20260923</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020619&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020711&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>D-11</t>
+          <t>D-9</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>옹진군</t>
+          <t>김제시</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>인천옹진백령 국민임대주택 예비입주자 모집</t>
+          <t>(26.9.10)김제대검산, 정읍시기, 정읍첨단 행복주택 입주자격완화 예비자 모집 공고(소득·총자산요건 배제 및 무주택요건 완화)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2271,37 +2267,37 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>20260922</t>
+          <t>20260923</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020578&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020344&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>D-11</t>
+          <t>D-9</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>옹진군</t>
+          <t>익산시</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>인천옹진연평 국민임대주택 예비입주자 모집</t>
+          <t>익산한스빌 국민임대주택 예비입주자 자격완화 모집 공고</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2316,110 +2312,110 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>20260922</t>
+          <t>20260923</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020697&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020694&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>D-11</t>
+          <t>D-9</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>횡성군</t>
+          <t>경산시</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>강원횡성 통합공공임대주택 입주자 모집</t>
+          <t>대구혁신10, 경산하양3 행복주택 입주자격완화 선계약 후검증 동호지정 입주자 모집</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>통합공공임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>20260923</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020627&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=48&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020682&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-15</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>김포시</t>
+          <t>동구</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>김포시 국민임대주택 예비입주자 모집(2026.09.07)</t>
+          <t>대구혁신10, 경산하양3 행복주택 입주자격완화 선계약 후검증 동호지정 입주자 모집</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>20260923</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020659&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020682&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-15</t>
         </is>
       </c>
     </row>
@@ -2431,12 +2427,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>화성시 효행구</t>
+          <t>김포시</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>화성서부권 국민임대주택 예비입주자 모집[입주자격완화]</t>
+          <t>김포지역 국민임대주택 예비입주자 모집 공고(26.09.07.)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2446,218 +2442,222 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260918</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>20260923</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020686&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020704&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-16</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>통영시</t>
+          <t>김포시</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>[경남지역본부]26년 3차 분양전환형 든든전세주택 예비입주자 모집 공고</t>
+          <t>김포지역 국민임대주택 예비입주자 모집 공고(26.09.07.)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260918</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>20260923</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020721&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020662&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-16</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr"/>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>안성시</t>
+        </is>
+      </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>[경남지역본부]26년 3차 비분양전환형 든든전세주택 입주자 모집 공고</t>
+          <t>안성금화 국민임대 입주자격완화 예비입주자 모집공고(2026.09.07)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>20260923</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020720&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020695&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-16</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>김해시</t>
+          <t>의정부시</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>[경남지역본부]26년 3차 신혼·신생아매입임대Ⅰ 예비입주자 모집공고</t>
+          <t>의정부송산3단지 공임50년 예비입주자 표준모집공고문</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>50년임대</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>20260923</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020722&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020670&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-16</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>양산시</t>
+          <t>북구</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>[경남지역본부]26년 3차 신혼·신생아매입임대Ⅱ(전세형) 예비입주자 모집공고</t>
+          <t>부산만덕5 2블록 10년 분양전환공공임대주택(e편한세상 금정산) 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>10년임대</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>20260923</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020723&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=0000061163&amp;ccrCnntSysDsCd=02&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-16</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>양산시</t>
+          <t>양주시</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>[경남지역본부]26년 3차 청년매입임대 예비입주자 모집공고</t>
+          <t>[경기북부] 2026년 하반기 일반 매입임대주택 입주자 모집공고</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2667,160 +2667,160 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>20260923</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020717&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020713&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-17</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>함양군</t>
+          <t>남양주시</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>경남 함양군 서하면 다자녀 매입임대주택 예비입주자 모집공고</t>
+          <t>남양주마석2단지 국민임대주택 예비입주자 모집공고(2026.9.7.)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>20260923</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020711&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020710&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-17</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>김제시</t>
+          <t>남양주시</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>(26.9.10)김제대검산, 정읍시기, 정읍첨단 행복주택 입주자격완화 예비자 모집 공고(소득·총자산요건 배제 및 무주택요건 완화)</t>
+          <t>남양주마석2단지 국민임대주택 예비입주자 모집공고(2026.9.7.)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>20260923</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020344&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020668&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-17</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>익산시</t>
+          <t>밀양시</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>익산한스빌 국민임대주택 예비입주자 자격완화 모집 공고</t>
+          <t>[경남지역본부] 일반 매입임대주택 입주자 모집 공고(김해시, 밀양시)</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>20260922</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>20260923</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020694&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020706&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-17</t>
         </is>
       </c>
     </row>
@@ -2830,194 +2830,190 @@
           <t>경북</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>경산시</t>
-        </is>
-      </c>
+      <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr">
         <is>
-          <t>대구혁신10, 경산하양3 행복주택 입주자격완화 선계약 후검증 동호지정 입주자 모집</t>
+          <t>[경북 포항,경주,영천] 일반 매입임대 입주자 모집공고</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260908</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020682&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020654&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>D-18</t>
+          <t>D-17</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>동구</t>
+          <t>포항시 북구</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>대구혁신10, 경산하양3 행복주택 입주자격완화 선계약 후검증 동호지정 입주자 모집</t>
+          <t>[경북 포항,경주,영천] 일반 매입임대 입주자 모집공고</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260908</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020682&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020601&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>D-18</t>
+          <t>D-17</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>김포시</t>
+          <t>청주시 서원구</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>김포지역 국민임대주택 예비입주자 모집 공고(26.09.07.)</t>
+          <t>청주산남2-1 영구임대주택 예비입주자 모집 공고(2026.08.28)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261002</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020704&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020625&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>D-19</t>
+          <t>D-18</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>김포시</t>
+          <t>당진시</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>김포지역 국민임대주택 예비입주자 모집 공고(26.09.07.)</t>
+          <t>[청년신혼부부매입임대리츠주택] 충남당진 송산청광플러스원 입주자격완화 상시모집</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260810</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020662&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020529&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>D-19</t>
+          <t>D-31</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>안성시</t>
+          <t>양산시</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>안성금화 국민임대 입주자격완화 예비입주자 모집공고(2026.09.07)</t>
+          <t>양산 사송A-4BL 국민임대주택(29A형)선착순 동호지정 모집(입주자격완화, 선계약 후검증)</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3027,132 +3023,132 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260813</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261029</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020695&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020495&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>D-19</t>
+          <t>D-45</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>의정부시</t>
+          <t>군산시</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>의정부송산3단지 공임50년 예비입주자 표준모집공고문</t>
+          <t>군산신역세권A3(내흥3) 영구임대주택 입주자 추가모집</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>50년임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261030</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020670&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019841&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>D-19</t>
+          <t>D-46</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>북구</t>
+          <t>칠곡군</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>부산만덕5 2블록 10년 분양전환공공임대주택(e편한세상 금정산) 예비입주자 모집공고</t>
+          <t>2026년 칠곡군 천원주택(신혼·신생아 매입임대주택Ⅰ) 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>10년임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260728</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261130</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=0000061163&amp;ccrCnntSysDsCd=02&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=e54448a5-4c8c-4c3d-bfcf-bc465f677408&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>19</v>
+        <v>77</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>D-19</t>
+          <t>D-77</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>포천시</t>
+          <t>칠곡군</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>[경기북부] 2026년 하반기 일반 매입임대주택 입주자 모집공고</t>
+          <t>2026년 칠곡군 천원주택(청년 매입임대주택) 입주자 및 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3162,87 +3158,87 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260728</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20261130</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020713&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=2e8989e9-02ae-48be-9591-f3c4c8e7fa39&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>D-20</t>
+          <t>D-77</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>남양주시</t>
+          <t>포항시 남구</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>남양주마석2단지 국민임대주택 예비입주자 모집공고(2026.9.7.)</t>
+          <t>포항블루밸리 행복주택 선착순 동호지정 상시모집(입주자격 완화, 통합공임 일반계층 추가, 선계약 후검증)</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20260707</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20261222</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020710&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020042&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>20</v>
+        <v>99</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>D-20</t>
+          <t>D-99</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>남양주시</t>
+          <t>삼척시</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>남양주마석2단지 국민임대주택 예비입주자 모집공고(2026.9.7.)</t>
+          <t>삼척시·정선군 국민임대 예비입주자 상시모집(26.6.10)</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3252,267 +3248,251 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20260624</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20261230</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020668&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020090&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H64" t="n">
-        <v>20</v>
+        <v>107</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>D-20</t>
+          <t>D-107</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>김해시</t>
-        </is>
-      </c>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr">
         <is>
-          <t>[경남지역본부] 일반 매입임대주택 입주자 모집 공고(김해시, 밀양시)</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020706&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>20</v>
+        <v>108</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>D-20</t>
+          <t>D-108</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>경북</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>영천시</t>
-        </is>
-      </c>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr">
         <is>
-          <t>[경북 포항,경주,영천] 일반 매입임대 입주자 모집공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>20260908</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020654&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>20</v>
+        <v>108</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>D-20</t>
+          <t>D-108</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>경북</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>경주시</t>
-        </is>
-      </c>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr">
         <is>
-          <t>[경북 포항,경주,영천] 일반 매입임대 입주자 모집공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>20260908</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020601&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>20</v>
+        <v>108</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>D-20</t>
+          <t>D-108</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>충북</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>청주시 서원구</t>
-        </is>
-      </c>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr">
         <is>
-          <t>청주산남2-1 영구임대주택 예비입주자 모집 공고(2026.08.28)</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020625&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>21</v>
+        <v>108</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>D-21</t>
+          <t>D-108</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>당진시</t>
+          <t>동해시</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>[청년신혼부부매입임대리츠주택] 충남당진 송산청광플러스원 입주자격완화 상시모집</t>
+          <t>동해유성,태백철암장미 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>20260810</t>
+          <t>20260212</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020529&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019312&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>34</v>
+        <v>108</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>D-34</t>
+          <t>D-108</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>양산시</t>
+          <t>동해시</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>양산 사송A-4BL 국민임대주택(29A형)선착순 동호지정 모집(입주자격완화, 선계약 후검증)</t>
+          <t>동해유성,태백철암장미 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3522,257 +3502,241 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>20260813</t>
+          <t>20260212</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>20261029</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020495&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019308&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>48</v>
+        <v>108</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>D-48</t>
+          <t>D-108</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>군산시</t>
+          <t>태백시</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>군산신역세권A3(내흥3) 영구임대주택 입주자 추가모집</t>
+          <t>태백궁전 국민임대 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260212</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>20261030</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019841&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019307&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>49</v>
+        <v>108</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>D-49</t>
+          <t>D-108</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>경북</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>칠곡군</t>
-        </is>
-      </c>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2026년 칠곡군 천원주택(신혼·신생아 매입임대주택Ⅰ) 예비입주자 모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>20260728</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>20261130</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=e54448a5-4c8c-4c3d-bfcf-bc465f677408&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>80</v>
+        <v>108</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>D-80</t>
+          <t>D-108</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>경북</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>칠곡군</t>
-        </is>
-      </c>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2026년 칠곡군 천원주택(청년 매입임대주택) 입주자 및 예비입주자 모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>20260728</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>20261130</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=2e8989e9-02ae-48be-9591-f3c4c8e7fa39&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>80</v>
+        <v>108</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>D-80</t>
+          <t>D-108</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>경북</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>포항시 남구</t>
-        </is>
-      </c>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr"/>
       <c r="C74" t="inlineStr">
         <is>
-          <t>포항블루밸리 행복주택 선착순 동호지정 상시모집(입주자격 완화, 통합공임 일반계층 추가, 선계약 후검증)</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>20260707</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>20261222</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020042&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>D-102</t>
+          <t>D-108</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>강원</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>삼척시</t>
-        </is>
-      </c>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr"/>
       <c r="C75" t="inlineStr">
         <is>
-          <t>삼척시·정선군 국민임대 예비입주자 상시모집(26.6.10)</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>20260624</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>20261230</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020090&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H75" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>D-110</t>
+          <t>D-108</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
@@ -3802,18 +3766,18 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>D-111</t>
+          <t>D-108</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -3843,18 +3807,18 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>D-111</t>
+          <t>D-108</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
@@ -3884,18 +3848,18 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>D-111</t>
+          <t>D-108</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
@@ -3925,38 +3889,34 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>D-111</t>
+          <t>D-108</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>강원</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>동해시</t>
-        </is>
-      </c>
+          <t>경북</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr"/>
       <c r="C80" t="inlineStr">
         <is>
-          <t>동해유성,태백철암장미 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>20260212</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3966,42 +3926,38 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019312&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H80" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>D-111</t>
+          <t>D-108</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>강원</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>동해시</t>
-        </is>
-      </c>
+          <t>경북</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr"/>
       <c r="C81" t="inlineStr">
         <is>
-          <t>동해유성,태백철암장미 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>20260212</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -4011,42 +3967,38 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019308&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H81" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>D-111</t>
+          <t>D-108</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>강원</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>태백시</t>
-        </is>
-      </c>
+          <t>경북</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr"/>
       <c r="C82" t="inlineStr">
         <is>
-          <t>태백궁전 국민임대 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>20260212</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -4056,28 +4008,28 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019307&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H82" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>D-111</t>
+          <t>D-108</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4087,7 +4039,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -4097,28 +4049,28 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H83" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>D-111</t>
+          <t>D-108</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4138,28 +4090,28 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H84" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>D-111</t>
+          <t>D-108</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4179,28 +4131,28 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H85" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>D-111</t>
+          <t>D-108</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4210,7 +4162,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -4220,28 +4172,28 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H86" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>D-111</t>
+          <t>D-108</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -4251,7 +4203,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -4261,28 +4213,28 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H87" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>D-111</t>
+          <t>D-108</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>대전</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -4302,28 +4254,28 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H88" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>D-111</t>
+          <t>D-108</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>대전</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -4343,28 +4295,28 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H89" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>D-111</t>
+          <t>D-108</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>대전</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -4374,7 +4326,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -4384,28 +4336,28 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H90" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>D-111</t>
+          <t>D-108</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>대전</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -4415,7 +4367,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -4425,28 +4377,28 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H91" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>D-111</t>
+          <t>D-108</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -4466,28 +4418,28 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H92" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>D-111</t>
+          <t>D-108</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -4507,28 +4459,28 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H93" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>D-111</t>
+          <t>D-108</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -4538,7 +4490,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -4548,28 +4500,28 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H94" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>D-111</t>
+          <t>D-108</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -4579,7 +4531,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -4589,28 +4541,28 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H95" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>D-111</t>
+          <t>D-108</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -4630,28 +4582,28 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H96" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>D-111</t>
+          <t>D-108</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -4671,28 +4623,28 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H97" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>D-111</t>
+          <t>D-108</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -4702,7 +4654,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -4712,28 +4664,28 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H98" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>D-111</t>
+          <t>D-108</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>대전</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -4743,7 +4695,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -4753,28 +4705,28 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H99" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>D-111</t>
+          <t>D-108</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>대전</t>
+          <t>세종</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -4794,28 +4746,28 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H100" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>D-111</t>
+          <t>D-108</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>대전</t>
+          <t>세종</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -4835,28 +4787,28 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H101" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>D-111</t>
+          <t>D-108</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>대전</t>
+          <t>세종</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -4866,7 +4818,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -4876,28 +4828,28 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H102" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>D-111</t>
+          <t>D-108</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>세종</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -4907,7 +4859,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4917,28 +4869,28 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H103" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>D-111</t>
+          <t>D-108</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>울산</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -4958,28 +4910,28 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H104" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>D-111</t>
+          <t>D-108</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>울산</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -4999,28 +4951,28 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H105" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>D-111</t>
+          <t>D-108</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>울산</t>
         </is>
       </c>
       <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -5030,7 +4982,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -5040,28 +4992,28 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H106" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>D-111</t>
+          <t>D-108</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>울산</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -5071,7 +5023,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -5081,28 +5033,28 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H107" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>D-111</t>
+          <t>D-108</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -5122,28 +5074,28 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H108" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>D-111</t>
+          <t>D-108</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -5163,28 +5115,28 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H109" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>D-111</t>
+          <t>D-108</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B110" t="inlineStr"/>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -5194,7 +5146,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -5204,28 +5156,28 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H110" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>D-111</t>
+          <t>D-108</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>세종</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -5235,7 +5187,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -5245,28 +5197,28 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H111" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>D-111</t>
+          <t>D-108</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>세종</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -5286,28 +5238,28 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H112" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>D-111</t>
+          <t>D-108</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>세종</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -5327,28 +5279,28 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H113" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>D-111</t>
+          <t>D-108</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>세종</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B114" t="inlineStr"/>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -5358,7 +5310,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -5368,28 +5320,28 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H114" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>D-111</t>
+          <t>D-108</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>울산</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B115" t="inlineStr"/>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -5399,7 +5351,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -5409,38 +5361,42 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H115" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>D-111</t>
+          <t>D-108</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>울산</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr"/>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>김제시</t>
+        </is>
+      </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>김제검산1단지 영구임대주택 예비입주자 모집 공고(상시모집)</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260101</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -5450,38 +5406,42 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019412&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H116" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>D-111</t>
+          <t>D-108</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>울산</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr"/>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>남원시</t>
+        </is>
+      </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>남원노암 공공임대 50년 예비입주자 모집</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>50년임대</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -5491,38 +5451,42 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020623&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H117" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>D-111</t>
+          <t>D-108</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>울산</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr"/>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>남원시</t>
+        </is>
+      </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>남원노암단지 영구임대주택 입주자격완화 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -5532,38 +5496,42 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020649&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H118" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>D-111</t>
+          <t>D-108</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>인천</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr"/>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>전주시 완산구</t>
+        </is>
+      </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>전주시(전주평화1,전주평화4) 영구임대주택 예비입주자 모집 공고(공고일:2026.02.10.)</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260303</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -5573,28 +5541,28 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019241&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H119" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>D-111</t>
+          <t>D-108</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -5614,28 +5582,28 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H120" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>D-111</t>
+          <t>D-108</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -5655,28 +5623,28 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H121" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>D-111</t>
+          <t>D-108</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="B122" t="inlineStr"/>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -5686,7 +5654,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -5696,28 +5664,28 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H122" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>D-111</t>
+          <t>D-108</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="B123" t="inlineStr"/>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -5727,7 +5695,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -5737,28 +5705,28 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H123" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>D-111</t>
+          <t>D-108</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -5778,28 +5746,28 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H124" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>D-111</t>
+          <t>D-108</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B125" t="inlineStr"/>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -5819,28 +5787,28 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H125" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>D-111</t>
+          <t>D-108</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -5850,7 +5818,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -5860,42 +5828,38 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H126" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>D-111</t>
+          <t>D-108</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>전북</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>김제시</t>
-        </is>
-      </c>
+          <t>충남</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr"/>
       <c r="C127" t="inlineStr">
         <is>
-          <t>김제검산1단지 영구임대주택 예비입주자 모집 공고(상시모집)</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>20260101</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -5905,42 +5869,42 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019412&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H127" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>D-111</t>
+          <t>D-108</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>남원시</t>
+          <t>당진시</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>남원노암 공공임대 50년 예비입주자 모집</t>
+          <t>[청년신혼부부매입임대리츠주택] 충남당진 송산청광플러스원 입주자격완화 상시모집</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>50년임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260316</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -5950,42 +5914,38 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020623&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019433&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H128" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>D-111</t>
+          <t>D-108</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>전북</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>남원시</t>
-        </is>
-      </c>
+          <t>충북</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr"/>
       <c r="C129" t="inlineStr">
         <is>
-          <t>남원노암단지 영구임대주택 입주자격완화 예비입주자 모집공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -5995,42 +5955,38 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020649&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H129" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>D-111</t>
+          <t>D-108</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>전북</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>전주시 완산구</t>
-        </is>
-      </c>
+          <t>충북</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr"/>
       <c r="C130" t="inlineStr">
         <is>
-          <t>전주시(전주평화1,전주평화4) 영구임대주택 예비입주자 모집 공고(공고일:2026.02.10.)</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>20260303</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -6040,28 +5996,28 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019241&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H130" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>D-111</t>
+          <t>D-108</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B131" t="inlineStr"/>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -6081,28 +6037,28 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H131" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>D-111</t>
+          <t>D-108</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B132" t="inlineStr"/>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -6112,7 +6068,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -6122,650 +6078,195 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H132" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>D-111</t>
+          <t>D-108</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>제주</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr"/>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>삼척시</t>
+        </is>
+      </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>삼척도계·정선신동 국민임대주택 예비입주자 입주자격완화 공고</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20270129</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020581&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H133" t="n">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>D-111</t>
+          <t>D-137</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>제주</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr"/>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>군산시</t>
+        </is>
+      </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>군산시 국민임대주택 입주자 선착순 상시 모집(경암부향 등 7개 단지)</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260812</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20270731</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020453&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H134" t="n">
-        <v>111</v>
+        <v>320</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>D-111</t>
+          <t>D-320</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>충남</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr"/>
+          <t>울산</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>울주군</t>
+        </is>
+      </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>울산광역시 국민임대주택 예비입주자 정례모집 공고(2025.09.15.)</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20250929</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20291001</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300018799&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H135" t="n">
-        <v>111</v>
+        <v>1113</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>D-111</t>
+          <t>D-1113</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>충남</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr"/>
+          <t>울산</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>울주군</t>
+        </is>
+      </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>울산광역시 국민임대주택 예비입주자 정례모집 공고(2025.09.15.)</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20250929</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20291001</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300018780&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H136" t="n">
-        <v>111</v>
+        <v>1113</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>D-111</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>충남</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr"/>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>전세임대</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>20260324</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>20261231</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
-        </is>
-      </c>
-      <c r="H137" t="n">
-        <v>111</v>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>D-111</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>충남</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr"/>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>전세임대</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>20260224</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>20261231</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
-        </is>
-      </c>
-      <c r="H138" t="n">
-        <v>111</v>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>D-111</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>충남</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>당진시</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>[청년신혼부부매입임대리츠주택] 충남당진 송산청광플러스원 입주자격완화 상시모집</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>매입임대</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>20260316</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>20261231</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019433&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
-        </is>
-      </c>
-      <c r="H139" t="n">
-        <v>111</v>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>D-111</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>충북</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr"/>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>전세임대</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>20260324</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>20261231</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
-        </is>
-      </c>
-      <c r="H140" t="n">
-        <v>111</v>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>D-111</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>충북</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr"/>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>전세임대</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>20260324</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>20261231</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
-        </is>
-      </c>
-      <c r="H141" t="n">
-        <v>111</v>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>D-111</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>충북</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr"/>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>전세임대</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>20260324</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>20261231</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
-        </is>
-      </c>
-      <c r="H142" t="n">
-        <v>111</v>
-      </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>D-111</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>충북</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr"/>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>전세임대</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>20260224</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>20261231</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
-        </is>
-      </c>
-      <c r="H143" t="n">
-        <v>111</v>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>D-111</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>강원</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>삼척시</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>삼척도계·정선신동 국민임대주택 예비입주자 입주자격완화 공고</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>국민임대</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>20260915</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>20270129</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020581&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
-        </is>
-      </c>
-      <c r="H144" t="n">
-        <v>140</v>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>D-140</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>전북</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>군산시</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>군산시 국민임대주택 입주자 선착순 상시 모집(경암부향 등 7개 단지)</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>국민임대</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>20260812</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>20270731</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020453&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
-        </is>
-      </c>
-      <c r="H145" t="n">
-        <v>323</v>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>D-323</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>울산</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>울주군</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>울산광역시 국민임대주택 예비입주자 정례모집 공고(2025.09.15.)</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>국민임대</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>20250929</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>20291001</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300018799&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
-        </is>
-      </c>
-      <c r="H146" t="n">
-        <v>1116</v>
-      </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>D-1116</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>울산</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>울주군</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>울산광역시 국민임대주택 예비입주자 정례모집 공고(2025.09.15.)</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>국민임대</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>20250929</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>20291001</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300018780&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
-        </is>
-      </c>
-      <c r="H147" t="n">
-        <v>1116</v>
-      </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>D-1116</t>
+          <t>D-1113</t>
         </is>
       </c>
     </row>

--- a/housing_notices.xlsx
+++ b/housing_notices.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I136"/>
+  <dimension ref="A1:I162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,17 +466,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>김제시</t>
+          <t>춘천시</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026년 한부모주거지원사업 매입주택 입주자 모집</t>
+          <t>[강원지역본부] 26년 3차 신혼신생아1 매입임대주택 예비자 모집공고</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -486,47 +486,47 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>20260901</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260916</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.gimje.go.kr/board/list.gimje?boardId=BBS_0000027&amp;listRow=10&amp;listCel=1&amp;menuCd=DOM_000000104001000000&amp;orderBy=REGISTER_DATE%20DESC&amp;paging=ok&amp;categoryCode1=DEPART01,DEPART2005_1,DEPART02,DEPART03,DEPART06,DEPART07,DEPART08,DEPART09,DEPART11,DEPART22,DEPART15,DEPART13,DEPART10,DEPART42,DEPAR</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020675&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>오늘 마감</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>남원시</t>
+          <t>강릉시</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>남원노암 공공임대 50년 예비입주자 모집</t>
+          <t>[강원지역본부] 26년 3차 신혼신생아2(전세형) 매입임대주택 예비자 모집공고</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>50년임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -536,87 +536,87 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260916</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020681&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020679&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>오늘 마감</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>익산시</t>
+          <t>강릉시</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>익산부송3단지 50년 공공임대 예비입주자 모집</t>
+          <t>[강원지역본부] 26년 3차 청년 매입임대주택 예비자 모집공고</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>50년임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260916</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020624&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020673&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>오늘 마감</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>익산시</t>
+          <t>양산시</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>익산시 국민임대주택 예비입주자 모집 공고(26.09.03)</t>
+          <t>양산사송 A-8BL 영구임대주택 입주자격완화 예비입주자 모집</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -626,57 +626,57 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260916</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020636&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020658&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>오늘 마감</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>천안시 서북구</t>
+          <t>군산시</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026년 하반기 충남형 행복주택 매입임대 예비입주자 모집(천안, 보령, 서산)</t>
+          <t>군산시 국민임대주택 예비입주자 모집 공고(26.09.03)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260916</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://apply.cndc.kr/</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020663&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -691,37 +691,37 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>예산군</t>
+          <t>김제시</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026년 하반기 충남형 행복주택(꿈비채) 예비입주자 모집 공고문(당진, 천안, 예산)</t>
+          <t>김제하동 국민임대주택 모집공고</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://apply.cndc.kr/</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020701&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -736,82 +736,82 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>춘천시</t>
+          <t>서산시</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>[강원지역본부] 26년 3차 신혼신생아1 매입임대주택 예비자 모집공고</t>
+          <t>서산석림3단지 50년공공임대주택 예비입주자 모집공고(2026.09.01.)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>50년임대</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>20260916</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020675&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020657&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>강릉시</t>
+          <t>부천시 원미구</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>[강원지역본부] 26년 3차 신혼신생아2(전세형) 매입임대주택 예비자 모집공고</t>
+          <t>부천시 영구임대주택 예비입주자 모집 (중동한라1, 중동덕유1)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260916</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>20260916</t>
+          <t>20260918</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020679&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020678&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -826,37 +826,37 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>강릉시</t>
+          <t>안산시 단원구</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>[강원지역본부] 26년 3차 청년 매입임대주택 예비자 모집공고</t>
+          <t>안산 선부동 행복주택 예비입주자(주거급여)모집 공고</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260903</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>20260916</t>
+          <t>20260918</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020673&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://www.ansanuc.net/homenew/12286/20328/bbsList.do</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -871,37 +871,37 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>양산시</t>
+          <t>서귀포시</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>양산사송 A-8BL 영구임대주택 입주자격완화 예비입주자 모집</t>
+          <t>[제주지역본부] 다자녀 매입임대주택 예비입주자 모집 공고(서귀포시)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>20260916</t>
+          <t>20260918</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020658&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020691&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -916,152 +916,140 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>전북</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>군산시</t>
-        </is>
-      </c>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>군산시 국민임대주택 예비입주자 모집 공고(26.09.03)</t>
+          <t>[경기남부] 용인시 신혼·신생아 매입임대주택Ⅱ(전세형) 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>20260916</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>20260917</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020663&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020702&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>전북</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>김제시</t>
-        </is>
-      </c>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>김제하동 국민임대주택 모집공고</t>
+          <t>[경기남부] 용인시 청년 매입임대주택 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>20260917</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020701&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020699&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>충남</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>서산시</t>
-        </is>
-      </c>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>서산석림3단지 50년공공임대주택 예비입주자 모집공고(2026.09.01.)</t>
+          <t>[경기남부] 화성시·평택시 신혼·신생아 매입임대주택Ⅱ(전세형) 예비입주자 [후순번] 모집공고</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>50년임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>20260917</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020657&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020703&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>부천시 원미구</t>
+          <t>포항시 북구</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>부천시 영구임대주택 예비입주자 모집 (중동한라1, 중동덕유1)</t>
+          <t>포항창포 영구임대아파트 예비입주자 모집</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1071,115 +1059,115 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>20260916</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020678&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020651&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>D-4</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>안산시 단원구</t>
+          <t>포항시 북구</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>안산 선부동 행복주택 예비입주자(주거급여)모집 공고</t>
+          <t>포항학산 영구임대아파트 예비입주자 모집</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>20260903</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.ansanuc.net/homenew/12286/20328/bbsList.do</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020650&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>D-4</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>서귀포시</t>
+          <t>부천시 오정구</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>[제주지역본부] 다자녀 매입임대주택 예비입주자 모집 공고(서귀포시)</t>
+          <t>2026년 9월 부천시 국민임대주택 예비입주자 모집 공고(2026.09.07)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>20260917</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260922</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020691&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020652&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>D-4</t>
+          <t>D-6</t>
         </is>
       </c>
     </row>
@@ -1192,7 +1180,7 @@
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>[경기남부] 용인시 신혼·신생아 매입임대주택Ⅱ(전세형) 예비입주자 모집공고</t>
+          <t>26-4차 인천본부 든든전세주택 입주자 모집공고(인천, 부천)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1202,25 +1190,25 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>20260917</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260922</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020702&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020725&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-6</t>
         </is>
       </c>
     </row>
@@ -1233,7 +1221,7 @@
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>[경기남부] 용인시 청년 매입임대주택 예비입주자 모집공고</t>
+          <t>26-4차 인천본부 든든전세주택 입주자 모집공고(인천, 부천)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1243,177 +1231,177 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>20260917</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260922</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020699&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020715&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-6</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>평택시</t>
+          <t>경주시</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>[경기남부] 화성시·평택시 신혼·신생아 매입임대주택Ⅱ(전세형) 예비입주자 [후순번] 모집공고</t>
+          <t>경주시, 영천시, 포항시 부도매입(국민임대)주택 입주자격완화 모집공고</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>20260917</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260922</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020703&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020635&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-6</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>포항시 북구</t>
+          <t>계양구</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>포항창포 영구임대아파트 예비입주자 모집</t>
+          <t>26-4차 인천본부 든든전세주택 입주자 모집공고(인천, 부천)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260922</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020651&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020725&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-6</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>포항시 북구</t>
+          <t>계양구</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>포항학산 영구임대아파트 예비입주자 모집</t>
+          <t>26-4차 인천본부 든든전세주택 입주자 모집공고(인천, 부천)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260922</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020650&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020715&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-6</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>부천시 오정구</t>
+          <t>남동구</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026년 9월 부천시 국민임대주택 예비입주자 모집 공고(2026.09.07)</t>
+          <t>26년 9월 인천시 남동구 국민임대주택 예비입주자 모집 공고(2026.09.07)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1433,33 +1421,37 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020652&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020619&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-6</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>경기</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
+          <t>인천</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>옹진군</t>
+        </is>
+      </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>26-4차 인천본부 든든전세주택 입주자 모집공고(인천, 부천)</t>
+          <t>인천옹진백령 국민임대주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1474,38 +1466,42 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020725&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020578&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-6</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>경기</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
+          <t>인천</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>옹진군</t>
+        </is>
+      </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>26-4차 인천본부 든든전세주택 입주자 모집공고(인천, 부천)</t>
+          <t>인천옹진연평 국민임대주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260922</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1515,77 +1511,77 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020715&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020697&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-6</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>경주시</t>
+          <t>횡성군</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>경주시, 영천시, 포항시 부도매입(국민임대)주택 입주자격완화 모집공고</t>
+          <t>강원횡성 통합공공임대주택 입주자 모집</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>통합공공임대</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>20260922</t>
+          <t>20260923</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020635&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020627&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=48&amp;mi=1026</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-7</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>계양구</t>
+          <t>시흥시</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>26-4차 인천본부 든든전세주택 입주자 모집공고(인천, 부천)</t>
+          <t>[온라인 접수 불가, 관할 주거복지지사 현장접수] 경기남부지역본부 2026년 일반 매입임대주택 입주자 모집공고</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1600,42 +1596,42 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>20260922</t>
+          <t>20260923</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020725&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020731&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-7</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>계양구</t>
+          <t>김포시</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>26-4차 인천본부 든든전세주택 입주자 모집공고(인천, 부천)</t>
+          <t>김포시 국민임대주택 예비입주자 모집(2026.09.07)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1645,37 +1641,37 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>20260922</t>
+          <t>20260923</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020715&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020659&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-7</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>남동구</t>
+          <t>화성시 효행구</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>26년 9월 인천시 남동구 국민임대주택 예비입주자 모집 공고(2026.09.07)</t>
+          <t>화성서부권 국민임대주택 예비입주자 모집[입주자격완화]</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1690,42 +1686,42 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>20260922</t>
+          <t>20260923</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020619&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020686&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-7</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>옹진군</t>
+          <t>통영시</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>인천옹진백령 국민임대주택 예비입주자 모집</t>
+          <t>[경남지역본부]26년 3차 분양전환형 든든전세주택 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1735,87 +1731,87 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>20260922</t>
+          <t>20260923</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020578&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020721&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-7</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>옹진군</t>
+          <t>김해시</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>인천옹진연평 국민임대주택 예비입주자 모집</t>
+          <t>[경남지역본부]26년 3차 비분양전환형 든든전세주택 입주자 모집 공고</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>20260922</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>20260922</t>
+          <t>20260923</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020697&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020720&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-7</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>횡성군</t>
+          <t>진주시</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>강원횡성 통합공공임대주택 입주자 모집</t>
+          <t>[경남지역본부]26년 3차 신혼·신생아매입임대Ⅰ 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>통합공공임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1830,32 +1826,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020627&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=48&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020722&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>D-9</t>
+          <t>D-7</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>오산시</t>
+          <t>양산시</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>[온라인 접수 불가, 관할 주거복지지사 현장접수] 경기남부지역본부 2026년 일반 매입임대주택 입주자 모집공고</t>
+          <t>[경남지역본부]26년 3차 신혼·신생아매입임대Ⅱ(전세형) 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1875,37 +1871,37 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020731&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020723&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>D-9</t>
+          <t>D-7</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>김포시</t>
+          <t>양산시</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>김포시 국민임대주택 예비입주자 모집(2026.09.07)</t>
+          <t>[경남지역본부]26년 3차 청년매입임대 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1920,42 +1916,42 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020659&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020717&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>D-9</t>
+          <t>D-7</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>화성시 효행구</t>
+          <t>함양군</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>화성서부권 국민임대주택 예비입주자 모집[입주자격완화]</t>
+          <t>경남 함양군 서하면 다자녀 매입임대주택 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1965,37 +1961,37 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020686&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020711&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>D-9</t>
+          <t>D-7</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>통영시</t>
+          <t>달서구</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>[경남지역본부]26년 3차 분양전환형 든든전세주택 예비입주자 모집 공고</t>
+          <t>대구죽전 행복주택(산업단지형) 예비 입주자 모집</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2010,33 +2006,37 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020721&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020760&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>D-9</t>
+          <t>D-7</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr"/>
+          <t>대구</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>달서구</t>
+        </is>
+      </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>[경남지역본부]26년 3차 비분양전환형 든든전세주택 입주자 모집 공고</t>
+          <t>대구죽전 행복주택(산업단지형) 예비 입주자 모집</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2051,33 +2051,37 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020720&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020751&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>D-9</t>
+          <t>D-7</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr"/>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>김제시</t>
+        </is>
+      </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>[경남지역본부]26년 3차 신혼·신생아매입임대Ⅰ 예비입주자 모집공고</t>
+          <t>(26.9.10)김제대검산, 정읍시기, 정읍첨단 행복주택 입주자격완화 예비자 모집 공고(소득·총자산요건 배제 및 무주택요건 완화)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2092,42 +2096,42 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020722&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020344&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>D-9</t>
+          <t>D-7</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>양산시</t>
+          <t>익산시</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>[경남지역본부]26년 3차 신혼·신생아매입임대Ⅱ(전세형) 예비입주자 모집공고</t>
+          <t>익산한스빌 국민임대주택 예비입주자 자격완화 모집 공고</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260922</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2137,60 +2141,60 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020723&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020694&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>D-9</t>
+          <t>D-7</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>양산시</t>
+          <t>칠곡군</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>[경남지역본부]26년 3차 청년매입임대 예비입주자 모집공고</t>
+          <t>칠곡왜관4 국민임대아파트 예비입주자 모집(51형)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>20260923</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020717&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020696&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>D-9</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
@@ -2202,130 +2206,130 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>함양군</t>
+          <t>양산시</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>경남 함양군 서하면 다자녀 매입임대주택 예비입주자 모집공고</t>
+          <t>[양산시지역]양산대석휴먼시아 국민임대주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>20260923</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020711&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020754&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>D-9</t>
+          <t>D-13</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>김제시</t>
+          <t>창녕군</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>(26.9.10)김제대검산, 정읍시기, 정읍첨단 행복주택 입주자격완화 예비자 모집 공고(소득·총자산요건 배제 및 무주택요건 완화)</t>
+          <t>창녕창녕 국민임대주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>20260923</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020344&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020724&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>D-9</t>
+          <t>D-13</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>익산시</t>
+          <t>경산시</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>익산한스빌 국민임대주택 예비입주자 자격완화 모집 공고</t>
+          <t>경산백천1단지 50년 공공임대주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>50년임대</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>20260922</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>20260923</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020694&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020728&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>D-9</t>
+          <t>D-13</t>
         </is>
       </c>
     </row>
@@ -2366,11 +2370,11 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>D-15</t>
+          <t>D-13</t>
         </is>
       </c>
     </row>
@@ -2411,28 +2415,28 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>D-15</t>
+          <t>D-13</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>김포시</t>
+          <t>기장군</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>김포지역 국민임대주택 예비입주자 모집 공고(26.09.07.)</t>
+          <t>부산광역시 국민임대주택 예비입주자 정례모집 공고(2026.09.15.)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2442,42 +2446,42 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020704&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020758&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>D-16</t>
+          <t>D-13</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>김포시</t>
+          <t>기장군</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>김포지역 국민임대주택 예비입주자 모집 공고(26.09.07.)</t>
+          <t>부산광역시 기장군 정관7국민임대 소득완화 모집공고</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2487,42 +2491,42 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020662&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020655&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>D-16</t>
+          <t>D-13</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>안성시</t>
+          <t>군산시</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>안성금화 국민임대 입주자격완화 예비입주자 모집공고(2026.09.07)</t>
+          <t>군산구암 국민임대주택 예비입주자 모집 공고(‘26.9.15.)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2532,92 +2536,92 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020695&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020743&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>D-16</t>
+          <t>D-13</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>의정부시</t>
+          <t>음성군</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>의정부송산3단지 공임50년 예비입주자 표준모집공고문</t>
+          <t>음성군 국민임대주택 예비입주자 모집(2026.09.15.)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>50년임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020670&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020698&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>D-16</t>
+          <t>D-13</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>북구</t>
+          <t>원주시</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>부산만덕5 2블록 10년 분양전환공공임대주택(e편한세상 금정산) 예비입주자 모집공고</t>
+          <t>원주시지역 국민임대주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>10년임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2632,37 +2636,37 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=0000061163&amp;ccrCnntSysDsCd=02&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020767&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>D-16</t>
+          <t>D-14</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>양주시</t>
+          <t>원주시</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>[경기북부] 2026년 하반기 일반 매입임대주택 입주자 모집공고</t>
+          <t>원주시지역 국민임대주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2672,20 +2676,20 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020713&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020677&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>D-17</t>
+          <t>D-14</t>
         </is>
       </c>
     </row>
@@ -2697,12 +2701,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>남양주시</t>
+          <t>김포시</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>남양주마석2단지 국민임대주택 예비입주자 모집공고(2026.9.7.)</t>
+          <t>김포지역 국민임대주택 예비입주자 모집 공고(26.09.07.)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2712,25 +2716,25 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
+          <t>20260918</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
           <t>20260930</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>20261001</t>
-        </is>
-      </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020710&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020704&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>D-17</t>
+          <t>D-14</t>
         </is>
       </c>
     </row>
@@ -2742,12 +2746,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>남양주시</t>
+          <t>김포시</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>남양주마석2단지 국민임대주택 예비입주자 모집공고(2026.9.7.)</t>
+          <t>김포지역 국민임대주택 예비입주자 모집 공고(26.09.07.)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2757,201 +2761,205 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
+          <t>20260918</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
           <t>20260930</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>20261001</t>
-        </is>
-      </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020668&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020662&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>D-17</t>
+          <t>D-14</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>밀양시</t>
+          <t>안성시</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>[경남지역본부] 일반 매입임대주택 입주자 모집 공고(김해시, 밀양시)</t>
+          <t>안성금화 국민임대 입주자격완화 예비입주자 모집공고(2026.09.07)</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020706&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020695&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>D-17</t>
+          <t>D-14</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>경북</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr"/>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>의정부시</t>
+        </is>
+      </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>[경북 포항,경주,영천] 일반 매입임대 입주자 모집공고</t>
+          <t>의정부송산3단지 공임50년 예비입주자 표준모집공고문</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>50년임대</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>20260908</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020654&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020670&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>D-17</t>
+          <t>D-14</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>포항시 북구</t>
+          <t>화성시 동탄구</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>[경북 포항,경주,영천] 일반 매입임대 입주자 모집공고</t>
+          <t>화성동탄2 10년 분양전환공공임대주택(리츠) 예비입주자모집공고(‘26.09)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>10년임대</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>20260908</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020601&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=0000061173&amp;ccrCnntSysDsCd=02&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>D-17</t>
+          <t>D-14</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>청주시 서원구</t>
+          <t>북구</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>청주산남2-1 영구임대주택 예비입주자 모집 공고(2026.08.28)</t>
+          <t>부산만덕5 2블록 10년 분양전환공공임대주택(e편한세상 금정산) 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>10년임대</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020625&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=0000061163&amp;ccrCnntSysDsCd=02&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>D-18</t>
+          <t>D-14</t>
         </is>
       </c>
     </row>
@@ -2963,57 +2971,57 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>당진시</t>
+          <t>아산시</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>[청년신혼부부매입임대리츠주택] 충남당진 송산청광플러스원 입주자격완화 상시모집</t>
+          <t>아산신창소화,아산인주 국민임대주택 예비입주자 모집공고(2026.09.15)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>20260810</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020529&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020726&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>D-31</t>
+          <t>D-14</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>양산시</t>
+          <t>천안시 동남구</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>양산 사송A-4BL 국민임대주택(29A형)선착순 동호지정 모집(입주자격완화, 선계약 후검증)</t>
+          <t>천안병천신한 국민임대주택 예비입주자 모집공고(2026.09.15)</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3023,222 +3031,222 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>20260813</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>20261029</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020495&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020714&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>D-45</t>
+          <t>D-14</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>군산시</t>
+          <t>홍성군</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>군산신역세권A3(내흥3) 영구임대주택 입주자 추가모집</t>
+          <t>홍성남장2 국민임대주택 예비입주자 모집공고(2026.09.15)</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>20261030</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019841&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020729&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>D-46</t>
+          <t>D-14</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>칠곡군</t>
+          <t>원주시</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026년 칠곡군 천원주택(신혼·신생아 매입임대주택Ⅰ) 예비입주자 모집 공고</t>
+          <t>원주무실1 국민임대주택 예비입주자 모집(26.09.15공고)</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>20260728</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>20261130</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=e54448a5-4c8c-4c3d-bfcf-bc465f677408&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020739&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>77</v>
+        <v>15</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>D-77</t>
+          <t>D-15</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>칠곡군</t>
+          <t>춘천시</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026년 칠곡군 천원주택(청년 매입임대주택) 입주자 및 예비입주자 모집 공고</t>
+          <t>춘천시, 홍천군지역 국민임대주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>20260728</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>20261130</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=2e8989e9-02ae-48be-9591-f3c4c8e7fa39&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020741&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>77</v>
+        <v>15</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>D-77</t>
+          <t>D-15</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>포항시 남구</t>
+          <t>하남시</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>포항블루밸리 행복주택 선착순 동호지정 상시모집(입주자격 완화, 통합공임 일반계층 추가, 선계약 후검증)</t>
+          <t>[경기북부] 2026년 하반기 일반 매입임대주택 입주자 모집공고</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>20260707</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>20261222</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020042&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020713&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>99</v>
+        <v>15</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>D-99</t>
+          <t>D-15</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>삼척시</t>
+          <t>남양주시</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>삼척시·정선군 국민임대 예비입주자 상시모집(26.6.10)</t>
+          <t>남양주마석2단지 국민임대주택 예비입주자 모집공고(2026.9.7.)</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3248,296 +3256,308 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>20260624</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>20261230</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020090&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020710&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H64" t="n">
-        <v>107</v>
+        <v>15</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>D-107</t>
+          <t>D-15</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>강원</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr"/>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>남양주시</t>
+        </is>
+      </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>남양주마석2단지 국민임대주택 예비입주자 모집공고(2026.9.7.)</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020668&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>108</v>
+        <v>15</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>D-108</t>
+          <t>D-15</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>강원</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr"/>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>김해시</t>
+        </is>
+      </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>[경남지역본부] 일반 매입임대주택 입주자 모집 공고(김해시, 밀양시)</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020706&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>108</v>
+        <v>15</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>D-108</t>
+          <t>D-15</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>강원</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr"/>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>김해시</t>
+        </is>
+      </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>김해진영6단지 국민임대주택 예비입주자 모집(‘26.09.15. 공고)</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020716&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>108</v>
+        <v>15</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>D-108</t>
+          <t>D-15</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>강원</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr"/>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>남해군</t>
+        </is>
+      </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>남해평리휴먼시아 국민임대주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020757&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>108</v>
+        <v>15</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>D-108</t>
+          <t>D-15</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>강원</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>동해시</t>
-        </is>
-      </c>
+          <t>경북</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr">
         <is>
-          <t>동해유성,태백철암장미 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
+          <t>[경북 포항,경주,영천] 일반 매입임대 입주자 모집공고</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>20260212</t>
+          <t>20260908</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019312&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020654&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>108</v>
+        <v>15</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>D-108</t>
+          <t>D-15</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>동해시</t>
+          <t>포항시 북구</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>동해유성,태백철암장미 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
+          <t>[경북 포항,경주,영천] 일반 매입임대 입주자 모집공고</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>20260212</t>
+          <t>20260908</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019308&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020601&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>108</v>
+        <v>15</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>D-108</t>
+          <t>D-15</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>태백시</t>
+          <t>칠곡군</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>태백궁전 국민임대 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
+          <t>칠곡북삼휴먼시아 국민임대주택 예비입주자 모집(45형)</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3547,817 +3567,893 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>20260212</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019307&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020719&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>108</v>
+        <v>15</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>D-108</t>
+          <t>D-15</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>경기</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr"/>
+          <t>울산</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>울주군</t>
+        </is>
+      </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>울산광역시 국민임대주택 예비입주자 정례모집 공고(2026.09.15.)</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020745&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>108</v>
+        <v>15</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>D-108</t>
+          <t>D-15</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>경기</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr"/>
+          <t>충북</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>괴산군</t>
+        </is>
+      </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>괴산군지역 국민임대주택 예비입주자 모집 공고[2026.09.15]</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020683&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>108</v>
+        <v>15</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>D-108</t>
+          <t>D-15</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>경기</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr"/>
+          <t>충북</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>음성군</t>
+        </is>
+      </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>음성신천 국민임대주택 예비입주자 모집 공고[2026.09.15]</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020684&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>108</v>
+        <v>15</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>D-108</t>
+          <t>D-15</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>경기</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr"/>
+          <t>충북</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>청주시 서원구</t>
+        </is>
+      </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>청주가경4 국민임대주택 예비입주자 모집 공고[2026.09.15]</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020752&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H75" t="n">
-        <v>108</v>
+        <v>15</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>D-108</t>
+          <t>D-15</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr"/>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>원주시</t>
+        </is>
+      </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>원주문막1 국민임대주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20261002</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261002</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020738&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H76" t="n">
-        <v>108</v>
+        <v>16</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>D-108</t>
+          <t>D-16</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr"/>
+          <t>경북</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>김천시</t>
+        </is>
+      </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>김천부곡2 영구임대주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261002</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020680&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>108</v>
+        <v>16</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>D-108</t>
+          <t>D-16</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr"/>
+          <t>충북</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>청주시 서원구</t>
+        </is>
+      </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>청주산남2-1 영구임대주택 예비입주자 모집 공고(2026.08.28)</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261002</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020625&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H78" t="n">
-        <v>108</v>
+        <v>16</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>D-108</t>
+          <t>D-16</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr"/>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>원주시</t>
+        </is>
+      </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>원주태장4 국민임대주택 예비입주자 모집공고(2026.09.15)</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020740&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H79" t="n">
-        <v>108</v>
+        <v>21</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>D-108</t>
+          <t>D-21</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>경북</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr"/>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>전주시 완산구</t>
+        </is>
+      </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>전주동서학 통합공공임대(일자리연계형 지원주택) 최초 입주자 모집</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>통합공공임대</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020742&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=48&amp;mi=1026</t>
         </is>
       </c>
       <c r="H80" t="n">
-        <v>108</v>
+        <v>22</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>D-108</t>
+          <t>D-22</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>경북</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr"/>
+          <t>충남</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>아산시</t>
+        </is>
+      </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>아산탕정2 국민임대주택 예비입주자 모집공고(2026.09.15)</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020726&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H81" t="n">
-        <v>108</v>
+        <v>28</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>D-108</t>
+          <t>D-28</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>경북</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr"/>
+          <t>충남</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>당진시</t>
+        </is>
+      </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>[청년신혼부부매입임대리츠주택] 충남당진 송산청광플러스원 입주자격완화 상시모집</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260810</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020529&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H82" t="n">
-        <v>108</v>
+        <v>29</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>D-108</t>
+          <t>D-29</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>경북</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr"/>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>태백시</t>
+        </is>
+      </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>태백철암1 국민임대주택 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261028</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020735&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H83" t="n">
-        <v>108</v>
+        <v>42</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>D-108</t>
+          <t>D-42</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>대구</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr"/>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>양산시</t>
+        </is>
+      </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>양산 사송A-4BL 국민임대주택(29A형)선착순 동호지정 모집(입주자격완화, 선계약 후검증)</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260813</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261029</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020495&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H84" t="n">
-        <v>108</v>
+        <v>43</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>D-108</t>
+          <t>D-43</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>대구</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr"/>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>군산시</t>
+        </is>
+      </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>군산신역세권A3(내흥3) 영구임대주택 입주자 추가모집</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261030</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019841&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H85" t="n">
-        <v>108</v>
+        <v>44</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>D-108</t>
+          <t>D-44</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>대구</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr"/>
+          <t>경북</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>칠곡군</t>
+        </is>
+      </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 칠곡군 천원주택(신혼·신생아 매입임대주택Ⅰ) 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260728</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261130</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=e54448a5-4c8c-4c3d-bfcf-bc465f677408&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
         </is>
       </c>
       <c r="H86" t="n">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>D-108</t>
+          <t>D-75</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>대구</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr"/>
+          <t>경북</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>칠곡군</t>
+        </is>
+      </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 칠곡군 천원주택(청년 매입임대주택) 입주자 및 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260728</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261130</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=2e8989e9-02ae-48be-9591-f3c4c8e7fa39&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
         </is>
       </c>
       <c r="H87" t="n">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>D-108</t>
+          <t>D-75</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>대전</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr"/>
+          <t>경북</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>포항시 남구</t>
+        </is>
+      </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>포항블루밸리 행복주택 선착순 동호지정 상시모집(입주자격 완화, 통합공임 일반계층 추가, 선계약 후검증)</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260707</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261222</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020042&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H88" t="n">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>D-108</t>
+          <t>D-97</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>대전</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr"/>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>삼척시</t>
+        </is>
+      </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>삼척시·정선군 국민임대 예비입주자 상시모집(26.6.10)</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260624</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261230</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020090&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H89" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>D-108</t>
+          <t>D-105</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>대전</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr"/>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>태백시</t>
+        </is>
+      </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>태백장성 국민임대주택 예비입주자 입주자격완화 상시모집</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261230</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020730&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H90" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>D-108</t>
+          <t>D-105</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>대전</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -4367,7 +4463,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -4377,28 +4473,28 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H91" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>D-108</t>
+          <t>D-106</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -4418,28 +4514,28 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H92" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>D-108</t>
+          <t>D-106</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -4459,28 +4555,28 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H93" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>D-108</t>
+          <t>D-106</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -4490,7 +4586,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -4500,38 +4596,42 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H94" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>D-108</t>
+          <t>D-106</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>부산</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr"/>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>동해시</t>
+        </is>
+      </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>동해유성,태백철암장미 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260212</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -4541,38 +4641,42 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019312&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H95" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>D-108</t>
+          <t>D-106</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>서울</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr"/>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>동해시</t>
+        </is>
+      </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>동해유성,태백철암장미 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260212</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -4582,38 +4686,42 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019308&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H96" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>D-108</t>
+          <t>D-106</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>서울</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr"/>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>태백시</t>
+        </is>
+      </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>태백궁전 국민임대 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260212</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -4623,28 +4731,28 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019307&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H97" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>D-108</t>
+          <t>D-106</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -4664,28 +4772,28 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H98" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>D-108</t>
+          <t>D-106</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -4695,7 +4803,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -4705,28 +4813,28 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H99" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>D-108</t>
+          <t>D-106</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>세종</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -4746,28 +4854,28 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H100" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>D-108</t>
+          <t>D-106</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>세종</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -4777,7 +4885,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -4787,28 +4895,28 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H101" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>D-108</t>
+          <t>D-106</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>세종</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -4828,28 +4936,28 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H102" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>D-108</t>
+          <t>D-106</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>세종</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -4859,7 +4967,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4869,28 +4977,28 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H103" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>D-108</t>
+          <t>D-106</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>울산</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -4910,28 +5018,28 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H104" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>D-108</t>
+          <t>D-106</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>울산</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -4941,7 +5049,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4951,28 +5059,28 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H105" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>D-108</t>
+          <t>D-106</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>울산</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -4992,28 +5100,28 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H106" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>D-108</t>
+          <t>D-106</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>울산</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -5023,7 +5131,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -5033,28 +5141,28 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H107" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>D-108</t>
+          <t>D-106</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -5074,28 +5182,28 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H108" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>D-108</t>
+          <t>D-106</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -5105,7 +5213,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -5115,28 +5223,28 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H109" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>D-108</t>
+          <t>D-106</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B110" t="inlineStr"/>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -5156,28 +5264,28 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H110" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>D-108</t>
+          <t>D-106</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -5187,7 +5295,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -5197,28 +5305,28 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H111" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>D-108</t>
+          <t>D-106</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -5238,28 +5346,28 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H112" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>D-108</t>
+          <t>D-106</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -5269,7 +5377,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -5279,28 +5387,28 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H113" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>D-108</t>
+          <t>D-106</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>대전</t>
         </is>
       </c>
       <c r="B114" t="inlineStr"/>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -5320,28 +5428,28 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H114" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>D-108</t>
+          <t>D-106</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>대전</t>
         </is>
       </c>
       <c r="B115" t="inlineStr"/>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -5351,7 +5459,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -5361,42 +5469,38 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H115" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>D-108</t>
+          <t>D-106</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>전북</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>김제시</t>
-        </is>
-      </c>
+          <t>대전</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr"/>
       <c r="C116" t="inlineStr">
         <is>
-          <t>김제검산1단지 영구임대주택 예비입주자 모집 공고(상시모집)</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>20260101</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -5406,42 +5510,38 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019412&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H116" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>D-108</t>
+          <t>D-106</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>전북</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>남원시</t>
-        </is>
-      </c>
+          <t>대전</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr"/>
       <c r="C117" t="inlineStr">
         <is>
-          <t>남원노암 공공임대 50년 예비입주자 모집</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>50년임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -5451,42 +5551,38 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020623&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H117" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>D-108</t>
+          <t>D-106</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>전북</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>남원시</t>
-        </is>
-      </c>
+          <t>부산</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr"/>
       <c r="C118" t="inlineStr">
         <is>
-          <t>남원노암단지 영구임대주택 입주자격완화 예비입주자 모집공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -5496,42 +5592,38 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020649&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H118" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>D-108</t>
+          <t>D-106</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>전북</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>전주시 완산구</t>
-        </is>
-      </c>
+          <t>부산</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr"/>
       <c r="C119" t="inlineStr">
         <is>
-          <t>전주시(전주평화1,전주평화4) 영구임대주택 예비입주자 모집 공고(공고일:2026.02.10.)</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>20260303</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -5541,28 +5633,28 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019241&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H119" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>D-108</t>
+          <t>D-106</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -5582,28 +5674,28 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H120" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>D-108</t>
+          <t>D-106</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -5613,7 +5705,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -5623,28 +5715,28 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H121" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>D-108</t>
+          <t>D-106</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B122" t="inlineStr"/>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -5664,28 +5756,28 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H122" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>D-108</t>
+          <t>D-106</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B123" t="inlineStr"/>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -5695,7 +5787,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -5705,28 +5797,28 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H123" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>D-108</t>
+          <t>D-106</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -5746,28 +5838,28 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H124" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>D-108</t>
+          <t>D-106</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B125" t="inlineStr"/>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -5777,7 +5869,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -5787,28 +5879,28 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H125" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>D-108</t>
+          <t>D-106</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>세종</t>
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -5828,28 +5920,28 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H126" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>D-108</t>
+          <t>D-106</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>세종</t>
         </is>
       </c>
       <c r="B127" t="inlineStr"/>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -5859,7 +5951,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -5869,42 +5961,38 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H127" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>D-108</t>
+          <t>D-106</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>충남</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>당진시</t>
-        </is>
-      </c>
+          <t>세종</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr"/>
       <c r="C128" t="inlineStr">
         <is>
-          <t>[청년신혼부부매입임대리츠주택] 충남당진 송산청광플러스원 입주자격완화 상시모집</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>20260316</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -5914,28 +6002,28 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019433&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H128" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>D-108</t>
+          <t>D-106</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>세종</t>
         </is>
       </c>
       <c r="B129" t="inlineStr"/>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -5945,7 +6033,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -5955,28 +6043,28 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H129" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>D-108</t>
+          <t>D-106</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>울산</t>
         </is>
       </c>
       <c r="B130" t="inlineStr"/>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -5996,28 +6084,28 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H130" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>D-108</t>
+          <t>D-106</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>울산</t>
         </is>
       </c>
       <c r="B131" t="inlineStr"/>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -6037,28 +6125,28 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H131" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>D-108</t>
+          <t>D-106</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>울산</t>
         </is>
       </c>
       <c r="B132" t="inlineStr"/>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -6068,7 +6156,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -6078,195 +6166,1281 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H132" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>D-108</t>
+          <t>D-106</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>강원</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>삼척시</t>
-        </is>
-      </c>
+          <t>울산</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr"/>
       <c r="C133" t="inlineStr">
         <is>
-          <t>삼척도계·정선신동 국민임대주택 예비입주자 입주자격완화 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>20270129</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020581&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H133" t="n">
-        <v>137</v>
+        <v>106</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>D-137</t>
+          <t>D-106</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>전북</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>군산시</t>
-        </is>
-      </c>
+          <t>인천</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr"/>
       <c r="C134" t="inlineStr">
         <is>
-          <t>군산시 국민임대주택 입주자 선착순 상시 모집(경암부향 등 7개 단지)</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>20260812</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>20270731</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020453&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H134" t="n">
-        <v>320</v>
+        <v>106</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>D-320</t>
+          <t>D-106</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>울산</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>울주군</t>
-        </is>
-      </c>
+          <t>인천</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr"/>
       <c r="C135" t="inlineStr">
         <is>
-          <t>울산광역시 국민임대주택 예비입주자 정례모집 공고(2025.09.15.)</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>20250929</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>20291001</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300018799&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H135" t="n">
-        <v>1113</v>
+        <v>106</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>D-1113</t>
+          <t>D-106</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
+          <t>인천</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr"/>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H136" t="n">
+        <v>106</v>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>D-106</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>인천</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr"/>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>20260224</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H137" t="n">
+        <v>106</v>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>D-106</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr"/>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H138" t="n">
+        <v>106</v>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>D-106</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr"/>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H139" t="n">
+        <v>106</v>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>D-106</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr"/>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H140" t="n">
+        <v>106</v>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>D-106</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr"/>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>20260224</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H141" t="n">
+        <v>106</v>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>D-106</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>김제시</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>김제검산1단지 영구임대주택 예비입주자 모집 공고(상시모집)</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>영구임대</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019412&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H142" t="n">
+        <v>106</v>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>D-106</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>남원시</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>남원노암 공공임대 50년 예비입주자 모집</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>50년임대</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>20260921</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020623&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H143" t="n">
+        <v>106</v>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>D-106</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>남원시</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>남원노암단지 영구임대주택 입주자격완화 예비입주자 모집공고</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>영구임대</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>20260921</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020649&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H144" t="n">
+        <v>106</v>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>D-106</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>전주시 완산구</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>전주시(전주평화1,전주평화4) 영구임대주택 예비입주자 모집 공고(공고일:2026.02.10.)</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>영구임대</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>20260303</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019241&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H145" t="n">
+        <v>106</v>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>D-106</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>제주</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr"/>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H146" t="n">
+        <v>106</v>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>D-106</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>제주</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr"/>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H147" t="n">
+        <v>106</v>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>D-106</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>제주</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr"/>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H148" t="n">
+        <v>106</v>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>D-106</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>제주</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr"/>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>20260224</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H149" t="n">
+        <v>106</v>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>D-106</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>충남</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr"/>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H150" t="n">
+        <v>106</v>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>D-106</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>충남</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr"/>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H151" t="n">
+        <v>106</v>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>D-106</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>충남</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr"/>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H152" t="n">
+        <v>106</v>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>D-106</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>충남</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr"/>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>20260224</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H153" t="n">
+        <v>106</v>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>D-106</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>충남</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>당진시</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>[청년신혼부부매입임대리츠주택] 충남당진 송산청광플러스원 입주자격완화 상시모집</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>매입임대</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>20260316</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019433&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H154" t="n">
+        <v>106</v>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>D-106</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>충북</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr"/>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H155" t="n">
+        <v>106</v>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>D-106</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>충북</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr"/>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H156" t="n">
+        <v>106</v>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>D-106</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>충북</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr"/>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H157" t="n">
+        <v>106</v>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>D-106</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>충북</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr"/>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>20260224</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H158" t="n">
+        <v>106</v>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>D-106</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>삼척시</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>삼척도계·정선신동 국민임대주택 예비입주자 입주자격완화 공고</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>국민임대</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>20270129</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020581&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H159" t="n">
+        <v>135</v>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>D-135</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>군산시</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>군산시 국민임대주택 입주자 선착순 상시 모집(경암부향 등 7개 단지)</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>국민임대</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>20260812</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>20270731</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020453&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H160" t="n">
+        <v>318</v>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>D-318</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
           <t>울산</t>
         </is>
       </c>
-      <c r="B136" t="inlineStr">
+      <c r="B161" t="inlineStr">
         <is>
           <t>울주군</t>
         </is>
       </c>
-      <c r="C136" t="inlineStr">
+      <c r="C161" t="inlineStr">
         <is>
           <t>울산광역시 국민임대주택 예비입주자 정례모집 공고(2025.09.15.)</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr">
+      <c r="D161" t="inlineStr">
         <is>
           <t>국민임대</t>
         </is>
       </c>
-      <c r="E136" t="inlineStr">
+      <c r="E161" t="inlineStr">
         <is>
           <t>20250929</t>
         </is>
       </c>
-      <c r="F136" t="inlineStr">
+      <c r="F161" t="inlineStr">
         <is>
           <t>20291001</t>
         </is>
       </c>
-      <c r="G136" t="inlineStr">
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300018799&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H161" t="n">
+        <v>1111</v>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>D-1111</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>울산</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>울주군</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>울산광역시 국민임대주택 예비입주자 정례모집 공고(2025.09.15.)</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>국민임대</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>20250929</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>20291001</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
         <is>
           <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300018780&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
-      <c r="H136" t="n">
-        <v>1113</v>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>D-1113</t>
+      <c r="H162" t="n">
+        <v>1111</v>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>D-1111</t>
         </is>
       </c>
     </row>

--- a/housing_notices.xlsx
+++ b/housing_notices.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I162"/>
+  <dimension ref="A1:I172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,37 +466,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>춘천시</t>
+          <t>군산시</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>[강원지역본부] 26년 3차 신혼신생아1 매입임대주택 예비자 모집공고</t>
+          <t>군산시 국민임대주택 예비입주자 모집 공고(26.09.03)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260916</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>20260916</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020675&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020663&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -511,37 +511,37 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>강릉시</t>
+          <t>김제시</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>[강원지역본부] 26년 3차 신혼신생아2(전세형) 매입임대주택 예비자 모집공고</t>
+          <t>김제하동 국민임대주택 모집공고</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>20260916</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020679&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020701&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -556,37 +556,37 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>강릉시</t>
+          <t>서산시</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>[강원지역본부] 26년 3차 청년 매입임대주택 예비자 모집공고</t>
+          <t>서산석림3단지 50년공공임대주택 예비입주자 모집공고(2026.09.01.)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>50년임대</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>20260916</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020673&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020657&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -601,17 +601,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>양산시</t>
+          <t>부천시 원미구</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>양산사송 A-8BL 영구임대주택 입주자격완화 예비입주자 모집</t>
+          <t>부천시 영구임대주택 예비입주자 모집 (중동한라1, 중동덕유1)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -621,62 +621,62 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260916</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>20260916</t>
+          <t>20260918</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020658&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020678&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>오늘 마감</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>군산시</t>
+          <t>안산시 단원구</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>군산시 국민임대주택 예비입주자 모집 공고(26.09.03)</t>
+          <t>안산 선부동 행복주택 예비입주자(주거급여)모집 공고</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>20260916</t>
+          <t>20260903</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>20260917</t>
+          <t>20260918</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020663&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://www.ansanuc.net/homenew/12286/20328/bbsList.do</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -691,37 +691,37 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>김제시</t>
+          <t>서귀포시</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>김제하동 국민임대주택 모집공고</t>
+          <t>[제주지역본부] 다자녀 매입임대주택 예비입주자 모집 공고(서귀포시)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>20260917</t>
+          <t>20260918</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020701&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020691&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -736,45 +736,41 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>충남</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>서산시</t>
-        </is>
-      </c>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>서산석림3단지 50년공공임대주택 예비입주자 모집공고(2026.09.01.)</t>
+          <t>[경기남부] 용인시 신혼·신생아 매입임대주택Ⅱ(전세형) 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>50년임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>20260917</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020657&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020702&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>D-4</t>
         </is>
       </c>
     </row>
@@ -784,42 +780,38 @@
           <t>경기</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>부천시 원미구</t>
-        </is>
-      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>부천시 영구임대주택 예비입주자 모집 (중동한라1, 중동덕유1)</t>
+          <t>[경기남부] 용인시 청년 매입임대주택 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>20260916</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020678&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020699&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>D-4</t>
         </is>
       </c>
     </row>
@@ -829,110 +821,110 @@
           <t>경기</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>안산시 단원구</t>
-        </is>
-      </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>안산 선부동 행복주택 예비입주자(주거급여)모집 공고</t>
+          <t>[경기남부] 화성시·평택시 신혼·신생아 매입임대주택Ⅱ(전세형) 예비입주자 [후순번] 모집공고</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>20260903</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.ansanuc.net/homenew/12286/20328/bbsList.do</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020703&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>D-4</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>서귀포시</t>
+          <t>포항시 북구</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>[제주지역본부] 다자녀 매입임대주택 예비입주자 모집 공고(서귀포시)</t>
+          <t>포항창포 영구임대아파트 예비입주자 모집</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>20260917</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020691&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020651&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>D-4</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>경기</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
+          <t>경북</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>포항시 북구</t>
+        </is>
+      </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>[경기남부] 용인시 신혼·신생아 매입임대주택Ⅱ(전세형) 예비입주자 모집공고</t>
+          <t>포항학산 영구임대아파트 예비입주자 모집</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>20260917</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -942,15 +934,15 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020702&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020650&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-4</t>
         </is>
       </c>
     </row>
@@ -960,30 +952,34 @@
           <t>경기</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>부천시 오정구</t>
+        </is>
+      </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>[경기남부] 용인시 청년 매입임대주택 예비입주자 모집공고</t>
+          <t>2026년 9월 부천시 국민임대주택 예비입주자 모집 공고(2026.09.07)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>20260917</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260922</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020699&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020652&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -1004,7 +1000,7 @@
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>[경기남부] 화성시·평택시 신혼·신생아 매입임대주택Ⅱ(전세형) 예비입주자 [후순번] 모집공고</t>
+          <t>26-4차 인천본부 든든전세주택 입주자 모집공고(인천, 부천)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1014,17 +1010,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>20260917</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260922</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020703&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020725&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -1039,37 +1035,33 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>경북</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>포항시 북구</t>
-        </is>
-      </c>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>포항창포 영구임대아파트 예비입주자 모집</t>
+          <t>26-4차 인천본부 든든전세주택 입주자 모집공고(인천, 부천)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260922</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020651&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020715&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -1089,32 +1081,32 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>포항시 북구</t>
+          <t>경주시</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>포항학산 영구임대아파트 예비입주자 모집</t>
+          <t>경주시, 영천시, 포항시 부도매입(국민임대)주택 입주자격완화 모집공고</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260922</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020650&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020635&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -1129,22 +1121,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>부천시 오정구</t>
+          <t>서해구</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026년 9월 부천시 국민임대주택 예비입주자 모집 공고(2026.09.07)</t>
+          <t>26-4차 인천본부 든든전세주택 입주자 모집공고(인천, 부천)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1159,25 +1151,29 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020652&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020725&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>경기</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
+          <t>인천</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>미추홀구</t>
+        </is>
+      </c>
       <c r="C18" t="inlineStr">
         <is>
           <t>26-4차 인천본부 든든전세주택 입주자 모집공고(인천, 부천)</t>
@@ -1200,33 +1196,37 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020725&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020715&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>경기</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
+          <t>인천</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>남동구</t>
+        </is>
+      </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>26-4차 인천본부 든든전세주택 입주자 모집공고(인천, 부천)</t>
+          <t>26년 9월 인천시 남동구 국민임대주택 예비입주자 모집 공고(2026.09.07)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1241,32 +1241,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020715&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020619&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>경주시</t>
+          <t>옹진군</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>경주시, 영천시, 포항시 부도매입(국민임대)주택 입주자격완화 모집공고</t>
+          <t>인천옹진백령 국민임대주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1286,15 +1286,15 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020635&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020578&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
@@ -1306,22 +1306,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>계양구</t>
+          <t>옹진군</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>26-4차 인천본부 든든전세주택 입주자 모집공고(인천, 부천)</t>
+          <t>인천옹진연평 국민임대주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260922</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1331,37 +1331,37 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020725&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020697&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>계양구</t>
+          <t>횡성군</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>26-4차 인천본부 든든전세주택 입주자 모집공고(인천, 부천)</t>
+          <t>강원횡성 통합공공임대주택 입주자 모집</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>통합공공임대</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>20260922</t>
+          <t>20260923</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020715&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020627&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=48&amp;mi=1026</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -1391,22 +1391,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>남동구</t>
+          <t>안성시</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>26년 9월 인천시 남동구 국민임대주택 예비입주자 모집 공고(2026.09.07)</t>
+          <t>[온라인 접수 불가, 관할 주거복지지사 현장접수] 경기남부지역본부 2026년 일반 매입임대주택 입주자 모집공고</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1416,12 +1416,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>20260922</t>
+          <t>20260923</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020619&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020769&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -1436,22 +1436,18 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>인천</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>옹진군</t>
-        </is>
-      </c>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
-          <t>인천옹진백령 국민임대주택 예비입주자 모집</t>
+          <t>[온라인 접수 불가, 관할 주거복지지사 현장접수] 경기남부지역본부 2026년 일반 매입임대주택 입주자 모집공고</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1461,12 +1457,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>20260922</t>
+          <t>20260923</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020578&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020731&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -1481,17 +1477,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>옹진군</t>
+          <t>김포시</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>인천옹진연평 국민임대주택 예비입주자 모집</t>
+          <t>김포시 국민임대주택 예비입주자 모집(2026.09.07)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1501,17 +1497,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>20260922</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>20260922</t>
+          <t>20260923</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020697&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020659&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -1526,22 +1522,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>횡성군</t>
+          <t>화성시 효행구</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>강원횡성 통합공공임대주택 입주자 모집</t>
+          <t>화성서부권 국민임대주택 예비입주자 모집[입주자격완화]</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>통합공공임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1556,32 +1552,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020627&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=48&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020686&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-6</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>시흥시</t>
+          <t>양산시</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>[온라인 접수 불가, 관할 주거복지지사 현장접수] 경기남부지역본부 2026년 일반 매입임대주택 입주자 모집공고</t>
+          <t>[경남지역본부]26년 3차 분양전환형 든든전세주택 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1601,37 +1597,37 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020731&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020721&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-6</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>김포시</t>
+          <t>김해시</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>김포시 국민임대주택 예비입주자 모집(2026.09.07)</t>
+          <t>[경남지역본부]26년 3차 비분양전환형 든든전세주택 입주자 모집 공고</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1646,37 +1642,33 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020659&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020720&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-6</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>경기</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>화성시 효행구</t>
-        </is>
-      </c>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
-          <t>화성서부권 국민임대주택 예비입주자 모집[입주자격완화]</t>
+          <t>[경남지역본부]26년 3차 신혼·신생아매입임대Ⅰ 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1691,15 +1683,15 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020686&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020722&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-6</t>
         </is>
       </c>
     </row>
@@ -1711,12 +1703,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>통영시</t>
+          <t>양산시</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>[경남지역본부]26년 3차 분양전환형 든든전세주택 예비입주자 모집 공고</t>
+          <t>[경남지역본부]26년 3차 신혼·신생아매입임대Ⅱ(전세형) 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1736,15 +1728,15 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020721&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020723&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-6</t>
         </is>
       </c>
     </row>
@@ -1756,12 +1748,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>김해시</t>
+          <t>진주시</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>[경남지역본부]26년 3차 비분양전환형 든든전세주택 입주자 모집 공고</t>
+          <t>[경남지역본부]26년 3차 청년매입임대 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1781,15 +1773,15 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020720&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020717&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-6</t>
         </is>
       </c>
     </row>
@@ -1801,12 +1793,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>진주시</t>
+          <t>함양군</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>[경남지역본부]26년 3차 신혼·신생아매입임대Ⅰ 예비입주자 모집공고</t>
+          <t>경남 함양군 서하면 다자녀 매입임대주택 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1816,7 +1808,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1826,37 +1818,37 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020722&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020711&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-6</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>양산시</t>
+          <t>달서구</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>[경남지역본부]26년 3차 신혼·신생아매입임대Ⅱ(전세형) 예비입주자 모집공고</t>
+          <t>대구죽전 행복주택(산업단지형) 예비 입주자 모집</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1871,37 +1863,37 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020723&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020763&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-6</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>양산시</t>
+          <t>달서구</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>[경남지역본부]26년 3차 청년매입임대 예비입주자 모집공고</t>
+          <t>대구죽전 행복주택(산업단지형) 예비 입주자 모집</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1916,42 +1908,42 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020717&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020760&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-6</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>함양군</t>
+          <t>달서구</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>경남 함양군 서하면 다자녀 매입임대주택 예비입주자 모집공고</t>
+          <t>대구죽전 행복주택(산업단지형) 예비 입주자 모집</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1961,32 +1953,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020711&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020751&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-6</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>달서구</t>
+          <t>김제시</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>대구죽전 행복주택(산업단지형) 예비 입주자 모집</t>
+          <t>(26.9.10)김제대검산, 정읍시기, 정읍첨단 행복주택 입주자격완화 예비자 모집 공고(소득·총자산요건 배제 및 무주택요건 완화)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2006,42 +1998,42 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020760&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020344&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-6</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>달서구</t>
+          <t>익산시</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>대구죽전 행복주택(산업단지형) 예비 입주자 모집</t>
+          <t>익산한스빌 국민임대주택 예비입주자 자격완화 모집 공고</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260922</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2051,77 +2043,77 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020751&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020694&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-6</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>김제시</t>
+          <t>칠곡군</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>(26.9.10)김제대검산, 정읍시기, 정읍첨단 행복주택 입주자격완화 예비자 모집 공고(소득·총자산요건 배제 및 무주택요건 완화)</t>
+          <t>칠곡왜관4 국민임대아파트 예비입주자 모집(51형)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>20260923</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020344&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020696&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-11</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>익산시</t>
+          <t>양산시</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>익산한스빌 국민임대주택 예비입주자 자격완화 모집 공고</t>
+          <t>[양산시지역]양산대석휴먼시아 국민임대주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2131,42 +2123,42 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>20260922</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>20260923</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020694&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020754&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>칠곡군</t>
+          <t>양산시</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>칠곡왜관4 국민임대아파트 예비입주자 모집(51형)</t>
+          <t>양산시 국민임대주택 예비입주자 완화 모집(‘26.09.15)_소득, 자산, 무주택 요건 완화 / 계약금 인하</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2181,12 +2173,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020696&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020796&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H40" t="n">
@@ -2211,7 +2203,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>[양산시지역]양산대석휴먼시아 국민임대주택 예비입주자 모집</t>
+          <t>양산시 국민임대주택 예비입주자 완화 모집(‘26.09.15)_소득, 자산, 무주택 요건 완화 / 계약금 인하</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2221,25 +2213,25 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
+          <t>20260928</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
           <t>20260929</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>20260929</t>
-        </is>
-      </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020754&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020794&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>D-13</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
@@ -2251,12 +2243,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>창녕군</t>
+          <t>양산시</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>창녕창녕 국민임대주택 예비입주자 모집</t>
+          <t>양산시 국민임대주택 예비입주자 완화 모집(‘26.09.15)_소득, 자산, 무주택 요건 완화 / 계약금 인하</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2266,47 +2258,47 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
+          <t>20260928</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
           <t>20260929</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>20260929</t>
-        </is>
-      </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020724&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020732&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>D-13</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>경산시</t>
+          <t>창녕군</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>경산백천1단지 50년 공공임대주택 예비입주자 모집</t>
+          <t>창녕창녕 국민임대주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>50년임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2321,15 +2313,15 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020728&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020724&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>D-13</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
@@ -2346,17 +2338,17 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>대구혁신10, 경산하양3 행복주택 입주자격완화 선계약 후검증 동호지정 입주자 모집</t>
+          <t>경산백천1단지 50년 공공임대주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>50년임대</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2366,27 +2358,27 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020682&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020728&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>D-13</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>동구</t>
+          <t>경산시</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2415,56 +2407,56 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>D-13</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>기장군</t>
+          <t>동구</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>부산광역시 국민임대주택 예비입주자 정례모집 공고(2026.09.15.)</t>
+          <t>대구혁신10, 경산하양3 행복주택 입주자격완화 선계약 후검증 동호지정 입주자 모집</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
+          <t>20260928</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
           <t>20260929</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>20260929</t>
-        </is>
-      </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020758&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020682&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>D-13</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
@@ -2481,7 +2473,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관7국민임대 소득완화 모집공고</t>
+          <t>부산광역시 국민임대주택 예비입주자 정례모집 공고(2026.09.15.)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2491,7 +2483,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2501,32 +2493,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020655&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020788&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>D-13</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>군산시</t>
+          <t>기장군</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>군산구암 국민임대주택 예비입주자 모집 공고(‘26.9.15.)</t>
+          <t>부산광역시 국민임대주택 예비입주자 정례모집 공고(2026.09.15.)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2546,32 +2538,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020743&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020758&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>D-13</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>음성군</t>
+          <t>기장군</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>음성군 국민임대주택 예비입주자 모집(2026.09.15.)</t>
+          <t>부산광역시 기장군 정관7국민임대 소득완화 모집공고</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2581,42 +2573,42 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
+          <t>20260928</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
           <t>20260929</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>20260929</t>
-        </is>
-      </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020698&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020655&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>D-13</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>원주시</t>
+          <t>군산시</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>원주시지역 국민임대주택 예비입주자 모집</t>
+          <t>군산구암 국민임대주택 예비입주자 모집 공고(‘26.9.15.)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2631,37 +2623,37 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020767&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020743&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>원주시</t>
+          <t>음성군</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>원주시지역 국민임대주택 예비입주자 모집</t>
+          <t>음성군 국민임대주택 예비입주자 모집(2026.09.15.)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2676,37 +2668,37 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020677&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020698&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>김포시</t>
+          <t>원주시</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>김포지역 국민임대주택 예비입주자 모집 공고(26.09.07.)</t>
+          <t>원주시지역 국민임대주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2716,7 +2708,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2726,32 +2718,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020704&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020783&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>D-13</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>김포시</t>
+          <t>원주시</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>김포지역 국민임대주택 예비입주자 모집 공고(26.09.07.)</t>
+          <t>원주시지역 국민임대주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2761,7 +2753,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2771,32 +2763,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020662&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020767&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>D-13</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>안성시</t>
+          <t>원주시</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>안성금화 국민임대 입주자격완화 예비입주자 모집공고(2026.09.07)</t>
+          <t>원주시지역 국민임대주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2806,7 +2798,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2816,15 +2808,15 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020695&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020677&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>D-13</t>
         </is>
       </c>
     </row>
@@ -2836,40 +2828,40 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>의정부시</t>
+          <t>김포시</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>의정부송산3단지 공임50년 예비입주자 표준모집공고문</t>
+          <t>김포지역 국민임대주택 예비입주자 모집 공고(26.09.07.)</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>50년임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
+          <t>20260918</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
           <t>20260930</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>20260930</t>
-        </is>
-      </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020670&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020704&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>D-13</t>
         </is>
       </c>
     </row>
@@ -2881,22 +2873,22 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>화성시 동탄구</t>
+          <t>김포시</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>화성동탄2 10년 분양전환공공임대주택(리츠) 예비입주자모집공고(‘26.09)</t>
+          <t>김포지역 국민임대주택 예비입주자 모집 공고(26.09.07.)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>10년임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260918</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2906,42 +2898,42 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=0000061173&amp;ccrCnntSysDsCd=02&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020662&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>D-13</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>북구</t>
+          <t>안성시</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>부산만덕5 2블록 10년 분양전환공공임대주택(e편한세상 금정산) 예비입주자 모집공고</t>
+          <t>안성금화 국민임대 입주자격완화 예비입주자 모집공고(2026.09.07)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>10년임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2951,42 +2943,42 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=0000061163&amp;ccrCnntSysDsCd=02&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020695&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>D-13</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>아산시</t>
+          <t>의정부시</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>아산신창소화,아산인주 국민임대주택 예비입주자 모집공고(2026.09.15)</t>
+          <t>의정부송산3단지 공임50년 예비입주자 표준모집공고문</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>50년임대</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2996,167 +2988,167 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020726&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020670&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>D-13</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>천안시 동남구</t>
+          <t>화성시 동탄구</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>천안병천신한 국민임대주택 예비입주자 모집공고(2026.09.15)</t>
+          <t>화성동탄2 10년 분양전환공공임대주택(리츠) 예비입주자모집공고(‘26.09)</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>10년임대</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
+          <t>20260929</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
           <t>20260930</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>20260930</t>
-        </is>
-      </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020714&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=0000061173&amp;ccrCnntSysDsCd=02&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>D-13</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>홍성군</t>
+          <t>북구</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>홍성남장2 국민임대주택 예비입주자 모집공고(2026.09.15)</t>
+          <t>부산만덕5 2블록 10년 분양전환공공임대주택(e편한세상 금정산) 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>10년임대</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
+          <t>20260929</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
           <t>20260930</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>20260930</t>
-        </is>
-      </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020729&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=0000061163&amp;ccrCnntSysDsCd=02&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>D-13</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>원주시</t>
+          <t>남동구</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>원주무실1 국민임대주택 예비입주자 모집(26.09.15공고)</t>
+          <t>‘26년 9월 인천시(남동구) 행복주택 입주자격완화 예비입주자 모집</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020739&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020744&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>D-15</t>
+          <t>D-13</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>춘천시</t>
+          <t>아산시</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>춘천시, 홍천군지역 국민임대주택 예비입주자 모집</t>
+          <t>아산신창소화,아산인주 국민임대주택 예비입주자 모집공고(2026.09.15)</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3166,132 +3158,132 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020741&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020726&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>D-15</t>
+          <t>D-13</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>하남시</t>
+          <t>천안시 동남구</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>[경기북부] 2026년 하반기 일반 매입임대주택 입주자 모집공고</t>
+          <t>천안병천신한 국민임대주택 예비입주자 모집공고(2026.09.15)</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020713&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020714&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>D-15</t>
+          <t>D-13</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>남양주시</t>
+          <t>천안시 서북구</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>남양주마석2단지 국민임대주택 예비입주자 모집공고(2026.9.7.)</t>
+          <t>천안쌍용5-2 공임50년 예비입주자 모집공고(2026.09.16)</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>50년임대</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
+          <t>20260929</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
           <t>20260930</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>20261001</t>
-        </is>
-      </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020710&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019790&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H64" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>D-15</t>
+          <t>D-13</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>남양주시</t>
+          <t>홍성군</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>남양주마석2단지 국민임대주택 예비입주자 모집공고(2026.9.7.)</t>
+          <t>홍성남장2 국민임대주택 예비입주자 모집공고(2026.09.15)</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3306,47 +3298,47 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020668&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020729&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>D-15</t>
+          <t>D-13</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>김해시</t>
+          <t>원주시</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>[경남지역본부] 일반 매입임대주택 입주자 모집 공고(김해시, 밀양시)</t>
+          <t>원주무실1 국민임대주택 예비입주자 모집(26.09.15공고)</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -3356,32 +3348,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020706&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020792&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>D-15</t>
+          <t>D-14</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>김해시</t>
+          <t>원주시</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>김해진영6단지 국민임대주택 예비입주자 모집(‘26.09.15. 공고)</t>
+          <t>원주무실1 국민임대주택 예비입주자 모집(26.09.15공고)</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3391,7 +3383,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -3401,32 +3393,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020716&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020739&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>D-15</t>
+          <t>D-14</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>남해군</t>
+          <t>춘천시</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>남해평리휴먼시아 국민임대주택 예비입주자 모집</t>
+          <t>춘천시, 홍천군지역 국민임대주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3436,38 +3428,42 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
+          <t>20260929</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
           <t>20261001</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>20261001</t>
-        </is>
-      </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020757&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020741&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>D-15</t>
+          <t>D-14</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>경북</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr"/>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>동두천시</t>
+        </is>
+      </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>[경북 포항,경주,영천] 일반 매입임대 입주자 모집공고</t>
+          <t>[경기북부] 2026년 하반기 일반 매입임대주택 입주자 모집공고</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3477,7 +3473,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>20260908</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3487,42 +3483,42 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020654&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020713&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>D-15</t>
+          <t>D-14</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>포항시 북구</t>
+          <t>남양주시</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>[경북 포항,경주,영천] 일반 매입임대 입주자 모집공고</t>
+          <t>남양주마석2단지 국민임대주택 예비입주자 모집공고(2026.9.7.)</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>20260908</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3532,32 +3528,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020601&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020710&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>D-15</t>
+          <t>D-14</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>칠곡군</t>
+          <t>남양주시</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>칠곡북삼휴먼시아 국민임대주택 예비입주자 모집(45형)</t>
+          <t>남양주마석2단지 국민임대주택 예비입주자 모집공고(2026.9.7.)</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3567,47 +3563,47 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
           <t>20261001</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>20261001</t>
-        </is>
-      </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020719&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020668&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>D-15</t>
+          <t>D-14</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>울산</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>울주군</t>
+          <t>김해시</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>울산광역시 국민임대주택 예비입주자 정례모집 공고(2026.09.15.)</t>
+          <t>[경남지역본부] 일반 매입임대주택 입주자 모집 공고(김해시, 밀양시)</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -3622,32 +3618,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020745&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020706&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>D-15</t>
+          <t>D-14</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>괴산군</t>
+          <t>김해시</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>괴산군지역 국민임대주택 예비입주자 모집 공고[2026.09.15]</t>
+          <t>김해진영6단지 국민임대주택 예비입주자 모집(‘26.09.15. 공고)</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3657,42 +3653,42 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
           <t>20261001</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>20261001</t>
-        </is>
-      </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020683&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020716&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>D-15</t>
+          <t>D-14</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>음성군</t>
+          <t>남해군</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>음성신천 국민임대주택 예비입주자 모집 공고[2026.09.15]</t>
+          <t>남해평리휴먼시아 국민임대주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -3712,105 +3708,105 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020684&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020757&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>D-15</t>
+          <t>D-14</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>청주시 서원구</t>
+          <t>경주시</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>청주가경4 국민임대주택 예비입주자 모집 공고[2026.09.15]</t>
+          <t>[경북 포항,경주,영천] 일반 매입임대 입주자 모집공고</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
+          <t>20260908</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
           <t>20261001</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>20261001</t>
-        </is>
-      </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020752&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020654&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H75" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>D-15</t>
+          <t>D-14</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>원주시</t>
+          <t>영천시</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>원주문막1 국민임대주택 예비입주자 모집</t>
+          <t>[경북 포항,경주,영천] 일반 매입임대 입주자 모집공고</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20260908</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020738&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020601&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H76" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>D-16</t>
+          <t>D-14</t>
         </is>
       </c>
     </row>
@@ -3822,17 +3818,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>김천시</t>
+          <t>구미시</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>김천부곡2 영구임대주택 예비입주자 모집</t>
+          <t>경북서부지역(구미시, 김천시, 의성군) 국민임대 예비입주자 모집</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -3842,82 +3838,82 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020680&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020709&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>D-16</t>
+          <t>D-14</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>청주시 서원구</t>
+          <t>칠곡군</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>청주산남2-1 영구임대주택 예비입주자 모집 공고(2026.08.28)</t>
+          <t>칠곡북삼휴먼시아 국민임대주택 예비입주자 모집(45형)</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020625&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020786&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H78" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>D-16</t>
+          <t>D-14</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>원주시</t>
+          <t>칠곡군</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>원주태장4 국민임대주택 예비입주자 모집공고(2026.09.15)</t>
+          <t>칠곡북삼휴먼시아 국민임대주택 예비입주자 모집(45형)</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -3927,87 +3923,87 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020740&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020719&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H79" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>D-21</t>
+          <t>D-14</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>울산</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>전주시 완산구</t>
+          <t>울주군</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>전주동서학 통합공공임대(일자리연계형 지원주택) 최초 입주자 모집</t>
+          <t>울산광역시 국민임대주택 예비입주자 정례모집 공고(2026.09.15.)</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>통합공공임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
+          <t>20260929</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
           <t>20261001</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>20261008</t>
-        </is>
-      </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020742&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=48&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020745&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H80" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>D-22</t>
+          <t>D-14</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>아산시</t>
+          <t>괴산군</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>아산탕정2 국민임대주택 예비입주자 모집공고(2026.09.15)</t>
+          <t>괴산군지역 국민임대주택 예비입주자 모집 공고[2026.09.15]</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4017,87 +4013,87 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020726&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020683&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H81" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>D-28</t>
+          <t>D-14</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>당진시</t>
+          <t>음성군</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>[청년신혼부부매입임대리츠주택] 충남당진 송산청광플러스원 입주자격완화 상시모집</t>
+          <t>음성신천 국민임대주택 예비입주자 모집 공고[2026.09.15]</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>20260810</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020529&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020684&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H82" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>D-29</t>
+          <t>D-14</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>태백시</t>
+          <t>청주시 서원구</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>태백철암1 국민임대주택 예비입주자 모집 공고</t>
+          <t>청주가경4 국민임대주택 예비입주자 모집 공고[2026.09.15]</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4107,42 +4103,42 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>20261028</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020735&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020752&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H83" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>D-42</t>
+          <t>D-14</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>양산시</t>
+          <t>원주시</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>양산 사송A-4BL 국민임대주택(29A형)선착순 동호지정 모집(입주자격완화, 선계약 후검증)</t>
+          <t>원주문막1 국민임대주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4152,42 +4148,42 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>20260813</t>
+          <t>20261002</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>20261029</t>
+          <t>20261002</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020495&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020738&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H84" t="n">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>D-43</t>
+          <t>D-15</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>군산시</t>
+          <t>김천시</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>군산신역세권A3(내흥3) 영구임대주택 입주자 추가모집</t>
+          <t>김천부곡2 영구임대주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4197,222 +4193,222 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>20261030</t>
+          <t>20261002</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019841&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020680&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H85" t="n">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>D-44</t>
+          <t>D-15</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>칠곡군</t>
+          <t>완주군</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2026년 칠곡군 천원주택(신혼·신생아 매입임대주택Ⅰ) 예비입주자 모집 공고</t>
+          <t>전주시, 완주군 국민임대주택 예비입주자 모집 공고(‘26.9.15.)</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>20260728</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>20261130</t>
+          <t>20261002</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=e54448a5-4c8c-4c3d-bfcf-bc465f677408&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020733&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H86" t="n">
-        <v>75</v>
+        <v>15</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>D-75</t>
+          <t>D-15</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>칠곡군</t>
+          <t>청주시 서원구</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2026년 칠곡군 천원주택(청년 매입임대주택) 입주자 및 예비입주자 모집 공고</t>
+          <t>청주산남2-1 영구임대주택 예비입주자 모집 공고(2026.08.28)</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>20260728</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>20261130</t>
+          <t>20261002</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=2e8989e9-02ae-48be-9591-f3c4c8e7fa39&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020625&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H87" t="n">
-        <v>75</v>
+        <v>15</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>D-75</t>
+          <t>D-15</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>포항시 남구</t>
+          <t>원주시</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>포항블루밸리 행복주택 선착순 동호지정 상시모집(입주자격 완화, 통합공임 일반계층 추가, 선계약 후검증)</t>
+          <t>원주태장4 국민임대주택 예비입주자 모집공고(2026.09.15)</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>20260707</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>20261222</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020042&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020740&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H88" t="n">
-        <v>97</v>
+        <v>20</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>D-97</t>
+          <t>D-20</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>삼척시</t>
+          <t>전주시 완산구</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>삼척시·정선군 국민임대 예비입주자 상시모집(26.6.10)</t>
+          <t>전주동서학 통합공공임대(일자리연계형 지원주택) 최초 입주자 모집</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>통합공공임대</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>20260624</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>20261230</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020090&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020742&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=48&amp;mi=1026</t>
         </is>
       </c>
       <c r="H89" t="n">
-        <v>105</v>
+        <v>21</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>D-105</t>
+          <t>D-21</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>태백시</t>
+          <t>고령군</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>태백장성 국민임대주택 예비입주자 입주자격완화 상시모집</t>
+          <t>대구서부권 고령다산2 국민임대 입주자격완화 모집공고</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -4422,107 +4418,115 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>20261230</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020730&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020746&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H90" t="n">
-        <v>105</v>
+        <v>27</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>D-105</t>
+          <t>D-27</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>강원</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr"/>
+          <t>충남</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>아산시</t>
+        </is>
+      </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>아산탕정2 국민임대주택 예비입주자 모집공고(2026.09.15)</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020726&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H91" t="n">
-        <v>106</v>
+        <v>27</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>D-106</t>
+          <t>D-27</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>강원</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr"/>
+          <t>충남</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>당진시</t>
+        </is>
+      </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>[청년신혼부부매입임대리츠주택] 충남당진 송산청광플러스원 입주자격완화 상시모집</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260810</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020529&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H92" t="n">
-        <v>106</v>
+        <v>28</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>D-106</t>
+          <t>D-28</t>
         </is>
       </c>
     </row>
@@ -4532,350 +4536,370 @@
           <t>강원</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr"/>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>태백시</t>
+        </is>
+      </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>태백철암1 국민임대주택 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261028</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020735&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H93" t="n">
-        <v>106</v>
+        <v>41</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>D-106</t>
+          <t>D-41</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>강원</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr"/>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>양산시</t>
+        </is>
+      </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>양산 사송A-4BL 국민임대주택(29A형)선착순 동호지정 모집(입주자격완화, 선계약 후검증)</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260813</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261029</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020495&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H94" t="n">
-        <v>106</v>
+        <v>42</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>D-106</t>
+          <t>D-42</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>동해시</t>
+          <t>군산시</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>동해유성,태백철암장미 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
+          <t>군산신역세권A3(내흥3) 영구임대주택 입주자 추가모집</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>20260212</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261030</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019312&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019841&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H95" t="n">
-        <v>106</v>
+        <v>43</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>D-106</t>
+          <t>D-43</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>동해시</t>
+          <t>칠곡군</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>동해유성,태백철암장미 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
+          <t>2026년 칠곡군 천원주택(신혼·신생아 매입임대주택Ⅰ) 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>20260212</t>
+          <t>20260728</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261130</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019308&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=e54448a5-4c8c-4c3d-bfcf-bc465f677408&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
         </is>
       </c>
       <c r="H96" t="n">
-        <v>106</v>
+        <v>74</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>D-106</t>
+          <t>D-74</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>태백시</t>
+          <t>칠곡군</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>태백궁전 국민임대 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
+          <t>2026년 칠곡군 천원주택(청년 매입임대주택) 입주자 및 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>20260212</t>
+          <t>20260728</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261130</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019307&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=2e8989e9-02ae-48be-9591-f3c4c8e7fa39&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
         </is>
       </c>
       <c r="H97" t="n">
-        <v>106</v>
+        <v>74</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>D-106</t>
+          <t>D-74</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>경기</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr"/>
+          <t>경북</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>포항시 남구</t>
+        </is>
+      </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>포항블루밸리 행복주택 선착순 동호지정 상시모집(입주자격 완화, 통합공임 일반계층 추가, 선계약 후검증)</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260707</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261222</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020042&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H98" t="n">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>D-106</t>
+          <t>D-96</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>경기</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr"/>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>삼척시</t>
+        </is>
+      </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>삼척시·정선군 국민임대 예비입주자 상시모집(26.6.10)</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260624</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261230</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020090&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H99" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>D-106</t>
+          <t>D-104</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>경기</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr"/>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>태백시</t>
+        </is>
+      </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>태백장성 국민임대주택 예비입주자 입주자격완화 상시모집</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261230</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020730&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H100" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>D-106</t>
+          <t>D-104</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -4885,7 +4909,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -4895,28 +4919,28 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H101" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>D-106</t>
+          <t>D-105</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -4936,28 +4960,28 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H102" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>D-106</t>
+          <t>D-105</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -4977,28 +5001,28 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H103" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>D-106</t>
+          <t>D-105</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -5008,7 +5032,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -5018,38 +5042,42 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H104" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>D-106</t>
+          <t>D-105</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr"/>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>동해시</t>
+        </is>
+      </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>동해유성,태백철암장미 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260212</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -5059,38 +5087,42 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019312&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H105" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>D-106</t>
+          <t>D-105</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>경북</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr"/>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>동해시</t>
+        </is>
+      </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>동해유성,태백철암장미 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260212</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -5100,38 +5132,42 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019308&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H106" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>D-106</t>
+          <t>D-105</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>경북</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr"/>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>태백시</t>
+        </is>
+      </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>태백궁전 국민임대 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260212</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -5141,28 +5177,28 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019307&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H107" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>D-106</t>
+          <t>D-105</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -5182,28 +5218,28 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H108" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>D-106</t>
+          <t>D-105</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -5213,7 +5249,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -5223,28 +5259,28 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H109" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>D-106</t>
+          <t>D-105</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B110" t="inlineStr"/>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -5264,28 +5300,28 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H110" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>D-106</t>
+          <t>D-105</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -5295,7 +5331,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -5305,28 +5341,28 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H111" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>D-106</t>
+          <t>D-105</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -5346,28 +5382,28 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H112" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>D-106</t>
+          <t>D-105</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -5377,7 +5413,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -5387,28 +5423,28 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H113" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>D-106</t>
+          <t>D-105</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>대전</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B114" t="inlineStr"/>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -5428,28 +5464,28 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H114" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>D-106</t>
+          <t>D-105</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>대전</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B115" t="inlineStr"/>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -5459,7 +5495,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -5469,28 +5505,28 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H115" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>D-106</t>
+          <t>D-105</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>대전</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -5510,28 +5546,28 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H116" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>D-106</t>
+          <t>D-105</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>대전</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -5541,7 +5577,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -5551,28 +5587,28 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H117" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>D-106</t>
+          <t>D-105</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -5592,28 +5628,28 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H118" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>D-106</t>
+          <t>D-105</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B119" t="inlineStr"/>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -5623,7 +5659,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -5633,28 +5669,28 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H119" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>D-106</t>
+          <t>D-105</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -5674,28 +5710,28 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H120" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>D-106</t>
+          <t>D-105</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -5705,7 +5741,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -5715,28 +5751,28 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H121" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>D-106</t>
+          <t>D-105</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B122" t="inlineStr"/>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -5756,28 +5792,28 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H122" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>D-106</t>
+          <t>D-105</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B123" t="inlineStr"/>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -5787,7 +5823,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -5797,28 +5833,28 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H123" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>D-106</t>
+          <t>D-105</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>대전</t>
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -5838,28 +5874,28 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H124" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>D-106</t>
+          <t>D-105</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>대전</t>
         </is>
       </c>
       <c r="B125" t="inlineStr"/>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -5869,7 +5905,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -5879,28 +5915,28 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H125" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>D-106</t>
+          <t>D-105</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>세종</t>
+          <t>대전</t>
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -5920,28 +5956,28 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H126" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>D-106</t>
+          <t>D-105</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>세종</t>
+          <t>대전</t>
         </is>
       </c>
       <c r="B127" t="inlineStr"/>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -5951,7 +5987,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -5961,28 +5997,28 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H127" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>D-106</t>
+          <t>D-105</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>세종</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B128" t="inlineStr"/>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -6002,28 +6038,28 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H128" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>D-106</t>
+          <t>D-105</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>세종</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B129" t="inlineStr"/>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -6033,7 +6069,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -6043,28 +6079,28 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H129" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>D-106</t>
+          <t>D-105</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>울산</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B130" t="inlineStr"/>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -6084,28 +6120,28 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H130" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>D-106</t>
+          <t>D-105</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>울산</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B131" t="inlineStr"/>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -6115,7 +6151,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -6125,28 +6161,28 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H131" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>D-106</t>
+          <t>D-105</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>울산</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B132" t="inlineStr"/>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -6166,28 +6202,28 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H132" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>D-106</t>
+          <t>D-105</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>울산</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B133" t="inlineStr"/>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -6197,7 +6233,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -6207,28 +6243,28 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H133" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>D-106</t>
+          <t>D-105</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B134" t="inlineStr"/>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -6248,28 +6284,28 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H134" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>D-106</t>
+          <t>D-105</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -6279,7 +6315,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -6289,28 +6325,28 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H135" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>D-106</t>
+          <t>D-105</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>세종</t>
         </is>
       </c>
       <c r="B136" t="inlineStr"/>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -6330,28 +6366,28 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H136" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>D-106</t>
+          <t>D-105</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>세종</t>
         </is>
       </c>
       <c r="B137" t="inlineStr"/>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -6361,7 +6397,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -6371,28 +6407,28 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H137" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>D-106</t>
+          <t>D-105</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>세종</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -6412,28 +6448,28 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H138" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>D-106</t>
+          <t>D-105</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>세종</t>
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -6443,7 +6479,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -6453,28 +6489,28 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H139" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>D-106</t>
+          <t>D-105</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>울산</t>
         </is>
       </c>
       <c r="B140" t="inlineStr"/>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -6494,28 +6530,28 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H140" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>D-106</t>
+          <t>D-105</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>울산</t>
         </is>
       </c>
       <c r="B141" t="inlineStr"/>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -6525,7 +6561,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -6535,42 +6571,38 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H141" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>D-106</t>
+          <t>D-105</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>전북</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>김제시</t>
-        </is>
-      </c>
+          <t>울산</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr"/>
       <c r="C142" t="inlineStr">
         <is>
-          <t>김제검산1단지 영구임대주택 예비입주자 모집 공고(상시모집)</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>20260101</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -6580,42 +6612,38 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019412&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H142" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>D-106</t>
+          <t>D-105</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>전북</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>남원시</t>
-        </is>
-      </c>
+          <t>울산</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr"/>
       <c r="C143" t="inlineStr">
         <is>
-          <t>남원노암 공공임대 50년 예비입주자 모집</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>50년임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -6625,42 +6653,38 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020623&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H143" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>D-106</t>
+          <t>D-105</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>전북</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>남원시</t>
-        </is>
-      </c>
+          <t>인천</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr"/>
       <c r="C144" t="inlineStr">
         <is>
-          <t>남원노암단지 영구임대주택 입주자격완화 예비입주자 모집공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -6670,42 +6694,38 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020649&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H144" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>D-106</t>
+          <t>D-105</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>전북</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>전주시 완산구</t>
-        </is>
-      </c>
+          <t>인천</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr"/>
       <c r="C145" t="inlineStr">
         <is>
-          <t>전주시(전주평화1,전주평화4) 영구임대주택 예비입주자 모집 공고(공고일:2026.02.10.)</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>20260303</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -6715,28 +6735,28 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019241&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H145" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>D-106</t>
+          <t>D-105</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B146" t="inlineStr"/>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -6756,28 +6776,28 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H146" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>D-106</t>
+          <t>D-105</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B147" t="inlineStr"/>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -6787,7 +6807,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -6797,28 +6817,28 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H147" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>D-106</t>
+          <t>D-105</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B148" t="inlineStr"/>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -6838,28 +6858,28 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H148" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>D-106</t>
+          <t>D-105</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B149" t="inlineStr"/>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -6869,7 +6889,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -6879,28 +6899,28 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H149" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>D-106</t>
+          <t>D-105</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B150" t="inlineStr"/>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -6920,28 +6940,28 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H150" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>D-106</t>
+          <t>D-105</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B151" t="inlineStr"/>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -6951,7 +6971,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -6961,38 +6981,42 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H151" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>D-106</t>
+          <t>D-105</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>충남</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr"/>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>김제시</t>
+        </is>
+      </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>김제검산1단지 영구임대주택 예비입주자 모집 공고(상시모집)</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260101</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -7002,38 +7026,42 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019412&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H152" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>D-106</t>
+          <t>D-105</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>충남</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr"/>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>남원시</t>
+        </is>
+      </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>남원노암 공공임대 50년 예비입주자 모집</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>50년임대</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -7043,42 +7071,42 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020623&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H153" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>D-106</t>
+          <t>D-105</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>당진시</t>
+          <t>남원시</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>[청년신혼부부매입임대리츠주택] 충남당진 송산청광플러스원 입주자격완화 상시모집</t>
+          <t>남원노암단지 영구임대주택 입주자격완화 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>20260316</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -7088,38 +7116,42 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019433&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020649&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H154" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>D-106</t>
+          <t>D-105</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>충북</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr"/>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>전주시 완산구</t>
+        </is>
+      </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>전주시(전주평화1,전주평화4) 영구임대주택 예비입주자 모집 공고(공고일:2026.02.10.)</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260303</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -7129,28 +7161,28 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019241&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H155" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>D-106</t>
+          <t>D-105</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="B156" t="inlineStr"/>
       <c r="C156" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -7170,28 +7202,28 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H156" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>D-106</t>
+          <t>D-105</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="B157" t="inlineStr"/>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -7211,28 +7243,28 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H157" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>D-106</t>
+          <t>D-105</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="B158" t="inlineStr"/>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -7242,7 +7274,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -7252,195 +7284,609 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H158" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>D-106</t>
+          <t>D-105</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>강원</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>삼척시</t>
-        </is>
-      </c>
+          <t>제주</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr"/>
       <c r="C159" t="inlineStr">
         <is>
-          <t>삼척도계·정선신동 국민임대주택 예비입주자 입주자격완화 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>20270129</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020581&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H159" t="n">
-        <v>135</v>
+        <v>105</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>D-135</t>
+          <t>D-105</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>전북</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>군산시</t>
-        </is>
-      </c>
+          <t>충남</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr"/>
       <c r="C160" t="inlineStr">
         <is>
-          <t>군산시 국민임대주택 입주자 선착순 상시 모집(경암부향 등 7개 단지)</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>20260812</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>20270731</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020453&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H160" t="n">
-        <v>318</v>
+        <v>105</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>D-318</t>
+          <t>D-105</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>울산</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>울주군</t>
-        </is>
-      </c>
+          <t>충남</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr"/>
       <c r="C161" t="inlineStr">
         <is>
-          <t>울산광역시 국민임대주택 예비입주자 정례모집 공고(2025.09.15.)</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>20250929</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>20291001</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300018799&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H161" t="n">
-        <v>1111</v>
+        <v>105</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>D-1111</t>
+          <t>D-105</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
+          <t>충남</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr"/>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H162" t="n">
+        <v>105</v>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>D-105</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>충남</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr"/>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>20260224</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H163" t="n">
+        <v>105</v>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>D-105</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>충남</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>당진시</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>[청년신혼부부매입임대리츠주택] 충남당진 송산청광플러스원 입주자격완화 상시모집</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>매입임대</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>20260316</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019433&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H164" t="n">
+        <v>105</v>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>D-105</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>충북</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr"/>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H165" t="n">
+        <v>105</v>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>D-105</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>충북</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr"/>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H166" t="n">
+        <v>105</v>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>D-105</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>충북</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr"/>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H167" t="n">
+        <v>105</v>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>D-105</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>충북</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr"/>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>20260224</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H168" t="n">
+        <v>105</v>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>D-105</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>삼척시</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>삼척도계·정선신동 국민임대주택 예비입주자 입주자격완화 공고</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>국민임대</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>20270129</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020581&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H169" t="n">
+        <v>134</v>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>D-134</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>군산시</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>군산시 국민임대주택 입주자 선착순 상시 모집(경암부향 등 7개 단지)</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>국민임대</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>20260812</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>20270731</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020453&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H170" t="n">
+        <v>317</v>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>D-317</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
           <t>울산</t>
         </is>
       </c>
-      <c r="B162" t="inlineStr">
+      <c r="B171" t="inlineStr">
         <is>
           <t>울주군</t>
         </is>
       </c>
-      <c r="C162" t="inlineStr">
+      <c r="C171" t="inlineStr">
         <is>
           <t>울산광역시 국민임대주택 예비입주자 정례모집 공고(2025.09.15.)</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr">
+      <c r="D171" t="inlineStr">
         <is>
           <t>국민임대</t>
         </is>
       </c>
-      <c r="E162" t="inlineStr">
+      <c r="E171" t="inlineStr">
         <is>
           <t>20250929</t>
         </is>
       </c>
-      <c r="F162" t="inlineStr">
+      <c r="F171" t="inlineStr">
         <is>
           <t>20291001</t>
         </is>
       </c>
-      <c r="G162" t="inlineStr">
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300018799&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H171" t="n">
+        <v>1110</v>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>D-1110</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>울산</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>울주군</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>울산광역시 국민임대주택 예비입주자 정례모집 공고(2025.09.15.)</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>국민임대</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>20250929</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>20291001</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
         <is>
           <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300018780&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
-      <c r="H162" t="n">
-        <v>1111</v>
-      </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>D-1111</t>
+      <c r="H172" t="n">
+        <v>1110</v>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>D-1110</t>
         </is>
       </c>
     </row>

--- a/housing_notices.xlsx
+++ b/housing_notices.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I172"/>
+  <dimension ref="A1:I189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,22 +466,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>군산시</t>
+          <t>부천시 원미구</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>군산시 국민임대주택 예비입주자 모집 공고(26.09.03)</t>
+          <t>부천시 영구임대주택 예비입주자 모집 (중동한라1, 중동덕유1)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -491,12 +491,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>20260917</t>
+          <t>20260918</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020663&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020678&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -511,37 +511,37 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>김제시</t>
+          <t>안산시 단원구</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>김제하동 국민임대주택 모집공고</t>
+          <t>안산 선부동 행복주택 예비입주자(주거급여)모집 공고</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260903</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>20260917</t>
+          <t>20260918</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020701&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://www.ansanuc.net/homenew/12286/20328/bbsList.do</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -556,37 +556,37 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>서산시</t>
+          <t>서귀포시</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>서산석림3단지 50년공공임대주택 예비입주자 모집공고(2026.09.01.)</t>
+          <t>[제주지역본부] 다자녀 매입임대주택 예비입주자 모집 공고(서귀포시)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>50년임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>20260917</t>
+          <t>20260918</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020657&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020691&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -604,42 +604,38 @@
           <t>경기</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>부천시 원미구</t>
-        </is>
-      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>부천시 영구임대주택 예비입주자 모집 (중동한라1, 중동덕유1)</t>
+          <t>[경기남부] 용인시 신혼·신생아 매입임대주택Ⅱ(전세형) 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>20260916</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020678&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020702&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
@@ -649,59 +645,55 @@
           <t>경기</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>안산시 단원구</t>
-        </is>
-      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>안산 선부동 행복주택 예비입주자(주거급여)모집 공고</t>
+          <t>[경기남부] 용인시 청년 매입임대주택 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>20260903</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.ansanuc.net/homenew/12286/20328/bbsList.do</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020699&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>서귀포시</t>
+          <t>평택시</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>[제주지역본부] 다자녀 매입임대주택 예비입주자 모집 공고(서귀포시)</t>
+          <t>[경기남부] 화성시·평택시 신혼·신생아 매입임대주택Ⅱ(전세형) 예비입주자 [후순번] 모집공고</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -716,43 +708,47 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020691&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020703&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>경기</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
+          <t>경북</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>포항시 북구</t>
+        </is>
+      </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>[경기남부] 용인시 신혼·신생아 매입임대주택Ⅱ(전세형) 예비입주자 모집공고</t>
+          <t>포항창포 영구임대아파트 예비입주자 모집</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>20260917</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -762,38 +758,42 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020702&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020651&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>D-4</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>경기</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
+          <t>경북</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>포항시 북구</t>
+        </is>
+      </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>[경기남부] 용인시 청년 매입임대주택 예비입주자 모집공고</t>
+          <t>포항학산 영구임대아파트 예비입주자 모집</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>20260917</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -803,15 +803,15 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020699&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020650&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>D-4</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
@@ -821,30 +821,34 @@
           <t>경기</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>부천시 오정구</t>
+        </is>
+      </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>[경기남부] 화성시·평택시 신혼·신생아 매입임대주택Ⅱ(전세형) 예비입주자 [후순번] 모집공고</t>
+          <t>2026년 9월 부천시 국민임대주택 예비입주자 모집 공고(2026.09.07)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>20260917</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260922</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020703&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020652&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -859,37 +863,33 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>경북</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>포항시 북구</t>
-        </is>
-      </c>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>포항창포 영구임대아파트 예비입주자 모집</t>
+          <t>26-4차 인천본부 든든전세주택 입주자 모집공고(인천, 부천)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260922</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020651&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020725&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -904,37 +904,33 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>경북</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>포항시 북구</t>
-        </is>
-      </c>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>포항학산 영구임대아파트 예비입주자 모집</t>
+          <t>26-4차 인천본부 든든전세주택 입주자 모집공고(인천, 부천)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260922</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020650&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020715&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -949,17 +945,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>부천시 오정구</t>
+          <t>경주시</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026년 9월 부천시 국민임대주택 예비입주자 모집 공고(2026.09.07)</t>
+          <t>경주시, 영천시, 포항시 부도매입(국민임대)주택 입주자격완화 모집공고</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -969,7 +965,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -979,25 +975,29 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020652&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020635&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-4</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>경기</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
+          <t>인천</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>미추홀구</t>
+        </is>
+      </c>
       <c r="C14" t="inlineStr">
         <is>
           <t>26-4차 인천본부 든든전세주택 입주자 모집공고(인천, 부천)</t>
@@ -1024,21 +1024,25 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-4</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>경기</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
+          <t>인천</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>부평구</t>
+        </is>
+      </c>
       <c r="C15" t="inlineStr">
         <is>
           <t>26-4차 인천본부 든든전세주택 입주자 모집공고(인천, 부천)</t>
@@ -1065,28 +1069,28 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-4</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>경주시</t>
+          <t>남동구</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>경주시, 영천시, 포항시 부도매입(국민임대)주택 입주자격완화 모집공고</t>
+          <t>26년 9월 인천시 남동구 국민임대주택 예비입주자 모집 공고(2026.09.07)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1096,7 +1100,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1106,15 +1110,15 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020635&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020619&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-4</t>
         </is>
       </c>
     </row>
@@ -1126,17 +1130,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>서해구</t>
+          <t>옹진군</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>26-4차 인천본부 든든전세주택 입주자 모집공고(인천, 부천)</t>
+          <t>인천옹진백령 국민임대주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1151,15 +1155,15 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020725&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020578&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-4</t>
         </is>
       </c>
     </row>
@@ -1171,22 +1175,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>미추홀구</t>
+          <t>옹진군</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>26-4차 인천본부 든든전세주택 입주자 모집공고(인천, 부천)</t>
+          <t>인천옹진연평 국민임대주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260922</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1196,37 +1200,37 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020715&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020697&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-4</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>남동구</t>
+          <t>횡성군</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>26년 9월 인천시 남동구 국민임대주택 예비입주자 모집 공고(2026.09.07)</t>
+          <t>강원횡성 통합공공임대주택 입주자 모집</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>통합공공임대</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1236,12 +1240,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>20260922</t>
+          <t>20260923</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020619&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020627&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=48&amp;mi=1026</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -1256,22 +1260,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>옹진군</t>
+          <t>안성시</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>인천옹진백령 국민임대주택 예비입주자 모집</t>
+          <t>[온라인 접수 불가, 관할 주거복지지사 현장접수] 경기남부지역본부 2026년 일반 매입임대주택 입주자 모집공고</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1281,12 +1285,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>20260922</t>
+          <t>20260923</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020578&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020769&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -1301,37 +1305,33 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>인천</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>옹진군</t>
-        </is>
-      </c>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>인천옹진연평 국민임대주택 예비입주자 모집</t>
+          <t>[온라인 접수 불가, 관할 주거복지지사 현장접수] 경기남부지역본부 2026년 일반 매입임대주택 입주자 모집공고</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>20260922</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>20260922</t>
+          <t>20260923</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020697&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020731&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -1346,22 +1346,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>횡성군</t>
+          <t>김포시</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>강원횡성 통합공공임대주택 입주자 모집</t>
+          <t>김포시 국민임대주택 예비입주자 모집(2026.09.07)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>통합공공임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1376,15 +1376,15 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020627&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=48&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020659&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
@@ -1396,17 +1396,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>안성시</t>
+          <t>화성시 효행구</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>[온라인 접수 불가, 관할 주거복지지사 현장접수] 경기남부지역본부 2026년 일반 매입임대주택 입주자 모집공고</t>
+          <t>화성서부권 국민임대주택 예비입주자 모집[입주자격완화]</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1421,28 +1421,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020769&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020686&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>경기</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>양산시</t>
+        </is>
+      </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>[온라인 접수 불가, 관할 주거복지지사 현장접수] 경기남부지역본부 2026년 일반 매입임대주택 입주자 모집공고</t>
+          <t>[경남지역본부]26년 3차 분양전환형 든든전세주택 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1462,37 +1466,37 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020731&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020721&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>김포시</t>
+          <t>김해시</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>김포시 국민임대주택 예비입주자 모집(2026.09.07)</t>
+          <t>[경남지역본부]26년 3차 비분양전환형 든든전세주택 입주자 모집 공고</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1507,37 +1511,33 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020659&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020720&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>경기</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>화성시 효행구</t>
-        </is>
-      </c>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
-          <t>화성서부권 국민임대주택 예비입주자 모집[입주자격완화]</t>
+          <t>[경남지역본부]26년 3차 신혼·신생아매입임대Ⅰ 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1552,15 +1552,15 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020686&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020722&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
@@ -1577,7 +1577,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>[경남지역본부]26년 3차 분양전환형 든든전세주택 예비입주자 모집 공고</t>
+          <t>[경남지역본부]26년 3차 신혼·신생아매입임대Ⅱ(전세형) 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1597,15 +1597,15 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020721&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020723&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
@@ -1617,12 +1617,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>김해시</t>
+          <t>진주시</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>[경남지역본부]26년 3차 비분양전환형 든든전세주택 입주자 모집 공고</t>
+          <t>[경남지역본부]26년 3차 청년매입임대 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1642,15 +1642,15 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020720&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020717&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
@@ -1660,10 +1660,14 @@
           <t>경남</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>함양군</t>
+        </is>
+      </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>[경남지역본부]26년 3차 신혼·신생아매입임대Ⅰ 예비입주자 모집공고</t>
+          <t>경남 함양군 서하면 다자녀 매입임대주택 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1673,7 +1677,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1683,37 +1687,37 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020722&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020711&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>양산시</t>
+          <t>달서구</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>[경남지역본부]26년 3차 신혼·신생아매입임대Ⅱ(전세형) 예비입주자 모집공고</t>
+          <t>대구죽전 행복주택(산업단지형) 예비 입주자 모집</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1728,37 +1732,37 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020723&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020763&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>진주시</t>
+          <t>달서구</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>[경남지역본부]26년 3차 청년매입임대 예비입주자 모집공고</t>
+          <t>대구죽전 행복주택(산업단지형) 예비 입주자 모집</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1773,42 +1777,42 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020717&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020760&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>함양군</t>
+          <t>달서구</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>경남 함양군 서하면 다자녀 매입임대주택 예비입주자 모집공고</t>
+          <t>대구죽전 행복주택(산업단지형) 예비 입주자 모집</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1818,32 +1822,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020711&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020751&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>달서구</t>
+          <t>김제시</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>대구죽전 행복주택(산업단지형) 예비 입주자 모집</t>
+          <t>(26.9.10)김제대검산, 정읍시기, 정읍첨단 행복주택 입주자격완화 예비자 모집 공고(소득·총자산요건 배제 및 무주택요건 완화)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1863,42 +1867,42 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020763&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020344&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>달서구</t>
+          <t>익산시</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>대구죽전 행복주택(산업단지형) 예비 입주자 모집</t>
+          <t>익산한스빌 국민임대주택 예비입주자 자격완화 모집 공고</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260922</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1908,122 +1912,122 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020760&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020694&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>달서구</t>
+          <t>칠곡군</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>대구죽전 행복주택(산업단지형) 예비 입주자 모집</t>
+          <t>칠곡왜관4 국민임대아파트 예비입주자 모집(51형)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>20260923</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020751&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020696&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>김제시</t>
+          <t>양산시</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>(26.9.10)김제대검산, 정읍시기, 정읍첨단 행복주택 입주자격완화 예비자 모집 공고(소득·총자산요건 배제 및 무주택요건 완화)</t>
+          <t>[양산시지역]양산대석휴먼시아 국민임대주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>20260923</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020344&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020754&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-11</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>익산시</t>
+          <t>양산시</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>익산한스빌 국민임대주택 예비입주자 자격완화 모집 공고</t>
+          <t>양산시 국민임대주택 예비입주자 완화 모집(‘26.09.15)_소득, 자산, 무주택 요건 완화 / 계약금 인하</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2033,42 +2037,42 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>20260922</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>20260923</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020694&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020796&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-11</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>칠곡군</t>
+          <t>양산시</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>칠곡왜관4 국민임대아파트 예비입주자 모집(51형)</t>
+          <t>양산시 국민임대주택 예비입주자 완화 모집(‘26.09.15)_소득, 자산, 무주택 요건 완화 / 계약금 인하</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2083,12 +2087,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020696&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020794&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H38" t="n">
@@ -2113,7 +2117,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>[양산시지역]양산대석휴먼시아 국민임대주택 예비입주자 모집</t>
+          <t>양산시 국민임대주택 예비입주자 완화 모집(‘26.09.15)_소득, 자산, 무주택 요건 완화 / 계약금 인하</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2123,25 +2127,25 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
+          <t>20260928</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
           <t>20260929</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>20260929</t>
-        </is>
-      </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020754&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020732&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-11</t>
         </is>
       </c>
     </row>
@@ -2153,12 +2157,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>양산시</t>
+          <t>창녕군</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>양산시 국민임대주택 예비입주자 완화 모집(‘26.09.15)_소득, 자산, 무주택 요건 완화 / 계약금 인하</t>
+          <t>창녕창녕 국민임대주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2168,7 +2172,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2178,42 +2182,42 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020796&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020724&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-11</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>양산시</t>
+          <t>경산시</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>양산시 국민임대주택 예비입주자 완화 모집(‘26.09.15)_소득, 자산, 무주택 요건 완화 / 계약금 인하</t>
+          <t>경산백천1단지 50년 공공임대주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>50년임대</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2223,37 +2227,37 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020794&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020728&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-11</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>양산시</t>
+          <t>경산시</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>양산시 국민임대주택 예비입주자 완화 모집(‘26.09.15)_소득, 자산, 무주택 요건 완화 / 계약금 인하</t>
+          <t>대구혁신10, 경산하양3 행복주택 입주자격완화 선계약 후검증 동호지정 입주자 모집</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2268,82 +2272,82 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020732&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020682&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-11</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>창녕군</t>
+          <t>동구</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>창녕창녕 국민임대주택 예비입주자 모집</t>
+          <t>대구혁신10, 경산하양3 행복주택 입주자격완화 선계약 후검증 동호지정 입주자 모집</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
+          <t>20260928</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
           <t>20260929</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>20260929</t>
-        </is>
-      </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020724&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020682&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-11</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>경산시</t>
+          <t>기장군</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>경산백천1단지 50년 공공임대주택 예비입주자 모집</t>
+          <t>부산광역시 국민임대주택 예비입주자 정례모집 공고(2026.09.15.)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>50년임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2358,42 +2362,42 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020728&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020788&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-11</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>경산시</t>
+          <t>기장군</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>대구혁신10, 경산하양3 행복주택 입주자격완화 선계약 후검증 동호지정 입주자 모집</t>
+          <t>부산광역시 국민임대주택 예비입주자 정례모집 공고(2026.09.15.)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2403,37 +2407,37 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020682&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020758&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-11</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>동구</t>
+          <t>기장군</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>대구혁신10, 경산하양3 행복주택 입주자격완화 선계약 후검증 동호지정 입주자 모집</t>
+          <t>부산광역시 기장군 정관7국민임대 소득완화 모집공고</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2448,32 +2452,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020682&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020655&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-11</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>기장군</t>
+          <t>군산시</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>부산광역시 국민임대주택 예비입주자 정례모집 공고(2026.09.15.)</t>
+          <t>군산구암 국민임대주택 예비입주자 모집 공고(‘26.9.15.)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2493,32 +2497,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020788&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020743&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-11</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>기장군</t>
+          <t>음성군</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>부산광역시 국민임대주택 예비입주자 정례모집 공고(2026.09.15.)</t>
+          <t>음성군 국민임대주택 예비입주자 모집(2026.09.15.)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2538,32 +2542,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020758&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020698&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-11</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>기장군</t>
+          <t>원주시</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관7국민임대 소득완화 모집공고</t>
+          <t>원주시지역 국민임대주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2573,17 +2577,17 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020655&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020783&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H49" t="n">
@@ -2598,17 +2602,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>군산시</t>
+          <t>원주시</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>군산구암 국민임대주택 예비입주자 모집 공고(‘26.9.15.)</t>
+          <t>원주시지역 국민임대주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2623,12 +2627,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020743&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020767&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H50" t="n">
@@ -2643,17 +2647,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>음성군</t>
+          <t>원주시</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>음성군 국민임대주택 예비입주자 모집(2026.09.15.)</t>
+          <t>원주시지역 국민임대주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2668,12 +2672,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020698&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020677&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H51" t="n">
@@ -2688,27 +2692,27 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>원주시</t>
+          <t>부천시 소사구</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>원주시지역 국민임대주택 예비입주자 모집</t>
+          <t>[인천]26년 7차 신혼·신생아Ⅰ 예비입주자 모집공고(인천,부천)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2718,42 +2722,42 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020783&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020795&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>D-13</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>원주시</t>
+          <t>부천시 원미구</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>원주시지역 국민임대주택 예비입주자 모집</t>
+          <t>[인천]26년 7차 신혼·신생아Ⅱ(전세형) 예비입주자 모집공고(인천,부천)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2763,42 +2767,42 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020767&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020797&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>D-13</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>원주시</t>
+          <t>부천시 오정구</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>원주시지역 국민임대주택 예비입주자 모집</t>
+          <t>[인천지역본부] 26년 7차 청년 매입임대주택 예비입주자 모집공고(인천,부천)</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2808,15 +2812,15 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020677&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020798&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>D-13</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
@@ -2857,11 +2861,11 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>D-13</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
@@ -2902,11 +2906,11 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>D-13</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
@@ -2947,11 +2951,11 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>D-13</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
@@ -2992,11 +2996,11 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>D-13</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
@@ -3033,32 +3037,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=0000061173&amp;ccrCnntSysDsCd=02&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=0000061177&amp;ccrCnntSysDsCd=02&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>D-13</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>북구</t>
+          <t>화성시 동탄구</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>부산만덕5 2블록 10년 분양전환공공임대주택(e편한세상 금정산) 예비입주자 모집공고</t>
+          <t>화성동탄2 10년 분양전환공공임대주택(리츠) 예비입주자모집공고(‘26.09)</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3078,37 +3082,37 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=0000061163&amp;ccrCnntSysDsCd=02&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=0000061173&amp;ccrCnntSysDsCd=02&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>D-13</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>남동구</t>
+          <t>진주시</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>‘26년 9월 인천시(남동구) 행복주택 입주자격완화 예비입주자 모집</t>
+          <t>2026년 진주정촌올리움 국민임대 예비입주자 1차 모집 공고</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3123,37 +3127,37 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020744&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://www.gndc.co.kr/boardview/boardview.do?seqId=0000006202&amp;BBS_ID=B491A490314446318099F9D828047900&amp;IPDS_IDX=F7054C80FACF4D22AD23CAD92547CE03&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>D-13</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>아산시</t>
+          <t>연제구</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>아산신창소화,아산인주 국민임대주택 예비입주자 모집공고(2026.09.15)</t>
+          <t>[부산]청년매입임대주택 예비입주자 모집 공고(복사)</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3168,87 +3172,87 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020726&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020790&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>D-13</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>천안시 동남구</t>
+          <t>사하구</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>천안병천신한 국민임대주택 예비입주자 모집공고(2026.09.15)</t>
+          <t>[부산울산]신혼부부Ⅰ 매입임대주택 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
+          <t>20260928</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
           <t>20260930</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>20260930</t>
-        </is>
-      </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020714&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020791&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>D-13</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>천안시 서북구</t>
+          <t>강서구</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>천안쌍용5-2 공임50년 예비입주자 모집공고(2026.09.16)</t>
+          <t>[부산울산]신혼부부Ⅱ(전세형) 매입임대주택 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>50년임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3258,212 +3262,212 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019790&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020789&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H64" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>D-13</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>홍성군</t>
+          <t>북구</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>홍성남장2 국민임대주택 예비입주자 모집공고(2026.09.15)</t>
+          <t>부산만덕5 2블록 10년 분양전환공공임대주택(e편한세상 금정산) 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>10년임대</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
+          <t>20260929</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
           <t>20260930</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>20260930</t>
-        </is>
-      </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020729&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=0000061163&amp;ccrCnntSysDsCd=02&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>D-13</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>원주시</t>
+          <t>송파구</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>원주무실1 국민임대주택 예비입주자 모집(26.09.15공고)</t>
+          <t>[서울지역본부] 26년 3차 신혼·신생아 매입임대Ⅰ 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020792&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020750&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>원주시</t>
+          <t>서초구</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>원주무실1 국민임대주택 예비입주자 모집(26.09.15공고)</t>
+          <t>[서울지역본부] 26년 3차 신혼·신생아매입임대주택Ⅱ(전세형) 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020739&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020749&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>춘천시</t>
+          <t>영등포구</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>춘천시, 홍천군지역 국민임대주택 예비입주자 모집</t>
+          <t>[서울지역본부] 26년 3차 청년 매입임대주택 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020741&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020759&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>울산</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>동두천시</t>
+          <t>남구</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>[경기북부] 2026년 하반기 일반 매입임대주택 입주자 모집공고</t>
+          <t>[부산울산]신혼부부Ⅱ(전세형) 매입임대주택 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3473,132 +3477,132 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020713&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020789&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>남양주시</t>
+          <t>제물포구</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>남양주마석2단지 국민임대주택 예비입주자 모집공고(2026.9.7.)</t>
+          <t>[인천]26년 7차 신혼·신생아Ⅰ 예비입주자 모집공고(인천,부천)</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
+          <t>20260928</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
           <t>20260930</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>20261001</t>
-        </is>
-      </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020710&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020795&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>남양주시</t>
+          <t>서해구</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>남양주마석2단지 국민임대주택 예비입주자 모집공고(2026.9.7.)</t>
+          <t>[인천]26년 7차 신혼·신생아Ⅱ(전세형) 예비입주자 모집공고(인천,부천)</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
+          <t>20260928</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
           <t>20260930</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>20261001</t>
-        </is>
-      </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020668&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020797&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>김해시</t>
+          <t>제물포구</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>[경남지역본부] 일반 매입임대주택 입주자 모집 공고(김해시, 밀양시)</t>
+          <t>[인천지역본부] 26년 7차 청년 매입임대주택 예비입주자 모집공고(인천,부천)</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3608,87 +3612,87 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020706&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020798&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>김해시</t>
+          <t>남동구</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>김해진영6단지 국민임대주택 예비입주자 모집(‘26.09.15. 공고)</t>
+          <t>‘26년 9월 인천시(남동구) 행복주택 입주자격완화 예비입주자 모집</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
+          <t>20260928</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
           <t>20260930</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>20261001</t>
-        </is>
-      </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020716&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020744&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>남해군</t>
+          <t>아산시</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>남해평리휴먼시아 국민임대주택 예비입주자 모집</t>
+          <t>아산신창소화,아산인주 국민임대주택 예비입주자 모집공고(2026.09.15)</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -3698,132 +3702,132 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020757&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020726&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>경주시</t>
+          <t>천안시 동남구</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>[경북 포항,경주,영천] 일반 매입임대 입주자 모집공고</t>
+          <t>천안병천신한 국민임대주택 예비입주자 모집공고(2026.09.15)</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>20260908</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020654&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020714&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H75" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>영천시</t>
+          <t>천안시 서북구</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>[경북 포항,경주,영천] 일반 매입임대 입주자 모집공고</t>
+          <t>천안쌍용5-2 공임50년 예비입주자 모집공고(2026.09.16)</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>50년임대</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>20260908</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020601&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019790&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H76" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>구미시</t>
+          <t>홍성군</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>경북서부지역(구미시, 김천시, 의성군) 국민임대 예비입주자 모집</t>
+          <t>홍성남장2 국민임대주택 예비입주자 모집공고(2026.09.15)</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -3833,177 +3837,177 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020709&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020729&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>칠곡군</t>
+          <t>청주시 흥덕구</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>칠곡북삼휴먼시아 국민임대주택 예비입주자 모집(45형)</t>
+          <t>[충북지역본부]신혼·신생아 매입임대주택Ⅰ 예비입주자 모집공고(260917)</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020786&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020776&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H78" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>칠곡군</t>
+          <t>청주시 상당구</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>칠곡북삼휴먼시아 국민임대주택 예비입주자 모집(45형)</t>
+          <t>[충북지역본부]신혼·신생아 매입임대주택Ⅱ(전세형) 예비입주자 모집공고(260917)</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020719&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020774&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H79" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>울산</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>울주군</t>
+          <t>청주시 상당구</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>울산광역시 국민임대주택 예비입주자 정례모집 공고(2026.09.15.)</t>
+          <t>[충북지역본부]청년 매입임대주택 예비입주자 모집 공고(260917)</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020745&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020778&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H80" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>괴산군</t>
+          <t>원주시</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>괴산군지역 국민임대주택 예비입주자 모집 공고[2026.09.15]</t>
+          <t>원주무실1 국민임대주택 예비입주자 모집(26.09.15공고)</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4023,32 +4027,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020683&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020792&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H81" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>D-13</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>음성군</t>
+          <t>원주시</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>음성신천 국민임대주택 예비입주자 모집 공고[2026.09.15]</t>
+          <t>원주무실1 국민임대주택 예비입주자 모집(26.09.15공고)</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4068,32 +4072,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020684&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020739&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H82" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>D-13</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>청주시 서원구</t>
+          <t>춘천시</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>청주가경4 국민임대주택 예비입주자 모집 공고[2026.09.15]</t>
+          <t>춘천시, 홍천군지역 국민임대주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4103,132 +4107,132 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
+          <t>20260929</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
           <t>20261001</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>20261001</t>
-        </is>
-      </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020752&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020741&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H83" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>D-13</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>원주시</t>
+          <t>동두천시</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>원주문막1 국민임대주택 예비입주자 모집</t>
+          <t>[경기북부] 2026년 하반기 일반 매입임대주택 입주자 모집공고</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020738&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020713&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H84" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>D-15</t>
+          <t>D-13</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>김천시</t>
+          <t>남양주시</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>김천부곡2 영구임대주택 예비입주자 모집</t>
+          <t>남양주마석2단지 국민임대주택 예비입주자 모집공고(2026.9.7.)</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020680&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020710&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H85" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>D-15</t>
+          <t>D-13</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>완주군</t>
+          <t>남양주시</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>전주시, 완주군 국민임대주택 예비입주자 모집 공고(‘26.9.15.)</t>
+          <t>남양주마석2단지 국민임대주택 예비입주자 모집공고(2026.9.7.)</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4238,87 +4242,87 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020733&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020668&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H86" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>D-15</t>
+          <t>D-13</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>청주시 서원구</t>
+          <t>김해시</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>청주산남2-1 영구임대주택 예비입주자 모집 공고(2026.08.28)</t>
+          <t>[경남지역본부] 일반 매입임대주택 입주자 모집 공고(김해시, 밀양시)</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020625&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020706&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H87" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>D-15</t>
+          <t>D-13</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>원주시</t>
+          <t>김해시</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>원주태장4 국민임대주택 예비입주자 모집공고(2026.09.15)</t>
+          <t>김해진영6단지 국민임대주택 예비입주자 모집(‘26.09.15. 공고)</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -4328,47 +4332,47 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020740&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020716&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H88" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>D-20</t>
+          <t>D-13</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>전주시 완산구</t>
+          <t>남해군</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>전주동서학 통합공공임대(일자리연계형 지원주택) 최초 입주자 모집</t>
+          <t>남해평리휴먼시아 국민임대주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>통합공공임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -4378,20 +4382,20 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020742&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=48&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020757&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H89" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>D-21</t>
+          <t>D-13</t>
         </is>
       </c>
     </row>
@@ -4403,147 +4407,147 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>고령군</t>
+          <t>경주시</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>대구서부권 고령다산2 국민임대 입주자격완화 모집공고</t>
+          <t>[경북 포항,경주,영천] 일반 매입임대 입주자 모집공고</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20260908</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020746&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020654&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H90" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>D-27</t>
+          <t>D-13</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>아산시</t>
+          <t>영천시</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>아산탕정2 국민임대주택 예비입주자 모집공고(2026.09.15)</t>
+          <t>[경북 포항,경주,영천] 일반 매입임대 입주자 모집공고</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20260908</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020726&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020601&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H91" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>D-27</t>
+          <t>D-13</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>당진시</t>
+          <t>구미시</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>[청년신혼부부매입임대리츠주택] 충남당진 송산청광플러스원 입주자격완화 상시모집</t>
+          <t>경북서부지역(구미시, 김천시, 의성군) 국민임대 예비입주자 모집</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>20260810</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020529&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020709&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H92" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>D-28</t>
+          <t>D-13</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>태백시</t>
+          <t>칠곡군</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>태백철암1 국민임대주택 예비입주자 모집 공고</t>
+          <t>칠곡북삼휴먼시아 국민임대주택 예비입주자 모집(45형)</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -4553,42 +4557,42 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>20261028</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020735&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020786&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H93" t="n">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>D-41</t>
+          <t>D-13</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>양산시</t>
+          <t>칠곡군</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>양산 사송A-4BL 국민임대주택(29A형)선착순 동호지정 모집(입주자격완화, 선계약 후검증)</t>
+          <t>칠곡북삼휴먼시아 국민임대주택 예비입주자 모집(45형)</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -4598,222 +4602,222 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>20260813</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>20261029</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020495&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020719&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H94" t="n">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>D-42</t>
+          <t>D-13</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>군산시</t>
+          <t>강서구</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>군산신역세권A3(내흥3) 영구임대주택 입주자 추가모집</t>
+          <t>강서염창 통합공공임대주택 최초 입주자 모집공고</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>통합공공임대</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>20261030</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019841&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020753&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=48&amp;mi=1026</t>
         </is>
       </c>
       <c r="H95" t="n">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>D-43</t>
+          <t>D-13</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>울산</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>칠곡군</t>
+          <t>울주군</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2026년 칠곡군 천원주택(신혼·신생아 매입임대주택Ⅰ) 예비입주자 모집 공고</t>
+          <t>울산광역시 국민임대주택 예비입주자 정례모집 공고(2026.09.15.)</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>20260728</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>20261130</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=e54448a5-4c8c-4c3d-bfcf-bc465f677408&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020745&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H96" t="n">
-        <v>74</v>
+        <v>13</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>D-74</t>
+          <t>D-13</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>칠곡군</t>
+          <t>괴산군</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2026년 칠곡군 천원주택(청년 매입임대주택) 입주자 및 예비입주자 모집 공고</t>
+          <t>괴산군지역 국민임대주택 예비입주자 모집 공고[2026.09.15]</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>20260728</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>20261130</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=2e8989e9-02ae-48be-9591-f3c4c8e7fa39&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020683&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H97" t="n">
-        <v>74</v>
+        <v>13</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>D-74</t>
+          <t>D-13</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>포항시 남구</t>
+          <t>음성군</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>포항블루밸리 행복주택 선착순 동호지정 상시모집(입주자격 완화, 통합공임 일반계층 추가, 선계약 후검증)</t>
+          <t>음성신천 국민임대주택 예비입주자 모집 공고[2026.09.15]</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>20260707</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>20261222</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020042&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020684&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H98" t="n">
-        <v>96</v>
+        <v>13</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>D-96</t>
+          <t>D-13</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>삼척시</t>
+          <t>청주시 서원구</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>삼척시·정선군 국민임대 예비입주자 상시모집(26.6.10)</t>
+          <t>청주가경4 국민임대주택 예비입주자 모집 공고[2026.09.15]</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -4823,25 +4827,25 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>20260624</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>20261230</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020090&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020752&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H99" t="n">
-        <v>104</v>
+        <v>13</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>D-104</t>
+          <t>D-13</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4857,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>태백시</t>
+          <t>원주시</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>태백장성 국민임대주택 예비입주자 입주자격완화 상시모집</t>
+          <t>원주문막1 국민임대주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -4868,148 +4872,160 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20261002</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>20261230</t>
+          <t>20261002</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020730&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020738&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H100" t="n">
-        <v>104</v>
+        <v>14</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>D-104</t>
+          <t>D-14</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>강원</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr"/>
+          <t>경북</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>김천시</t>
+        </is>
+      </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>김천부곡2 영구임대주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261002</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020680&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H101" t="n">
-        <v>105</v>
+        <v>14</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>D-105</t>
+          <t>D-14</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>강원</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr"/>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>완주군</t>
+        </is>
+      </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>전주시, 완주군 국민임대주택 예비입주자 모집 공고(‘26.9.15.)</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261002</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020733&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H102" t="n">
-        <v>105</v>
+        <v>14</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>D-105</t>
+          <t>D-14</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>강원</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr"/>
+          <t>충북</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>청주시 서원구</t>
+        </is>
+      </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>청주산남2-1 영구임대주택 예비입주자 모집 공고(2026.08.28)</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261002</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020625&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H103" t="n">
-        <v>105</v>
+        <v>14</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>D-105</t>
+          <t>D-14</t>
         </is>
       </c>
     </row>
@@ -5019,100 +5035,104 @@
           <t>강원</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr"/>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>원주시</t>
+        </is>
+      </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>원주태장4 국민임대주택 예비입주자 모집공고(2026.09.15)</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020740&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H104" t="n">
-        <v>105</v>
+        <v>19</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>D-105</t>
+          <t>D-19</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>동해시</t>
+          <t>전주시 완산구</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>동해유성,태백철암장미 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
+          <t>전주동서학 통합공공임대(일자리연계형 지원주택) 최초 입주자 모집</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>통합공공임대</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>20260212</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019312&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020742&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=48&amp;mi=1026</t>
         </is>
       </c>
       <c r="H105" t="n">
-        <v>105</v>
+        <v>20</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>D-105</t>
+          <t>D-20</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>동해시</t>
+          <t>고령군</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>동해유성,태백철암장미 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
+          <t>대구서부권 고령다산2 국민임대 입주자격완화 모집공고</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -5122,42 +5142,42 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>20260212</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019308&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020746&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H106" t="n">
-        <v>105</v>
+        <v>26</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>D-105</t>
+          <t>D-26</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>태백시</t>
+          <t>아산시</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>태백궁전 국민임대 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
+          <t>아산탕정2 국민임대주택 예비입주자 모집공고(2026.09.15)</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -5167,448 +5187,488 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>20260212</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019307&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020726&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H107" t="n">
-        <v>105</v>
+        <v>26</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>D-105</t>
+          <t>D-26</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>경기</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr"/>
+          <t>충남</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>당진시</t>
+        </is>
+      </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>[청년신혼부부매입임대리츠주택] 충남당진 송산청광플러스원 입주자격완화 상시모집</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260810</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020529&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H108" t="n">
-        <v>105</v>
+        <v>27</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>D-105</t>
+          <t>D-27</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>경기</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr"/>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>태백시</t>
+        </is>
+      </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>태백철암1 국민임대주택 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261028</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020735&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H109" t="n">
-        <v>105</v>
+        <v>40</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>D-105</t>
+          <t>D-40</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>경기</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr"/>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>양산시</t>
+        </is>
+      </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>양산 사송A-4BL 국민임대주택(29A형)선착순 동호지정 모집(입주자격완화, 선계약 후검증)</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260813</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261029</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020495&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H110" t="n">
-        <v>105</v>
+        <v>41</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>D-105</t>
+          <t>D-41</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>경기</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr"/>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>태백시</t>
+        </is>
+      </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>태백소도 국민임대주택 예비입주자 상시모집(26.9.17 공고)</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261030</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020793&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H111" t="n">
-        <v>105</v>
+        <v>42</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>D-105</t>
+          <t>D-42</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr"/>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>군산시</t>
+        </is>
+      </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>군산신역세권A3(내흥3) 영구임대주택 입주자 추가모집</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261030</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019841&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H112" t="n">
-        <v>105</v>
+        <v>42</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>D-105</t>
+          <t>D-42</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr"/>
+          <t>경북</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>칠곡군</t>
+        </is>
+      </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 칠곡군 천원주택(신혼·신생아 매입임대주택Ⅰ) 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260728</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261130</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=e54448a5-4c8c-4c3d-bfcf-bc465f677408&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
         </is>
       </c>
       <c r="H113" t="n">
-        <v>105</v>
+        <v>73</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>D-105</t>
+          <t>D-73</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr"/>
+          <t>경북</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>칠곡군</t>
+        </is>
+      </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 칠곡군 천원주택(청년 매입임대주택) 입주자 및 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260728</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261130</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=2e8989e9-02ae-48be-9591-f3c4c8e7fa39&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
         </is>
       </c>
       <c r="H114" t="n">
-        <v>105</v>
+        <v>73</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>D-105</t>
+          <t>D-73</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr"/>
+          <t>경북</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>포항시 남구</t>
+        </is>
+      </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>포항블루밸리 행복주택 선착순 동호지정 상시모집(입주자격 완화, 통합공임 일반계층 추가, 선계약 후검증)</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260707</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261222</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020042&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H115" t="n">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>D-105</t>
+          <t>D-95</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>경북</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr"/>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>삼척시</t>
+        </is>
+      </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>삼척시·정선군 국민임대 예비입주자 상시모집(26.6.10)</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260624</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261230</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020090&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H116" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>D-105</t>
+          <t>D-103</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>경북</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr"/>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>태백시</t>
+        </is>
+      </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>태백장성 국민임대주택 예비입주자 입주자격완화 상시모집</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261230</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020730&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H117" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>D-105</t>
+          <t>D-103</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -5628,28 +5688,28 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H118" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>D-105</t>
+          <t>D-104</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B119" t="inlineStr"/>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -5659,7 +5719,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -5669,28 +5729,28 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H119" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>D-105</t>
+          <t>D-104</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -5710,28 +5770,28 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H120" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>D-105</t>
+          <t>D-104</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -5741,7 +5801,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -5751,38 +5811,42 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H121" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>D-105</t>
+          <t>D-104</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>대구</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr"/>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>동해시</t>
+        </is>
+      </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>동해유성,태백철암장미 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260212</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -5792,38 +5856,42 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019312&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H122" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>D-105</t>
+          <t>D-104</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>대구</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr"/>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>동해시</t>
+        </is>
+      </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>동해유성,태백철암장미 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260212</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -5833,38 +5901,42 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019308&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H123" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>D-105</t>
+          <t>D-104</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>대전</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr"/>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>태백시</t>
+        </is>
+      </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>태백궁전 국민임대 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260212</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -5874,28 +5946,28 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019307&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H124" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>D-105</t>
+          <t>D-104</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>대전</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B125" t="inlineStr"/>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -5915,28 +5987,28 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H125" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>D-105</t>
+          <t>D-104</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>대전</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -5956,28 +6028,28 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H126" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>D-105</t>
+          <t>D-104</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>대전</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B127" t="inlineStr"/>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -5987,7 +6059,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -5997,28 +6069,28 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H127" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>D-105</t>
+          <t>D-104</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B128" t="inlineStr"/>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -6028,7 +6100,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -6038,28 +6110,28 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H128" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>D-105</t>
+          <t>D-104</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B129" t="inlineStr"/>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -6079,28 +6151,28 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H129" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>D-105</t>
+          <t>D-104</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B130" t="inlineStr"/>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -6120,28 +6192,28 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H130" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>D-105</t>
+          <t>D-104</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B131" t="inlineStr"/>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -6151,7 +6223,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -6161,28 +6233,28 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H131" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>D-105</t>
+          <t>D-104</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B132" t="inlineStr"/>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -6192,7 +6264,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -6202,28 +6274,28 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H132" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>D-105</t>
+          <t>D-104</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B133" t="inlineStr"/>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -6243,28 +6315,28 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H133" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>D-105</t>
+          <t>D-104</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B134" t="inlineStr"/>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -6284,28 +6356,28 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H134" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>D-105</t>
+          <t>D-104</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -6315,7 +6387,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -6325,28 +6397,28 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H135" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>D-105</t>
+          <t>D-104</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>세종</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B136" t="inlineStr"/>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -6356,7 +6428,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -6366,28 +6438,28 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H136" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>D-105</t>
+          <t>D-104</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>세종</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B137" t="inlineStr"/>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -6407,28 +6479,28 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H137" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>D-105</t>
+          <t>D-104</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>세종</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -6448,28 +6520,28 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H138" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>D-105</t>
+          <t>D-104</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>세종</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -6479,7 +6551,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -6489,28 +6561,28 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H139" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>D-105</t>
+          <t>D-104</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>울산</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B140" t="inlineStr"/>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -6520,7 +6592,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -6530,28 +6602,28 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H140" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>D-105</t>
+          <t>D-104</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>울산</t>
+          <t>대전</t>
         </is>
       </c>
       <c r="B141" t="inlineStr"/>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -6571,28 +6643,28 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H141" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>D-105</t>
+          <t>D-104</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>울산</t>
+          <t>대전</t>
         </is>
       </c>
       <c r="B142" t="inlineStr"/>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -6612,28 +6684,28 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H142" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>D-105</t>
+          <t>D-104</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>울산</t>
+          <t>대전</t>
         </is>
       </c>
       <c r="B143" t="inlineStr"/>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -6643,7 +6715,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -6653,28 +6725,28 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H143" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>D-105</t>
+          <t>D-104</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>대전</t>
         </is>
       </c>
       <c r="B144" t="inlineStr"/>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -6684,7 +6756,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -6694,28 +6766,28 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H144" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>D-105</t>
+          <t>D-104</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B145" t="inlineStr"/>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -6735,28 +6807,28 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H145" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>D-105</t>
+          <t>D-104</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B146" t="inlineStr"/>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -6776,28 +6848,28 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H146" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>D-105</t>
+          <t>D-104</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B147" t="inlineStr"/>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -6807,7 +6879,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -6817,28 +6889,28 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H147" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>D-105</t>
+          <t>D-104</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B148" t="inlineStr"/>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -6848,7 +6920,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -6858,28 +6930,28 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H148" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>D-105</t>
+          <t>D-104</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B149" t="inlineStr"/>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -6899,28 +6971,28 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H149" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>D-105</t>
+          <t>D-104</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B150" t="inlineStr"/>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -6940,28 +7012,28 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H150" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>D-105</t>
+          <t>D-104</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B151" t="inlineStr"/>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -6971,7 +7043,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -6981,42 +7053,38 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H151" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>D-105</t>
+          <t>D-104</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>전북</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>김제시</t>
-        </is>
-      </c>
+          <t>서울</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr"/>
       <c r="C152" t="inlineStr">
         <is>
-          <t>김제검산1단지 영구임대주택 예비입주자 모집 공고(상시모집)</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>20260101</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -7026,42 +7094,38 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019412&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H152" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>D-105</t>
+          <t>D-104</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>전북</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>남원시</t>
-        </is>
-      </c>
+          <t>세종</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr"/>
       <c r="C153" t="inlineStr">
         <is>
-          <t>남원노암 공공임대 50년 예비입주자 모집</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>50년임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -7071,42 +7135,38 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020623&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H153" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>D-105</t>
+          <t>D-104</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>전북</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>남원시</t>
-        </is>
-      </c>
+          <t>세종</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr"/>
       <c r="C154" t="inlineStr">
         <is>
-          <t>남원노암단지 영구임대주택 입주자격완화 예비입주자 모집공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -7116,42 +7176,38 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020649&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H154" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>D-105</t>
+          <t>D-104</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>전북</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>전주시 완산구</t>
-        </is>
-      </c>
+          <t>세종</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr"/>
       <c r="C155" t="inlineStr">
         <is>
-          <t>전주시(전주평화1,전주평화4) 영구임대주택 예비입주자 모집 공고(공고일:2026.02.10.)</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>20260303</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -7161,28 +7217,28 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019241&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H155" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>D-105</t>
+          <t>D-104</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>세종</t>
         </is>
       </c>
       <c r="B156" t="inlineStr"/>
       <c r="C156" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -7192,7 +7248,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -7202,28 +7258,28 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H156" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>D-105</t>
+          <t>D-104</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>울산</t>
         </is>
       </c>
       <c r="B157" t="inlineStr"/>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -7243,28 +7299,28 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H157" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>D-105</t>
+          <t>D-104</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>울산</t>
         </is>
       </c>
       <c r="B158" t="inlineStr"/>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -7284,28 +7340,28 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H158" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>D-105</t>
+          <t>D-104</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>울산</t>
         </is>
       </c>
       <c r="B159" t="inlineStr"/>
       <c r="C159" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -7315,7 +7371,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -7325,28 +7381,28 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H159" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>D-105</t>
+          <t>D-104</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>울산</t>
         </is>
       </c>
       <c r="B160" t="inlineStr"/>
       <c r="C160" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -7356,7 +7412,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -7366,28 +7422,28 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H160" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>D-105</t>
+          <t>D-104</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B161" t="inlineStr"/>
       <c r="C161" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -7407,28 +7463,28 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H161" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>D-105</t>
+          <t>D-104</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B162" t="inlineStr"/>
       <c r="C162" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -7448,28 +7504,28 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H162" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>D-105</t>
+          <t>D-104</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B163" t="inlineStr"/>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -7479,7 +7535,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -7489,42 +7545,38 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H163" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>D-105</t>
+          <t>D-104</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>충남</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>당진시</t>
-        </is>
-      </c>
+          <t>인천</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr"/>
       <c r="C164" t="inlineStr">
         <is>
-          <t>[청년신혼부부매입임대리츠주택] 충남당진 송산청광플러스원 입주자격완화 상시모집</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>20260316</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -7534,22 +7586,22 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019433&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H164" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>D-105</t>
+          <t>D-104</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B165" t="inlineStr"/>
@@ -7579,18 +7631,18 @@
         </is>
       </c>
       <c r="H165" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>D-105</t>
+          <t>D-104</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B166" t="inlineStr"/>
@@ -7620,18 +7672,18 @@
         </is>
       </c>
       <c r="H166" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>D-105</t>
+          <t>D-104</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B167" t="inlineStr"/>
@@ -7661,18 +7713,18 @@
         </is>
       </c>
       <c r="H167" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>D-105</t>
+          <t>D-104</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B168" t="inlineStr"/>
@@ -7702,56 +7754,56 @@
         </is>
       </c>
       <c r="H168" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>D-105</t>
+          <t>D-104</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>삼척시</t>
+          <t>김제시</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>삼척도계·정선신동 국민임대주택 예비입주자 입주자격완화 공고</t>
+          <t>김제검산1단지 영구임대주택 예비입주자 모집 공고(상시모집)</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260101</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>20270129</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020581&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019412&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H169" t="n">
-        <v>134</v>
+        <v>104</v>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>D-134</t>
+          <t>D-104</t>
         </is>
       </c>
     </row>
@@ -7763,130 +7815,847 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>군산시</t>
+          <t>남원시</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>군산시 국민임대주택 입주자 선착순 상시 모집(경암부향 등 7개 단지)</t>
+          <t>남원노암 공공임대 50년 예비입주자 모집</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>50년임대</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>20260812</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>20270731</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020453&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020623&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H170" t="n">
-        <v>317</v>
+        <v>104</v>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>D-317</t>
+          <t>D-104</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>울산</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>울주군</t>
+          <t>남원시</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>울산광역시 국민임대주택 예비입주자 정례모집 공고(2025.09.15.)</t>
+          <t>남원노암단지 영구임대주택 입주자격완화 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>20250929</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>20291001</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300018799&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020649&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H171" t="n">
-        <v>1110</v>
+        <v>104</v>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>D-1110</t>
+          <t>D-104</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>전주시 완산구</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>전주시(전주평화1,전주평화4) 영구임대주택 예비입주자 모집 공고(공고일:2026.02.10.)</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>영구임대</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>20260303</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019241&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H172" t="n">
+        <v>104</v>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>D-104</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>제주</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr"/>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H173" t="n">
+        <v>104</v>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>D-104</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>제주</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr"/>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H174" t="n">
+        <v>104</v>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>D-104</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>제주</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr"/>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H175" t="n">
+        <v>104</v>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>D-104</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>제주</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr"/>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>20260224</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H176" t="n">
+        <v>104</v>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>D-104</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>충남</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr"/>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H177" t="n">
+        <v>104</v>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>D-104</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>충남</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr"/>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H178" t="n">
+        <v>104</v>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>D-104</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>충남</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr"/>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H179" t="n">
+        <v>104</v>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>D-104</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>충남</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr"/>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>20260224</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H180" t="n">
+        <v>104</v>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>D-104</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>충남</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>당진시</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>[청년신혼부부매입임대리츠주택] 충남당진 송산청광플러스원 입주자격완화 상시모집</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>매입임대</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>20260316</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019433&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H181" t="n">
+        <v>104</v>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>D-104</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>충북</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr"/>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H182" t="n">
+        <v>104</v>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>D-104</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>충북</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr"/>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H183" t="n">
+        <v>104</v>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>D-104</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>충북</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr"/>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H184" t="n">
+        <v>104</v>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>D-104</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>충북</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr"/>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>20260224</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H185" t="n">
+        <v>104</v>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>D-104</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>삼척시</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>삼척도계·정선신동 국민임대주택 예비입주자 입주자격완화 공고</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>국민임대</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>20270129</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020581&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H186" t="n">
+        <v>133</v>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>D-133</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>군산시</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>군산시 국민임대주택 입주자 선착순 상시 모집(경암부향 등 7개 단지)</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>국민임대</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>20260812</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>20270731</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020453&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H187" t="n">
+        <v>316</v>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>D-316</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
           <t>울산</t>
         </is>
       </c>
-      <c r="B172" t="inlineStr">
+      <c r="B188" t="inlineStr">
         <is>
           <t>울주군</t>
         </is>
       </c>
-      <c r="C172" t="inlineStr">
+      <c r="C188" t="inlineStr">
         <is>
           <t>울산광역시 국민임대주택 예비입주자 정례모집 공고(2025.09.15.)</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr">
+      <c r="D188" t="inlineStr">
         <is>
           <t>국민임대</t>
         </is>
       </c>
-      <c r="E172" t="inlineStr">
+      <c r="E188" t="inlineStr">
         <is>
           <t>20250929</t>
         </is>
       </c>
-      <c r="F172" t="inlineStr">
+      <c r="F188" t="inlineStr">
         <is>
           <t>20291001</t>
         </is>
       </c>
-      <c r="G172" t="inlineStr">
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300018799&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H188" t="n">
+        <v>1109</v>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>D-1109</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>울산</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>울주군</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>울산광역시 국민임대주택 예비입주자 정례모집 공고(2025.09.15.)</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>국민임대</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>20250929</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>20291001</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
         <is>
           <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300018780&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
-      <c r="H172" t="n">
-        <v>1110</v>
-      </c>
-      <c r="I172" t="inlineStr">
-        <is>
-          <t>D-1110</t>
+      <c r="H189" t="n">
+        <v>1109</v>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>D-1109</t>
         </is>
       </c>
     </row>

--- a/housing_notices.xlsx
+++ b/housing_notices.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I189"/>
+  <dimension ref="A1:I188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,42 +469,38 @@
           <t>경기</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>부천시 원미구</t>
-        </is>
-      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>부천시 영구임대주택 예비입주자 모집 (중동한라1, 중동덕유1)</t>
+          <t>[경기남부] 용인시 신혼·신생아 매입임대주택Ⅱ(전세형) 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>20260916</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020678&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020702&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>오늘 마감</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
@@ -514,59 +510,55 @@
           <t>경기</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>안산시 단원구</t>
-        </is>
-      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
-          <t>안산 선부동 행복주택 예비입주자(주거급여)모집 공고</t>
+          <t>[경기남부] 용인시 청년 매입임대주택 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>20260903</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.ansanuc.net/homenew/12286/20328/bbsList.do</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020699&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>오늘 마감</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>서귀포시</t>
+          <t>평택시</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>[제주지역본부] 다자녀 매입임대주택 예비입주자 모집 공고(서귀포시)</t>
+          <t>[경기남부] 화성시·평택시 신혼·신생아 매입임대주택Ⅱ(전세형) 예비입주자 [후순번] 모집공고</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -581,43 +573,47 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020691&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020703&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>오늘 마감</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>경기</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
+          <t>경북</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>포항시 북구</t>
+        </is>
+      </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>[경기남부] 용인시 신혼·신생아 매입임대주택Ⅱ(전세형) 예비입주자 모집공고</t>
+          <t>포항창포 영구임대아파트 예비입주자 모집</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>20260917</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -627,38 +623,42 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020702&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020651&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>경기</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
+          <t>경북</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>포항시 북구</t>
+        </is>
+      </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>[경기남부] 용인시 청년 매입임대주택 예비입주자 모집공고</t>
+          <t>포항학산 영구임대아파트 예비입주자 모집</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>20260917</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -668,15 +668,15 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020699&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020650&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
@@ -688,147 +688,139 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>평택시</t>
+          <t>부천시 오정구</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>[경기남부] 화성시·평택시 신혼·신생아 매입임대주택Ⅱ(전세형) 예비입주자 [후순번] 모집공고</t>
+          <t>2026년 9월 부천시 국민임대주택 예비입주자 모집 공고(2026.09.07)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>20260917</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260922</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020703&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020652&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>경북</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>포항시 북구</t>
-        </is>
-      </c>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>포항창포 영구임대아파트 예비입주자 모집</t>
+          <t>26-4차 인천본부 든든전세주택 입주자 모집공고(인천, 부천)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260922</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020651&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020725&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>경북</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>포항시 북구</t>
-        </is>
-      </c>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>포항학산 영구임대아파트 예비입주자 모집</t>
+          <t>26-4차 인천본부 든든전세주택 입주자 모집공고(인천, 부천)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260922</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020650&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020715&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>부천시 오정구</t>
+          <t>경주시</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026년 9월 부천시 국민임대주택 예비입주자 모집 공고(2026.09.07)</t>
+          <t>경주시, 영천시, 포항시 부도매입(국민임대)주택 입주자격완화 모집공고</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -838,7 +830,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -848,25 +840,29 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020652&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020635&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>D-4</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>경기</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
+          <t>인천</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>미추홀구</t>
+        </is>
+      </c>
       <c r="C11" t="inlineStr">
         <is>
           <t>26-4차 인천본부 든든전세주택 입주자 모집공고(인천, 부천)</t>
@@ -893,21 +889,25 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>D-4</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>경기</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
+          <t>인천</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>부평구</t>
+        </is>
+      </c>
       <c r="C12" t="inlineStr">
         <is>
           <t>26-4차 인천본부 든든전세주택 입주자 모집공고(인천, 부천)</t>
@@ -934,28 +934,28 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>D-4</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>경주시</t>
+          <t>남동구</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>경주시, 영천시, 포항시 부도매입(국민임대)주택 입주자격완화 모집공고</t>
+          <t>26년 9월 인천시 남동구 국민임대주택 예비입주자 모집 공고(2026.09.07)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -965,7 +965,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -975,15 +975,15 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020635&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020619&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>D-4</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
@@ -995,17 +995,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>미추홀구</t>
+          <t>옹진군</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>26-4차 인천본부 든든전세주택 입주자 모집공고(인천, 부천)</t>
+          <t>인천옹진백령 국민임대주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1020,15 +1020,15 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020725&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020578&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>D-4</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
@@ -1040,22 +1040,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>부평구</t>
+          <t>옹진군</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>26-4차 인천본부 든든전세주택 입주자 모집공고(인천, 부천)</t>
+          <t>인천옹진연평 국민임대주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260922</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1065,37 +1065,37 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020715&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020697&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>D-4</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>남동구</t>
+          <t>횡성군</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>26년 9월 인천시 남동구 국민임대주택 예비입주자 모집 공고(2026.09.07)</t>
+          <t>강원횡성 통합공공임대주택 입주자 모집</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>통합공공임대</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1105,42 +1105,42 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>20260922</t>
+          <t>20260923</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020619&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020627&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=48&amp;mi=1026</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>D-4</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>옹진군</t>
+          <t>안성시</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>인천옹진백령 국민임대주택 예비입주자 모집</t>
+          <t>[온라인 접수 불가, 관할 주거복지지사 현장접수] 경기남부지역본부 2026년 일반 매입임대주택 입주자 모집공고</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1150,87 +1150,87 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>20260922</t>
+          <t>20260923</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020578&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020769&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>D-4</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>옹진군</t>
+          <t>여주시</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>인천옹진연평 국민임대주택 예비입주자 모집</t>
+          <t>[온라인 접수 불가, 관할 주거복지지사 현장접수] 경기남부지역본부 2026년 일반 매입임대주택 입주자 모집공고</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>20260922</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>20260922</t>
+          <t>20260923</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020697&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020731&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>D-4</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>횡성군</t>
+          <t>김포시</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>강원횡성 통합공공임대주택 입주자 모집</t>
+          <t>김포시 국민임대주택 예비입주자 모집(2026.09.07)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>통합공공임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1245,15 +1245,15 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020627&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=48&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020659&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
@@ -1265,17 +1265,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>안성시</t>
+          <t>화성시 효행구</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>[온라인 접수 불가, 관할 주거복지지사 현장접수] 경기남부지역본부 2026년 일반 매입임대주택 입주자 모집공고</t>
+          <t>화성서부권 국민임대주택 예비입주자 모집[입주자격완화]</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1290,28 +1290,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020769&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020686&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>경기</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>양산시</t>
+        </is>
+      </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>[온라인 접수 불가, 관할 주거복지지사 현장접수] 경기남부지역본부 2026년 일반 매입임대주택 입주자 모집공고</t>
+          <t>[경남지역본부]26년 3차 분양전환형 든든전세주택 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1331,37 +1335,37 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020731&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020721&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>김포시</t>
+          <t>김해시</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>김포시 국민임대주택 예비입주자 모집(2026.09.07)</t>
+          <t>[경남지역본부]26년 3차 비분양전환형 든든전세주택 입주자 모집 공고</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1376,37 +1380,33 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020659&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020720&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>경기</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>화성시 효행구</t>
-        </is>
-      </c>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>화성서부권 국민임대주택 예비입주자 모집[입주자격완화]</t>
+          <t>[경남지역본부]26년 3차 신혼·신생아매입임대Ⅰ 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1421,15 +1421,15 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020686&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020722&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>[경남지역본부]26년 3차 분양전환형 든든전세주택 예비입주자 모집 공고</t>
+          <t>[경남지역본부]26년 3차 신혼·신생아매입임대Ⅱ(전세형) 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1466,15 +1466,15 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020721&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020723&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
@@ -1486,12 +1486,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>김해시</t>
+          <t>진주시</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>[경남지역본부]26년 3차 비분양전환형 든든전세주택 입주자 모집 공고</t>
+          <t>[경남지역본부]26년 3차 청년매입임대 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1511,15 +1511,15 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020720&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020717&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
@@ -1529,10 +1529,14 @@
           <t>경남</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>함양군</t>
+        </is>
+      </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>[경남지역본부]26년 3차 신혼·신생아매입임대Ⅰ 예비입주자 모집공고</t>
+          <t>경남 함양군 서하면 다자녀 매입임대주택 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1542,7 +1546,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1552,37 +1556,37 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020722&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020711&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>양산시</t>
+          <t>달서구</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>[경남지역본부]26년 3차 신혼·신생아매입임대Ⅱ(전세형) 예비입주자 모집공고</t>
+          <t>대구죽전 행복주택(산업단지형) 예비 입주자 모집</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1597,37 +1601,37 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020723&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020763&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>진주시</t>
+          <t>달서구</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>[경남지역본부]26년 3차 청년매입임대 예비입주자 모집공고</t>
+          <t>대구죽전 행복주택(산업단지형) 예비 입주자 모집</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1642,42 +1646,42 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020717&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020760&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>함양군</t>
+          <t>달서구</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>경남 함양군 서하면 다자녀 매입임대주택 예비입주자 모집공고</t>
+          <t>대구죽전 행복주택(산업단지형) 예비 입주자 모집</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1687,32 +1691,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020711&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020751&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>달서구</t>
+          <t>김제시</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>대구죽전 행복주택(산업단지형) 예비 입주자 모집</t>
+          <t>(26.9.10)김제대검산, 정읍시기, 정읍첨단 행복주택 입주자격완화 예비자 모집 공고(소득·총자산요건 배제 및 무주택요건 완화)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1732,42 +1736,42 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020763&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020344&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>달서구</t>
+          <t>익산시</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>대구죽전 행복주택(산업단지형) 예비 입주자 모집</t>
+          <t>익산한스빌 국민임대주택 예비입주자 자격완화 모집 공고</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260922</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1777,122 +1781,122 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020760&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020694&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>달서구</t>
+          <t>칠곡군</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>대구죽전 행복주택(산업단지형) 예비 입주자 모집</t>
+          <t>칠곡왜관4 국민임대아파트 예비입주자 모집(51형)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>20260923</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020751&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020696&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-8</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>김제시</t>
+          <t>양산시</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>(26.9.10)김제대검산, 정읍시기, 정읍첨단 행복주택 입주자격완화 예비자 모집 공고(소득·총자산요건 배제 및 무주택요건 완화)</t>
+          <t>[양산시지역]양산대석휴먼시아 국민임대주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>20260923</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020344&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020754&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-9</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>익산시</t>
+          <t>양산시</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>익산한스빌 국민임대주택 예비입주자 자격완화 모집 공고</t>
+          <t>양산시 국민임대주택 예비입주자 완화 모집(‘26.09.15)_소득, 자산, 무주택 요건 완화 / 계약금 인하</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1902,42 +1906,42 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>20260922</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>20260923</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020694&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020796&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-9</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>칠곡군</t>
+          <t>양산시</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>칠곡왜관4 국민임대아파트 예비입주자 모집(51형)</t>
+          <t>양산시 국민임대주택 예비입주자 완화 모집(‘26.09.15)_소득, 자산, 무주택 요건 완화 / 계약금 인하</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1952,20 +1956,20 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020696&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020794&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>D-9</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1986,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>[양산시지역]양산대석휴먼시아 국민임대주택 예비입주자 모집</t>
+          <t>양산시 국민임대주택 예비입주자 완화 모집(‘26.09.15)_소득, 자산, 무주택 요건 완화 / 계약금 인하</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1992,25 +1996,25 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
+          <t>20260928</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
           <t>20260929</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>20260929</t>
-        </is>
-      </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020754&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020732&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>D-11</t>
+          <t>D-9</t>
         </is>
       </c>
     </row>
@@ -2022,12 +2026,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>양산시</t>
+          <t>창녕군</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>양산시 국민임대주택 예비입주자 완화 모집(‘26.09.15)_소득, 자산, 무주택 요건 완화 / 계약금 인하</t>
+          <t>창녕창녕 국민임대주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2037,7 +2041,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2047,42 +2051,42 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020796&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020724&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>D-11</t>
+          <t>D-9</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>양산시</t>
+          <t>경산시</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>양산시 국민임대주택 예비입주자 완화 모집(‘26.09.15)_소득, 자산, 무주택 요건 완화 / 계약금 인하</t>
+          <t>경산백천1단지 50년 공공임대주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>50년임대</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2092,37 +2096,37 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020794&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020728&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>D-11</t>
+          <t>D-9</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>양산시</t>
+          <t>경산시</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>양산시 국민임대주택 예비입주자 완화 모집(‘26.09.15)_소득, 자산, 무주택 요건 완화 / 계약금 인하</t>
+          <t>대구혁신10, 경산하양3 행복주택 입주자격완화 선계약 후검증 동호지정 입주자 모집</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2137,82 +2141,82 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020732&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020682&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>D-11</t>
+          <t>D-9</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>창녕군</t>
+          <t>동구</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>창녕창녕 국민임대주택 예비입주자 모집</t>
+          <t>대구혁신10, 경산하양3 행복주택 입주자격완화 선계약 후검증 동호지정 입주자 모집</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
+          <t>20260928</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
           <t>20260929</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>20260929</t>
-        </is>
-      </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020724&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020682&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>D-11</t>
+          <t>D-9</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>경산시</t>
+          <t>기장군</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>경산백천1단지 50년 공공임대주택 예비입주자 모집</t>
+          <t>부산광역시 국민임대주택 예비입주자 정례모집 공고(2026.09.15.)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>50년임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2227,42 +2231,42 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020728&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020788&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>D-11</t>
+          <t>D-9</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>경산시</t>
+          <t>기장군</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>대구혁신10, 경산하양3 행복주택 입주자격완화 선계약 후검증 동호지정 입주자 모집</t>
+          <t>부산광역시 국민임대주택 예비입주자 정례모집 공고(2026.09.15.)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2272,37 +2276,37 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020682&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020758&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>D-11</t>
+          <t>D-9</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>동구</t>
+          <t>기장군</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>대구혁신10, 경산하양3 행복주택 입주자격완화 선계약 후검증 동호지정 입주자 모집</t>
+          <t>부산광역시 기장군 정관7국민임대 소득완화 모집공고</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2317,32 +2321,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020682&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020655&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>D-11</t>
+          <t>D-9</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>기장군</t>
+          <t>군산시</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>부산광역시 국민임대주택 예비입주자 정례모집 공고(2026.09.15.)</t>
+          <t>군산구암 국민임대주택 예비입주자 모집 공고(‘26.9.15.)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2362,37 +2366,37 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020788&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020743&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>D-11</t>
+          <t>D-9</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>기장군</t>
+          <t>군산시</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>부산광역시 국민임대주택 예비입주자 정례모집 공고(2026.09.15.)</t>
+          <t>군산나운4 영구임대주택 입주자격완화 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2407,32 +2411,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020758&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020801&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>D-11</t>
+          <t>D-9</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>기장군</t>
+          <t>음성군</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관7국민임대 소득완화 모집공고</t>
+          <t>음성군 국민임대주택 예비입주자 모집(2026.09.15.)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2442,7 +2446,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2452,32 +2456,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020655&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020698&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>D-11</t>
+          <t>D-9</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>군산시</t>
+          <t>원주시</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>군산구암 국민임대주택 예비입주자 모집 공고(‘26.9.15.)</t>
+          <t>원주시지역 국민임대주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2492,37 +2496,37 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020743&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020783&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>D-11</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>음성군</t>
+          <t>원주시</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>음성군 국민임대주택 예비입주자 모집(2026.09.15.)</t>
+          <t>원주시지역 국민임대주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2537,20 +2541,20 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020698&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020767&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>D-11</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
@@ -2587,42 +2591,42 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020783&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020677&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>원주시</t>
+          <t>부천시 소사구</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>원주시지역 국민임대주택 예비입주자 모집</t>
+          <t>[인천]26년 7차 신혼·신생아Ⅰ 예비입주자 모집공고(인천,부천)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2632,42 +2636,42 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020767&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020795&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>원주시</t>
+          <t>부천시 원미구</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>원주시지역 국민임대주택 예비입주자 모집</t>
+          <t>[인천]26년 7차 신혼·신생아Ⅱ(전세형) 예비입주자 모집공고(인천,부천)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2677,15 +2681,15 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020677&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020797&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
@@ -2697,12 +2701,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>부천시 소사구</t>
+          <t>부천시 오정구</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>[인천]26년 7차 신혼·신생아Ⅰ 예비입주자 모집공고(인천,부천)</t>
+          <t>[인천지역본부] 26년 7차 청년 매입임대주택 예비입주자 모집공고(인천,부천)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2722,15 +2726,15 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020795&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020798&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
@@ -2742,22 +2746,22 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>부천시 원미구</t>
+          <t>김포시</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>[인천]26년 7차 신혼·신생아Ⅱ(전세형) 예비입주자 모집공고(인천,부천)</t>
+          <t>김포지역 국민임대주택 예비입주자 모집 공고(26.09.07.)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260918</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2767,15 +2771,15 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020797&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020704&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
@@ -2787,22 +2791,22 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>부천시 오정구</t>
+          <t>김포시</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>[인천지역본부] 26년 7차 청년 매입임대주택 예비입주자 모집공고(인천,부천)</t>
+          <t>김포지역 국민임대주택 예비입주자 모집 공고(26.09.07.)</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260918</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2812,15 +2816,15 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020798&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020662&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
@@ -2832,12 +2836,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>김포시</t>
+          <t>안성시</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>김포지역 국민임대주택 예비입주자 모집 공고(26.09.07.)</t>
+          <t>안성금화 국민임대 입주자격완화 예비입주자 모집공고(2026.09.07)</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2847,7 +2851,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2857,15 +2861,15 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020704&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020695&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
@@ -2877,22 +2881,22 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>김포시</t>
+          <t>의정부시</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>김포지역 국민임대주택 예비입주자 모집 공고(26.09.07.)</t>
+          <t>의정부송산3단지 공임50년 예비입주자 표준모집공고문</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>50년임대</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2902,15 +2906,15 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020662&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020670&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
@@ -2922,22 +2926,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>안성시</t>
+          <t>화성시 동탄구</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>안성금화 국민임대 입주자격완화 예비입주자 모집공고(2026.09.07)</t>
+          <t>화성동탄2 10년 분양전환공공임대주택(리츠) 예비입주자모집공고(‘26.09)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>10년임대</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2947,15 +2951,15 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020695&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=0000061177&amp;ccrCnntSysDsCd=02&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
@@ -2967,67 +2971,67 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>의정부시</t>
+          <t>화성시 동탄구</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>의정부송산3단지 공임50년 예비입주자 표준모집공고문</t>
+          <t>화성동탄2 10년 분양전환공공임대주택(리츠) 예비입주자모집공고(‘26.09)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>50년임대</t>
+          <t>10년임대</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
+          <t>20260929</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
           <t>20260930</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>20260930</t>
-        </is>
-      </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020670&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=0000061173&amp;ccrCnntSysDsCd=02&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>화성시 동탄구</t>
+          <t>진주시</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>화성동탄2 10년 분양전환공공임대주택(리츠) 예비입주자모집공고(‘26.09)</t>
+          <t>2026년 진주정촌올리움 국민임대 예비입주자 1차 모집 공고</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>10년임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -3037,42 +3041,42 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=0000061177&amp;ccrCnntSysDsCd=02&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://www.gndc.co.kr/boardview/boardview.do?seqId=0000006202&amp;BBS_ID=B491A490314446318099F9D828047900&amp;IPDS_IDX=F7054C80FACF4D22AD23CAD92547CE03&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>화성시 동탄구</t>
+          <t>연제구</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>화성동탄2 10년 분양전환공공임대주택(리츠) 예비입주자모집공고(‘26.09)</t>
+          <t>[부산]청년매입임대주택 예비입주자 모집 공고(복사)</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>10년임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -3082,37 +3086,37 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=0000061173&amp;ccrCnntSysDsCd=02&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020790&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>진주시</t>
+          <t>사하구</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026년 진주정촌올리움 국민임대 예비입주자 1차 모집 공고</t>
+          <t>[부산울산]신혼부부Ⅰ 매입임대주택 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3127,15 +3131,15 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.gndc.co.kr/boardview/boardview.do?seqId=0000006202&amp;BBS_ID=B491A490314446318099F9D828047900&amp;IPDS_IDX=F7054C80FACF4D22AD23CAD92547CE03&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020791&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
@@ -3147,12 +3151,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>연제구</t>
+          <t>강서구</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>[부산]청년매입임대주택 예비입주자 모집 공고(복사)</t>
+          <t>[부산울산]신혼부부Ⅱ(전세형) 매입임대주택 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3172,15 +3176,15 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020790&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020789&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
@@ -3192,22 +3196,22 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>사하구</t>
+          <t>북구</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>[부산울산]신혼부부Ⅰ 매입임대주택 예비입주자 모집 공고</t>
+          <t>부산만덕5 2블록 10년 분양전환공공임대주택(e편한세상 금정산) 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>10년임대</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3217,32 +3221,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020791&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=0000061163&amp;ccrCnntSysDsCd=02&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>강서구</t>
+          <t>송파구</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>[부산울산]신혼부부Ⅱ(전세형) 매입임대주택 예비입주자 모집공고</t>
+          <t>[서울지역본부] 26년 3차 신혼·신생아 매입임대Ⅰ 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3262,42 +3266,42 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020789&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020750&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H64" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>북구</t>
+          <t>서초구</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>부산만덕5 2블록 10년 분양전환공공임대주택(e편한세상 금정산) 예비입주자 모집공고</t>
+          <t>[서울지역본부] 26년 3차 신혼·신생아매입임대주택Ⅱ(전세형) 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>10년임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -3307,15 +3311,15 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=0000061163&amp;ccrCnntSysDsCd=02&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020749&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
@@ -3327,12 +3331,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>송파구</t>
+          <t>영등포구</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>[서울지역본부] 26년 3차 신혼·신생아 매입임대Ⅰ 예비입주자 모집공고</t>
+          <t>[서울지역본부] 26년 3차 청년 매입임대주택 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3352,32 +3356,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020750&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020759&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>울산</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>서초구</t>
+          <t>남구</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>[서울지역본부] 26년 3차 신혼·신생아매입임대주택Ⅱ(전세형) 예비입주자 모집공고</t>
+          <t>[부산울산]신혼부부Ⅱ(전세형) 매입임대주택 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3397,32 +3401,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020749&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020789&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>영등포구</t>
+          <t>제물포구</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>[서울지역본부] 26년 3차 청년 매입임대주택 예비입주자 모집공고</t>
+          <t>[인천]26년 7차 신혼·신생아Ⅰ 예비입주자 모집공고(인천,부천)</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3442,32 +3446,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020759&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020795&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>울산</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>남구</t>
+          <t>서해구</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>[부산울산]신혼부부Ⅱ(전세형) 매입임대주택 예비입주자 모집공고</t>
+          <t>[인천]26년 7차 신혼·신생아Ⅱ(전세형) 예비입주자 모집공고(인천,부천)</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3487,15 +3491,15 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020789&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020797&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
@@ -3512,7 +3516,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>[인천]26년 7차 신혼·신생아Ⅰ 예비입주자 모집공고(인천,부천)</t>
+          <t>[인천지역본부] 26년 7차 청년 매입임대주택 예비입주자 모집공고(인천,부천)</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3532,15 +3536,15 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020795&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020798&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
@@ -3552,17 +3556,17 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>서해구</t>
+          <t>남동구</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>[인천]26년 7차 신혼·신생아Ⅱ(전세형) 예비입주자 모집공고(인천,부천)</t>
+          <t>‘26년 9월 인천시(남동구) 행복주택 입주자격완화 예비입주자 모집</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -3577,37 +3581,37 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020797&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020744&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>제물포구</t>
+          <t>아산시</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>[인천지역본부] 26년 7차 청년 매입임대주택 예비입주자 모집공고(인천,부천)</t>
+          <t>아산신창소화,아산인주 국민임대주택 예비입주자 모집공고(2026.09.15)</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -3622,42 +3626,42 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020798&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020726&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>남동구</t>
+          <t>천안시 동남구</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>‘26년 9월 인천시(남동구) 행복주택 입주자격완화 예비입주자 모집</t>
+          <t>천안병천신한 국민임대주택 예비입주자 모집공고(2026.09.15)</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3667,15 +3671,15 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020744&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020714&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
@@ -3687,22 +3691,22 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>아산시</t>
+          <t>천안시 서북구</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>아산신창소화,아산인주 국민임대주택 예비입주자 모집공고(2026.09.15)</t>
+          <t>천안쌍용5-2 공임50년 예비입주자 모집공고(2026.09.16)</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>50년임대</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3712,15 +3716,15 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020726&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019790&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
@@ -3732,12 +3736,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>천안시 동남구</t>
+          <t>홍성군</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>천안병천신한 국민임대주택 예비입주자 모집공고(2026.09.15)</t>
+          <t>홍성남장2 국민임대주택 예비입주자 모집공고(2026.09.15)</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -3757,42 +3761,42 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020714&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020729&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H75" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>천안시 서북구</t>
+          <t>청주시 흥덕구</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>천안쌍용5-2 공임50년 예비입주자 모집공고(2026.09.16)</t>
+          <t>[충북지역본부]신혼·신생아 매입임대주택Ⅰ 예비입주자 모집공고(260917)</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>50년임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3802,60 +3806,60 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019790&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020776&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H76" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>홍성군</t>
+          <t>청주시 상당구</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>홍성남장2 국민임대주택 예비입주자 모집공고(2026.09.15)</t>
+          <t>[충북지역본부]신혼·신생아 매입임대주택Ⅱ(전세형) 예비입주자 모집공고(260917)</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
+          <t>20260928</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
           <t>20260930</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>20260930</t>
-        </is>
-      </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020729&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020774&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
@@ -3867,12 +3871,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>청주시 흥덕구</t>
+          <t>청주시 상당구</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>[충북지역본부]신혼·신생아 매입임대주택Ⅰ 예비입주자 모집공고(260917)</t>
+          <t>[충북지역본부]청년 매입임대주택 예비입주자 모집 공고(260917)</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -3892,105 +3896,105 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020776&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020778&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H78" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>청주시 상당구</t>
+          <t>원주시</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>[충북지역본부]신혼·신생아 매입임대주택Ⅱ(전세형) 예비입주자 모집공고(260917)</t>
+          <t>원주무실1 국민임대주택 예비입주자 모집(26.09.15공고)</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020774&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020792&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H79" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-11</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>청주시 상당구</t>
+          <t>원주시</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>[충북지역본부]청년 매입임대주택 예비입주자 모집 공고(260917)</t>
+          <t>원주무실1 국민임대주택 예비입주자 모집(26.09.15공고)</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020778&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020739&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H80" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-11</t>
         </is>
       </c>
     </row>
@@ -4002,12 +4006,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>원주시</t>
+          <t>춘천시</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>원주무실1 국민임대주택 예비입주자 모집(26.09.15공고)</t>
+          <t>춘천시, 홍천군지역 국민임대주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4017,87 +4021,87 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
+          <t>20260929</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
           <t>20261001</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>20261001</t>
-        </is>
-      </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020792&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020741&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H81" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>D-13</t>
+          <t>D-11</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>원주시</t>
+          <t>포천시</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>원주무실1 국민임대주택 예비입주자 모집(26.09.15공고)</t>
+          <t>[경기북부] 2026년 하반기 일반 매입임대주택 입주자 모집공고</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
+          <t>20260929</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
           <t>20261001</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>20261001</t>
-        </is>
-      </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020739&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020713&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H82" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>D-13</t>
+          <t>D-11</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>춘천시</t>
+          <t>남양주시</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>춘천시, 홍천군지역 국민임대주택 예비입주자 모집</t>
+          <t>남양주마석2단지 국민임대주택 예비입주자 모집공고(2026.9.7.)</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4107,7 +4111,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -4117,15 +4121,15 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020741&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020710&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H83" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>D-13</t>
+          <t>D-11</t>
         </is>
       </c>
     </row>
@@ -4137,22 +4141,22 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>동두천시</t>
+          <t>남양주시</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>[경기북부] 2026년 하반기 일반 매입임대주택 입주자 모집공고</t>
+          <t>남양주마석2단지 국민임대주택 예비입주자 모집공고(2026.9.7.)</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -4162,42 +4166,42 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020713&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020668&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H84" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>D-13</t>
+          <t>D-11</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>남양주시</t>
+          <t>김해시</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>남양주마석2단지 국민임대주택 예비입주자 모집공고(2026.9.7.)</t>
+          <t>[경남지역본부] 일반 매입임대주택 입주자 모집 공고(김해시, 밀양시)</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -4207,32 +4211,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020710&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020706&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H85" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>D-13</t>
+          <t>D-11</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>남양주시</t>
+          <t>김해시</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>남양주마석2단지 국민임대주택 예비입주자 모집공고(2026.9.7.)</t>
+          <t>김해진영6단지 국민임대주택 예비입주자 모집(‘26.09.15. 공고)</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4252,15 +4256,15 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020668&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020716&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H86" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>D-13</t>
+          <t>D-11</t>
         </is>
       </c>
     </row>
@@ -4272,22 +4276,22 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>김해시</t>
+          <t>남해군</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>[경남지역본부] 일반 매입임대주택 입주자 모집 공고(김해시, 밀양시)</t>
+          <t>남해평리휴먼시아 국민임대주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -4297,42 +4301,42 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020706&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020757&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H87" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>D-13</t>
+          <t>D-11</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>김해시</t>
+          <t>경주시</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>김해진영6단지 국민임대주택 예비입주자 모집(‘26.09.15. 공고)</t>
+          <t>[경북 포항,경주,영천] 일반 매입임대 입주자 모집공고</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20260908</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -4342,60 +4346,60 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020716&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020654&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H88" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>D-13</t>
+          <t>D-11</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>남해군</t>
+          <t>영천시</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>남해평리휴먼시아 국민임대주택 예비입주자 모집</t>
+          <t>[경북 포항,경주,영천] 일반 매입임대 입주자 모집공고</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
+          <t>20260908</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
           <t>20261001</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>20261001</t>
-        </is>
-      </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020757&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020601&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H89" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>D-13</t>
+          <t>D-11</t>
         </is>
       </c>
     </row>
@@ -4407,22 +4411,22 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>경주시</t>
+          <t>구미시</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>[경북 포항,경주,영천] 일반 매입임대 입주자 모집공고</t>
+          <t>경북서부지역(구미시, 김천시, 의성군) 국민임대 예비입주자 모집</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>20260908</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -4432,15 +4436,15 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020654&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020709&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H90" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>D-13</t>
+          <t>D-11</t>
         </is>
       </c>
     </row>
@@ -4452,22 +4456,22 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>영천시</t>
+          <t>칠곡군</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>[경북 포항,경주,영천] 일반 매입임대 입주자 모집공고</t>
+          <t>칠곡북삼휴먼시아 국민임대주택 예비입주자 모집(45형)</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>20260908</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -4477,15 +4481,15 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020601&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020786&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H91" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>D-13</t>
+          <t>D-11</t>
         </is>
       </c>
     </row>
@@ -4497,12 +4501,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>구미시</t>
+          <t>칠곡군</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>경북서부지역(구미시, 김천시, 의성군) 국민임대 예비입주자 모집</t>
+          <t>칠곡북삼휴먼시아 국민임대주택 예비입주자 모집(45형)</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -4512,7 +4516,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -4522,77 +4526,77 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020709&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020719&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H92" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>D-13</t>
+          <t>D-11</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>칠곡군</t>
+          <t>강서구</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>칠곡북삼휴먼시아 국민임대주택 예비입주자 모집(45형)</t>
+          <t>강서염창 통합공공임대주택 최초 입주자 모집공고</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>통합공공임대</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
+          <t>20260929</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
           <t>20261001</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>20261001</t>
-        </is>
-      </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020786&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020753&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=48&amp;mi=1026</t>
         </is>
       </c>
       <c r="H93" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>D-13</t>
+          <t>D-11</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>울산</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>칠곡군</t>
+          <t>울주군</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>칠곡북삼휴먼시아 국민임대주택 예비입주자 모집(45형)</t>
+          <t>울산광역시 국민임대주택 예비입주자 정례모집 공고(2026.09.15.)</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -4602,52 +4606,52 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
+          <t>20260929</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
           <t>20261001</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>20261001</t>
-        </is>
-      </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020719&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020745&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H94" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>D-13</t>
+          <t>D-11</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>강서구</t>
+          <t>괴산군</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>강서염창 통합공공임대주택 최초 입주자 모집공고</t>
+          <t>괴산군지역 국민임대주택 예비입주자 모집 공고[2026.09.15]</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>통합공공임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -4657,32 +4661,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020753&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=48&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020683&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H95" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>D-13</t>
+          <t>D-11</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>울산</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>울주군</t>
+          <t>음성군</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>울산광역시 국민임대주택 예비입주자 정례모집 공고(2026.09.15.)</t>
+          <t>음성신천 국민임대주택 예비입주자 모집 공고[2026.09.15]</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -4692,7 +4696,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -4702,15 +4706,15 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020745&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020684&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H96" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>D-13</t>
+          <t>D-11</t>
         </is>
       </c>
     </row>
@@ -4722,12 +4726,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>괴산군</t>
+          <t>청주시 서원구</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>괴산군지역 국민임대주택 예비입주자 모집 공고[2026.09.15]</t>
+          <t>청주가경4 국민임대주택 예비입주자 모집 공고[2026.09.15]</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -4747,32 +4751,32 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020683&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020752&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H97" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>D-13</t>
+          <t>D-11</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>음성군</t>
+          <t>원주시</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>음성신천 국민임대주택 예비입주자 모집 공고[2026.09.15]</t>
+          <t>원주문막1 국민임대주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -4782,87 +4786,87 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20261002</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20261002</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020684&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020738&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H98" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>D-13</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>청주시 서원구</t>
+          <t>김천시</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>청주가경4 국민임대주택 예비입주자 모집 공고[2026.09.15]</t>
+          <t>김천부곡2 영구임대주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20261002</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020752&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020680&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H99" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>D-13</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>원주시</t>
+          <t>완주군</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>원주문막1 국민임대주택 예비입주자 모집</t>
+          <t>전주시, 완주군 국민임대주택 예비입주자 모집 공고(‘26.9.15.)</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -4872,52 +4876,52 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
+          <t>20260929</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
           <t>20261002</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>20261002</t>
-        </is>
-      </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020738&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020733&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H100" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>김천시</t>
+          <t>제주시</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>김천부곡2 영구임대주택 예비입주자 모집</t>
+          <t>제주 일도.삼도행복주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -4927,42 +4931,42 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020680&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020804&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H101" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>완주군</t>
+          <t>청주시 서원구</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>전주시, 완주군 국민임대주택 예비입주자 모집 공고(‘26.9.15.)</t>
+          <t>청주산남2-1 영구임대주택 예비입주자 모집 공고(2026.08.28)</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -4972,167 +4976,167 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020733&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020625&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H102" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>청주시 서원구</t>
+          <t>원주시</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>청주산남2-1 영구임대주택 예비입주자 모집 공고(2026.08.28)</t>
+          <t>원주태장4 국민임대주택 예비입주자 모집공고(2026.09.15)</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020625&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020740&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H103" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>D-17</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>원주시</t>
+          <t>전주시 완산구</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>원주태장4 국민임대주택 예비입주자 모집공고(2026.09.15)</t>
+          <t>전주동서학 통합공공임대(일자리연계형 지원주택) 최초 입주자 모집</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>통합공공임대</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020740&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020742&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=48&amp;mi=1026</t>
         </is>
       </c>
       <c r="H104" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>D-19</t>
+          <t>D-18</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>전주시 완산구</t>
+          <t>고령군</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>전주동서학 통합공공임대(일자리연계형 지원주택) 최초 입주자 모집</t>
+          <t>대구서부권 고령다산2 국민임대 입주자격완화 모집공고</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>통합공공임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020742&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=48&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020746&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H105" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>D-20</t>
+          <t>D-24</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>고령군</t>
+          <t>아산시</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>대구서부권 고령다산2 국민임대 입주자격완화 모집공고</t>
+          <t>아산탕정2 국민임대주택 예비입주자 모집공고(2026.09.15)</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -5152,15 +5156,15 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020746&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020726&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H106" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>D-26</t>
+          <t>D-24</t>
         </is>
       </c>
     </row>
@@ -5172,102 +5176,102 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>아산시</t>
+          <t>당진시</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>아산탕정2 국민임대주택 예비입주자 모집공고(2026.09.15)</t>
+          <t>[청년신혼부부매입임대리츠주택] 충남당진 송산청광플러스원 입주자격완화 상시모집</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20260810</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020726&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020529&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H107" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>D-26</t>
+          <t>D-25</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>당진시</t>
+          <t>태백시</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>[청년신혼부부매입임대리츠주택] 충남당진 송산청광플러스원 입주자격완화 상시모집</t>
+          <t>태백철암1 국민임대주택 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>20260810</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261028</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020529&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020735&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H108" t="n">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>D-27</t>
+          <t>D-38</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>태백시</t>
+          <t>양산시</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>태백철암1 국민임대주택 예비입주자 모집 공고</t>
+          <t>양산 사송A-4BL 국민임대주택(29A형)선착순 동호지정 모집(입주자격완화, 선계약 후검증)</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -5277,42 +5281,42 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260813</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>20261028</t>
+          <t>20261029</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020735&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020495&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H109" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>D-40</t>
+          <t>D-39</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>양산시</t>
+          <t>태백시</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>양산 사송A-4BL 국민임대주택(29A형)선착순 동호지정 모집(입주자격완화, 선계약 후검증)</t>
+          <t>태백소도 국민임대주택 예비입주자 상시모집(26.9.17 공고)</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -5322,52 +5326,52 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>20260813</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>20261029</t>
+          <t>20261030</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020495&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020793&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H110" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>D-41</t>
+          <t>D-40</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>태백시</t>
+          <t>군산시</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>태백소도 국민임대주택 예비입주자 상시모집(26.9.17 공고)</t>
+          <t>군산신역세권A3(내흥3) 영구임대주택 입주자 추가모집</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -5377,60 +5381,60 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020793&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019841&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H111" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>D-42</t>
+          <t>D-40</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>군산시</t>
+          <t>칠곡군</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>군산신역세권A3(내흥3) 영구임대주택 입주자 추가모집</t>
+          <t>2026년 칠곡군 천원주택(신혼·신생아 매입임대주택Ⅰ) 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260728</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>20261030</t>
+          <t>20261130</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019841&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=e54448a5-4c8c-4c3d-bfcf-bc465f677408&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
         </is>
       </c>
       <c r="H112" t="n">
-        <v>42</v>
+        <v>71</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>D-42</t>
+          <t>D-71</t>
         </is>
       </c>
     </row>
@@ -5447,7 +5451,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2026년 칠곡군 천원주택(신혼·신생아 매입임대주택Ⅰ) 예비입주자 모집 공고</t>
+          <t>2026년 칠곡군 천원주택(청년 매입임대주택) 입주자 및 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -5467,15 +5471,15 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=e54448a5-4c8c-4c3d-bfcf-bc465f677408&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
+          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=2e8989e9-02ae-48be-9591-f3c4c8e7fa39&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
         </is>
       </c>
       <c r="H113" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>D-73</t>
+          <t>D-71</t>
         </is>
       </c>
     </row>
@@ -5487,85 +5491,85 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>칠곡군</t>
+          <t>포항시 남구</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2026년 칠곡군 천원주택(청년 매입임대주택) 입주자 및 예비입주자 모집 공고</t>
+          <t>포항블루밸리 행복주택 선착순 동호지정 상시모집(입주자격 완화, 통합공임 일반계층 추가, 선계약 후검증)</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>20260728</t>
+          <t>20260707</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>20261130</t>
+          <t>20261222</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=2e8989e9-02ae-48be-9591-f3c4c8e7fa39&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020042&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H114" t="n">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>D-73</t>
+          <t>D-93</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>포항시 남구</t>
+          <t>삼척시</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>포항블루밸리 행복주택 선착순 동호지정 상시모집(입주자격 완화, 통합공임 일반계층 추가, 선계약 후검증)</t>
+          <t>삼척시·정선군 국민임대 예비입주자 상시모집(26.6.10)</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>20260707</t>
+          <t>20260624</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>20261222</t>
+          <t>20261230</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020042&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020090&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H115" t="n">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>D-95</t>
+          <t>D-101</t>
         </is>
       </c>
     </row>
@@ -5577,12 +5581,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>삼척시</t>
+          <t>태백시</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>삼척시·정선군 국민임대 예비입주자 상시모집(26.6.10)</t>
+          <t>태백장성 국민임대주택 예비입주자 입주자격완화 상시모집</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -5592,7 +5596,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>20260624</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -5602,15 +5606,15 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020090&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020730&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H116" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>D-103</t>
+          <t>D-101</t>
         </is>
       </c>
     </row>
@@ -5620,42 +5624,38 @@
           <t>강원</t>
         </is>
       </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>태백시</t>
-        </is>
-      </c>
+      <c r="B117" t="inlineStr"/>
       <c r="C117" t="inlineStr">
         <is>
-          <t>태백장성 국민임대주택 예비입주자 입주자격완화 상시모집</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>20261230</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020730&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H117" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>D-103</t>
+          <t>D-102</t>
         </is>
       </c>
     </row>
@@ -5668,7 +5668,7 @@
       <c r="B118" t="inlineStr"/>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -5688,15 +5688,15 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H118" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>D-104</t>
+          <t>D-102</t>
         </is>
       </c>
     </row>
@@ -5709,7 +5709,7 @@
       <c r="B119" t="inlineStr"/>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -5729,15 +5729,15 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H119" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>D-104</t>
+          <t>D-102</t>
         </is>
       </c>
     </row>
@@ -5750,7 +5750,7 @@
       <c r="B120" t="inlineStr"/>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -5760,7 +5760,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -5770,15 +5770,15 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H120" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>D-104</t>
+          <t>D-102</t>
         </is>
       </c>
     </row>
@@ -5788,20 +5788,24 @@
           <t>강원</t>
         </is>
       </c>
-      <c r="B121" t="inlineStr"/>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>동해시</t>
+        </is>
+      </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>동해유성,태백철암장미 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260212</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -5811,15 +5815,15 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019312&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H121" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>D-104</t>
+          <t>D-102</t>
         </is>
       </c>
     </row>
@@ -5856,15 +5860,15 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019312&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019308&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H122" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>D-104</t>
+          <t>D-102</t>
         </is>
       </c>
     </row>
@@ -5876,12 +5880,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>동해시</t>
+          <t>태백시</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>동해유성,태백철암장미 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
+          <t>태백궁전 국민임대 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -5901,42 +5905,38 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019308&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019307&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H123" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>D-104</t>
+          <t>D-102</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>강원</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>태백시</t>
-        </is>
-      </c>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr"/>
       <c r="C124" t="inlineStr">
         <is>
-          <t>태백궁전 국민임대 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>20260212</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -5946,15 +5946,15 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019307&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H124" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>D-104</t>
+          <t>D-102</t>
         </is>
       </c>
     </row>
@@ -5967,7 +5967,7 @@
       <c r="B125" t="inlineStr"/>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -5987,15 +5987,15 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H125" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>D-104</t>
+          <t>D-102</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       <c r="B126" t="inlineStr"/>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -6028,15 +6028,15 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H126" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>D-104</t>
+          <t>D-102</t>
         </is>
       </c>
     </row>
@@ -6049,7 +6049,7 @@
       <c r="B127" t="inlineStr"/>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -6059,7 +6059,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -6069,28 +6069,28 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H127" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>D-104</t>
+          <t>D-102</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B128" t="inlineStr"/>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -6100,7 +6100,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -6110,15 +6110,15 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H128" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>D-104</t>
+          <t>D-102</t>
         </is>
       </c>
     </row>
@@ -6131,7 +6131,7 @@
       <c r="B129" t="inlineStr"/>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -6151,15 +6151,15 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H129" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>D-104</t>
+          <t>D-102</t>
         </is>
       </c>
     </row>
@@ -6172,7 +6172,7 @@
       <c r="B130" t="inlineStr"/>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -6192,15 +6192,15 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H130" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>D-104</t>
+          <t>D-102</t>
         </is>
       </c>
     </row>
@@ -6213,7 +6213,7 @@
       <c r="B131" t="inlineStr"/>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -6223,7 +6223,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -6233,28 +6233,28 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H131" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>D-104</t>
+          <t>D-102</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B132" t="inlineStr"/>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -6264,7 +6264,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -6274,15 +6274,15 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H132" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>D-104</t>
+          <t>D-102</t>
         </is>
       </c>
     </row>
@@ -6295,7 +6295,7 @@
       <c r="B133" t="inlineStr"/>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -6315,15 +6315,15 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H133" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>D-104</t>
+          <t>D-102</t>
         </is>
       </c>
     </row>
@@ -6336,7 +6336,7 @@
       <c r="B134" t="inlineStr"/>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -6356,15 +6356,15 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H134" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>D-104</t>
+          <t>D-102</t>
         </is>
       </c>
     </row>
@@ -6377,7 +6377,7 @@
       <c r="B135" t="inlineStr"/>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -6387,7 +6387,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -6397,28 +6397,28 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H135" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>D-104</t>
+          <t>D-102</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B136" t="inlineStr"/>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -6428,7 +6428,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -6438,15 +6438,15 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H136" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>D-104</t>
+          <t>D-102</t>
         </is>
       </c>
     </row>
@@ -6459,7 +6459,7 @@
       <c r="B137" t="inlineStr"/>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -6479,15 +6479,15 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H137" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>D-104</t>
+          <t>D-102</t>
         </is>
       </c>
     </row>
@@ -6500,7 +6500,7 @@
       <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -6520,15 +6520,15 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H138" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>D-104</t>
+          <t>D-102</t>
         </is>
       </c>
     </row>
@@ -6541,7 +6541,7 @@
       <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -6551,7 +6551,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -6561,28 +6561,28 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H139" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>D-104</t>
+          <t>D-102</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>대전</t>
         </is>
       </c>
       <c r="B140" t="inlineStr"/>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -6592,7 +6592,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -6602,15 +6602,15 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H140" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>D-104</t>
+          <t>D-102</t>
         </is>
       </c>
     </row>
@@ -6623,7 +6623,7 @@
       <c r="B141" t="inlineStr"/>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -6643,15 +6643,15 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H141" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>D-104</t>
+          <t>D-102</t>
         </is>
       </c>
     </row>
@@ -6664,7 +6664,7 @@
       <c r="B142" t="inlineStr"/>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -6684,15 +6684,15 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H142" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>D-104</t>
+          <t>D-102</t>
         </is>
       </c>
     </row>
@@ -6705,7 +6705,7 @@
       <c r="B143" t="inlineStr"/>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -6715,7 +6715,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -6725,28 +6725,28 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H143" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>D-104</t>
+          <t>D-102</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>대전</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B144" t="inlineStr"/>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -6756,7 +6756,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -6766,15 +6766,15 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H144" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>D-104</t>
+          <t>D-102</t>
         </is>
       </c>
     </row>
@@ -6787,7 +6787,7 @@
       <c r="B145" t="inlineStr"/>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -6807,15 +6807,15 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H145" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>D-104</t>
+          <t>D-102</t>
         </is>
       </c>
     </row>
@@ -6828,7 +6828,7 @@
       <c r="B146" t="inlineStr"/>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -6848,15 +6848,15 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H146" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>D-104</t>
+          <t>D-102</t>
         </is>
       </c>
     </row>
@@ -6869,7 +6869,7 @@
       <c r="B147" t="inlineStr"/>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -6879,7 +6879,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -6889,28 +6889,28 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H147" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>D-104</t>
+          <t>D-102</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B148" t="inlineStr"/>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -6920,7 +6920,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -6930,15 +6930,15 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H148" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>D-104</t>
+          <t>D-102</t>
         </is>
       </c>
     </row>
@@ -6951,7 +6951,7 @@
       <c r="B149" t="inlineStr"/>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -6971,15 +6971,15 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H149" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>D-104</t>
+          <t>D-102</t>
         </is>
       </c>
     </row>
@@ -6992,7 +6992,7 @@
       <c r="B150" t="inlineStr"/>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -7012,15 +7012,15 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H150" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>D-104</t>
+          <t>D-102</t>
         </is>
       </c>
     </row>
@@ -7033,7 +7033,7 @@
       <c r="B151" t="inlineStr"/>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -7053,28 +7053,28 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H151" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>D-104</t>
+          <t>D-102</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>세종</t>
         </is>
       </c>
       <c r="B152" t="inlineStr"/>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -7084,7 +7084,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -7094,15 +7094,15 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H152" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>D-104</t>
+          <t>D-102</t>
         </is>
       </c>
     </row>
@@ -7115,7 +7115,7 @@
       <c r="B153" t="inlineStr"/>
       <c r="C153" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -7135,15 +7135,15 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H153" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>D-104</t>
+          <t>D-102</t>
         </is>
       </c>
     </row>
@@ -7156,7 +7156,7 @@
       <c r="B154" t="inlineStr"/>
       <c r="C154" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -7176,15 +7176,15 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H154" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>D-104</t>
+          <t>D-102</t>
         </is>
       </c>
     </row>
@@ -7197,7 +7197,7 @@
       <c r="B155" t="inlineStr"/>
       <c r="C155" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -7207,7 +7207,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -7217,28 +7217,28 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H155" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>D-104</t>
+          <t>D-102</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>세종</t>
+          <t>울산</t>
         </is>
       </c>
       <c r="B156" t="inlineStr"/>
       <c r="C156" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -7248,7 +7248,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -7258,15 +7258,15 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H156" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>D-104</t>
+          <t>D-102</t>
         </is>
       </c>
     </row>
@@ -7279,7 +7279,7 @@
       <c r="B157" t="inlineStr"/>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -7299,15 +7299,15 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H157" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>D-104</t>
+          <t>D-102</t>
         </is>
       </c>
     </row>
@@ -7320,7 +7320,7 @@
       <c r="B158" t="inlineStr"/>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -7340,15 +7340,15 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H158" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>D-104</t>
+          <t>D-102</t>
         </is>
       </c>
     </row>
@@ -7361,7 +7361,7 @@
       <c r="B159" t="inlineStr"/>
       <c r="C159" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -7371,7 +7371,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -7381,28 +7381,28 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H159" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>D-104</t>
+          <t>D-102</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>울산</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B160" t="inlineStr"/>
       <c r="C160" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -7412,7 +7412,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -7422,15 +7422,15 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H160" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>D-104</t>
+          <t>D-102</t>
         </is>
       </c>
     </row>
@@ -7443,7 +7443,7 @@
       <c r="B161" t="inlineStr"/>
       <c r="C161" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -7463,15 +7463,15 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H161" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>D-104</t>
+          <t>D-102</t>
         </is>
       </c>
     </row>
@@ -7484,7 +7484,7 @@
       <c r="B162" t="inlineStr"/>
       <c r="C162" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -7504,15 +7504,15 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H162" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>D-104</t>
+          <t>D-102</t>
         </is>
       </c>
     </row>
@@ -7525,7 +7525,7 @@
       <c r="B163" t="inlineStr"/>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -7535,7 +7535,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -7545,28 +7545,28 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H163" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>D-104</t>
+          <t>D-102</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B164" t="inlineStr"/>
       <c r="C164" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -7576,7 +7576,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -7586,15 +7586,15 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H164" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>D-104</t>
+          <t>D-102</t>
         </is>
       </c>
     </row>
@@ -7607,7 +7607,7 @@
       <c r="B165" t="inlineStr"/>
       <c r="C165" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -7627,15 +7627,15 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H165" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>D-104</t>
+          <t>D-102</t>
         </is>
       </c>
     </row>
@@ -7648,7 +7648,7 @@
       <c r="B166" t="inlineStr"/>
       <c r="C166" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -7668,15 +7668,15 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H166" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>D-104</t>
+          <t>D-102</t>
         </is>
       </c>
     </row>
@@ -7689,7 +7689,7 @@
       <c r="B167" t="inlineStr"/>
       <c r="C167" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -7699,7 +7699,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -7709,15 +7709,15 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H167" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>D-104</t>
+          <t>D-102</t>
         </is>
       </c>
     </row>
@@ -7727,20 +7727,24 @@
           <t>전북</t>
         </is>
       </c>
-      <c r="B168" t="inlineStr"/>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>김제시</t>
+        </is>
+      </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>김제검산1단지 영구임대주택 예비입주자 모집 공고(상시모집)</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260101</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -7750,15 +7754,15 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019412&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H168" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>D-104</t>
+          <t>D-102</t>
         </is>
       </c>
     </row>
@@ -7770,22 +7774,22 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>김제시</t>
+          <t>남원시</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>김제검산1단지 영구임대주택 예비입주자 모집 공고(상시모집)</t>
+          <t>남원노암 공공임대 50년 예비입주자 모집</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>50년임대</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>20260101</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -7795,15 +7799,15 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019412&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020623&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H169" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>D-104</t>
+          <t>D-102</t>
         </is>
       </c>
     </row>
@@ -7820,12 +7824,12 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>남원노암 공공임대 50년 예비입주자 모집</t>
+          <t>남원노암단지 영구임대주택 입주자격완화 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>50년임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -7840,15 +7844,15 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020623&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020649&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H170" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>D-104</t>
+          <t>D-102</t>
         </is>
       </c>
     </row>
@@ -7860,12 +7864,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>남원시</t>
+          <t>전주시 완산구</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>남원노암단지 영구임대주택 입주자격완화 예비입주자 모집공고</t>
+          <t>전주시(전주평화1,전주평화4) 영구임대주택 예비입주자 모집 공고(공고일:2026.02.10.)</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -7875,7 +7879,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260303</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -7885,42 +7889,38 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020649&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019241&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H171" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>D-104</t>
+          <t>D-102</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>전북</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>전주시 완산구</t>
-        </is>
-      </c>
+          <t>제주</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr"/>
       <c r="C172" t="inlineStr">
         <is>
-          <t>전주시(전주평화1,전주평화4) 영구임대주택 예비입주자 모집 공고(공고일:2026.02.10.)</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>20260303</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -7930,15 +7930,15 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019241&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H172" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>D-104</t>
+          <t>D-102</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       <c r="B173" t="inlineStr"/>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -7971,15 +7971,15 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H173" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>D-104</t>
+          <t>D-102</t>
         </is>
       </c>
     </row>
@@ -7992,7 +7992,7 @@
       <c r="B174" t="inlineStr"/>
       <c r="C174" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -8012,15 +8012,15 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H174" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>D-104</t>
+          <t>D-102</t>
         </is>
       </c>
     </row>
@@ -8033,7 +8033,7 @@
       <c r="B175" t="inlineStr"/>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -8043,7 +8043,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -8053,28 +8053,28 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H175" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>D-104</t>
+          <t>D-102</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B176" t="inlineStr"/>
       <c r="C176" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -8084,7 +8084,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -8094,15 +8094,15 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H176" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>D-104</t>
+          <t>D-102</t>
         </is>
       </c>
     </row>
@@ -8115,7 +8115,7 @@
       <c r="B177" t="inlineStr"/>
       <c r="C177" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -8135,15 +8135,15 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H177" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>D-104</t>
+          <t>D-102</t>
         </is>
       </c>
     </row>
@@ -8156,7 +8156,7 @@
       <c r="B178" t="inlineStr"/>
       <c r="C178" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -8176,15 +8176,15 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H178" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>D-104</t>
+          <t>D-102</t>
         </is>
       </c>
     </row>
@@ -8197,7 +8197,7 @@
       <c r="B179" t="inlineStr"/>
       <c r="C179" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -8207,7 +8207,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -8217,15 +8217,15 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H179" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>D-104</t>
+          <t>D-102</t>
         </is>
       </c>
     </row>
@@ -8235,20 +8235,24 @@
           <t>충남</t>
         </is>
       </c>
-      <c r="B180" t="inlineStr"/>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>당진시</t>
+        </is>
+      </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>[청년신혼부부매입임대리츠주택] 충남당진 송산청광플러스원 입주자격완화 상시모집</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260316</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -8258,42 +8262,38 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019433&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H180" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>D-104</t>
+          <t>D-102</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>충남</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>당진시</t>
-        </is>
-      </c>
+          <t>충북</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr"/>
       <c r="C181" t="inlineStr">
         <is>
-          <t>[청년신혼부부매입임대리츠주택] 충남당진 송산청광플러스원 입주자격완화 상시모집</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>20260316</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -8303,15 +8303,15 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019433&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H181" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>D-104</t>
+          <t>D-102</t>
         </is>
       </c>
     </row>
@@ -8324,7 +8324,7 @@
       <c r="B182" t="inlineStr"/>
       <c r="C182" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -8344,15 +8344,15 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H182" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>D-104</t>
+          <t>D-102</t>
         </is>
       </c>
     </row>
@@ -8365,7 +8365,7 @@
       <c r="B183" t="inlineStr"/>
       <c r="C183" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -8385,15 +8385,15 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H183" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>D-104</t>
+          <t>D-102</t>
         </is>
       </c>
     </row>
@@ -8406,7 +8406,7 @@
       <c r="B184" t="inlineStr"/>
       <c r="C184" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -8426,73 +8426,77 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H184" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>D-104</t>
+          <t>D-102</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>충북</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr"/>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>삼척시</t>
+        </is>
+      </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>삼척도계·정선신동 국민임대주택 예비입주자 입주자격완화 공고</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20270129</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020581&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H185" t="n">
-        <v>104</v>
+        <v>131</v>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>D-104</t>
+          <t>D-131</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>삼척시</t>
+          <t>군산시</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>삼척도계·정선신동 국민임대주택 예비입주자 입주자격완화 공고</t>
+          <t>군산시 국민임대주택 입주자 선착순 상시 모집(경암부향 등 7개 단지)</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -8502,42 +8506,42 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260812</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>20270129</t>
+          <t>20270731</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020581&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020453&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H186" t="n">
-        <v>133</v>
+        <v>314</v>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>D-133</t>
+          <t>D-314</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>울산</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>군산시</t>
+          <t>울주군</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>군산시 국민임대주택 입주자 선착순 상시 모집(경암부향 등 7개 단지)</t>
+          <t>울산광역시 국민임대주택 예비입주자 정례모집 공고(2025.09.15.)</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -8547,25 +8551,25 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>20260812</t>
+          <t>20250929</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>20270731</t>
+          <t>20291001</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020453&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300018799&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H187" t="n">
-        <v>316</v>
+        <v>1107</v>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>D-316</t>
+          <t>D-1107</t>
         </is>
       </c>
     </row>
@@ -8602,60 +8606,15 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300018799&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300018780&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H188" t="n">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>D-1109</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>울산</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>울주군</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>울산광역시 국민임대주택 예비입주자 정례모집 공고(2025.09.15.)</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>국민임대</t>
-        </is>
-      </c>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>20250929</t>
-        </is>
-      </c>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>20291001</t>
-        </is>
-      </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300018780&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
-        </is>
-      </c>
-      <c r="H189" t="n">
-        <v>1109</v>
-      </c>
-      <c r="I189" t="inlineStr">
-        <is>
-          <t>D-1109</t>
+          <t>D-1107</t>
         </is>
       </c>
     </row>

--- a/housing_notices.xlsx
+++ b/housing_notices.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I188"/>
+  <dimension ref="A1:I193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,41 +466,45 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>경기</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>횡성군</t>
+        </is>
+      </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>[경기남부] 용인시 신혼·신생아 매입임대주택Ⅱ(전세형) 예비입주자 모집공고</t>
+          <t>강원횡성 통합공공임대주택 입주자 모집</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>통합공공임대</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>20260917</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260923</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020702&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020627&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=48&amp;mi=1026</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>오늘 마감</t>
         </is>
       </c>
     </row>
@@ -510,10 +514,14 @@
           <t>경기</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>시흥시</t>
+        </is>
+      </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>[경기남부] 용인시 청년 매입임대주택 예비입주자 모집공고</t>
+          <t>[온라인 접수 불가, 관할 주거복지지사 현장접수] 경기남부지역본부 2026년 일반 매입임대주택 입주자 모집공고</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -523,25 +531,25 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>20260917</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260923</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020699&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020769&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>오늘 마감</t>
         </is>
       </c>
     </row>
@@ -558,7 +566,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>[경기남부] 화성시·평택시 신혼·신생아 매입임대주택Ⅱ(전세형) 예비입주자 [후순번] 모집공고</t>
+          <t>[온라인 접수 불가, 관할 주거복지지사 현장접수] 경기남부지역본부 2026년 일반 매입임대주택 입주자 모집공고</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -568,137 +576,137 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>20260917</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260923</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020703&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020731&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>오늘 마감</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>포항시 북구</t>
+          <t>김포시</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>포항창포 영구임대아파트 예비입주자 모집</t>
+          <t>김포시 국민임대주택 예비입주자 모집(2026.09.07)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260923</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020651&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020659&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>오늘 마감</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>포항시 북구</t>
+          <t>화성시 효행구</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>포항학산 영구임대아파트 예비입주자 모집</t>
+          <t>화성서부권 국민임대주택 예비입주자 모집[입주자격완화]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260923</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020650&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020686&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>오늘 마감</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>부천시 오정구</t>
+          <t>양산시</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026년 9월 부천시 국민임대주택 예비입주자 모집 공고(2026.09.07)</t>
+          <t>[경남지역본부]26년 3차 분양전환형 든든전세주택 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -708,33 +716,37 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>20260922</t>
+          <t>20260923</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020652&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020721&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>오늘 마감</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>경기</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>김해시</t>
+        </is>
+      </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>26-4차 인천본부 든든전세주택 입주자 모집공고(인천, 부천)</t>
+          <t>[경남지역본부]26년 3차 비분양전환형 든든전세주택 입주자 모집 공고</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -749,33 +761,33 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>20260922</t>
+          <t>20260923</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020725&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020720&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>오늘 마감</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>26-4차 인천본부 든든전세주택 입주자 모집공고(인천, 부천)</t>
+          <t>[경남지역본부]26년 3차 신혼·신생아매입임대Ⅰ 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -790,82 +802,82 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>20260922</t>
+          <t>20260923</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020715&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020722&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>오늘 마감</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>경주시</t>
+          <t>양산시</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>경주시, 영천시, 포항시 부도매입(국민임대)주택 입주자격완화 모집공고</t>
+          <t>[경남지역본부]26년 3차 신혼·신생아매입임대Ⅱ(전세형) 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>20260922</t>
+          <t>20260923</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020635&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020723&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>오늘 마감</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>미추홀구</t>
+          <t>진주시</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>26-4차 인천본부 든든전세주택 입주자 모집공고(인천, 부천)</t>
+          <t>[경남지역본부]26년 3차 청년매입임대 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -880,37 +892,37 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>20260922</t>
+          <t>20260923</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020725&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020717&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>오늘 마감</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>부평구</t>
+          <t>함양군</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>26-4차 인천본부 든든전세주택 입주자 모집공고(인천, 부천)</t>
+          <t>경남 함양군 서하면 다자녀 매입임대주택 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -920,47 +932,47 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>20260922</t>
+          <t>20260923</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020715&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020711&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>오늘 마감</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>남동구</t>
+          <t>달서구</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>26년 9월 인천시 남동구 국민임대주택 예비입주자 모집 공고(2026.09.07)</t>
+          <t>대구죽전 행복주택(산업단지형) 예비 입주자 모집</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -970,42 +982,42 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>20260922</t>
+          <t>20260923</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020619&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020813&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>오늘 마감</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>옹진군</t>
+          <t>달서구</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>인천옹진백령 국민임대주택 예비입주자 모집</t>
+          <t>대구죽전 행복주택(산업단지형) 예비 입주자 모집</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1015,87 +1027,87 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>20260922</t>
+          <t>20260923</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020578&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020763&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>오늘 마감</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>옹진군</t>
+          <t>달서구</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>인천옹진연평 국민임대주택 예비입주자 모집</t>
+          <t>대구죽전 행복주택(산업단지형) 예비 입주자 모집</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>20260922</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>20260922</t>
+          <t>20260923</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020697&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020760&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>오늘 마감</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>횡성군</t>
+          <t>달서구</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>강원횡성 통합공공임대주택 입주자 모집</t>
+          <t>대구죽전 행복주택(산업단지형) 예비 입주자 모집</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>통합공공임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1110,37 +1122,37 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020627&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=48&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020751&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>오늘 마감</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>안성시</t>
+          <t>김제시</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>[온라인 접수 불가, 관할 주거복지지사 현장접수] 경기남부지역본부 2026년 일반 매입임대주택 입주자 모집공고</t>
+          <t>(26.9.10)김제대검산, 정읍시기, 정읍첨단 행복주택 입주자격완화 예비자 모집 공고(소득·총자산요건 배제 및 무주택요건 완화)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1155,42 +1167,42 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-    